--- a/internacional/2_8/Contraste_biologia.xlsx
+++ b/internacional/2_8/Contraste_biologia.xlsx
@@ -898,7 +898,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Enfermedades infecciosas y no infecciosas</t>
+          <t>Energía de los alimentos y balance energético</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -907,28 +907,25 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F6" t="n">
         <v>8</v>
       </c>
       <c r="G6" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H6" t="n">
-        <v>3</v>
-      </c>
-      <c r="J6" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="K6" t="n">
         <v>4</v>
       </c>
       <c r="L6" t="n">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -939,9 +936,6 @@
       <c r="Q6" t="n">
         <v>1</v>
       </c>
-      <c r="S6" t="n">
-        <v>1</v>
-      </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
@@ -952,7 +946,7 @@
         <v>1</v>
       </c>
       <c r="AF6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
@@ -961,14 +955,14 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Fósiles y registro fósil</t>
+          <t>Enfermedades infecciosas y no infecciosas</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -986,22 +980,19 @@
         <v>8</v>
       </c>
       <c r="G7" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H7" t="n">
+        <v>3</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K7" t="n">
         <v>4</v>
       </c>
-      <c r="I7" t="n">
-        <v>5</v>
-      </c>
-      <c r="J7" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K7" t="n">
-        <v>3</v>
-      </c>
-      <c r="M7" t="n">
-        <v>4.5</v>
+      <c r="L7" t="n">
+        <v>7.5</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1012,16 +1003,16 @@
       <c r="Q7" t="n">
         <v>1</v>
       </c>
-      <c r="R7" t="n">
-        <v>1</v>
-      </c>
       <c r="S7" t="n">
         <v>1</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
       </c>
-      <c r="V7" t="n">
+      <c r="U7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z7" t="n">
         <v>1</v>
       </c>
       <c r="AF7" t="n">
@@ -1041,7 +1032,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Grupos de plantas</t>
+          <t>Fósiles y registro fósil</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1062,13 +1053,19 @@
         <v>2</v>
       </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>4</v>
+      </c>
+      <c r="I8" t="n">
+        <v>5</v>
       </c>
       <c r="J8" t="n">
         <v>4.5</v>
       </c>
-      <c r="L8" t="n">
-        <v>5</v>
+      <c r="K8" t="n">
+        <v>3</v>
+      </c>
+      <c r="M8" t="n">
+        <v>4.5</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1079,10 +1076,16 @@
       <c r="Q8" t="n">
         <v>1</v>
       </c>
+      <c r="R8" t="n">
+        <v>1</v>
+      </c>
       <c r="S8" t="n">
         <v>1</v>
       </c>
-      <c r="U8" t="n">
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="V8" t="n">
         <v>1</v>
       </c>
       <c r="AF8" t="n">
@@ -1102,7 +1105,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Herencia de rasgos</t>
+          <t>Grupos de plantas</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1123,20 +1126,14 @@
         <v>2</v>
       </c>
       <c r="H9" t="n">
-        <v>3</v>
-      </c>
-      <c r="I9" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J9" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="L9" t="n">
         <v>5</v>
       </c>
-      <c r="M9" t="n">
-        <v>4.5</v>
-      </c>
       <c r="O9" t="n">
         <v>1</v>
       </c>
@@ -1146,16 +1143,10 @@
       <c r="Q9" t="n">
         <v>1</v>
       </c>
-      <c r="R9" t="n">
-        <v>1</v>
-      </c>
       <c r="S9" t="n">
         <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>1</v>
-      </c>
-      <c r="V9" t="n">
         <v>1</v>
       </c>
       <c r="AF9" t="n">
@@ -1175,7 +1166,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Historia de la vida en la Tierra</t>
+          <t>Herencia de rasgos</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1184,22 +1175,31 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F10" t="n">
         <v>8</v>
       </c>
       <c r="G10" t="n">
-        <v>4</v>
+        <v>2</v>
+      </c>
+      <c r="H10" t="n">
+        <v>3</v>
       </c>
       <c r="I10" t="n">
         <v>8</v>
       </c>
+      <c r="J10" t="n">
+        <v>7</v>
+      </c>
+      <c r="L10" t="n">
+        <v>5</v>
+      </c>
       <c r="M10" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="O10" t="n">
         <v>1</v>
@@ -1207,14 +1207,23 @@
       <c r="P10" t="n">
         <v>1</v>
       </c>
+      <c r="Q10" t="n">
+        <v>1</v>
+      </c>
       <c r="R10" t="n">
         <v>1</v>
       </c>
+      <c r="S10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
+      </c>
       <c r="V10" t="n">
         <v>1</v>
       </c>
       <c r="AF10" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
@@ -1230,7 +1239,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Inmunidad activa, pasiva y vacunas</t>
+          <t>Historia de la vida en la Tierra</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1248,10 +1257,13 @@
         <v>8</v>
       </c>
       <c r="G11" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="H11" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="I11" t="n">
+        <v>8</v>
+      </c>
+      <c r="M11" t="n">
+        <v>7</v>
       </c>
       <c r="O11" t="n">
         <v>1</v>
@@ -1259,14 +1271,14 @@
       <c r="P11" t="n">
         <v>1</v>
       </c>
-      <c r="Q11" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z11" t="n">
+      <c r="R11" t="n">
+        <v>1</v>
+      </c>
+      <c r="V11" t="n">
         <v>1</v>
       </c>
       <c r="AF11" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
@@ -1282,7 +1294,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Intercambio de gases en animales</t>
+          <t>Inmunidad activa, pasiva y vacunas</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1291,31 +1303,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F12" t="n">
         <v>8</v>
       </c>
       <c r="G12" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="H12" t="n">
-        <v>7</v>
-      </c>
-      <c r="I12" t="n">
-        <v>5</v>
-      </c>
-      <c r="J12" t="n">
-        <v>7</v>
-      </c>
-      <c r="L12" t="n">
-        <v>5</v>
-      </c>
-      <c r="M12" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O12" t="n">
         <v>1</v>
@@ -1326,20 +1326,11 @@
       <c r="Q12" t="n">
         <v>1</v>
       </c>
-      <c r="R12" t="n">
-        <v>1</v>
-      </c>
-      <c r="S12" t="n">
-        <v>1</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1</v>
-      </c>
-      <c r="V12" t="n">
+      <c r="Z12" t="n">
         <v>1</v>
       </c>
       <c r="AF12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
@@ -1355,7 +1346,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Microorganismos</t>
+          <t>Intercambio de gases en animales</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1364,25 +1355,28 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F13" t="n">
+        <v>8</v>
+      </c>
+      <c r="G13" t="n">
+        <v>6</v>
+      </c>
+      <c r="H13" t="n">
+        <v>7</v>
+      </c>
+      <c r="I13" t="n">
         <v>5</v>
       </c>
-      <c r="G13" t="n">
-        <v>4</v>
-      </c>
-      <c r="H13" t="n">
-        <v>2</v>
-      </c>
       <c r="J13" t="n">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="L13" t="n">
-        <v>7.5</v>
+        <v>5</v>
       </c>
       <c r="M13" t="n">
         <v>7</v>
@@ -1396,6 +1390,9 @@
       <c r="Q13" t="n">
         <v>1</v>
       </c>
+      <c r="R13" t="n">
+        <v>1</v>
+      </c>
       <c r="S13" t="n">
         <v>1</v>
       </c>
@@ -1405,11 +1402,8 @@
       <c r="V13" t="n">
         <v>1</v>
       </c>
-      <c r="Z13" t="n">
-        <v>1</v>
-      </c>
       <c r="AF13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
@@ -1425,7 +1419,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Nutrientes y sus funciones</t>
+          <t>Meiosis</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1434,44 +1428,38 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D14" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F14" t="n">
         <v>8</v>
       </c>
       <c r="G14" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="J14" t="n">
+        <v>7</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF14" t="n">
         <v>6</v>
       </c>
-      <c r="H14" t="n">
-        <v>2</v>
-      </c>
-      <c r="L14" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="O14" t="n">
-        <v>1</v>
-      </c>
-      <c r="P14" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>4</v>
-      </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
@@ -1483,7 +1471,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Redes tróficas</t>
+          <t>Microorganismos</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1492,40 +1480,28 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D15" t="n">
-        <v>4</v>
-      </c>
-      <c r="E15" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F15" t="n">
         <v>5</v>
       </c>
       <c r="G15" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H15" t="n">
-        <v>7</v>
-      </c>
-      <c r="I15" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J15" t="n">
         <v>2.5</v>
       </c>
-      <c r="K15" t="n">
-        <v>3</v>
-      </c>
       <c r="L15" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="M15" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="N15" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O15" t="n">
         <v>1</v>
@@ -1536,23 +1512,20 @@
       <c r="Q15" t="n">
         <v>1</v>
       </c>
-      <c r="R15" t="n">
-        <v>1</v>
-      </c>
       <c r="S15" t="n">
         <v>1</v>
       </c>
-      <c r="T15" t="n">
-        <v>1</v>
-      </c>
       <c r="U15" t="n">
         <v>1</v>
       </c>
       <c r="V15" t="n">
         <v>1</v>
       </c>
+      <c r="Z15" t="n">
+        <v>1</v>
+      </c>
       <c r="AF15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
@@ -1568,7 +1541,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Grandes grupos taxonómicos</t>
+          <t>Nutrientes y sus funciones</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1583,43 +1556,34 @@
         <v>2</v>
       </c>
       <c r="F16" t="n">
+        <v>8</v>
+      </c>
+      <c r="G16" t="n">
+        <v>6</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2</v>
+      </c>
+      <c r="L16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF16" t="n">
         <v>4</v>
-      </c>
-      <c r="G16" t="n">
-        <v>4</v>
-      </c>
-      <c r="H16" t="n">
-        <v>4</v>
-      </c>
-      <c r="J16" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K16" t="n">
-        <v>5</v>
-      </c>
-      <c r="L16" t="n">
-        <v>3</v>
-      </c>
-      <c r="O16" t="n">
-        <v>1</v>
-      </c>
-      <c r="P16" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1</v>
-      </c>
-      <c r="S16" t="n">
-        <v>1</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>2</v>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
@@ -1635,7 +1599,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Simbiosis: mutualismo, comensalismo y parasitismo</t>
+          <t>Redes tróficas</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1649,8 +1613,11 @@
       <c r="D17" t="n">
         <v>4</v>
       </c>
+      <c r="E17" t="n">
+        <v>6</v>
+      </c>
       <c r="F17" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G17" t="n">
         <v>6</v>
@@ -1658,15 +1625,24 @@
       <c r="H17" t="n">
         <v>7</v>
       </c>
+      <c r="I17" t="n">
+        <v>8</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2.5</v>
+      </c>
       <c r="K17" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L17" t="n">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="M17" t="n">
         <v>4.5</v>
       </c>
+      <c r="N17" t="n">
+        <v>1</v>
+      </c>
       <c r="O17" t="n">
         <v>1</v>
       </c>
@@ -1674,6 +1650,12 @@
         <v>1</v>
       </c>
       <c r="Q17" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1</v>
+      </c>
+      <c r="S17" t="n">
         <v>1</v>
       </c>
       <c r="T17" t="n">
@@ -1702,7 +1684,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sistema excretor</t>
+          <t>Grandes grupos taxonómicos</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1711,25 +1693,28 @@
         </is>
       </c>
       <c r="C18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2</v>
+      </c>
+      <c r="F18" t="n">
         <v>4</v>
       </c>
-      <c r="D18" t="n">
+      <c r="G18" t="n">
         <v>4</v>
       </c>
-      <c r="F18" t="n">
-        <v>8</v>
-      </c>
-      <c r="G18" t="n">
-        <v>8.5</v>
-      </c>
       <c r="H18" t="n">
+        <v>4</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K18" t="n">
         <v>5</v>
       </c>
-      <c r="I18" t="n">
-        <v>7</v>
-      </c>
-      <c r="J18" t="n">
-        <v>7</v>
+      <c r="L18" t="n">
+        <v>3</v>
       </c>
       <c r="O18" t="n">
         <v>1</v>
@@ -1740,14 +1725,17 @@
       <c r="Q18" t="n">
         <v>1</v>
       </c>
-      <c r="R18" t="n">
-        <v>1</v>
-      </c>
       <c r="S18" t="n">
         <v>1</v>
       </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
+      </c>
       <c r="AF18" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
@@ -1763,7 +1751,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sistema nervioso</t>
+          <t>Simbiosis: mutualismo, comensalismo y parasitismo</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1777,9 +1765,6 @@
       <c r="D19" t="n">
         <v>4</v>
       </c>
-      <c r="E19" t="n">
-        <v>8</v>
-      </c>
       <c r="F19" t="n">
         <v>8</v>
       </c>
@@ -1787,22 +1772,16 @@
         <v>6</v>
       </c>
       <c r="H19" t="n">
+        <v>7</v>
+      </c>
+      <c r="K19" t="n">
         <v>5</v>
       </c>
-      <c r="I19" t="n">
-        <v>7</v>
-      </c>
-      <c r="J19" t="n">
-        <v>7</v>
-      </c>
-      <c r="K19" t="n">
-        <v>4</v>
+      <c r="L19" t="n">
+        <v>7.5</v>
       </c>
       <c r="M19" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N19" t="n">
-        <v>1</v>
+        <v>4.5</v>
       </c>
       <c r="O19" t="n">
         <v>1</v>
@@ -1813,19 +1792,13 @@
       <c r="Q19" t="n">
         <v>1</v>
       </c>
-      <c r="R19" t="n">
-        <v>1</v>
-      </c>
-      <c r="S19" t="n">
-        <v>1</v>
-      </c>
       <c r="T19" t="n">
         <v>1</v>
       </c>
+      <c r="U19" t="n">
+        <v>1</v>
+      </c>
       <c r="V19" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z19" t="n">
         <v>1</v>
       </c>
       <c r="AF19" t="n">
@@ -1845,7 +1818,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sostenibilidad de la biosfera</t>
+          <t>Sistema excretor</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1854,61 +1827,43 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D20" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F20" t="n">
-        <v>2.5</v>
+        <v>8</v>
       </c>
       <c r="G20" t="n">
         <v>8.5</v>
       </c>
       <c r="H20" t="n">
+        <v>5</v>
+      </c>
+      <c r="I20" t="n">
+        <v>7</v>
+      </c>
+      <c r="J20" t="n">
+        <v>7</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF20" t="n">
         <v>4</v>
-      </c>
-      <c r="I20" t="n">
-        <v>8</v>
-      </c>
-      <c r="J20" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K20" t="n">
-        <v>2</v>
-      </c>
-      <c r="L20" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="M20" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O20" t="n">
-        <v>1</v>
-      </c>
-      <c r="P20" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>1</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1</v>
-      </c>
-      <c r="S20" t="n">
-        <v>1</v>
-      </c>
-      <c r="T20" t="n">
-        <v>1</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>2</v>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
@@ -1924,7 +1879,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Tipos de patógenos</t>
+          <t>Sistema nervioso</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1933,25 +1888,37 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D21" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="E21" t="n">
+        <v>8</v>
       </c>
       <c r="F21" t="n">
         <v>8</v>
       </c>
       <c r="G21" t="n">
-        <v>8.5</v>
+        <v>6</v>
       </c>
       <c r="H21" t="n">
-        <v>3</v>
-      </c>
-      <c r="L21" t="n">
-        <v>7.5</v>
+        <v>5</v>
+      </c>
+      <c r="I21" t="n">
+        <v>7</v>
+      </c>
+      <c r="J21" t="n">
+        <v>7</v>
+      </c>
+      <c r="K21" t="n">
+        <v>4</v>
       </c>
       <c r="M21" t="n">
-        <v>7</v>
+        <v>2.5</v>
+      </c>
+      <c r="N21" t="n">
+        <v>1</v>
       </c>
       <c r="O21" t="n">
         <v>1</v>
@@ -1962,7 +1929,13 @@
       <c r="Q21" t="n">
         <v>1</v>
       </c>
-      <c r="U21" t="n">
+      <c r="R21" t="n">
+        <v>1</v>
+      </c>
+      <c r="S21" t="n">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
         <v>1</v>
       </c>
       <c r="V21" t="n">
@@ -1972,7 +1945,7 @@
         <v>1</v>
       </c>
       <c r="AF21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
@@ -1988,34 +1961,43 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ADN y cromosomas</t>
+          <t>Sostenibilidad de la biosfera</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D22" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F22" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G22" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H22" t="n">
+        <v>4</v>
+      </c>
+      <c r="I22" t="n">
         <v>8</v>
       </c>
-      <c r="G22" t="n">
-        <v>6</v>
-      </c>
       <c r="J22" t="n">
-        <v>7</v>
+        <v>2.5</v>
+      </c>
+      <c r="K22" t="n">
+        <v>2</v>
       </c>
       <c r="L22" t="n">
-        <v>7.5</v>
+        <v>4.5</v>
       </c>
       <c r="M22" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="O22" t="n">
         <v>1</v>
@@ -2023,60 +2005,69 @@
       <c r="P22" t="n">
         <v>1</v>
       </c>
+      <c r="Q22" t="n">
+        <v>1</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1</v>
+      </c>
       <c r="S22" t="n">
         <v>1</v>
       </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
       <c r="U22" t="n">
         <v>1</v>
       </c>
       <c r="V22" t="n">
         <v>1</v>
       </c>
-      <c r="Z22" t="n">
-        <v>1</v>
-      </c>
       <c r="AF22" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Agricultura y seguridad alimentaria</t>
+          <t>Tipos de patógenos</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F23" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G23" t="n">
-        <v>6</v>
-      </c>
-      <c r="K23" t="n">
-        <v>2</v>
+        <v>8.5</v>
+      </c>
+      <c r="H23" t="n">
+        <v>3</v>
+      </c>
+      <c r="L23" t="n">
+        <v>7.5</v>
       </c>
       <c r="M23" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="O23" t="n">
         <v>1</v>
@@ -2084,72 +2075,63 @@
       <c r="P23" t="n">
         <v>1</v>
       </c>
-      <c r="T23" t="n">
+      <c r="Q23" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" t="n">
         <v>1</v>
       </c>
       <c r="V23" t="n">
         <v>1</v>
       </c>
+      <c r="Z23" t="n">
+        <v>1</v>
+      </c>
       <c r="AF23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Biodiversidad</t>
+          <t>Transmisión de patógenos</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D24" t="n">
-        <v>2</v>
-      </c>
-      <c r="E24" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F24" t="n">
-        <v>2.5</v>
+        <v>8</v>
       </c>
       <c r="G24" t="n">
-        <v>2</v>
+        <v>8.5</v>
       </c>
       <c r="H24" t="n">
-        <v>2</v>
-      </c>
-      <c r="I24" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J24" t="n">
         <v>2.5</v>
       </c>
-      <c r="K24" t="n">
-        <v>2</v>
-      </c>
       <c r="L24" t="n">
-        <v>3</v>
-      </c>
-      <c r="M24" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N24" t="n">
-        <v>1</v>
+        <v>7.5</v>
       </c>
       <c r="O24" t="n">
         <v>1</v>
@@ -2160,27 +2142,18 @@
       <c r="Q24" t="n">
         <v>1</v>
       </c>
-      <c r="R24" t="n">
-        <v>1</v>
-      </c>
       <c r="S24" t="n">
         <v>1</v>
       </c>
-      <c r="T24" t="n">
-        <v>1</v>
-      </c>
       <c r="U24" t="n">
         <v>1</v>
       </c>
-      <c r="V24" t="n">
-        <v>1</v>
-      </c>
       <c r="AF24" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="AG24" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH24" t="inlineStr">
@@ -2192,7 +2165,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Biomoléculas</t>
+          <t>Adaptaciones conductuales</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2201,28 +2174,37 @@
         </is>
       </c>
       <c r="C25" t="n">
+        <v>3</v>
+      </c>
+      <c r="D25" t="n">
+        <v>3</v>
+      </c>
+      <c r="E25" t="n">
+        <v>4</v>
+      </c>
+      <c r="F25" t="n">
+        <v>5</v>
+      </c>
+      <c r="G25" t="n">
+        <v>4</v>
+      </c>
+      <c r="H25" t="n">
+        <v>3</v>
+      </c>
+      <c r="I25" t="n">
+        <v>3</v>
+      </c>
+      <c r="J25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L25" t="n">
         <v>6</v>
       </c>
-      <c r="D25" t="n">
-        <v>6</v>
-      </c>
-      <c r="F25" t="n">
-        <v>8</v>
-      </c>
-      <c r="G25" t="n">
-        <v>6</v>
-      </c>
-      <c r="H25" t="n">
-        <v>2</v>
-      </c>
-      <c r="J25" t="n">
-        <v>7</v>
-      </c>
-      <c r="L25" t="n">
-        <v>7.5</v>
-      </c>
       <c r="M25" t="n">
-        <v>7</v>
+        <v>4.5</v>
+      </c>
+      <c r="N25" t="n">
+        <v>1</v>
       </c>
       <c r="O25" t="n">
         <v>1</v>
@@ -2233,6 +2215,9 @@
       <c r="Q25" t="n">
         <v>1</v>
       </c>
+      <c r="R25" t="n">
+        <v>1</v>
+      </c>
       <c r="S25" t="n">
         <v>1</v>
       </c>
@@ -2242,11 +2227,8 @@
       <c r="V25" t="n">
         <v>1</v>
       </c>
-      <c r="Z25" t="n">
-        <v>1</v>
-      </c>
       <c r="AF25" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AG25" t="inlineStr">
         <is>
@@ -2255,14 +2237,14 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>tardio</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Cadena alimentaria</t>
+          <t>ADN y cromosomas</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2271,67 +2253,46 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D26" t="n">
-        <v>4</v>
-      </c>
-      <c r="E26" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F26" t="n">
-        <v>2.5</v>
+        <v>8</v>
       </c>
       <c r="G26" t="n">
-        <v>2</v>
-      </c>
-      <c r="H26" t="n">
-        <v>3</v>
-      </c>
-      <c r="I26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J26" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K26" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="L26" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="M26" t="n">
+        <v>7</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1</v>
+      </c>
+      <c r="P26" t="n">
+        <v>1</v>
+      </c>
+      <c r="S26" t="n">
+        <v>1</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF26" t="n">
         <v>6</v>
-      </c>
-      <c r="M26" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="N26" t="n">
-        <v>1</v>
-      </c>
-      <c r="O26" t="n">
-        <v>1</v>
-      </c>
-      <c r="P26" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>1</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1</v>
-      </c>
-      <c r="S26" t="n">
-        <v>1</v>
-      </c>
-      <c r="T26" t="n">
-        <v>1</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>4</v>
       </c>
       <c r="AG26" t="inlineStr">
         <is>
@@ -2347,7 +2308,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Célula animal y célula vegetal</t>
+          <t>Agricultura y seguridad alimentaria</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2356,67 +2317,37 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D27" t="n">
-        <v>6</v>
-      </c>
-      <c r="E27" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F27" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G27" t="n">
         <v>6</v>
       </c>
-      <c r="H27" t="n">
-        <v>5</v>
-      </c>
-      <c r="I27" t="n">
-        <v>7</v>
-      </c>
-      <c r="J27" t="n">
+      <c r="K27" t="n">
+        <v>2</v>
+      </c>
+      <c r="M27" t="n">
         <v>4.5</v>
       </c>
-      <c r="K27" t="n">
-        <v>7</v>
-      </c>
-      <c r="L27" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="M27" t="n">
-        <v>7</v>
-      </c>
-      <c r="N27" t="n">
-        <v>1</v>
-      </c>
       <c r="O27" t="n">
         <v>1</v>
       </c>
       <c r="P27" t="n">
         <v>1</v>
       </c>
-      <c r="Q27" t="n">
-        <v>1</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1</v>
-      </c>
-      <c r="S27" t="n">
-        <v>1</v>
-      </c>
       <c r="T27" t="n">
         <v>1</v>
       </c>
-      <c r="U27" t="n">
-        <v>1</v>
-      </c>
       <c r="V27" t="n">
         <v>1</v>
       </c>
       <c r="AF27" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AG27" t="inlineStr">
         <is>
@@ -2432,7 +2363,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Ciclo de vida de las plantas</t>
+          <t>Biodiversidad</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2447,10 +2378,10 @@
         <v>2</v>
       </c>
       <c r="E28" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F28" t="n">
-        <v>8</v>
+        <v>2.5</v>
       </c>
       <c r="G28" t="n">
         <v>2</v>
@@ -2459,7 +2390,7 @@
         <v>2</v>
       </c>
       <c r="I28" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J28" t="n">
         <v>2.5</v>
@@ -2517,7 +2448,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Ciclo de vida de los animales</t>
+          <t>Biomoléculas</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2526,37 +2457,28 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D29" t="n">
-        <v>3</v>
-      </c>
-      <c r="E29" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F29" t="n">
         <v>8</v>
       </c>
       <c r="G29" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H29" t="n">
         <v>2</v>
       </c>
-      <c r="I29" t="n">
-        <v>2</v>
-      </c>
       <c r="J29" t="n">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="L29" t="n">
-        <v>3</v>
+        <v>7.5</v>
       </c>
       <c r="M29" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N29" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O29" t="n">
         <v>1</v>
@@ -2567,9 +2489,6 @@
       <c r="Q29" t="n">
         <v>1</v>
       </c>
-      <c r="R29" t="n">
-        <v>1</v>
-      </c>
       <c r="S29" t="n">
         <v>1</v>
       </c>
@@ -2579,8 +2498,11 @@
       <c r="V29" t="n">
         <v>1</v>
       </c>
+      <c r="Z29" t="n">
+        <v>1</v>
+      </c>
       <c r="AF29" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AG29" t="inlineStr">
         <is>
@@ -2596,7 +2518,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Clasificación de seres vivos por sus rasgos</t>
+          <t>Biotecnología vegetal y agroindustria</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2605,40 +2527,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D30" t="n">
-        <v>2</v>
-      </c>
-      <c r="E30" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F30" t="n">
-        <v>2.5</v>
+        <v>8</v>
       </c>
       <c r="G30" t="n">
-        <v>2</v>
-      </c>
-      <c r="H30" t="n">
-        <v>2</v>
-      </c>
-      <c r="I30" t="n">
-        <v>2</v>
-      </c>
-      <c r="J30" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K30" t="n">
-        <v>3</v>
-      </c>
-      <c r="L30" t="n">
-        <v>3</v>
+        <v>8.5</v>
       </c>
       <c r="M30" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N30" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O30" t="n">
         <v>1</v>
@@ -2646,42 +2547,27 @@
       <c r="P30" t="n">
         <v>1</v>
       </c>
-      <c r="Q30" t="n">
-        <v>1</v>
-      </c>
-      <c r="R30" t="n">
-        <v>1</v>
-      </c>
-      <c r="S30" t="n">
-        <v>1</v>
-      </c>
-      <c r="T30" t="n">
-        <v>1</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1</v>
-      </c>
       <c r="V30" t="n">
         <v>1</v>
       </c>
       <c r="AF30" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AG30" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Competencia por recursos</t>
+          <t>Cadena alimentaria</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2695,8 +2581,11 @@
       <c r="D31" t="n">
         <v>4</v>
       </c>
+      <c r="E31" t="n">
+        <v>3</v>
+      </c>
       <c r="F31" t="n">
-        <v>8</v>
+        <v>2.5</v>
       </c>
       <c r="G31" t="n">
         <v>2</v>
@@ -2707,12 +2596,21 @@
       <c r="I31" t="n">
         <v>5</v>
       </c>
+      <c r="J31" t="n">
+        <v>2.5</v>
+      </c>
       <c r="K31" t="n">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="L31" t="n">
+        <v>6</v>
       </c>
       <c r="M31" t="n">
         <v>4.5</v>
       </c>
+      <c r="N31" t="n">
+        <v>1</v>
+      </c>
       <c r="O31" t="n">
         <v>1</v>
       </c>
@@ -2725,7 +2623,13 @@
       <c r="R31" t="n">
         <v>1</v>
       </c>
+      <c r="S31" t="n">
+        <v>1</v>
+      </c>
       <c r="T31" t="n">
+        <v>1</v>
+      </c>
+      <c r="U31" t="n">
         <v>1</v>
       </c>
       <c r="V31" t="n">
@@ -2748,7 +2652,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Concepto de especie</t>
+          <t>Cambio climático y seres vivos</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2763,13 +2667,13 @@
         <v>7</v>
       </c>
       <c r="F32" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="G32" t="n">
-        <v>6</v>
-      </c>
-      <c r="J32" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="H32" t="n">
+        <v>7</v>
+      </c>
+      <c r="K32" t="n">
+        <v>5</v>
       </c>
       <c r="L32" t="n">
         <v>6</v>
@@ -2780,10 +2684,10 @@
       <c r="O32" t="n">
         <v>1</v>
       </c>
-      <c r="P32" t="n">
-        <v>1</v>
-      </c>
-      <c r="S32" t="n">
+      <c r="Q32" t="n">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
         <v>1</v>
       </c>
       <c r="U32" t="n">
@@ -2793,7 +2697,7 @@
         <v>1</v>
       </c>
       <c r="AF32" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AG32" t="inlineStr">
         <is>
@@ -2802,14 +2706,14 @@
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>tardio</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Contagio y prevención de enfermedades</t>
+          <t>Célula animal y célula vegetal</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2818,22 +2722,40 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D33" t="n">
-        <v>2</v>
+        <v>6</v>
+      </c>
+      <c r="E33" t="n">
+        <v>7</v>
       </c>
       <c r="F33" t="n">
         <v>8</v>
       </c>
       <c r="G33" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H33" t="n">
-        <v>3</v>
+        <v>5</v>
+      </c>
+      <c r="I33" t="n">
+        <v>7</v>
       </c>
       <c r="J33" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
+      </c>
+      <c r="K33" t="n">
+        <v>7</v>
+      </c>
+      <c r="L33" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="M33" t="n">
+        <v>7</v>
+      </c>
+      <c r="N33" t="n">
+        <v>1</v>
       </c>
       <c r="O33" t="n">
         <v>1</v>
@@ -2844,14 +2766,23 @@
       <c r="Q33" t="n">
         <v>1</v>
       </c>
+      <c r="R33" t="n">
+        <v>1</v>
+      </c>
       <c r="S33" t="n">
         <v>1</v>
       </c>
-      <c r="Z33" t="n">
+      <c r="T33" t="n">
+        <v>1</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
+      </c>
+      <c r="V33" t="n">
         <v>1</v>
       </c>
       <c r="AF33" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AG33" t="inlineStr">
         <is>
@@ -2867,7 +2798,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Crecimiento poblacional</t>
+          <t>Ciclo de vida de las plantas</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2876,29 +2807,59 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D34" t="n">
-        <v>6</v>
+        <v>2</v>
+      </c>
+      <c r="E34" t="n">
+        <v>2</v>
       </c>
       <c r="F34" t="n">
         <v>8</v>
       </c>
+      <c r="G34" t="n">
+        <v>2</v>
+      </c>
       <c r="H34" t="n">
-        <v>7</v>
+        <v>2</v>
+      </c>
+      <c r="I34" t="n">
+        <v>2</v>
+      </c>
+      <c r="J34" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K34" t="n">
+        <v>2</v>
       </c>
       <c r="L34" t="n">
-        <v>7.5</v>
+        <v>3</v>
       </c>
       <c r="M34" t="n">
-        <v>7</v>
+        <v>2.5</v>
+      </c>
+      <c r="N34" t="n">
+        <v>1</v>
       </c>
       <c r="O34" t="n">
         <v>1</v>
       </c>
+      <c r="P34" t="n">
+        <v>1</v>
+      </c>
       <c r="Q34" t="n">
         <v>1</v>
       </c>
+      <c r="R34" t="n">
+        <v>1</v>
+      </c>
+      <c r="S34" t="n">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1</v>
+      </c>
       <c r="U34" t="n">
         <v>1</v>
       </c>
@@ -2906,7 +2867,7 @@
         <v>1</v>
       </c>
       <c r="AF34" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AG34" t="inlineStr">
         <is>
@@ -2922,7 +2883,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Depredación</t>
+          <t>Ciclo de vida de los animales</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2931,28 +2892,37 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D35" t="n">
-        <v>4</v>
+        <v>3</v>
+      </c>
+      <c r="E35" t="n">
+        <v>2</v>
       </c>
       <c r="F35" t="n">
+        <v>8</v>
+      </c>
+      <c r="G35" t="n">
+        <v>2</v>
+      </c>
+      <c r="H35" t="n">
+        <v>2</v>
+      </c>
+      <c r="I35" t="n">
+        <v>2</v>
+      </c>
+      <c r="J35" t="n">
         <v>2.5</v>
       </c>
-      <c r="G35" t="n">
-        <v>2</v>
-      </c>
-      <c r="H35" t="n">
+      <c r="L35" t="n">
         <v>3</v>
       </c>
-      <c r="I35" t="n">
-        <v>5</v>
-      </c>
-      <c r="K35" t="n">
-        <v>5</v>
-      </c>
-      <c r="L35" t="n">
-        <v>6</v>
+      <c r="M35" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N35" t="n">
+        <v>1</v>
       </c>
       <c r="O35" t="n">
         <v>1</v>
@@ -2966,14 +2936,17 @@
       <c r="R35" t="n">
         <v>1</v>
       </c>
-      <c r="T35" t="n">
+      <c r="S35" t="n">
         <v>1</v>
       </c>
       <c r="U35" t="n">
         <v>1</v>
       </c>
+      <c r="V35" t="n">
+        <v>1</v>
+      </c>
       <c r="AF35" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AG35" t="inlineStr">
         <is>
@@ -2989,7 +2962,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Difusión y ósmosis</t>
+          <t>Papel de los seres vivos en el ciclo del agua</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2998,38 +2971,59 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D36" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G36" t="n">
-        <v>6</v>
+        <v>8.5</v>
+      </c>
+      <c r="H36" t="n">
+        <v>7</v>
+      </c>
+      <c r="I36" t="n">
+        <v>5</v>
+      </c>
+      <c r="J36" t="n">
+        <v>4.5</v>
       </c>
       <c r="K36" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L36" t="n">
-        <v>7.5</v>
+        <v>5</v>
+      </c>
+      <c r="M36" t="n">
+        <v>7</v>
       </c>
       <c r="P36" t="n">
         <v>1</v>
       </c>
+      <c r="Q36" t="n">
+        <v>1</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1</v>
+      </c>
+      <c r="S36" t="n">
+        <v>1</v>
+      </c>
       <c r="T36" t="n">
         <v>1</v>
       </c>
       <c r="U36" t="n">
         <v>1</v>
       </c>
-      <c r="Z36" t="n">
+      <c r="V36" t="n">
         <v>1</v>
       </c>
       <c r="AF36" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG36" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH36" t="inlineStr">
@@ -3041,7 +3035,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Digestión química y absorción de nutrientes</t>
+          <t>Ciclos del carbono y del oxígeno</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3050,28 +3044,37 @@
         </is>
       </c>
       <c r="C37" t="n">
+        <v>3</v>
+      </c>
+      <c r="D37" t="n">
+        <v>3</v>
+      </c>
+      <c r="E37" t="n">
         <v>8</v>
       </c>
-      <c r="D37" t="n">
-        <v>8</v>
-      </c>
       <c r="F37" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G37" t="n">
+        <v>6</v>
+      </c>
+      <c r="H37" t="n">
+        <v>5</v>
+      </c>
+      <c r="J37" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K37" t="n">
         <v>4</v>
-      </c>
-      <c r="I37" t="n">
-        <v>5</v>
-      </c>
-      <c r="J37" t="n">
-        <v>7</v>
       </c>
       <c r="L37" t="n">
         <v>7.5</v>
       </c>
       <c r="M37" t="n">
-        <v>7</v>
+        <v>2.5</v>
+      </c>
+      <c r="N37" t="n">
+        <v>1</v>
       </c>
       <c r="O37" t="n">
         <v>1</v>
@@ -3079,27 +3082,27 @@
       <c r="P37" t="n">
         <v>1</v>
       </c>
-      <c r="R37" t="n">
+      <c r="Q37" t="n">
         <v>1</v>
       </c>
       <c r="S37" t="n">
         <v>1</v>
       </c>
+      <c r="T37" t="n">
+        <v>1</v>
+      </c>
       <c r="U37" t="n">
         <v>1</v>
       </c>
       <c r="V37" t="n">
         <v>1</v>
       </c>
-      <c r="Z37" t="n">
-        <v>1</v>
-      </c>
       <c r="AF37" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AG37" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH37" t="inlineStr">
@@ -3111,7 +3114,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Estructuras celulares básicas</t>
+          <t>Circulación e intercambio capilar</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3120,41 +3123,23 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D38" t="n">
-        <v>6</v>
-      </c>
-      <c r="E38" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F38" t="n">
         <v>8</v>
       </c>
       <c r="G38" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H38" t="n">
-        <v>5</v>
-      </c>
-      <c r="I38" t="n">
-        <v>7</v>
-      </c>
-      <c r="J38" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K38" t="n">
         <v>7</v>
       </c>
       <c r="L38" t="n">
         <v>7.5</v>
       </c>
-      <c r="M38" t="n">
-        <v>7</v>
-      </c>
-      <c r="N38" t="n">
-        <v>1</v>
-      </c>
       <c r="O38" t="n">
         <v>1</v>
       </c>
@@ -3164,26 +3149,11 @@
       <c r="Q38" t="n">
         <v>1</v>
       </c>
-      <c r="R38" t="n">
-        <v>1</v>
-      </c>
-      <c r="S38" t="n">
-        <v>1</v>
-      </c>
-      <c r="T38" t="n">
-        <v>1</v>
-      </c>
       <c r="U38" t="n">
         <v>1</v>
       </c>
-      <c r="V38" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>1</v>
-      </c>
       <c r="AF38" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AG38" t="inlineStr">
         <is>
@@ -3192,14 +3162,14 @@
       </c>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>posterior</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Estructuras del cuerpo animal y su función</t>
+          <t>Clasificación de seres vivos por sus rasgos</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3226,16 +3196,16 @@
         <v>2</v>
       </c>
       <c r="I39" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J39" t="n">
         <v>2.5</v>
       </c>
       <c r="K39" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L39" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M39" t="n">
         <v>2.5</v>
@@ -3267,9 +3237,6 @@
       <c r="V39" t="n">
         <v>1</v>
       </c>
-      <c r="Z39" t="n">
-        <v>1</v>
-      </c>
       <c r="AF39" t="n">
         <v>2</v>
       </c>
@@ -3287,7 +3254,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Extinción de especies</t>
+          <t>Clasificación jerárquica y nomenclatura</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3296,28 +3263,28 @@
         </is>
       </c>
       <c r="C40" t="n">
+        <v>7</v>
+      </c>
+      <c r="D40" t="n">
+        <v>7</v>
+      </c>
+      <c r="F40" t="n">
         <v>5</v>
       </c>
-      <c r="D40" t="n">
+      <c r="G40" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H40" t="n">
+        <v>7</v>
+      </c>
+      <c r="J40" t="n">
+        <v>7</v>
+      </c>
+      <c r="K40" t="n">
         <v>5</v>
       </c>
-      <c r="F40" t="n">
-        <v>8</v>
-      </c>
-      <c r="G40" t="n">
-        <v>2</v>
-      </c>
-      <c r="H40" t="n">
-        <v>5</v>
-      </c>
-      <c r="K40" t="n">
-        <v>3</v>
-      </c>
-      <c r="L40" t="n">
-        <v>6</v>
-      </c>
       <c r="M40" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="O40" t="n">
         <v>1</v>
@@ -3328,21 +3295,21 @@
       <c r="Q40" t="n">
         <v>1</v>
       </c>
+      <c r="S40" t="n">
+        <v>1</v>
+      </c>
       <c r="T40" t="n">
         <v>1</v>
       </c>
-      <c r="U40" t="n">
-        <v>1</v>
-      </c>
       <c r="V40" t="n">
         <v>1</v>
       </c>
       <c r="AF40" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AG40" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH40" t="inlineStr">
@@ -3354,7 +3321,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Factores bióticos y abióticos</t>
+          <t>Competencia por recursos</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3368,36 +3335,24 @@
       <c r="D41" t="n">
         <v>4</v>
       </c>
-      <c r="E41" t="n">
-        <v>5</v>
-      </c>
       <c r="F41" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G41" t="n">
         <v>2</v>
       </c>
       <c r="H41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I41" t="n">
         <v>5</v>
       </c>
-      <c r="J41" t="n">
-        <v>2.5</v>
-      </c>
       <c r="K41" t="n">
-        <v>2</v>
-      </c>
-      <c r="L41" t="n">
+        <v>3</v>
+      </c>
+      <c r="M41" t="n">
         <v>4.5</v>
       </c>
-      <c r="M41" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N41" t="n">
-        <v>1</v>
-      </c>
       <c r="O41" t="n">
         <v>1</v>
       </c>
@@ -3410,13 +3365,7 @@
       <c r="R41" t="n">
         <v>1</v>
       </c>
-      <c r="S41" t="n">
-        <v>1</v>
-      </c>
       <c r="T41" t="n">
-        <v>1</v>
-      </c>
-      <c r="U41" t="n">
         <v>1</v>
       </c>
       <c r="V41" t="n">
@@ -3432,14 +3381,14 @@
       </c>
       <c r="AH41" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Fecundación y desarrollo embrionario</t>
+          <t>Concepto de especie</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3448,28 +3397,25 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F42" t="n">
-        <v>8</v>
+        <v>2.5</v>
       </c>
       <c r="G42" t="n">
         <v>6</v>
       </c>
-      <c r="H42" t="n">
-        <v>7</v>
-      </c>
-      <c r="I42" t="n">
-        <v>4</v>
-      </c>
       <c r="J42" t="n">
         <v>7</v>
       </c>
       <c r="L42" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="M42" t="n">
+        <v>4.5</v>
       </c>
       <c r="O42" t="n">
         <v>1</v>
@@ -3477,23 +3423,17 @@
       <c r="P42" t="n">
         <v>1</v>
       </c>
-      <c r="Q42" t="n">
-        <v>1</v>
-      </c>
-      <c r="R42" t="n">
-        <v>1</v>
-      </c>
       <c r="S42" t="n">
         <v>1</v>
       </c>
       <c r="U42" t="n">
         <v>1</v>
       </c>
-      <c r="Z42" t="n">
+      <c r="V42" t="n">
         <v>1</v>
       </c>
       <c r="AF42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG42" t="inlineStr">
         <is>
@@ -3509,7 +3449,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Flujo de energía y pirámides ecológicas</t>
+          <t>Contagio y prevención de enfermedades</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3518,30 +3458,24 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D43" t="n">
-        <v>7</v>
-      </c>
-      <c r="E43" t="n">
-        <v>6</v>
+        <v>2</v>
+      </c>
+      <c r="F43" t="n">
+        <v>8</v>
       </c>
       <c r="G43" t="n">
-        <v>8.5</v>
+        <v>2</v>
       </c>
       <c r="H43" t="n">
-        <v>5</v>
-      </c>
-      <c r="K43" t="n">
-        <v>6</v>
-      </c>
-      <c r="L43" t="n">
-        <v>6</v>
-      </c>
-      <c r="M43" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="N43" t="n">
+        <v>3</v>
+      </c>
+      <c r="J43" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O43" t="n">
         <v>1</v>
       </c>
       <c r="P43" t="n">
@@ -3550,17 +3484,14 @@
       <c r="Q43" t="n">
         <v>1</v>
       </c>
-      <c r="T43" t="n">
-        <v>1</v>
-      </c>
-      <c r="U43" t="n">
-        <v>1</v>
-      </c>
-      <c r="V43" t="n">
+      <c r="S43" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z43" t="n">
         <v>1</v>
       </c>
       <c r="AF43" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AG43" t="inlineStr">
         <is>
@@ -3576,7 +3507,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Genética humana y enfermedades hereditarias</t>
+          <t>Contaminación y sus efectos en los seres vivos</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3585,38 +3516,44 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D44" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F44" t="n">
-        <v>8</v>
-      </c>
-      <c r="G44" t="n">
-        <v>8.5</v>
+        <v>5</v>
       </c>
       <c r="H44" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="J44" t="n">
-        <v>7</v>
+        <v>2.5</v>
+      </c>
+      <c r="K44" t="n">
+        <v>4</v>
+      </c>
+      <c r="L44" t="n">
+        <v>6</v>
       </c>
       <c r="M44" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="O44" t="n">
         <v>1</v>
       </c>
-      <c r="P44" t="n">
-        <v>1</v>
-      </c>
       <c r="Q44" t="n">
         <v>1</v>
       </c>
       <c r="S44" t="n">
         <v>1</v>
       </c>
+      <c r="T44" t="n">
+        <v>1</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
+      </c>
       <c r="V44" t="n">
         <v>1</v>
       </c>
@@ -3624,11 +3561,11 @@
         <v>1</v>
       </c>
       <c r="AF44" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AG44" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH44" t="inlineStr">
@@ -3640,7 +3577,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Genotipo y fenotipo</t>
+          <t>Crecimiento poblacional</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3649,25 +3586,19 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D45" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F45" t="n">
         <v>8</v>
       </c>
-      <c r="G45" t="n">
-        <v>6</v>
-      </c>
       <c r="H45" t="n">
-        <v>3</v>
-      </c>
-      <c r="I45" t="n">
-        <v>8</v>
-      </c>
-      <c r="J45" t="n">
-        <v>7</v>
+        <v>7</v>
+      </c>
+      <c r="L45" t="n">
+        <v>7.5</v>
       </c>
       <c r="M45" t="n">
         <v>7</v>
@@ -3675,22 +3606,13 @@
       <c r="O45" t="n">
         <v>1</v>
       </c>
-      <c r="P45" t="n">
-        <v>1</v>
-      </c>
       <c r="Q45" t="n">
         <v>1</v>
       </c>
-      <c r="R45" t="n">
-        <v>1</v>
-      </c>
-      <c r="S45" t="n">
+      <c r="U45" t="n">
         <v>1</v>
       </c>
       <c r="V45" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z45" t="n">
         <v>1</v>
       </c>
       <c r="AF45" t="n">
@@ -3710,7 +3632,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Grupos de vertebrados</t>
+          <t>Depredación</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3719,10 +3641,10 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D46" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F46" t="n">
         <v>2.5</v>
@@ -3731,16 +3653,16 @@
         <v>2</v>
       </c>
       <c r="H46" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I46" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K46" t="n">
         <v>5</v>
       </c>
-      <c r="M46" t="n">
-        <v>2.5</v>
+      <c r="L46" t="n">
+        <v>6</v>
       </c>
       <c r="O46" t="n">
         <v>1</v>
@@ -3757,11 +3679,11 @@
       <c r="T46" t="n">
         <v>1</v>
       </c>
-      <c r="V46" t="n">
+      <c r="U46" t="n">
         <v>1</v>
       </c>
       <c r="AF46" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AG46" t="inlineStr">
         <is>
@@ -3777,7 +3699,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Hábitat y ecosistemas comunes</t>
+          <t>Diferenciación y especialización celular</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3786,71 +3708,50 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D47" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E47" t="n">
-        <v>2</v>
-      </c>
-      <c r="F47" t="n">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="G47" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H47" t="n">
-        <v>2</v>
-      </c>
-      <c r="I47" t="n">
-        <v>2</v>
-      </c>
-      <c r="J47" t="n">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="K47" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="L47" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="N47" t="n">
+        <v>1</v>
+      </c>
+      <c r="P47" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>1</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF47" t="n">
         <v>6</v>
       </c>
-      <c r="M47" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N47" t="n">
-        <v>1</v>
-      </c>
-      <c r="O47" t="n">
-        <v>1</v>
-      </c>
-      <c r="P47" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>1</v>
-      </c>
-      <c r="R47" t="n">
-        <v>1</v>
-      </c>
-      <c r="S47" t="n">
-        <v>1</v>
-      </c>
-      <c r="T47" t="n">
-        <v>1</v>
-      </c>
-      <c r="U47" t="n">
-        <v>1</v>
-      </c>
-      <c r="V47" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF47" t="n">
-        <v>2</v>
-      </c>
       <c r="AG47" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH47" t="inlineStr">
@@ -3862,7 +3763,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Hábitos de vida saludable</t>
+          <t>Difusión y ósmosis</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3871,41 +3772,23 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D48" t="n">
-        <v>2</v>
-      </c>
-      <c r="F48" t="n">
-        <v>2.5</v>
+        <v>6</v>
       </c>
       <c r="G48" t="n">
-        <v>2</v>
-      </c>
-      <c r="H48" t="n">
-        <v>2</v>
-      </c>
-      <c r="J48" t="n">
-        <v>2.5</v>
+        <v>6</v>
       </c>
       <c r="K48" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L48" t="n">
         <v>7.5</v>
       </c>
-      <c r="O48" t="n">
-        <v>1</v>
-      </c>
       <c r="P48" t="n">
         <v>1</v>
       </c>
-      <c r="Q48" t="n">
-        <v>1</v>
-      </c>
-      <c r="S48" t="n">
-        <v>1</v>
-      </c>
       <c r="T48" t="n">
         <v>1</v>
       </c>
@@ -3916,7 +3799,7 @@
         <v>1</v>
       </c>
       <c r="AF48" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AG48" t="inlineStr">
         <is>
@@ -3932,7 +3815,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Herencia mendeliana</t>
+          <t>Digestión química y absorción de nutrientes</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3941,49 +3824,52 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D49" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F49" t="n">
         <v>8</v>
       </c>
       <c r="G49" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="H49" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I49" t="n">
+        <v>5</v>
+      </c>
+      <c r="J49" t="n">
+        <v>7</v>
+      </c>
+      <c r="L49" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="M49" t="n">
+        <v>7</v>
+      </c>
+      <c r="O49" t="n">
+        <v>1</v>
+      </c>
+      <c r="P49" t="n">
+        <v>1</v>
+      </c>
+      <c r="R49" t="n">
+        <v>1</v>
+      </c>
+      <c r="S49" t="n">
+        <v>1</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
+      </c>
+      <c r="V49" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF49" t="n">
         <v>8</v>
-      </c>
-      <c r="J49" t="n">
-        <v>7</v>
-      </c>
-      <c r="M49" t="n">
-        <v>7</v>
-      </c>
-      <c r="O49" t="n">
-        <v>1</v>
-      </c>
-      <c r="P49" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>1</v>
-      </c>
-      <c r="R49" t="n">
-        <v>1</v>
-      </c>
-      <c r="S49" t="n">
-        <v>1</v>
-      </c>
-      <c r="V49" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF49" t="n">
-        <v>7</v>
       </c>
       <c r="AG49" t="inlineStr">
         <is>
@@ -3999,7 +3885,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Homeostasis</t>
+          <t>Diversidad genética de poblaciones</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4008,62 +3894,35 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D50" t="n">
-        <v>8</v>
-      </c>
-      <c r="E50" t="n">
-        <v>8</v>
-      </c>
-      <c r="F50" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G50" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="H50" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J50" t="n">
         <v>7</v>
       </c>
       <c r="K50" t="n">
-        <v>4</v>
-      </c>
-      <c r="M50" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="N50" t="n">
-        <v>1</v>
-      </c>
-      <c r="O50" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="P50" t="n">
         <v>1</v>
       </c>
-      <c r="Q50" t="n">
-        <v>1</v>
-      </c>
       <c r="S50" t="n">
         <v>1</v>
       </c>
       <c r="T50" t="n">
         <v>1</v>
       </c>
-      <c r="V50" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z50" t="n">
-        <v>1</v>
-      </c>
       <c r="AF50" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AG50" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH50" t="inlineStr">
@@ -4075,7 +3934,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Invertebrados e insectos</t>
+          <t>Enzimas</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4084,41 +3943,44 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D51" t="n">
-        <v>2</v>
-      </c>
-      <c r="F51" t="n">
-        <v>2.5</v>
+        <v>6</v>
       </c>
       <c r="G51" t="n">
-        <v>3</v>
-      </c>
-      <c r="H51" t="n">
-        <v>2</v>
-      </c>
-      <c r="I51" t="n">
-        <v>2</v>
-      </c>
-      <c r="O51" t="n">
-        <v>1</v>
+        <v>6</v>
+      </c>
+      <c r="J51" t="n">
+        <v>7</v>
+      </c>
+      <c r="L51" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="M51" t="n">
+        <v>7</v>
       </c>
       <c r="P51" t="n">
         <v>1</v>
       </c>
-      <c r="Q51" t="n">
-        <v>1</v>
-      </c>
-      <c r="R51" t="n">
+      <c r="S51" t="n">
+        <v>1</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
+      </c>
+      <c r="V51" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z51" t="n">
         <v>1</v>
       </c>
       <c r="AF51" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AG51" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH51" t="inlineStr">
@@ -4130,7 +3992,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Necesidades de los seres vivos</t>
+          <t>Propagación de enfermedades y control de brotes</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4139,43 +4001,19 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>2</v>
-      </c>
-      <c r="D52" t="n">
-        <v>2</v>
-      </c>
-      <c r="E52" t="n">
-        <v>2</v>
-      </c>
-      <c r="F52" t="n">
-        <v>2.5</v>
+        <v>11</v>
       </c>
       <c r="G52" t="n">
-        <v>2</v>
+        <v>8.5</v>
       </c>
       <c r="H52" t="n">
-        <v>2</v>
-      </c>
-      <c r="I52" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J52" t="n">
         <v>2.5</v>
       </c>
-      <c r="K52" t="n">
-        <v>2</v>
-      </c>
       <c r="L52" t="n">
-        <v>3</v>
-      </c>
-      <c r="M52" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N52" t="n">
-        <v>1</v>
-      </c>
-      <c r="O52" t="n">
-        <v>1</v>
+        <v>7.5</v>
       </c>
       <c r="P52" t="n">
         <v>1</v>
@@ -4183,39 +4021,30 @@
       <c r="Q52" t="n">
         <v>1</v>
       </c>
-      <c r="R52" t="n">
-        <v>1</v>
-      </c>
       <c r="S52" t="n">
         <v>1</v>
       </c>
-      <c r="T52" t="n">
-        <v>1</v>
-      </c>
       <c r="U52" t="n">
         <v>1</v>
       </c>
-      <c r="V52" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF52" t="n">
-        <v>2</v>
+      <c r="Z52" t="n">
+        <v>1</v>
       </c>
       <c r="AG52" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>no_aplica</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Órganos de los sentidos</t>
+          <t>Estructuras celulares básicas</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4224,28 +4053,40 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D53" t="n">
-        <v>4</v>
+        <v>6</v>
+      </c>
+      <c r="E53" t="n">
+        <v>7</v>
       </c>
       <c r="F53" t="n">
         <v>8</v>
       </c>
       <c r="G53" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H53" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I53" t="n">
         <v>7</v>
       </c>
       <c r="J53" t="n">
-        <v>7</v>
+        <v>4.5</v>
+      </c>
+      <c r="K53" t="n">
+        <v>7</v>
+      </c>
+      <c r="L53" t="n">
+        <v>7.5</v>
       </c>
       <c r="M53" t="n">
-        <v>2.5</v>
+        <v>7</v>
+      </c>
+      <c r="N53" t="n">
+        <v>1</v>
       </c>
       <c r="O53" t="n">
         <v>1</v>
@@ -4262,11 +4103,20 @@
       <c r="S53" t="n">
         <v>1</v>
       </c>
+      <c r="T53" t="n">
+        <v>1</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
+      </c>
       <c r="V53" t="n">
         <v>1</v>
       </c>
+      <c r="Z53" t="n">
+        <v>1</v>
+      </c>
       <c r="AF53" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AG53" t="inlineStr">
         <is>
@@ -4282,7 +4132,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Partes de la planta y sus funciones</t>
+          <t>Estructuras del cuerpo animal y su función</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4309,13 +4159,13 @@
         <v>2</v>
       </c>
       <c r="I54" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J54" t="n">
         <v>2.5</v>
       </c>
       <c r="K54" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L54" t="n">
         <v>4</v>
@@ -4350,6 +4200,9 @@
       <c r="V54" t="n">
         <v>1</v>
       </c>
+      <c r="Z54" t="n">
+        <v>1</v>
+      </c>
       <c r="AF54" t="n">
         <v>2</v>
       </c>
@@ -4367,7 +4220,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Productores, consumidores y descomponedores</t>
+          <t>Extinción de especies</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4376,40 +4229,28 @@
         </is>
       </c>
       <c r="C55" t="n">
+        <v>5</v>
+      </c>
+      <c r="D55" t="n">
+        <v>5</v>
+      </c>
+      <c r="F55" t="n">
+        <v>8</v>
+      </c>
+      <c r="G55" t="n">
+        <v>2</v>
+      </c>
+      <c r="H55" t="n">
+        <v>5</v>
+      </c>
+      <c r="K55" t="n">
         <v>3</v>
-      </c>
-      <c r="D55" t="n">
-        <v>3</v>
-      </c>
-      <c r="E55" t="n">
-        <v>3</v>
-      </c>
-      <c r="F55" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="G55" t="n">
-        <v>2</v>
-      </c>
-      <c r="H55" t="n">
-        <v>3</v>
-      </c>
-      <c r="I55" t="n">
-        <v>8</v>
-      </c>
-      <c r="J55" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K55" t="n">
-        <v>2</v>
       </c>
       <c r="L55" t="n">
         <v>6</v>
       </c>
       <c r="M55" t="n">
-        <v>7</v>
-      </c>
-      <c r="N55" t="n">
-        <v>1</v>
+        <v>4.5</v>
       </c>
       <c r="O55" t="n">
         <v>1</v>
@@ -4420,12 +4261,6 @@
       <c r="Q55" t="n">
         <v>1</v>
       </c>
-      <c r="R55" t="n">
-        <v>1</v>
-      </c>
-      <c r="S55" t="n">
-        <v>1</v>
-      </c>
       <c r="T55" t="n">
         <v>1</v>
       </c>
@@ -4436,7 +4271,7 @@
         <v>1</v>
       </c>
       <c r="AF55" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AG55" t="inlineStr">
         <is>
@@ -4452,7 +4287,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Reproducción sexual de las plantas con flor</t>
+          <t>Factores bióticos y abióticos</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4461,16 +4296,16 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D56" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E56" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F56" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G56" t="n">
         <v>2</v>
@@ -4479,44 +4314,50 @@
         <v>2</v>
       </c>
       <c r="I56" t="n">
+        <v>5</v>
+      </c>
+      <c r="J56" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K56" t="n">
+        <v>2</v>
+      </c>
+      <c r="L56" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="M56" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N56" t="n">
+        <v>1</v>
+      </c>
+      <c r="O56" t="n">
+        <v>1</v>
+      </c>
+      <c r="P56" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>1</v>
+      </c>
+      <c r="R56" t="n">
+        <v>1</v>
+      </c>
+      <c r="S56" t="n">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>1</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
+      </c>
+      <c r="V56" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF56" t="n">
         <v>4</v>
       </c>
-      <c r="K56" t="n">
-        <v>2</v>
-      </c>
-      <c r="L56" t="n">
-        <v>5</v>
-      </c>
-      <c r="M56" t="n">
-        <v>7</v>
-      </c>
-      <c r="N56" t="n">
-        <v>1</v>
-      </c>
-      <c r="O56" t="n">
-        <v>1</v>
-      </c>
-      <c r="P56" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q56" t="n">
-        <v>1</v>
-      </c>
-      <c r="R56" t="n">
-        <v>1</v>
-      </c>
-      <c r="T56" t="n">
-        <v>1</v>
-      </c>
-      <c r="U56" t="n">
-        <v>1</v>
-      </c>
-      <c r="V56" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF56" t="n">
-        <v>6</v>
-      </c>
       <c r="AG56" t="inlineStr">
         <is>
           <t>alineado</t>
@@ -4524,14 +4365,14 @@
       </c>
       <c r="AH56" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>tardio</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Reproducción sexual y asexual</t>
+          <t>Factores limitantes de las poblaciones</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4540,31 +4381,28 @@
         </is>
       </c>
       <c r="C57" t="n">
+        <v>7</v>
+      </c>
+      <c r="D57" t="n">
+        <v>7</v>
+      </c>
+      <c r="E57" t="n">
         <v>6</v>
-      </c>
-      <c r="D57" t="n">
-        <v>6</v>
-      </c>
-      <c r="E57" t="n">
-        <v>8</v>
       </c>
       <c r="F57" t="n">
         <v>8</v>
       </c>
       <c r="G57" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="K57" t="n">
         <v>3</v>
       </c>
-      <c r="H57" t="n">
-        <v>3</v>
-      </c>
-      <c r="I57" t="n">
-        <v>4</v>
-      </c>
       <c r="L57" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M57" t="n">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="N57" t="n">
         <v>1</v>
@@ -4575,10 +4413,7 @@
       <c r="P57" t="n">
         <v>1</v>
       </c>
-      <c r="Q57" t="n">
-        <v>1</v>
-      </c>
-      <c r="R57" t="n">
+      <c r="T57" t="n">
         <v>1</v>
       </c>
       <c r="U57" t="n">
@@ -4587,15 +4422,12 @@
       <c r="V57" t="n">
         <v>1</v>
       </c>
-      <c r="Z57" t="n">
-        <v>1</v>
-      </c>
       <c r="AF57" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG57" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH57" t="inlineStr">
@@ -4607,7 +4439,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Antibióticos y resistencia bacteriana</t>
+          <t>Fecundación y desarrollo embrionario</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4616,19 +4448,31 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D58" t="n">
-        <v>7</v>
+        <v>6</v>
+      </c>
+      <c r="F58" t="n">
+        <v>8</v>
       </c>
       <c r="G58" t="n">
-        <v>8.5</v>
+        <v>6</v>
       </c>
       <c r="H58" t="n">
+        <v>7</v>
+      </c>
+      <c r="I58" t="n">
         <v>4</v>
       </c>
+      <c r="J58" t="n">
+        <v>7</v>
+      </c>
       <c r="L58" t="n">
-        <v>7.5</v>
+        <v>5</v>
+      </c>
+      <c r="O58" t="n">
+        <v>1</v>
       </c>
       <c r="P58" t="n">
         <v>1</v>
@@ -4636,6 +4480,12 @@
       <c r="Q58" t="n">
         <v>1</v>
       </c>
+      <c r="R58" t="n">
+        <v>1</v>
+      </c>
+      <c r="S58" t="n">
+        <v>1</v>
+      </c>
       <c r="U58" t="n">
         <v>1</v>
       </c>
@@ -4643,7 +4493,7 @@
         <v>1</v>
       </c>
       <c r="AF58" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AG58" t="inlineStr">
         <is>
@@ -4659,7 +4509,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Respiración celular</t>
+          <t>Flujo de energía y pirámides ecológicas</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4668,56 +4518,38 @@
         </is>
       </c>
       <c r="C59" t="n">
+        <v>7</v>
+      </c>
+      <c r="D59" t="n">
+        <v>7</v>
+      </c>
+      <c r="E59" t="n">
         <v>6</v>
       </c>
-      <c r="D59" t="n">
+      <c r="G59" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H59" t="n">
+        <v>5</v>
+      </c>
+      <c r="K59" t="n">
         <v>6</v>
-      </c>
-      <c r="E59" t="n">
-        <v>8</v>
-      </c>
-      <c r="F59" t="n">
-        <v>5</v>
-      </c>
-      <c r="G59" t="n">
-        <v>6</v>
-      </c>
-      <c r="H59" t="n">
-        <v>7</v>
-      </c>
-      <c r="I59" t="n">
-        <v>7</v>
-      </c>
-      <c r="J59" t="n">
-        <v>7</v>
-      </c>
-      <c r="K59" t="n">
-        <v>7</v>
       </c>
       <c r="L59" t="n">
         <v>6</v>
       </c>
       <c r="M59" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="N59" t="n">
         <v>1</v>
       </c>
-      <c r="O59" t="n">
-        <v>1</v>
-      </c>
       <c r="P59" t="n">
         <v>1</v>
       </c>
       <c r="Q59" t="n">
         <v>1</v>
       </c>
-      <c r="R59" t="n">
-        <v>1</v>
-      </c>
-      <c r="S59" t="n">
-        <v>1</v>
-      </c>
       <c r="T59" t="n">
         <v>1</v>
       </c>
@@ -4728,7 +4560,7 @@
         <v>1</v>
       </c>
       <c r="AF59" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG59" t="inlineStr">
         <is>
@@ -4744,7 +4576,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Modelo estímulo-respuesta y retroalimentación negativa</t>
+          <t>Fotosíntesis</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4753,25 +4585,34 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>9</v>
+        <v>6</v>
+      </c>
+      <c r="D60" t="n">
+        <v>6</v>
       </c>
       <c r="E60" t="n">
         <v>8</v>
       </c>
       <c r="F60" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G60" t="n">
-        <v>8.5</v>
+        <v>6</v>
       </c>
       <c r="H60" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I60" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J60" t="n">
-        <v>7</v>
+        <v>4.5</v>
+      </c>
+      <c r="K60" t="n">
+        <v>2</v>
+      </c>
+      <c r="L60" t="n">
+        <v>6</v>
       </c>
       <c r="M60" t="n">
         <v>4.5</v>
@@ -4794,11 +4635,17 @@
       <c r="S60" t="n">
         <v>1</v>
       </c>
+      <c r="T60" t="n">
+        <v>1</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1</v>
+      </c>
       <c r="V60" t="n">
         <v>1</v>
       </c>
       <c r="AF60" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AG60" t="inlineStr">
         <is>
@@ -4807,14 +4654,14 @@
       </c>
       <c r="AH60" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>tardio</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Selección natural</t>
+          <t>Genes y alelos</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4823,33 +4670,39 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D61" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F61" t="n">
         <v>8</v>
       </c>
       <c r="G61" t="n">
-        <v>4</v>
-      </c>
-      <c r="K61" t="n">
-        <v>5</v>
-      </c>
-      <c r="L61" t="n">
         <v>6</v>
       </c>
+      <c r="H61" t="n">
+        <v>7</v>
+      </c>
+      <c r="I61" t="n">
+        <v>8</v>
+      </c>
+      <c r="J61" t="n">
+        <v>7</v>
+      </c>
       <c r="O61" t="n">
         <v>1</v>
       </c>
       <c r="P61" t="n">
         <v>1</v>
       </c>
-      <c r="T61" t="n">
-        <v>1</v>
-      </c>
-      <c r="U61" t="n">
+      <c r="Q61" t="n">
+        <v>1</v>
+      </c>
+      <c r="R61" t="n">
+        <v>1</v>
+      </c>
+      <c r="S61" t="n">
         <v>1</v>
       </c>
       <c r="Z61" t="n">
@@ -4860,7 +4713,7 @@
       </c>
       <c r="AG61" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH61" t="inlineStr">
@@ -4872,7 +4725,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Seres vivos y no vivos</t>
+          <t>Genética humana y enfermedades hereditarias</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4881,31 +4734,25 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D62" t="n">
-        <v>2</v>
-      </c>
-      <c r="E62" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F62" t="n">
-        <v>2.5</v>
+        <v>8</v>
       </c>
       <c r="G62" t="n">
-        <v>2</v>
+        <v>8.5</v>
       </c>
       <c r="H62" t="n">
-        <v>2</v>
-      </c>
-      <c r="L62" t="n">
-        <v>3</v>
+        <v>7</v>
+      </c>
+      <c r="J62" t="n">
+        <v>7</v>
       </c>
       <c r="M62" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N62" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O62" t="n">
         <v>1</v>
@@ -4916,14 +4763,17 @@
       <c r="Q62" t="n">
         <v>1</v>
       </c>
-      <c r="U62" t="n">
+      <c r="S62" t="n">
         <v>1</v>
       </c>
       <c r="V62" t="n">
         <v>1</v>
       </c>
+      <c r="Z62" t="n">
+        <v>1</v>
+      </c>
       <c r="AF62" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AG62" t="inlineStr">
         <is>
@@ -4939,7 +4789,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Sistema circulatorio</t>
+          <t>Genotipo y fenotipo</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4948,31 +4798,25 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D63" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F63" t="n">
         <v>8</v>
       </c>
       <c r="G63" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H63" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I63" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J63" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K63" t="n">
-        <v>4</v>
-      </c>
-      <c r="L63" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M63" t="n">
         <v>7</v>
@@ -4992,12 +4836,6 @@
       <c r="S63" t="n">
         <v>1</v>
       </c>
-      <c r="T63" t="n">
-        <v>1</v>
-      </c>
-      <c r="U63" t="n">
-        <v>1</v>
-      </c>
       <c r="V63" t="n">
         <v>1</v>
       </c>
@@ -5005,7 +4843,7 @@
         <v>1</v>
       </c>
       <c r="AF63" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AG63" t="inlineStr">
         <is>
@@ -5021,7 +4859,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Sistema digestivo</t>
+          <t>Grupos de alimentos y dieta balanceada</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5030,10 +4868,10 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D64" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F64" t="n">
         <v>8</v>
@@ -5042,22 +4880,16 @@
         <v>2</v>
       </c>
       <c r="H64" t="n">
-        <v>4</v>
-      </c>
-      <c r="I64" t="n">
-        <v>5</v>
-      </c>
-      <c r="J64" t="n">
-        <v>4.5</v>
+        <v>2</v>
       </c>
       <c r="K64" t="n">
         <v>4</v>
       </c>
       <c r="L64" t="n">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="M64" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="O64" t="n">
         <v>1</v>
@@ -5068,12 +4900,6 @@
       <c r="Q64" t="n">
         <v>1</v>
       </c>
-      <c r="R64" t="n">
-        <v>1</v>
-      </c>
-      <c r="S64" t="n">
-        <v>1</v>
-      </c>
       <c r="T64" t="n">
         <v>1</v>
       </c>
@@ -5087,11 +4913,11 @@
         <v>1</v>
       </c>
       <c r="AF64" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AG64" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH64" t="inlineStr">
@@ -5103,7 +4929,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Sistema endocrino y hormonas</t>
+          <t>Grupos de vertebrados</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5112,28 +4938,28 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>9</v>
-      </c>
-      <c r="E65" t="n">
-        <v>8</v>
+        <v>2</v>
+      </c>
+      <c r="D65" t="n">
+        <v>2</v>
       </c>
       <c r="F65" t="n">
-        <v>8</v>
+        <v>2.5</v>
       </c>
       <c r="G65" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="J65" t="n">
-        <v>7</v>
-      </c>
-      <c r="L65" t="n">
-        <v>7.5</v>
+        <v>2</v>
+      </c>
+      <c r="H65" t="n">
+        <v>2</v>
+      </c>
+      <c r="I65" t="n">
+        <v>4</v>
+      </c>
+      <c r="K65" t="n">
+        <v>5</v>
       </c>
       <c r="M65" t="n">
-        <v>7</v>
-      </c>
-      <c r="N65" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="O65" t="n">
         <v>1</v>
@@ -5141,20 +4967,20 @@
       <c r="P65" t="n">
         <v>1</v>
       </c>
-      <c r="S65" t="n">
-        <v>1</v>
-      </c>
-      <c r="U65" t="n">
+      <c r="Q65" t="n">
+        <v>1</v>
+      </c>
+      <c r="R65" t="n">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
         <v>1</v>
       </c>
       <c r="V65" t="n">
         <v>1</v>
       </c>
-      <c r="Z65" t="n">
-        <v>1</v>
-      </c>
       <c r="AF65" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="AG65" t="inlineStr">
         <is>
@@ -5170,7 +4996,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Sistema locomotor</t>
+          <t>Hábitat y ecosistemas comunes</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5179,13 +5005,16 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D66" t="n">
-        <v>4</v>
+        <v>2</v>
+      </c>
+      <c r="E66" t="n">
+        <v>2</v>
       </c>
       <c r="F66" t="n">
-        <v>8</v>
+        <v>2.5</v>
       </c>
       <c r="G66" t="n">
         <v>2</v>
@@ -5194,13 +5023,22 @@
         <v>2</v>
       </c>
       <c r="I66" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J66" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
+      </c>
+      <c r="K66" t="n">
+        <v>2</v>
+      </c>
+      <c r="L66" t="n">
+        <v>6</v>
       </c>
       <c r="M66" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
+      </c>
+      <c r="N66" t="n">
+        <v>1</v>
       </c>
       <c r="O66" t="n">
         <v>1</v>
@@ -5217,11 +5055,17 @@
       <c r="S66" t="n">
         <v>1</v>
       </c>
+      <c r="T66" t="n">
+        <v>1</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1</v>
+      </c>
       <c r="V66" t="n">
         <v>1</v>
       </c>
       <c r="AF66" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AG66" t="inlineStr">
         <is>
@@ -5237,7 +5081,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Tejidos vegetales</t>
+          <t>Hábitos de vida saludable</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5246,35 +5090,29 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D67" t="n">
-        <v>8</v>
-      </c>
-      <c r="E67" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F67" t="n">
-        <v>8</v>
+        <v>2.5</v>
       </c>
       <c r="G67" t="n">
-        <v>8.5</v>
+        <v>2</v>
       </c>
       <c r="H67" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="J67" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
+      </c>
+      <c r="K67" t="n">
+        <v>4</v>
       </c>
       <c r="L67" t="n">
         <v>7.5</v>
       </c>
-      <c r="M67" t="n">
-        <v>7</v>
-      </c>
-      <c r="N67" t="n">
-        <v>1</v>
-      </c>
       <c r="O67" t="n">
         <v>1</v>
       </c>
@@ -5287,14 +5125,17 @@
       <c r="S67" t="n">
         <v>1</v>
       </c>
+      <c r="T67" t="n">
+        <v>1</v>
+      </c>
       <c r="U67" t="n">
         <v>1</v>
       </c>
-      <c r="V67" t="n">
+      <c r="Z67" t="n">
         <v>1</v>
       </c>
       <c r="AF67" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AG67" t="inlineStr">
         <is>
@@ -5310,7 +5151,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Transporte en plantas: xilema y floema</t>
+          <t>Herencia mendeliana</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5319,29 +5160,32 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D68" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="F68" t="n">
+        <v>8</v>
       </c>
       <c r="G68" t="n">
-        <v>2</v>
+        <v>8.5</v>
       </c>
       <c r="H68" t="n">
         <v>7</v>
       </c>
       <c r="I68" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J68" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L68" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M68" t="n">
         <v>7</v>
       </c>
+      <c r="O68" t="n">
+        <v>1</v>
+      </c>
       <c r="P68" t="n">
         <v>1</v>
       </c>
@@ -5354,14 +5198,11 @@
       <c r="S68" t="n">
         <v>1</v>
       </c>
-      <c r="U68" t="n">
-        <v>1</v>
-      </c>
       <c r="V68" t="n">
         <v>1</v>
       </c>
       <c r="AF68" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AG68" t="inlineStr">
         <is>
@@ -5377,7 +5218,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Variación genética en la descendencia</t>
+          <t>Herencia ligada al sexo, alelos múltiples y poligénica</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5386,34 +5227,22 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D69" t="n">
-        <v>6</v>
-      </c>
-      <c r="F69" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G69" t="n">
-        <v>4</v>
+        <v>8.5</v>
       </c>
       <c r="H69" t="n">
         <v>7</v>
       </c>
-      <c r="I69" t="n">
-        <v>8</v>
-      </c>
-      <c r="K69" t="n">
-        <v>5</v>
-      </c>
-      <c r="L69" t="n">
-        <v>7.5</v>
+      <c r="J69" t="n">
+        <v>7</v>
       </c>
       <c r="M69" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O69" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="P69" t="n">
         <v>1</v>
@@ -5421,20 +5250,17 @@
       <c r="Q69" t="n">
         <v>1</v>
       </c>
-      <c r="R69" t="n">
-        <v>1</v>
-      </c>
-      <c r="T69" t="n">
-        <v>1</v>
-      </c>
-      <c r="U69" t="n">
+      <c r="S69" t="n">
         <v>1</v>
       </c>
       <c r="V69" t="n">
         <v>1</v>
       </c>
+      <c r="Z69" t="n">
+        <v>1</v>
+      </c>
       <c r="AF69" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AG69" t="inlineStr">
         <is>
@@ -5443,47 +5269,44 @@
       </c>
       <c r="AH69" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>posterior</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Adaptaciones conductuales</t>
+          <t>Homeostasis</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D70" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E70" t="n">
+        <v>8</v>
+      </c>
+      <c r="F70" t="n">
+        <v>8</v>
+      </c>
+      <c r="G70" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H70" t="n">
+        <v>7</v>
+      </c>
+      <c r="J70" t="n">
+        <v>7</v>
+      </c>
+      <c r="K70" t="n">
         <v>4</v>
-      </c>
-      <c r="F70" t="n">
-        <v>5</v>
-      </c>
-      <c r="G70" t="n">
-        <v>4</v>
-      </c>
-      <c r="H70" t="n">
-        <v>3</v>
-      </c>
-      <c r="I70" t="n">
-        <v>3</v>
-      </c>
-      <c r="J70" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="L70" t="n">
-        <v>6</v>
       </c>
       <c r="M70" t="n">
         <v>4.5</v>
@@ -5500,20 +5323,20 @@
       <c r="Q70" t="n">
         <v>1</v>
       </c>
-      <c r="R70" t="n">
-        <v>1</v>
-      </c>
       <c r="S70" t="n">
         <v>1</v>
       </c>
-      <c r="U70" t="n">
+      <c r="T70" t="n">
         <v>1</v>
       </c>
       <c r="V70" t="n">
         <v>1</v>
       </c>
+      <c r="Z70" t="n">
+        <v>1</v>
+      </c>
       <c r="AF70" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AG70" t="inlineStr">
         <is>
@@ -5522,35 +5345,53 @@
       </c>
       <c r="AH70" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>ATP y energía en los sistemas vivos</t>
+          <t>Impacto humano en los ecosistemas</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D71" t="n">
-        <v>6</v>
+        <v>2</v>
+      </c>
+      <c r="F71" t="n">
+        <v>2.5</v>
       </c>
       <c r="G71" t="n">
         <v>6</v>
       </c>
       <c r="H71" t="n">
-        <v>7</v>
+        <v>2</v>
+      </c>
+      <c r="I71" t="n">
+        <v>5</v>
       </c>
       <c r="J71" t="n">
-        <v>7</v>
+        <v>2.5</v>
+      </c>
+      <c r="K71" t="n">
+        <v>2</v>
+      </c>
+      <c r="L71" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="M71" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O71" t="n">
+        <v>1</v>
       </c>
       <c r="P71" t="n">
         <v>1</v>
@@ -5558,15 +5399,27 @@
       <c r="Q71" t="n">
         <v>1</v>
       </c>
+      <c r="R71" t="n">
+        <v>1</v>
+      </c>
       <c r="S71" t="n">
         <v>1</v>
       </c>
+      <c r="T71" t="n">
+        <v>1</v>
+      </c>
+      <c r="U71" t="n">
+        <v>1</v>
+      </c>
+      <c r="V71" t="n">
+        <v>1</v>
+      </c>
       <c r="AF71" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AG71" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH71" t="inlineStr">
@@ -5578,46 +5431,46 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Atributos de las poblaciones</t>
+          <t>Intercambio de gases en plantas</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D72" t="n">
-        <v>7</v>
-      </c>
-      <c r="F72" t="n">
         <v>8</v>
       </c>
       <c r="G72" t="n">
-        <v>8.5</v>
+        <v>6</v>
+      </c>
+      <c r="I72" t="n">
+        <v>7</v>
+      </c>
+      <c r="J72" t="n">
+        <v>4.5</v>
       </c>
       <c r="L72" t="n">
-        <v>6</v>
-      </c>
-      <c r="M72" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O72" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="P72" t="n">
         <v>1</v>
       </c>
+      <c r="R72" t="n">
+        <v>1</v>
+      </c>
+      <c r="S72" t="n">
+        <v>1</v>
+      </c>
       <c r="U72" t="n">
         <v>1</v>
       </c>
-      <c r="V72" t="n">
-        <v>1</v>
-      </c>
       <c r="AF72" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG72" t="inlineStr">
         <is>
@@ -5633,28 +5486,31 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Biotecnología vegetal y agroindustria</t>
+          <t>Invertebrados e insectos</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D73" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F73" t="n">
-        <v>8</v>
+        <v>2.5</v>
       </c>
       <c r="G73" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="M73" t="n">
-        <v>7</v>
+        <v>3</v>
+      </c>
+      <c r="H73" t="n">
+        <v>2</v>
+      </c>
+      <c r="I73" t="n">
+        <v>2</v>
       </c>
       <c r="O73" t="n">
         <v>1</v>
@@ -5662,61 +5518,88 @@
       <c r="P73" t="n">
         <v>1</v>
       </c>
-      <c r="V73" t="n">
+      <c r="Q73" t="n">
+        <v>1</v>
+      </c>
+      <c r="R73" t="n">
         <v>1</v>
       </c>
       <c r="AF73" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AG73" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Cambio climático y seres vivos</t>
+          <t>La célula como unidad de la vida</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D74" t="n">
+        <v>3</v>
+      </c>
+      <c r="E74" t="n">
         <v>7</v>
       </c>
       <c r="F74" t="n">
         <v>8</v>
       </c>
+      <c r="G74" t="n">
+        <v>6</v>
+      </c>
       <c r="H74" t="n">
-        <v>7</v>
+        <v>5</v>
+      </c>
+      <c r="I74" t="n">
+        <v>7</v>
+      </c>
+      <c r="J74" t="n">
+        <v>4.5</v>
       </c>
       <c r="K74" t="n">
+        <v>7</v>
+      </c>
+      <c r="L74" t="n">
         <v>5</v>
-      </c>
-      <c r="L74" t="n">
-        <v>6</v>
       </c>
       <c r="M74" t="n">
         <v>4.5</v>
       </c>
+      <c r="N74" t="n">
+        <v>1</v>
+      </c>
       <c r="O74" t="n">
         <v>1</v>
       </c>
+      <c r="P74" t="n">
+        <v>1</v>
+      </c>
       <c r="Q74" t="n">
         <v>1</v>
       </c>
+      <c r="R74" t="n">
+        <v>1</v>
+      </c>
+      <c r="S74" t="n">
+        <v>1</v>
+      </c>
       <c r="T74" t="n">
         <v>1</v>
       </c>
@@ -5727,35 +5610,35 @@
         <v>1</v>
       </c>
       <c r="AF74" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AG74" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Papel de los seres vivos en el ciclo del agua</t>
+          <t>Mitosis y ciclo celular</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D75" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G75" t="n">
         <v>8.5</v>
@@ -5764,16 +5647,16 @@
         <v>7</v>
       </c>
       <c r="I75" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J75" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="K75" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L75" t="n">
-        <v>5</v>
+        <v>7.5</v>
       </c>
       <c r="M75" t="n">
         <v>7</v>
@@ -5800,7 +5683,7 @@
         <v>1</v>
       </c>
       <c r="AF75" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AG75" t="inlineStr">
         <is>
@@ -5816,40 +5699,43 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Ciclos del carbono y del oxígeno</t>
+          <t>Necesidades de los seres vivos</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C76" t="n">
+        <v>2</v>
+      </c>
+      <c r="D76" t="n">
+        <v>2</v>
+      </c>
+      <c r="E76" t="n">
+        <v>2</v>
+      </c>
+      <c r="F76" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G76" t="n">
+        <v>2</v>
+      </c>
+      <c r="H76" t="n">
+        <v>2</v>
+      </c>
+      <c r="I76" t="n">
+        <v>4</v>
+      </c>
+      <c r="J76" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K76" t="n">
+        <v>2</v>
+      </c>
+      <c r="L76" t="n">
         <v>3</v>
-      </c>
-      <c r="D76" t="n">
-        <v>3</v>
-      </c>
-      <c r="E76" t="n">
-        <v>8</v>
-      </c>
-      <c r="F76" t="n">
-        <v>5</v>
-      </c>
-      <c r="G76" t="n">
-        <v>6</v>
-      </c>
-      <c r="H76" t="n">
-        <v>5</v>
-      </c>
-      <c r="J76" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K76" t="n">
-        <v>4</v>
-      </c>
-      <c r="L76" t="n">
-        <v>7.5</v>
       </c>
       <c r="M76" t="n">
         <v>2.5</v>
@@ -5866,6 +5752,9 @@
       <c r="Q76" t="n">
         <v>1</v>
       </c>
+      <c r="R76" t="n">
+        <v>1</v>
+      </c>
       <c r="S76" t="n">
         <v>1</v>
       </c>
@@ -5879,11 +5768,11 @@
         <v>1</v>
       </c>
       <c r="AF76" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AG76" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH76" t="inlineStr">
@@ -5895,62 +5784,131 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Ciclos del fósforo y del azufre</t>
+          <t>Niveles de organización de los seres vivos</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D77" t="n">
-        <v>8</v>
+        <v>4</v>
+      </c>
+      <c r="E77" t="n">
+        <v>7</v>
+      </c>
+      <c r="F77" t="n">
+        <v>5</v>
+      </c>
+      <c r="G77" t="n">
+        <v>6</v>
+      </c>
+      <c r="H77" t="n">
+        <v>7</v>
+      </c>
+      <c r="I77" t="n">
+        <v>5</v>
+      </c>
+      <c r="J77" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K77" t="n">
+        <v>7</v>
+      </c>
+      <c r="L77" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="M77" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="N77" t="n">
+        <v>1</v>
+      </c>
+      <c r="O77" t="n">
+        <v>1</v>
+      </c>
+      <c r="P77" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>1</v>
+      </c>
+      <c r="R77" t="n">
+        <v>1</v>
+      </c>
+      <c r="S77" t="n">
+        <v>1</v>
+      </c>
+      <c r="T77" t="n">
+        <v>1</v>
+      </c>
+      <c r="U77" t="n">
+        <v>1</v>
+      </c>
+      <c r="V77" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z77" t="n">
+        <v>1</v>
       </c>
       <c r="AF77" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="AG77" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Circulación e intercambio capilar</t>
+          <t>Nutrición autótrofa y heterótrofa</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D78" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F78" t="n">
-        <v>8</v>
+        <v>2.5</v>
       </c>
       <c r="G78" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H78" t="n">
-        <v>7</v>
+        <v>2</v>
+      </c>
+      <c r="I78" t="n">
+        <v>5</v>
+      </c>
+      <c r="J78" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K78" t="n">
+        <v>2</v>
       </c>
       <c r="L78" t="n">
-        <v>7.5</v>
+        <v>5</v>
+      </c>
+      <c r="M78" t="n">
+        <v>7</v>
       </c>
       <c r="O78" t="n">
         <v>1</v>
@@ -5961,57 +5919,69 @@
       <c r="Q78" t="n">
         <v>1</v>
       </c>
+      <c r="R78" t="n">
+        <v>1</v>
+      </c>
+      <c r="S78" t="n">
+        <v>1</v>
+      </c>
+      <c r="T78" t="n">
+        <v>1</v>
+      </c>
       <c r="U78" t="n">
         <v>1</v>
       </c>
+      <c r="V78" t="n">
+        <v>1</v>
+      </c>
       <c r="AF78" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="AG78" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Clasificación jerárquica y nomenclatura</t>
+          <t>Órganos de los sentidos</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D79" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F79" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G79" t="n">
-        <v>8.5</v>
+        <v>2</v>
       </c>
       <c r="H79" t="n">
+        <v>2</v>
+      </c>
+      <c r="I79" t="n">
         <v>7</v>
       </c>
       <c r="J79" t="n">
         <v>7</v>
       </c>
-      <c r="K79" t="n">
-        <v>5</v>
-      </c>
       <c r="M79" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="O79" t="n">
         <v>1</v>
@@ -6022,21 +5992,21 @@
       <c r="Q79" t="n">
         <v>1</v>
       </c>
+      <c r="R79" t="n">
+        <v>1</v>
+      </c>
       <c r="S79" t="n">
         <v>1</v>
       </c>
-      <c r="T79" t="n">
-        <v>1</v>
-      </c>
       <c r="V79" t="n">
         <v>1</v>
       </c>
       <c r="AF79" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AG79" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH79" t="inlineStr">
@@ -6048,12 +6018,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Contaminación y sus efectos en los seres vivos</t>
+          <t>Partes de la planta y sus funciones</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C80" t="n">
@@ -6062,30 +6032,48 @@
       <c r="D80" t="n">
         <v>2</v>
       </c>
+      <c r="E80" t="n">
+        <v>2</v>
+      </c>
       <c r="F80" t="n">
-        <v>5</v>
+        <v>2.5</v>
+      </c>
+      <c r="G80" t="n">
+        <v>2</v>
       </c>
       <c r="H80" t="n">
+        <v>2</v>
+      </c>
+      <c r="I80" t="n">
         <v>2</v>
       </c>
       <c r="J80" t="n">
         <v>2.5</v>
       </c>
       <c r="K80" t="n">
+        <v>2</v>
+      </c>
+      <c r="L80" t="n">
         <v>4</v>
-      </c>
-      <c r="L80" t="n">
-        <v>6</v>
       </c>
       <c r="M80" t="n">
         <v>2.5</v>
       </c>
+      <c r="N80" t="n">
+        <v>1</v>
+      </c>
       <c r="O80" t="n">
         <v>1</v>
       </c>
+      <c r="P80" t="n">
+        <v>1</v>
+      </c>
       <c r="Q80" t="n">
         <v>1</v>
       </c>
+      <c r="R80" t="n">
+        <v>1</v>
+      </c>
       <c r="S80" t="n">
         <v>1</v>
       </c>
@@ -6098,15 +6086,12 @@
       <c r="V80" t="n">
         <v>1</v>
       </c>
-      <c r="Z80" t="n">
-        <v>1</v>
-      </c>
       <c r="AF80" t="n">
         <v>2</v>
       </c>
       <c r="AG80" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH80" t="inlineStr">
@@ -6118,59 +6103,80 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Diferenciación y especialización celular</t>
+          <t>Productores, consumidores y descomponedores</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C81" t="n">
+        <v>3</v>
+      </c>
+      <c r="D81" t="n">
+        <v>3</v>
+      </c>
+      <c r="E81" t="n">
+        <v>3</v>
+      </c>
+      <c r="F81" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G81" t="n">
+        <v>2</v>
+      </c>
+      <c r="H81" t="n">
+        <v>3</v>
+      </c>
+      <c r="I81" t="n">
+        <v>8</v>
+      </c>
+      <c r="J81" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K81" t="n">
+        <v>2</v>
+      </c>
+      <c r="L81" t="n">
         <v>6</v>
       </c>
-      <c r="D81" t="n">
-        <v>6</v>
-      </c>
-      <c r="E81" t="n">
-        <v>7</v>
-      </c>
-      <c r="G81" t="n">
-        <v>6</v>
-      </c>
-      <c r="H81" t="n">
-        <v>7</v>
-      </c>
-      <c r="K81" t="n">
-        <v>7</v>
-      </c>
-      <c r="L81" t="n">
-        <v>7.5</v>
+      <c r="M81" t="n">
+        <v>7</v>
       </c>
       <c r="N81" t="n">
         <v>1</v>
       </c>
+      <c r="O81" t="n">
+        <v>1</v>
+      </c>
       <c r="P81" t="n">
         <v>1</v>
       </c>
       <c r="Q81" t="n">
         <v>1</v>
       </c>
+      <c r="R81" t="n">
+        <v>1</v>
+      </c>
+      <c r="S81" t="n">
+        <v>1</v>
+      </c>
       <c r="T81" t="n">
         <v>1</v>
       </c>
       <c r="U81" t="n">
         <v>1</v>
       </c>
-      <c r="Z81" t="n">
+      <c r="V81" t="n">
         <v>1</v>
       </c>
       <c r="AF81" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AG81" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH81" t="inlineStr">
@@ -6182,44 +6188,74 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Diversidad genética de poblaciones</t>
+          <t>Reproducción sexual de las plantas con flor</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D82" t="n">
-        <v>7</v>
+        <v>6</v>
+      </c>
+      <c r="E82" t="n">
+        <v>8</v>
+      </c>
+      <c r="F82" t="n">
+        <v>8</v>
       </c>
       <c r="G82" t="n">
+        <v>2</v>
+      </c>
+      <c r="H82" t="n">
+        <v>2</v>
+      </c>
+      <c r="I82" t="n">
+        <v>4</v>
+      </c>
+      <c r="K82" t="n">
+        <v>2</v>
+      </c>
+      <c r="L82" t="n">
+        <v>5</v>
+      </c>
+      <c r="M82" t="n">
+        <v>7</v>
+      </c>
+      <c r="N82" t="n">
+        <v>1</v>
+      </c>
+      <c r="O82" t="n">
+        <v>1</v>
+      </c>
+      <c r="P82" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>1</v>
+      </c>
+      <c r="R82" t="n">
+        <v>1</v>
+      </c>
+      <c r="T82" t="n">
+        <v>1</v>
+      </c>
+      <c r="U82" t="n">
+        <v>1</v>
+      </c>
+      <c r="V82" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF82" t="n">
         <v>6</v>
       </c>
-      <c r="J82" t="n">
-        <v>7</v>
-      </c>
-      <c r="K82" t="n">
-        <v>5</v>
-      </c>
-      <c r="P82" t="n">
-        <v>1</v>
-      </c>
-      <c r="S82" t="n">
-        <v>1</v>
-      </c>
-      <c r="T82" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF82" t="n">
-        <v>7</v>
-      </c>
       <c r="AG82" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH82" t="inlineStr">
@@ -6231,12 +6267,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Energía de los alimentos y balance energético</t>
+          <t>Reproducción humana y pubertad</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -6245,20 +6281,29 @@
       <c r="D83" t="n">
         <v>4</v>
       </c>
+      <c r="E83" t="n">
+        <v>8</v>
+      </c>
       <c r="F83" t="n">
         <v>8</v>
       </c>
       <c r="G83" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H83" t="n">
-        <v>2</v>
-      </c>
-      <c r="K83" t="n">
         <v>4</v>
       </c>
+      <c r="I83" t="n">
+        <v>4</v>
+      </c>
       <c r="L83" t="n">
-        <v>6</v>
+        <v>5</v>
+      </c>
+      <c r="M83" t="n">
+        <v>7</v>
+      </c>
+      <c r="N83" t="n">
+        <v>1</v>
       </c>
       <c r="O83" t="n">
         <v>1</v>
@@ -6269,10 +6314,13 @@
       <c r="Q83" t="n">
         <v>1</v>
       </c>
-      <c r="T83" t="n">
+      <c r="R83" t="n">
         <v>1</v>
       </c>
       <c r="U83" t="n">
+        <v>1</v>
+      </c>
+      <c r="V83" t="n">
         <v>1</v>
       </c>
       <c r="Z83" t="n">
@@ -6295,12 +6343,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Enzimas</t>
+          <t>Reproducción sexual y asexual</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -6309,22 +6357,40 @@
       <c r="D84" t="n">
         <v>6</v>
       </c>
+      <c r="E84" t="n">
+        <v>8</v>
+      </c>
+      <c r="F84" t="n">
+        <v>8</v>
+      </c>
       <c r="G84" t="n">
-        <v>6</v>
-      </c>
-      <c r="J84" t="n">
-        <v>7</v>
+        <v>3</v>
+      </c>
+      <c r="H84" t="n">
+        <v>3</v>
+      </c>
+      <c r="I84" t="n">
+        <v>4</v>
       </c>
       <c r="L84" t="n">
-        <v>7.5</v>
+        <v>5</v>
       </c>
       <c r="M84" t="n">
-        <v>7</v>
+        <v>2.5</v>
+      </c>
+      <c r="N84" t="n">
+        <v>1</v>
+      </c>
+      <c r="O84" t="n">
+        <v>1</v>
       </c>
       <c r="P84" t="n">
         <v>1</v>
       </c>
-      <c r="S84" t="n">
+      <c r="Q84" t="n">
+        <v>1</v>
+      </c>
+      <c r="R84" t="n">
         <v>1</v>
       </c>
       <c r="U84" t="n">
@@ -6341,7 +6407,7 @@
       </c>
       <c r="AG84" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH84" t="inlineStr">
@@ -6353,28 +6419,37 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Propagación de enfermedades y control de brotes</t>
+          <t>Requerimientos de materia y energía de la célula</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>11</v>
+        <v>6</v>
+      </c>
+      <c r="D85" t="n">
+        <v>6</v>
       </c>
       <c r="G85" t="n">
-        <v>8.5</v>
+        <v>6</v>
       </c>
       <c r="H85" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J85" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
+      </c>
+      <c r="K85" t="n">
+        <v>7</v>
       </c>
       <c r="L85" t="n">
-        <v>7.5</v>
+        <v>5</v>
+      </c>
+      <c r="M85" t="n">
+        <v>7</v>
       </c>
       <c r="P85" t="n">
         <v>1</v>
@@ -6385,32 +6460,41 @@
       <c r="S85" t="n">
         <v>1</v>
       </c>
+      <c r="T85" t="n">
+        <v>1</v>
+      </c>
       <c r="U85" t="n">
         <v>1</v>
       </c>
+      <c r="V85" t="n">
+        <v>1</v>
+      </c>
       <c r="Z85" t="n">
         <v>1</v>
       </c>
+      <c r="AF85" t="n">
+        <v>6</v>
+      </c>
       <c r="AG85" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
-          <t>no_aplica</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Especies clave</t>
+          <t>Antibióticos y resistencia bacteriana</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -6419,54 +6503,84 @@
       <c r="D86" t="n">
         <v>7</v>
       </c>
-      <c r="K86" t="n">
-        <v>3</v>
-      </c>
-      <c r="T86" t="n">
-        <v>1</v>
+      <c r="G86" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H86" t="n">
+        <v>4</v>
+      </c>
+      <c r="L86" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="P86" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>1</v>
+      </c>
+      <c r="U86" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z86" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF86" t="n">
+        <v>7</v>
       </c>
       <c r="AG86" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
-          <t>no_aplica</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Estrategias reproductivas y supervivencia de la descendencia</t>
+          <t>Respiración celular</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D87" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E87" t="n">
         <v>8</v>
       </c>
       <c r="F87" t="n">
-        <v>8</v>
+        <v>5</v>
+      </c>
+      <c r="G87" t="n">
+        <v>6</v>
       </c>
       <c r="H87" t="n">
-        <v>3</v>
+        <v>7</v>
+      </c>
+      <c r="I87" t="n">
+        <v>7</v>
+      </c>
+      <c r="J87" t="n">
+        <v>7</v>
+      </c>
+      <c r="K87" t="n">
+        <v>7</v>
       </c>
       <c r="L87" t="n">
         <v>6</v>
       </c>
       <c r="M87" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="N87" t="n">
         <v>1</v>
@@ -6474,9 +6588,21 @@
       <c r="O87" t="n">
         <v>1</v>
       </c>
+      <c r="P87" t="n">
+        <v>1</v>
+      </c>
       <c r="Q87" t="n">
         <v>1</v>
       </c>
+      <c r="R87" t="n">
+        <v>1</v>
+      </c>
+      <c r="S87" t="n">
+        <v>1</v>
+      </c>
+      <c r="T87" t="n">
+        <v>1</v>
+      </c>
       <c r="U87" t="n">
         <v>1</v>
       </c>
@@ -6484,38 +6610,38 @@
         <v>1</v>
       </c>
       <c r="AF87" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AG87" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Factores limitantes de las poblaciones</t>
+          <t>Respuesta de los seres vivos a estímulos</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D88" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E88" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F88" t="n">
         <v>8</v>
@@ -6523,14 +6649,23 @@
       <c r="G88" t="n">
         <v>8.5</v>
       </c>
+      <c r="H88" t="n">
+        <v>2</v>
+      </c>
+      <c r="I88" t="n">
+        <v>3</v>
+      </c>
+      <c r="J88" t="n">
+        <v>7</v>
+      </c>
       <c r="K88" t="n">
+        <v>2</v>
+      </c>
+      <c r="L88" t="n">
         <v>3</v>
       </c>
-      <c r="L88" t="n">
-        <v>6</v>
-      </c>
       <c r="M88" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="N88" t="n">
         <v>1</v>
@@ -6541,6 +6676,15 @@
       <c r="P88" t="n">
         <v>1</v>
       </c>
+      <c r="Q88" t="n">
+        <v>1</v>
+      </c>
+      <c r="R88" t="n">
+        <v>1</v>
+      </c>
+      <c r="S88" t="n">
+        <v>1</v>
+      </c>
       <c r="T88" t="n">
         <v>1</v>
       </c>
@@ -6551,11 +6695,11 @@
         <v>1</v>
       </c>
       <c r="AF88" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AG88" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH88" t="inlineStr">
@@ -6567,113 +6711,119 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Fases de la fotosíntesis y ciclo de Calvin</t>
+          <t>Modelo estímulo-respuesta y retroalimentación negativa</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>6</v>
-      </c>
-      <c r="D89" t="n">
-        <v>6</v>
+        <v>9</v>
+      </c>
+      <c r="E89" t="n">
+        <v>8</v>
       </c>
       <c r="F89" t="n">
         <v>8</v>
       </c>
+      <c r="G89" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H89" t="n">
+        <v>7</v>
+      </c>
+      <c r="I89" t="n">
+        <v>7</v>
+      </c>
+      <c r="J89" t="n">
+        <v>7</v>
+      </c>
+      <c r="M89" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="N89" t="n">
+        <v>1</v>
+      </c>
       <c r="O89" t="n">
         <v>1</v>
       </c>
+      <c r="P89" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>1</v>
+      </c>
+      <c r="R89" t="n">
+        <v>1</v>
+      </c>
+      <c r="S89" t="n">
+        <v>1</v>
+      </c>
+      <c r="V89" t="n">
+        <v>1</v>
+      </c>
       <c r="AF89" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG89" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Fotosíntesis</t>
+          <t>Selección natural</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D90" t="n">
-        <v>6</v>
-      </c>
-      <c r="E90" t="n">
+        <v>7</v>
+      </c>
+      <c r="F90" t="n">
         <v>8</v>
       </c>
-      <c r="F90" t="n">
+      <c r="G90" t="n">
+        <v>4</v>
+      </c>
+      <c r="K90" t="n">
         <v>5</v>
-      </c>
-      <c r="G90" t="n">
-        <v>6</v>
-      </c>
-      <c r="H90" t="n">
-        <v>2</v>
-      </c>
-      <c r="I90" t="n">
-        <v>4</v>
-      </c>
-      <c r="J90" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K90" t="n">
-        <v>2</v>
       </c>
       <c r="L90" t="n">
         <v>6</v>
       </c>
-      <c r="M90" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="N90" t="n">
-        <v>1</v>
-      </c>
       <c r="O90" t="n">
         <v>1</v>
       </c>
       <c r="P90" t="n">
         <v>1</v>
       </c>
-      <c r="Q90" t="n">
-        <v>1</v>
-      </c>
-      <c r="R90" t="n">
-        <v>1</v>
-      </c>
-      <c r="S90" t="n">
-        <v>1</v>
-      </c>
       <c r="T90" t="n">
         <v>1</v>
       </c>
       <c r="U90" t="n">
         <v>1</v>
       </c>
-      <c r="V90" t="n">
+      <c r="Z90" t="n">
         <v>1</v>
       </c>
       <c r="AF90" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG90" t="inlineStr">
         <is>
@@ -6682,41 +6832,47 @@
       </c>
       <c r="AH90" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Genes y alelos</t>
+          <t>Seres vivos y no vivos</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D91" t="n">
-        <v>6</v>
+        <v>2</v>
+      </c>
+      <c r="E91" t="n">
+        <v>2</v>
       </c>
       <c r="F91" t="n">
-        <v>8</v>
+        <v>2.5</v>
       </c>
       <c r="G91" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H91" t="n">
-        <v>7</v>
-      </c>
-      <c r="I91" t="n">
-        <v>8</v>
-      </c>
-      <c r="J91" t="n">
-        <v>7</v>
+        <v>2</v>
+      </c>
+      <c r="L91" t="n">
+        <v>3</v>
+      </c>
+      <c r="M91" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N91" t="n">
+        <v>1</v>
       </c>
       <c r="O91" t="n">
         <v>1</v>
@@ -6727,21 +6883,18 @@
       <c r="Q91" t="n">
         <v>1</v>
       </c>
-      <c r="R91" t="n">
-        <v>1</v>
-      </c>
-      <c r="S91" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z91" t="n">
+      <c r="U91" t="n">
+        <v>1</v>
+      </c>
+      <c r="V91" t="n">
         <v>1</v>
       </c>
       <c r="AF91" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AG91" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH91" t="inlineStr">
@@ -6753,37 +6906,43 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Grupos de alimentos y dieta balanceada</t>
+          <t>Sistema circulatorio</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D92" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F92" t="n">
         <v>8</v>
       </c>
       <c r="G92" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H92" t="n">
         <v>2</v>
+      </c>
+      <c r="I92" t="n">
+        <v>5</v>
+      </c>
+      <c r="J92" t="n">
+        <v>4.5</v>
       </c>
       <c r="K92" t="n">
         <v>4</v>
       </c>
       <c r="L92" t="n">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="M92" t="n">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="O92" t="n">
         <v>1</v>
@@ -6794,6 +6953,12 @@
       <c r="Q92" t="n">
         <v>1</v>
       </c>
+      <c r="R92" t="n">
+        <v>1</v>
+      </c>
+      <c r="S92" t="n">
+        <v>1</v>
+      </c>
       <c r="T92" t="n">
         <v>1</v>
       </c>
@@ -6807,11 +6972,11 @@
         <v>1</v>
       </c>
       <c r="AF92" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AG92" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH92" t="inlineStr">
@@ -6823,41 +6988,65 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Herencia ligada al sexo, alelos múltiples y poligénica</t>
+          <t>Sistema digestivo</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D93" t="n">
-        <v>7</v>
+        <v>4</v>
+      </c>
+      <c r="F93" t="n">
+        <v>8</v>
       </c>
       <c r="G93" t="n">
-        <v>8.5</v>
+        <v>2</v>
       </c>
       <c r="H93" t="n">
-        <v>7</v>
+        <v>4</v>
+      </c>
+      <c r="I93" t="n">
+        <v>5</v>
       </c>
       <c r="J93" t="n">
-        <v>7</v>
+        <v>4.5</v>
+      </c>
+      <c r="K93" t="n">
+        <v>4</v>
+      </c>
+      <c r="L93" t="n">
+        <v>4</v>
       </c>
       <c r="M93" t="n">
         <v>7</v>
       </c>
+      <c r="O93" t="n">
+        <v>1</v>
+      </c>
       <c r="P93" t="n">
         <v>1</v>
       </c>
       <c r="Q93" t="n">
         <v>1</v>
       </c>
+      <c r="R93" t="n">
+        <v>1</v>
+      </c>
       <c r="S93" t="n">
         <v>1</v>
       </c>
+      <c r="T93" t="n">
+        <v>1</v>
+      </c>
+      <c r="U93" t="n">
+        <v>1</v>
+      </c>
       <c r="V93" t="n">
         <v>1</v>
       </c>
@@ -6865,7 +7054,7 @@
         <v>1</v>
       </c>
       <c r="AF93" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="AG93" t="inlineStr">
         <is>
@@ -6874,50 +7063,44 @@
       </c>
       <c r="AH93" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Impacto humano en los ecosistemas</t>
+          <t>Sistema endocrino y hormonas</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>2</v>
-      </c>
-      <c r="D94" t="n">
-        <v>2</v>
+        <v>9</v>
+      </c>
+      <c r="E94" t="n">
+        <v>8</v>
       </c>
       <c r="F94" t="n">
-        <v>2.5</v>
+        <v>8</v>
       </c>
       <c r="G94" t="n">
-        <v>6</v>
-      </c>
-      <c r="H94" t="n">
-        <v>2</v>
-      </c>
-      <c r="I94" t="n">
-        <v>5</v>
+        <v>8.5</v>
       </c>
       <c r="J94" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K94" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="L94" t="n">
-        <v>4.5</v>
+        <v>7.5</v>
       </c>
       <c r="M94" t="n">
-        <v>2.5</v>
+        <v>7</v>
+      </c>
+      <c r="N94" t="n">
+        <v>1</v>
       </c>
       <c r="O94" t="n">
         <v>1</v>
@@ -6925,30 +7108,24 @@
       <c r="P94" t="n">
         <v>1</v>
       </c>
-      <c r="Q94" t="n">
-        <v>1</v>
-      </c>
-      <c r="R94" t="n">
-        <v>1</v>
-      </c>
       <c r="S94" t="n">
         <v>1</v>
       </c>
-      <c r="T94" t="n">
-        <v>1</v>
-      </c>
       <c r="U94" t="n">
         <v>1</v>
       </c>
       <c r="V94" t="n">
         <v>1</v>
       </c>
+      <c r="Z94" t="n">
+        <v>1</v>
+      </c>
       <c r="AF94" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="AG94" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH94" t="inlineStr">
@@ -6960,50 +7137,62 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Intercambio de gases en plantas</t>
+          <t>Sistema locomotor</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C95" t="n">
+        <v>4</v>
+      </c>
+      <c r="D95" t="n">
+        <v>4</v>
+      </c>
+      <c r="F95" t="n">
         <v>8</v>
       </c>
-      <c r="D95" t="n">
-        <v>8</v>
-      </c>
       <c r="G95" t="n">
-        <v>6</v>
+        <v>2</v>
+      </c>
+      <c r="H95" t="n">
+        <v>2</v>
       </c>
       <c r="I95" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J95" t="n">
         <v>4.5</v>
       </c>
-      <c r="L95" t="n">
-        <v>5</v>
+      <c r="M95" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O95" t="n">
+        <v>1</v>
       </c>
       <c r="P95" t="n">
         <v>1</v>
       </c>
+      <c r="Q95" t="n">
+        <v>1</v>
+      </c>
       <c r="R95" t="n">
         <v>1</v>
       </c>
       <c r="S95" t="n">
         <v>1</v>
       </c>
-      <c r="U95" t="n">
+      <c r="V95" t="n">
         <v>1</v>
       </c>
       <c r="AF95" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AG95" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH95" t="inlineStr">
@@ -7015,12 +7204,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>La célula como unidad de la vida</t>
+          <t>Sistema respiratorio</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C96" t="n">
@@ -7029,9 +7218,6 @@
       <c r="D96" t="n">
         <v>3</v>
       </c>
-      <c r="E96" t="n">
-        <v>7</v>
-      </c>
       <c r="F96" t="n">
         <v>8</v>
       </c>
@@ -7039,25 +7225,22 @@
         <v>6</v>
       </c>
       <c r="H96" t="n">
+        <v>2</v>
+      </c>
+      <c r="I96" t="n">
         <v>5</v>
-      </c>
-      <c r="I96" t="n">
-        <v>7</v>
       </c>
       <c r="J96" t="n">
         <v>4.5</v>
       </c>
       <c r="K96" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L96" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M96" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="N96" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O96" t="n">
         <v>1</v>
@@ -7083,8 +7266,11 @@
       <c r="V96" t="n">
         <v>1</v>
       </c>
+      <c r="Z96" t="n">
+        <v>1</v>
+      </c>
       <c r="AF96" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AG96" t="inlineStr">
         <is>
@@ -7100,19 +7286,22 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Meiosis</t>
+          <t>Tejidos animales</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D97" t="n">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="E97" t="n">
+        <v>7</v>
       </c>
       <c r="F97" t="n">
         <v>8</v>
@@ -7120,8 +7309,11 @@
       <c r="G97" t="n">
         <v>8.5</v>
       </c>
-      <c r="J97" t="n">
-        <v>7</v>
+      <c r="H97" t="n">
+        <v>7</v>
+      </c>
+      <c r="N97" t="n">
+        <v>1</v>
       </c>
       <c r="O97" t="n">
         <v>1</v>
@@ -7129,14 +7321,14 @@
       <c r="P97" t="n">
         <v>1</v>
       </c>
-      <c r="S97" t="n">
+      <c r="Q97" t="n">
         <v>1</v>
       </c>
       <c r="Z97" t="n">
         <v>1</v>
       </c>
       <c r="AF97" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AG97" t="inlineStr">
         <is>
@@ -7152,19 +7344,25 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Mitosis y ciclo celular</t>
+          <t>Tejidos vegetales</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D98" t="n">
-        <v>6</v>
+        <v>8</v>
+      </c>
+      <c r="E98" t="n">
+        <v>7</v>
+      </c>
+      <c r="F98" t="n">
+        <v>8</v>
       </c>
       <c r="G98" t="n">
         <v>8.5</v>
@@ -7172,14 +7370,8 @@
       <c r="H98" t="n">
         <v>7</v>
       </c>
-      <c r="I98" t="n">
-        <v>8</v>
-      </c>
       <c r="J98" t="n">
-        <v>7</v>
-      </c>
-      <c r="K98" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="L98" t="n">
         <v>7.5</v>
@@ -7187,21 +7379,21 @@
       <c r="M98" t="n">
         <v>7</v>
       </c>
+      <c r="N98" t="n">
+        <v>1</v>
+      </c>
+      <c r="O98" t="n">
+        <v>1</v>
+      </c>
       <c r="P98" t="n">
         <v>1</v>
       </c>
       <c r="Q98" t="n">
         <v>1</v>
       </c>
-      <c r="R98" t="n">
-        <v>1</v>
-      </c>
       <c r="S98" t="n">
         <v>1</v>
       </c>
-      <c r="T98" t="n">
-        <v>1</v>
-      </c>
       <c r="U98" t="n">
         <v>1</v>
       </c>
@@ -7209,11 +7401,11 @@
         <v>1</v>
       </c>
       <c r="AF98" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AG98" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH98" t="inlineStr">
@@ -7225,28 +7417,22 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Niveles de organización de los seres vivos</t>
+          <t>Transporte en plantas: xilema y floema</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D99" t="n">
-        <v>4</v>
-      </c>
-      <c r="E99" t="n">
-        <v>7</v>
-      </c>
-      <c r="F99" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G99" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H99" t="n">
         <v>7</v>
@@ -7257,20 +7443,11 @@
       <c r="J99" t="n">
         <v>4.5</v>
       </c>
-      <c r="K99" t="n">
-        <v>7</v>
-      </c>
       <c r="L99" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="M99" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="N99" t="n">
-        <v>1</v>
-      </c>
-      <c r="O99" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="P99" t="n">
         <v>1</v>
@@ -7284,24 +7461,18 @@
       <c r="S99" t="n">
         <v>1</v>
       </c>
-      <c r="T99" t="n">
-        <v>1</v>
-      </c>
       <c r="U99" t="n">
         <v>1</v>
       </c>
       <c r="V99" t="n">
         <v>1</v>
       </c>
-      <c r="Z99" t="n">
-        <v>1</v>
-      </c>
       <c r="AF99" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AG99" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH99" t="inlineStr">
@@ -7313,37 +7484,37 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Niveles de organización ecológica</t>
+          <t>Variación genética en la descendencia</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C100" t="n">
+        <v>6</v>
+      </c>
+      <c r="D100" t="n">
+        <v>6</v>
+      </c>
+      <c r="F100" t="n">
+        <v>8</v>
+      </c>
+      <c r="G100" t="n">
         <v>4</v>
       </c>
-      <c r="D100" t="n">
-        <v>4</v>
-      </c>
-      <c r="F100" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="G100" t="n">
-        <v>8.5</v>
-      </c>
       <c r="H100" t="n">
-        <v>3</v>
-      </c>
-      <c r="J100" t="n">
-        <v>2.5</v>
+        <v>7</v>
+      </c>
+      <c r="I100" t="n">
+        <v>8</v>
       </c>
       <c r="K100" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L100" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="M100" t="n">
         <v>4.5</v>
@@ -7357,7 +7528,7 @@
       <c r="Q100" t="n">
         <v>1</v>
       </c>
-      <c r="S100" t="n">
+      <c r="R100" t="n">
         <v>1</v>
       </c>
       <c r="T100" t="n">
@@ -7370,11 +7541,11 @@
         <v>1</v>
       </c>
       <c r="AF100" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AG100" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH100" t="inlineStr">
@@ -7386,7 +7557,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Nutrición autótrofa y heterótrofa</t>
+          <t>Especies clave</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -7395,77 +7566,32 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D101" t="n">
-        <v>2</v>
-      </c>
-      <c r="F101" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="G101" t="n">
-        <v>2</v>
-      </c>
-      <c r="H101" t="n">
-        <v>2</v>
-      </c>
-      <c r="I101" t="n">
-        <v>5</v>
-      </c>
-      <c r="J101" t="n">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="K101" t="n">
-        <v>2</v>
-      </c>
-      <c r="L101" t="n">
-        <v>5</v>
-      </c>
-      <c r="M101" t="n">
-        <v>7</v>
-      </c>
-      <c r="O101" t="n">
-        <v>1</v>
-      </c>
-      <c r="P101" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q101" t="n">
-        <v>1</v>
-      </c>
-      <c r="R101" t="n">
-        <v>1</v>
-      </c>
-      <c r="S101" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T101" t="n">
         <v>1</v>
       </c>
-      <c r="U101" t="n">
-        <v>1</v>
-      </c>
-      <c r="V101" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF101" t="n">
-        <v>3</v>
-      </c>
       <c r="AG101" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>no_aplica</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Organelos de la célula eucariota</t>
+          <t>Niveles de organización ecológica</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -7474,41 +7600,59 @@
         </is>
       </c>
       <c r="C102" t="n">
+        <v>4</v>
+      </c>
+      <c r="D102" t="n">
+        <v>4</v>
+      </c>
+      <c r="F102" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G102" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H102" t="n">
+        <v>3</v>
+      </c>
+      <c r="J102" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K102" t="n">
+        <v>3</v>
+      </c>
+      <c r="L102" t="n">
         <v>6</v>
       </c>
-      <c r="D102" t="n">
-        <v>6</v>
-      </c>
-      <c r="E102" t="n">
-        <v>7</v>
-      </c>
-      <c r="G102" t="n">
-        <v>6</v>
-      </c>
-      <c r="K102" t="n">
-        <v>7</v>
-      </c>
-      <c r="L102" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="N102" t="n">
+      <c r="M102" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O102" t="n">
         <v>1</v>
       </c>
       <c r="P102" t="n">
         <v>1</v>
       </c>
+      <c r="Q102" t="n">
+        <v>1</v>
+      </c>
+      <c r="S102" t="n">
+        <v>1</v>
+      </c>
       <c r="T102" t="n">
         <v>1</v>
       </c>
       <c r="U102" t="n">
         <v>1</v>
       </c>
+      <c r="V102" t="n">
+        <v>1</v>
+      </c>
       <c r="AF102" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AG102" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH102" t="inlineStr">
@@ -7587,32 +7731,41 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Proteínas: estructura y función</t>
+          <t>Adaptaciones fisiológicas</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>6</v>
-      </c>
-      <c r="D104" t="n">
-        <v>6</v>
-      </c>
-      <c r="G104" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="P104" t="n">
+        <v>10</v>
+      </c>
+      <c r="F104" t="n">
+        <v>8</v>
+      </c>
+      <c r="H104" t="n">
+        <v>3</v>
+      </c>
+      <c r="K104" t="n">
+        <v>5</v>
+      </c>
+      <c r="O104" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q104" t="n">
+        <v>1</v>
+      </c>
+      <c r="T104" t="n">
         <v>1</v>
       </c>
       <c r="AF104" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG104" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH104" t="inlineStr">
@@ -7624,49 +7777,25 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Relación superficie-volumen</t>
+          <t>Capacidad de carga</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>10</v>
-      </c>
-      <c r="F105" t="n">
-        <v>8</v>
-      </c>
-      <c r="G105" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="J105" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="K105" t="n">
-        <v>7</v>
-      </c>
-      <c r="L105" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="O105" t="n">
-        <v>1</v>
-      </c>
-      <c r="P105" t="n">
-        <v>1</v>
-      </c>
-      <c r="S105" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T105" t="n">
         <v>1</v>
       </c>
-      <c r="U105" t="n">
-        <v>1</v>
-      </c>
       <c r="AF105" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG105" t="inlineStr">
         <is>
@@ -7675,39 +7804,48 @@
       </c>
       <c r="AH105" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>posterior</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Relaciones intraespecíficas</t>
+          <t>Ciclo del nitrógeno</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>7</v>
-      </c>
-      <c r="D106" t="n">
-        <v>7</v>
-      </c>
-      <c r="M106" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="V106" t="n">
+        <v>9</v>
+      </c>
+      <c r="F106" t="n">
+        <v>8</v>
+      </c>
+      <c r="G106" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="K106" t="n">
+        <v>6</v>
+      </c>
+      <c r="O106" t="n">
+        <v>1</v>
+      </c>
+      <c r="P106" t="n">
+        <v>1</v>
+      </c>
+      <c r="T106" t="n">
         <v>1</v>
       </c>
       <c r="AF106" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AG106" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH106" t="inlineStr">
@@ -7719,271 +7857,127 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Reproducción humana y pubertad</t>
+          <t>Ciclos del fósforo y del azufre</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D107" t="n">
-        <v>4</v>
-      </c>
-      <c r="E107" t="n">
         <v>8</v>
       </c>
-      <c r="F107" t="n">
-        <v>8</v>
-      </c>
-      <c r="G107" t="n">
-        <v>3</v>
-      </c>
-      <c r="H107" t="n">
-        <v>4</v>
-      </c>
-      <c r="I107" t="n">
-        <v>4</v>
-      </c>
-      <c r="L107" t="n">
-        <v>5</v>
-      </c>
-      <c r="M107" t="n">
-        <v>7</v>
-      </c>
-      <c r="N107" t="n">
-        <v>1</v>
-      </c>
-      <c r="O107" t="n">
-        <v>1</v>
-      </c>
-      <c r="P107" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q107" t="n">
-        <v>1</v>
-      </c>
-      <c r="R107" t="n">
-        <v>1</v>
-      </c>
-      <c r="U107" t="n">
-        <v>1</v>
-      </c>
-      <c r="V107" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z107" t="n">
-        <v>1</v>
-      </c>
       <c r="AF107" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="AG107" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>posterior</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Requerimientos de materia y energía de la célula</t>
+          <t>Especiación y macroevolución</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>6</v>
-      </c>
-      <c r="D108" t="n">
-        <v>6</v>
+        <v>10</v>
+      </c>
+      <c r="F108" t="n">
+        <v>8</v>
       </c>
       <c r="G108" t="n">
-        <v>6</v>
-      </c>
-      <c r="H108" t="n">
-        <v>7</v>
-      </c>
-      <c r="J108" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K108" t="n">
-        <v>7</v>
-      </c>
-      <c r="L108" t="n">
-        <v>5</v>
-      </c>
-      <c r="M108" t="n">
-        <v>7</v>
+        <v>8.5</v>
+      </c>
+      <c r="O108" t="n">
+        <v>1</v>
       </c>
       <c r="P108" t="n">
         <v>1</v>
       </c>
-      <c r="Q108" t="n">
-        <v>1</v>
-      </c>
-      <c r="S108" t="n">
-        <v>1</v>
-      </c>
-      <c r="T108" t="n">
-        <v>1</v>
-      </c>
-      <c r="U108" t="n">
-        <v>1</v>
-      </c>
-      <c r="V108" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z108" t="n">
-        <v>1</v>
-      </c>
       <c r="AF108" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AG108" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH108" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>posterior</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Respuesta de los seres vivos a estímulos</t>
+          <t>Eutrofización</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D109" t="n">
-        <v>2</v>
-      </c>
-      <c r="E109" t="n">
-        <v>8</v>
-      </c>
-      <c r="F109" t="n">
-        <v>8</v>
-      </c>
-      <c r="G109" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="H109" t="n">
-        <v>2</v>
-      </c>
-      <c r="I109" t="n">
-        <v>3</v>
-      </c>
-      <c r="J109" t="n">
-        <v>7</v>
-      </c>
-      <c r="K109" t="n">
-        <v>2</v>
-      </c>
-      <c r="L109" t="n">
-        <v>3</v>
-      </c>
-      <c r="M109" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N109" t="n">
-        <v>1</v>
-      </c>
-      <c r="O109" t="n">
-        <v>1</v>
-      </c>
-      <c r="P109" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q109" t="n">
-        <v>1</v>
-      </c>
-      <c r="R109" t="n">
-        <v>1</v>
-      </c>
-      <c r="S109" t="n">
-        <v>1</v>
-      </c>
-      <c r="T109" t="n">
-        <v>1</v>
-      </c>
-      <c r="U109" t="n">
-        <v>1</v>
-      </c>
-      <c r="V109" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AF109" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="AG109" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>posterior</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Sistema respiratorio</t>
+          <t>Evidencias de la evolución</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>3</v>
-      </c>
-      <c r="D110" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F110" t="n">
         <v>8</v>
       </c>
       <c r="G110" t="n">
-        <v>6</v>
-      </c>
-      <c r="H110" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I110" t="n">
-        <v>5</v>
-      </c>
-      <c r="J110" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K110" t="n">
-        <v>4</v>
-      </c>
-      <c r="L110" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="M110" t="n">
         <v>7</v>
@@ -7994,87 +7988,51 @@
       <c r="P110" t="n">
         <v>1</v>
       </c>
-      <c r="Q110" t="n">
-        <v>1</v>
-      </c>
       <c r="R110" t="n">
         <v>1</v>
       </c>
-      <c r="S110" t="n">
-        <v>1</v>
-      </c>
-      <c r="T110" t="n">
-        <v>1</v>
-      </c>
-      <c r="U110" t="n">
-        <v>1</v>
-      </c>
       <c r="V110" t="n">
         <v>1</v>
       </c>
-      <c r="Z110" t="n">
-        <v>1</v>
-      </c>
       <c r="AF110" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AG110" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>posterior</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Tejidos animales</t>
+          <t>Fases de la fotosíntesis y ciclo de Calvin</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D111" t="n">
-        <v>4</v>
-      </c>
-      <c r="E111" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F111" t="n">
         <v>8</v>
       </c>
-      <c r="G111" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="H111" t="n">
-        <v>7</v>
-      </c>
-      <c r="N111" t="n">
-        <v>1</v>
-      </c>
       <c r="O111" t="n">
         <v>1</v>
       </c>
-      <c r="P111" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q111" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z111" t="n">
-        <v>1</v>
-      </c>
       <c r="AF111" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="AG111" t="inlineStr">
         <is>
@@ -8083,44 +8041,29 @@
       </c>
       <c r="AH111" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>posterior</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Transmisión de patógenos</t>
+          <t>Secuenciación del ADN y perfiles genéticos</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>3</v>
-      </c>
-      <c r="D112" t="n">
-        <v>3</v>
-      </c>
-      <c r="F112" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G112" t="n">
         <v>8.5</v>
       </c>
       <c r="H112" t="n">
-        <v>3</v>
-      </c>
-      <c r="J112" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="L112" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="O112" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="P112" t="n">
         <v>1</v>
@@ -8128,30 +8071,24 @@
       <c r="Q112" t="n">
         <v>1</v>
       </c>
-      <c r="S112" t="n">
-        <v>1</v>
-      </c>
-      <c r="U112" t="n">
-        <v>1</v>
-      </c>
       <c r="AF112" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG112" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>posterior</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Adaptaciones fisiológicas</t>
+          <t>Impulso nervioso y sinapsis</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -8165,19 +8102,13 @@
       <c r="F113" t="n">
         <v>8</v>
       </c>
-      <c r="H113" t="n">
-        <v>3</v>
-      </c>
-      <c r="K113" t="n">
-        <v>5</v>
+      <c r="J113" t="n">
+        <v>7</v>
       </c>
       <c r="O113" t="n">
         <v>1</v>
       </c>
-      <c r="Q113" t="n">
-        <v>1</v>
-      </c>
-      <c r="T113" t="n">
+      <c r="S113" t="n">
         <v>1</v>
       </c>
       <c r="AF113" t="n">
@@ -8197,7 +8128,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Capacidad de carga</t>
+          <t>Ingeniería genética y ADN recombinante</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -8206,16 +8137,37 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>11</v>
-      </c>
-      <c r="K114" t="n">
-        <v>3</v>
-      </c>
-      <c r="T114" t="n">
+        <v>9</v>
+      </c>
+      <c r="F114" t="n">
+        <v>8</v>
+      </c>
+      <c r="G114" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H114" t="n">
+        <v>7</v>
+      </c>
+      <c r="M114" t="n">
+        <v>7</v>
+      </c>
+      <c r="O114" t="n">
+        <v>1</v>
+      </c>
+      <c r="P114" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q114" t="n">
+        <v>1</v>
+      </c>
+      <c r="V114" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z114" t="n">
         <v>1</v>
       </c>
       <c r="AF114" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AG114" t="inlineStr">
         <is>
@@ -8231,7 +8183,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Ciclo del nitrógeno</t>
+          <t>Inmunidad adaptativa</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -8242,26 +8194,23 @@
       <c r="C115" t="n">
         <v>9</v>
       </c>
-      <c r="F115" t="n">
-        <v>8</v>
-      </c>
       <c r="G115" t="n">
         <v>8.5</v>
       </c>
-      <c r="K115" t="n">
-        <v>6</v>
-      </c>
-      <c r="O115" t="n">
-        <v>1</v>
+      <c r="M115" t="n">
+        <v>7</v>
       </c>
       <c r="P115" t="n">
         <v>1</v>
       </c>
-      <c r="T115" t="n">
+      <c r="V115" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z115" t="n">
         <v>1</v>
       </c>
       <c r="AF115" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG115" t="inlineStr">
         <is>
@@ -8277,7 +8226,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Especiación y macroevolución</t>
+          <t>Inmunidad innata</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -8286,18 +8235,18 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>10</v>
-      </c>
-      <c r="F116" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G116" t="n">
         <v>8.5</v>
       </c>
-      <c r="O116" t="n">
-        <v>1</v>
+      <c r="M116" t="n">
+        <v>7</v>
       </c>
       <c r="P116" t="n">
+        <v>1</v>
+      </c>
+      <c r="V116" t="n">
         <v>1</v>
       </c>
       <c r="AF116" t="n">
@@ -8317,7 +8266,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Eutrofización</t>
+          <t>Nutrición mineral de las plantas</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -8326,17 +8275,32 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>7</v>
-      </c>
-      <c r="D117" t="n">
-        <v>7</v>
+        <v>11</v>
+      </c>
+      <c r="F117" t="n">
+        <v>5</v>
+      </c>
+      <c r="G117" t="n">
+        <v>2</v>
+      </c>
+      <c r="I117" t="n">
+        <v>4</v>
+      </c>
+      <c r="O117" t="n">
+        <v>1</v>
+      </c>
+      <c r="P117" t="n">
+        <v>1</v>
+      </c>
+      <c r="R117" t="n">
+        <v>1</v>
       </c>
       <c r="AF117" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG117" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH117" t="inlineStr">
@@ -8348,7 +8312,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Evidencias de la evolución</t>
+          <t>Presión y flujo de fluidos en los seres vivos</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -8357,34 +8321,22 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>9</v>
-      </c>
-      <c r="F118" t="n">
-        <v>8</v>
-      </c>
-      <c r="G118" t="n">
-        <v>4</v>
-      </c>
-      <c r="I118" t="n">
-        <v>8</v>
+        <v>11</v>
+      </c>
+      <c r="H118" t="n">
+        <v>7</v>
       </c>
       <c r="M118" t="n">
         <v>7</v>
       </c>
-      <c r="O118" t="n">
-        <v>1</v>
-      </c>
-      <c r="P118" t="n">
-        <v>1</v>
-      </c>
-      <c r="R118" t="n">
+      <c r="Q118" t="n">
         <v>1</v>
       </c>
       <c r="V118" t="n">
         <v>1</v>
       </c>
       <c r="AF118" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AG118" t="inlineStr">
         <is>
@@ -8400,7 +8352,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Secuenciación del ADN y perfiles genéticos</t>
+          <t>Proteínas: estructura y función</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -8409,26 +8361,23 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>9</v>
+        <v>6</v>
+      </c>
+      <c r="D119" t="n">
+        <v>6</v>
       </c>
       <c r="G119" t="n">
         <v>8.5</v>
       </c>
-      <c r="H119" t="n">
-        <v>7</v>
-      </c>
       <c r="P119" t="n">
         <v>1</v>
       </c>
-      <c r="Q119" t="n">
-        <v>1</v>
-      </c>
       <c r="AF119" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG119" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH119" t="inlineStr">
@@ -8440,7 +8389,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Impulso nervioso y sinapsis</t>
+          <t>Regulación de la expresión génica</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -8449,22 +8398,22 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F120" t="n">
         <v>8</v>
       </c>
-      <c r="J120" t="n">
-        <v>7</v>
+      <c r="G120" t="n">
+        <v>8.5</v>
       </c>
       <c r="O120" t="n">
         <v>1</v>
       </c>
-      <c r="S120" t="n">
+      <c r="P120" t="n">
         <v>1</v>
       </c>
       <c r="AF120" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG120" t="inlineStr">
         <is>
@@ -8480,7 +8429,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Ingeniería genética y ADN recombinante</t>
+          <t>Relación superficie-volumen</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -8489,7 +8438,7 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F121" t="n">
         <v>8</v>
@@ -8497,11 +8446,14 @@
       <c r="G121" t="n">
         <v>8.5</v>
       </c>
-      <c r="H121" t="n">
-        <v>7</v>
-      </c>
-      <c r="M121" t="n">
-        <v>7</v>
+      <c r="J121" t="n">
+        <v>7</v>
+      </c>
+      <c r="K121" t="n">
+        <v>7</v>
+      </c>
+      <c r="L121" t="n">
+        <v>7.5</v>
       </c>
       <c r="O121" t="n">
         <v>1</v>
@@ -8509,17 +8461,17 @@
       <c r="P121" t="n">
         <v>1</v>
       </c>
-      <c r="Q121" t="n">
-        <v>1</v>
-      </c>
-      <c r="V121" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z121" t="n">
+      <c r="S121" t="n">
+        <v>1</v>
+      </c>
+      <c r="T121" t="n">
+        <v>1</v>
+      </c>
+      <c r="U121" t="n">
         <v>1</v>
       </c>
       <c r="AF121" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG121" t="inlineStr">
         <is>
@@ -8528,14 +8480,14 @@
       </c>
       <c r="AH121" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>tardio</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Inmunidad adaptativa</t>
+          <t>Relaciones intraespecíficas</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -8544,29 +8496,23 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>9</v>
-      </c>
-      <c r="G122" t="n">
-        <v>8.5</v>
+        <v>7</v>
+      </c>
+      <c r="D122" t="n">
+        <v>7</v>
       </c>
       <c r="M122" t="n">
-        <v>7</v>
-      </c>
-      <c r="P122" t="n">
-        <v>1</v>
+        <v>4.5</v>
       </c>
       <c r="V122" t="n">
         <v>1</v>
       </c>
-      <c r="Z122" t="n">
-        <v>1</v>
-      </c>
       <c r="AF122" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG122" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH122" t="inlineStr">
@@ -8578,7 +8524,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Inmunidad innata</t>
+          <t>Sistema inmunitario</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -8589,20 +8535,29 @@
       <c r="C123" t="n">
         <v>9</v>
       </c>
+      <c r="F123" t="n">
+        <v>8</v>
+      </c>
       <c r="G123" t="n">
         <v>8.5</v>
       </c>
       <c r="M123" t="n">
         <v>7</v>
       </c>
+      <c r="O123" t="n">
+        <v>1</v>
+      </c>
       <c r="P123" t="n">
         <v>1</v>
       </c>
       <c r="V123" t="n">
         <v>1</v>
       </c>
+      <c r="Z123" t="n">
+        <v>1</v>
+      </c>
       <c r="AF123" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG123" t="inlineStr">
         <is>
@@ -8618,7 +8573,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Nutrición mineral de las plantas</t>
+          <t>Termorregulación</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -8627,28 +8582,16 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F124" t="n">
-        <v>5</v>
-      </c>
-      <c r="G124" t="n">
-        <v>2</v>
-      </c>
-      <c r="I124" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="O124" t="n">
         <v>1</v>
       </c>
-      <c r="P124" t="n">
-        <v>1</v>
-      </c>
-      <c r="R124" t="n">
-        <v>1</v>
-      </c>
       <c r="AF124" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AG124" t="inlineStr">
         <is>
@@ -8664,7 +8607,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Presión y flujo de fluidos en los seres vivos</t>
+          <t>Virus</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -8673,22 +8616,34 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>11</v>
+        <v>9</v>
+      </c>
+      <c r="F125" t="n">
+        <v>8</v>
+      </c>
+      <c r="G125" t="n">
+        <v>8.5</v>
       </c>
       <c r="H125" t="n">
-        <v>7</v>
-      </c>
-      <c r="M125" t="n">
-        <v>7</v>
+        <v>4</v>
+      </c>
+      <c r="L125" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="O125" t="n">
+        <v>1</v>
+      </c>
+      <c r="P125" t="n">
+        <v>1</v>
       </c>
       <c r="Q125" t="n">
         <v>1</v>
       </c>
-      <c r="V125" t="n">
+      <c r="U125" t="n">
         <v>1</v>
       </c>
       <c r="AF125" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AG125" t="inlineStr">
         <is>
@@ -8704,182 +8659,191 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Regulación de la expresión génica</t>
+          <t>Acervo génico y frecuencias alélicas</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>9</v>
-      </c>
-      <c r="F126" t="n">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="D126" t="n">
+        <v>7</v>
       </c>
       <c r="G126" t="n">
         <v>8.5</v>
       </c>
-      <c r="O126" t="n">
-        <v>1</v>
-      </c>
       <c r="P126" t="n">
         <v>1</v>
       </c>
       <c r="AF126" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AG126" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH126" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Sistema inmunitario</t>
+          <t>ATP y energía en los sistemas vivos</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>9</v>
-      </c>
-      <c r="F127" t="n">
-        <v>8</v>
+        <v>6</v>
+      </c>
+      <c r="D127" t="n">
+        <v>6</v>
       </c>
       <c r="G127" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="M127" t="n">
-        <v>7</v>
-      </c>
-      <c r="O127" t="n">
-        <v>1</v>
+        <v>6</v>
+      </c>
+      <c r="H127" t="n">
+        <v>7</v>
+      </c>
+      <c r="J127" t="n">
+        <v>7</v>
       </c>
       <c r="P127" t="n">
         <v>1</v>
       </c>
-      <c r="V127" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z127" t="n">
+      <c r="Q127" t="n">
+        <v>1</v>
+      </c>
+      <c r="S127" t="n">
         <v>1</v>
       </c>
       <c r="AF127" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AG127" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH127" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Termorregulación</t>
+          <t>Atributos de las poblaciones</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>10</v>
+        <v>7</v>
+      </c>
+      <c r="D128" t="n">
+        <v>7</v>
       </c>
       <c r="F128" t="n">
         <v>8</v>
       </c>
+      <c r="G128" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="L128" t="n">
+        <v>6</v>
+      </c>
+      <c r="M128" t="n">
+        <v>4.5</v>
+      </c>
       <c r="O128" t="n">
         <v>1</v>
       </c>
+      <c r="P128" t="n">
+        <v>1</v>
+      </c>
+      <c r="U128" t="n">
+        <v>1</v>
+      </c>
+      <c r="V128" t="n">
+        <v>1</v>
+      </c>
       <c r="AF128" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AG128" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH128" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Virus</t>
+          <t>Biomas y clasificación de ambientes</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>9</v>
+        <v>4</v>
+      </c>
+      <c r="D129" t="n">
+        <v>4</v>
       </c>
       <c r="F129" t="n">
         <v>8</v>
       </c>
-      <c r="G129" t="n">
-        <v>8.5</v>
-      </c>
       <c r="H129" t="n">
+        <v>3</v>
+      </c>
+      <c r="O129" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF129" t="n">
         <v>4</v>
       </c>
-      <c r="L129" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="O129" t="n">
-        <v>1</v>
-      </c>
-      <c r="P129" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q129" t="n">
-        <v>1</v>
-      </c>
-      <c r="U129" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF129" t="n">
-        <v>9</v>
-      </c>
       <c r="AG129" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH129" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Acervo génico y frecuencias alélicas</t>
+          <t>Célula procariota y eucariota</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -8888,19 +8852,25 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D130" t="n">
-        <v>7</v>
+        <v>6</v>
+      </c>
+      <c r="F130" t="n">
+        <v>8</v>
       </c>
       <c r="G130" t="n">
         <v>8.5</v>
       </c>
+      <c r="O130" t="n">
+        <v>1</v>
+      </c>
       <c r="P130" t="n">
         <v>1</v>
       </c>
       <c r="AF130" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AG130" t="inlineStr">
         <is>
@@ -8916,7 +8886,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Biomas y clasificación de ambientes</t>
+          <t>Conservación e inocuidad de los alimentos</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -8925,16 +8895,16 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D131" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F131" t="n">
         <v>8</v>
       </c>
       <c r="H131" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O131" t="n">
         <v>1</v>
@@ -8943,7 +8913,7 @@
         <v>1</v>
       </c>
       <c r="AF131" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AG131" t="inlineStr">
         <is>
@@ -8959,7 +8929,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Célula procariota y eucariota</t>
+          <t>Ecosistemas acuáticos y marinos</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -8968,25 +8938,25 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D132" t="n">
-        <v>6</v>
-      </c>
-      <c r="F132" t="n">
-        <v>8</v>
-      </c>
-      <c r="G132" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="O132" t="n">
-        <v>1</v>
-      </c>
-      <c r="P132" t="n">
+        <v>4</v>
+      </c>
+      <c r="H132" t="n">
+        <v>7</v>
+      </c>
+      <c r="J132" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>1</v>
+      </c>
+      <c r="S132" t="n">
         <v>1</v>
       </c>
       <c r="AF132" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG132" t="inlineStr">
         <is>
@@ -9002,7 +8972,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Conservación e inocuidad de los alimentos</t>
+          <t>Ecosistemas naturales, rurales y urbanos</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -9016,16 +8986,16 @@
       <c r="D133" t="n">
         <v>2</v>
       </c>
-      <c r="F133" t="n">
-        <v>8</v>
-      </c>
       <c r="H133" t="n">
-        <v>2</v>
-      </c>
-      <c r="O133" t="n">
-        <v>1</v>
+        <v>7</v>
+      </c>
+      <c r="M133" t="n">
+        <v>2.5</v>
       </c>
       <c r="Q133" t="n">
+        <v>1</v>
+      </c>
+      <c r="V133" t="n">
         <v>1</v>
       </c>
       <c r="AF133" t="n">
@@ -9045,7 +9015,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Ecosistemas acuáticos y marinos</t>
+          <t>Estrategias reproductivas y supervivencia de la descendencia</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -9054,25 +9024,43 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D134" t="n">
-        <v>4</v>
+        <v>3</v>
+      </c>
+      <c r="E134" t="n">
+        <v>8</v>
+      </c>
+      <c r="F134" t="n">
+        <v>8</v>
       </c>
       <c r="H134" t="n">
-        <v>7</v>
-      </c>
-      <c r="J134" t="n">
-        <v>2.5</v>
+        <v>3</v>
+      </c>
+      <c r="L134" t="n">
+        <v>6</v>
+      </c>
+      <c r="M134" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="N134" t="n">
+        <v>1</v>
+      </c>
+      <c r="O134" t="n">
+        <v>1</v>
       </c>
       <c r="Q134" t="n">
         <v>1</v>
       </c>
-      <c r="S134" t="n">
+      <c r="U134" t="n">
+        <v>1</v>
+      </c>
+      <c r="V134" t="n">
         <v>1</v>
       </c>
       <c r="AF134" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AG134" t="inlineStr">
         <is>
@@ -9081,14 +9069,14 @@
       </c>
       <c r="AH134" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>adelantado</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Ecosistemas naturales, rurales y urbanos</t>
+          <t>Estructura del ADN</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -9097,25 +9085,22 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D135" t="n">
-        <v>2</v>
-      </c>
-      <c r="H135" t="n">
-        <v>7</v>
-      </c>
-      <c r="M135" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q135" t="n">
-        <v>1</v>
-      </c>
-      <c r="V135" t="n">
+        <v>6</v>
+      </c>
+      <c r="G135" t="n">
+        <v>6</v>
+      </c>
+      <c r="P135" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z135" t="n">
         <v>1</v>
       </c>
       <c r="AF135" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AG135" t="inlineStr">
         <is>
@@ -9131,7 +9116,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Estructura del ADN</t>
+          <t>Fermentación y respiración anaerobia</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -9140,22 +9125,25 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D136" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G136" t="n">
         <v>6</v>
       </c>
+      <c r="M136" t="n">
+        <v>7</v>
+      </c>
       <c r="P136" t="n">
         <v>1</v>
       </c>
-      <c r="Z136" t="n">
+      <c r="V136" t="n">
         <v>1</v>
       </c>
       <c r="AF136" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AG136" t="inlineStr">
         <is>
@@ -9171,7 +9159,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Fermentación y respiración anaerobia</t>
+          <t>Filogenia y parentesco evolutivo</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -9180,25 +9168,25 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D137" t="n">
-        <v>3</v>
+        <v>7</v>
+      </c>
+      <c r="F137" t="n">
+        <v>8</v>
       </c>
       <c r="G137" t="n">
-        <v>6</v>
-      </c>
-      <c r="M137" t="n">
-        <v>7</v>
+        <v>8.5</v>
+      </c>
+      <c r="O137" t="n">
+        <v>1</v>
       </c>
       <c r="P137" t="n">
         <v>1</v>
       </c>
-      <c r="V137" t="n">
-        <v>1</v>
-      </c>
       <c r="AF137" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AG137" t="inlineStr">
         <is>
@@ -9214,7 +9202,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Filogenia y parentesco evolutivo</t>
+          <t>Mecanismos de microevolución</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -9231,13 +9219,10 @@
       <c r="F138" t="n">
         <v>8</v>
       </c>
-      <c r="G138" t="n">
-        <v>8.5</v>
-      </c>
       <c r="O138" t="n">
         <v>1</v>
       </c>
-      <c r="P138" t="n">
+      <c r="Z138" t="n">
         <v>1</v>
       </c>
       <c r="AF138" t="n">
@@ -9257,7 +9242,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Mecanismos de microevolución</t>
+          <t>Medidas de biodiversidad</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -9271,13 +9256,10 @@
       <c r="D139" t="n">
         <v>7</v>
       </c>
-      <c r="F139" t="n">
-        <v>8</v>
-      </c>
-      <c r="O139" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z139" t="n">
+      <c r="H139" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q139" t="n">
         <v>1</v>
       </c>
       <c r="AF139" t="n">
@@ -9297,7 +9279,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Medidas de biodiversidad</t>
+          <t>Membrana celular</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -9306,19 +9288,28 @@
         </is>
       </c>
       <c r="C140" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D140" t="n">
-        <v>7</v>
-      </c>
-      <c r="H140" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q140" t="n">
+        <v>6</v>
+      </c>
+      <c r="G140" t="n">
+        <v>6</v>
+      </c>
+      <c r="K140" t="n">
+        <v>7</v>
+      </c>
+      <c r="P140" t="n">
+        <v>1</v>
+      </c>
+      <c r="T140" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z140" t="n">
         <v>1</v>
       </c>
       <c r="AF140" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AG140" t="inlineStr">
         <is>
@@ -9334,7 +9325,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Membrana celular</t>
+          <t>Modelos ecológicos basados en muestreo</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -9343,28 +9334,19 @@
         </is>
       </c>
       <c r="C141" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D141" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G141" t="n">
-        <v>6</v>
-      </c>
-      <c r="K141" t="n">
-        <v>7</v>
+        <v>8.5</v>
       </c>
       <c r="P141" t="n">
         <v>1</v>
       </c>
-      <c r="T141" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z141" t="n">
-        <v>1</v>
-      </c>
       <c r="AF141" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG141" t="inlineStr">
         <is>
@@ -9380,7 +9362,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Modelos ecológicos basados en muestreo</t>
+          <t>Mutaciones</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -9397,7 +9379,16 @@
       <c r="G142" t="n">
         <v>8.5</v>
       </c>
+      <c r="M142" t="n">
+        <v>7</v>
+      </c>
       <c r="P142" t="n">
+        <v>1</v>
+      </c>
+      <c r="V142" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z142" t="n">
         <v>1</v>
       </c>
       <c r="AF142" t="n">
@@ -9417,7 +9408,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Mutaciones</t>
+          <t>Nicho ecológico y exclusión competitiva</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -9426,28 +9417,19 @@
         </is>
       </c>
       <c r="C143" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D143" t="n">
-        <v>7</v>
-      </c>
-      <c r="G143" t="n">
-        <v>8.5</v>
+        <v>4</v>
       </c>
       <c r="M143" t="n">
         <v>7</v>
       </c>
-      <c r="P143" t="n">
-        <v>1</v>
-      </c>
       <c r="V143" t="n">
         <v>1</v>
       </c>
-      <c r="Z143" t="n">
-        <v>1</v>
-      </c>
       <c r="AF143" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AG143" t="inlineStr">
         <is>
@@ -9463,7 +9445,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Nicho ecológico y exclusión competitiva</t>
+          <t>Organelos de la célula eucariota</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -9472,19 +9454,37 @@
         </is>
       </c>
       <c r="C144" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D144" t="n">
-        <v>4</v>
-      </c>
-      <c r="M144" t="n">
-        <v>7</v>
-      </c>
-      <c r="V144" t="n">
+        <v>6</v>
+      </c>
+      <c r="E144" t="n">
+        <v>7</v>
+      </c>
+      <c r="G144" t="n">
+        <v>6</v>
+      </c>
+      <c r="K144" t="n">
+        <v>7</v>
+      </c>
+      <c r="L144" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="N144" t="n">
+        <v>1</v>
+      </c>
+      <c r="P144" t="n">
+        <v>1</v>
+      </c>
+      <c r="T144" t="n">
+        <v>1</v>
+      </c>
+      <c r="U144" t="n">
         <v>1</v>
       </c>
       <c r="AF144" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AG144" t="inlineStr">
         <is>
@@ -9493,7 +9493,7 @@
       </c>
       <c r="AH144" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>

--- a/internacional/2_8/Contraste_biologia.xlsx
+++ b/internacional/2_8/Contraste_biologia.xlsx
@@ -1541,7 +1541,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Nutrientes y sus funciones</t>
+          <t>Mitosis y ciclo celular</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1550,25 +1550,31 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D16" t="n">
-        <v>2</v>
-      </c>
-      <c r="F16" t="n">
+        <v>6</v>
+      </c>
+      <c r="G16" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H16" t="n">
+        <v>7</v>
+      </c>
+      <c r="I16" t="n">
         <v>8</v>
       </c>
-      <c r="G16" t="n">
-        <v>6</v>
-      </c>
-      <c r="H16" t="n">
-        <v>2</v>
+      <c r="J16" t="n">
+        <v>7</v>
+      </c>
+      <c r="K16" t="n">
+        <v>7</v>
       </c>
       <c r="L16" t="n">
         <v>7.5</v>
       </c>
-      <c r="O16" t="n">
-        <v>1</v>
+      <c r="M16" t="n">
+        <v>7</v>
       </c>
       <c r="P16" t="n">
         <v>1</v>
@@ -1576,14 +1582,23 @@
       <c r="Q16" t="n">
         <v>1</v>
       </c>
+      <c r="R16" t="n">
+        <v>1</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
       <c r="U16" t="n">
         <v>1</v>
       </c>
-      <c r="Z16" t="n">
+      <c r="V16" t="n">
         <v>1</v>
       </c>
       <c r="AF16" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
@@ -1592,14 +1607,14 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Redes tróficas</t>
+          <t>Nutrientes y sus funciones</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1608,40 +1623,22 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>4</v>
-      </c>
-      <c r="E17" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F17" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G17" t="n">
         <v>6</v>
       </c>
       <c r="H17" t="n">
-        <v>7</v>
-      </c>
-      <c r="I17" t="n">
-        <v>8</v>
-      </c>
-      <c r="J17" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L17" t="n">
-        <v>6</v>
-      </c>
-      <c r="M17" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="N17" t="n">
-        <v>1</v>
+        <v>7.5</v>
       </c>
       <c r="O17" t="n">
         <v>1</v>
@@ -1652,19 +1649,10 @@
       <c r="Q17" t="n">
         <v>1</v>
       </c>
-      <c r="R17" t="n">
-        <v>1</v>
-      </c>
-      <c r="S17" t="n">
-        <v>1</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1</v>
-      </c>
       <c r="U17" t="n">
         <v>1</v>
       </c>
-      <c r="V17" t="n">
+      <c r="Z17" t="n">
         <v>1</v>
       </c>
       <c r="AF17" t="n">
@@ -1684,7 +1672,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Grandes grupos taxonómicos</t>
+          <t>Redes tróficas</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1693,28 +1681,40 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>4</v>
+      </c>
+      <c r="E18" t="n">
+        <v>6</v>
       </c>
       <c r="F18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G18" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H18" t="n">
-        <v>4</v>
+        <v>7</v>
+      </c>
+      <c r="I18" t="n">
+        <v>8</v>
       </c>
       <c r="J18" t="n">
         <v>2.5</v>
       </c>
       <c r="K18" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L18" t="n">
-        <v>3</v>
+        <v>6</v>
+      </c>
+      <c r="M18" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="N18" t="n">
+        <v>1</v>
       </c>
       <c r="O18" t="n">
         <v>1</v>
@@ -1725,6 +1725,9 @@
       <c r="Q18" t="n">
         <v>1</v>
       </c>
+      <c r="R18" t="n">
+        <v>1</v>
+      </c>
       <c r="S18" t="n">
         <v>1</v>
       </c>
@@ -1734,8 +1737,11 @@
       <c r="U18" t="n">
         <v>1</v>
       </c>
+      <c r="V18" t="n">
+        <v>1</v>
+      </c>
       <c r="AF18" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
@@ -1751,7 +1757,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Simbiosis: mutualismo, comensalismo y parasitismo</t>
+          <t>Grandes grupos taxonómicos</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1760,28 +1766,28 @@
         </is>
       </c>
       <c r="C19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2</v>
+      </c>
+      <c r="F19" t="n">
         <v>4</v>
       </c>
-      <c r="D19" t="n">
+      <c r="G19" t="n">
         <v>4</v>
       </c>
-      <c r="F19" t="n">
-        <v>8</v>
-      </c>
-      <c r="G19" t="n">
-        <v>6</v>
-      </c>
       <c r="H19" t="n">
-        <v>7</v>
+        <v>4</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2.5</v>
       </c>
       <c r="K19" t="n">
         <v>5</v>
       </c>
       <c r="L19" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="M19" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="O19" t="n">
         <v>1</v>
@@ -1792,17 +1798,17 @@
       <c r="Q19" t="n">
         <v>1</v>
       </c>
+      <c r="S19" t="n">
+        <v>1</v>
+      </c>
       <c r="T19" t="n">
         <v>1</v>
       </c>
       <c r="U19" t="n">
         <v>1</v>
       </c>
-      <c r="V19" t="n">
-        <v>1</v>
-      </c>
       <c r="AF19" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
@@ -1818,7 +1824,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sistema excretor</t>
+          <t>Simbiosis: mutualismo, comensalismo y parasitismo</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1836,16 +1842,19 @@
         <v>8</v>
       </c>
       <c r="G20" t="n">
-        <v>8.5</v>
+        <v>6</v>
       </c>
       <c r="H20" t="n">
+        <v>7</v>
+      </c>
+      <c r="K20" t="n">
         <v>5</v>
       </c>
-      <c r="I20" t="n">
-        <v>7</v>
-      </c>
-      <c r="J20" t="n">
-        <v>7</v>
+      <c r="L20" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="M20" t="n">
+        <v>4.5</v>
       </c>
       <c r="O20" t="n">
         <v>1</v>
@@ -1856,10 +1865,13 @@
       <c r="Q20" t="n">
         <v>1</v>
       </c>
-      <c r="R20" t="n">
-        <v>1</v>
-      </c>
-      <c r="S20" t="n">
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
+      </c>
+      <c r="V20" t="n">
         <v>1</v>
       </c>
       <c r="AF20" t="n">
@@ -1879,7 +1891,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sistema nervioso</t>
+          <t>Sistema excretor</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1893,14 +1905,11 @@
       <c r="D21" t="n">
         <v>4</v>
       </c>
-      <c r="E21" t="n">
-        <v>8</v>
-      </c>
       <c r="F21" t="n">
         <v>8</v>
       </c>
       <c r="G21" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="H21" t="n">
         <v>5</v>
@@ -1911,15 +1920,6 @@
       <c r="J21" t="n">
         <v>7</v>
       </c>
-      <c r="K21" t="n">
-        <v>4</v>
-      </c>
-      <c r="M21" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N21" t="n">
-        <v>1</v>
-      </c>
       <c r="O21" t="n">
         <v>1</v>
       </c>
@@ -1933,15 +1933,6 @@
         <v>1</v>
       </c>
       <c r="S21" t="n">
-        <v>1</v>
-      </c>
-      <c r="T21" t="n">
-        <v>1</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z21" t="n">
         <v>1</v>
       </c>
       <c r="AF21" t="n">
@@ -1961,7 +1952,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sostenibilidad de la biosfera</t>
+          <t>Sistema nervioso</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1970,61 +1961,64 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D22" t="n">
-        <v>2</v>
+        <v>4</v>
+      </c>
+      <c r="E22" t="n">
+        <v>8</v>
       </c>
       <c r="F22" t="n">
+        <v>8</v>
+      </c>
+      <c r="G22" t="n">
+        <v>6</v>
+      </c>
+      <c r="H22" t="n">
+        <v>5</v>
+      </c>
+      <c r="I22" t="n">
+        <v>7</v>
+      </c>
+      <c r="J22" t="n">
+        <v>7</v>
+      </c>
+      <c r="K22" t="n">
+        <v>4</v>
+      </c>
+      <c r="M22" t="n">
         <v>2.5</v>
       </c>
-      <c r="G22" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="H22" t="n">
+      <c r="N22" t="n">
+        <v>1</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1</v>
+      </c>
+      <c r="S22" t="n">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF22" t="n">
         <v>4</v>
-      </c>
-      <c r="I22" t="n">
-        <v>8</v>
-      </c>
-      <c r="J22" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K22" t="n">
-        <v>2</v>
-      </c>
-      <c r="L22" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="M22" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O22" t="n">
-        <v>1</v>
-      </c>
-      <c r="P22" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>1</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1</v>
-      </c>
-      <c r="S22" t="n">
-        <v>1</v>
-      </c>
-      <c r="T22" t="n">
-        <v>1</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>2</v>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
@@ -2040,7 +2034,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Tipos de patógenos</t>
+          <t>Sostenibilidad de la biosfera</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2049,25 +2043,34 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F23" t="n">
-        <v>8</v>
+        <v>2.5</v>
       </c>
       <c r="G23" t="n">
         <v>8.5</v>
       </c>
       <c r="H23" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="I23" t="n">
+        <v>8</v>
+      </c>
+      <c r="J23" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K23" t="n">
+        <v>2</v>
       </c>
       <c r="L23" t="n">
-        <v>7.5</v>
+        <v>4.5</v>
       </c>
       <c r="M23" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="O23" t="n">
         <v>1</v>
@@ -2078,17 +2081,23 @@
       <c r="Q23" t="n">
         <v>1</v>
       </c>
+      <c r="R23" t="n">
+        <v>1</v>
+      </c>
+      <c r="S23" t="n">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1</v>
+      </c>
       <c r="U23" t="n">
         <v>1</v>
       </c>
       <c r="V23" t="n">
         <v>1</v>
       </c>
-      <c r="Z23" t="n">
-        <v>1</v>
-      </c>
       <c r="AF23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
@@ -2104,7 +2113,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Transmisión de patógenos</t>
+          <t>Tipos de patógenos</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2127,12 +2136,12 @@
       <c r="H24" t="n">
         <v>3</v>
       </c>
-      <c r="J24" t="n">
-        <v>2.5</v>
-      </c>
       <c r="L24" t="n">
         <v>7.5</v>
       </c>
+      <c r="M24" t="n">
+        <v>7</v>
+      </c>
       <c r="O24" t="n">
         <v>1</v>
       </c>
@@ -2142,14 +2151,17 @@
       <c r="Q24" t="n">
         <v>1</v>
       </c>
-      <c r="S24" t="n">
-        <v>1</v>
-      </c>
       <c r="U24" t="n">
         <v>1</v>
       </c>
+      <c r="V24" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>1</v>
+      </c>
       <c r="AF24" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="AG24" t="inlineStr">
         <is>
@@ -2158,19 +2170,19 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Adaptaciones conductuales</t>
+          <t>Transmisión de patógenos</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -2179,32 +2191,20 @@
       <c r="D25" t="n">
         <v>3</v>
       </c>
-      <c r="E25" t="n">
-        <v>4</v>
-      </c>
       <c r="F25" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G25" t="n">
-        <v>4</v>
+        <v>8.5</v>
       </c>
       <c r="H25" t="n">
         <v>3</v>
       </c>
-      <c r="I25" t="n">
-        <v>3</v>
-      </c>
       <c r="J25" t="n">
         <v>2.5</v>
       </c>
       <c r="L25" t="n">
-        <v>6</v>
-      </c>
-      <c r="M25" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="N25" t="n">
-        <v>1</v>
+        <v>7.5</v>
       </c>
       <c r="O25" t="n">
         <v>1</v>
@@ -2215,36 +2215,30 @@
       <c r="Q25" t="n">
         <v>1</v>
       </c>
-      <c r="R25" t="n">
-        <v>1</v>
-      </c>
       <c r="S25" t="n">
         <v>1</v>
       </c>
       <c r="U25" t="n">
         <v>1</v>
       </c>
-      <c r="V25" t="n">
-        <v>1</v>
-      </c>
       <c r="AF25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG25" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ADN y cromosomas</t>
+          <t>Adaptaciones conductuales</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2253,25 +2247,37 @@
         </is>
       </c>
       <c r="C26" t="n">
+        <v>3</v>
+      </c>
+      <c r="D26" t="n">
+        <v>3</v>
+      </c>
+      <c r="E26" t="n">
+        <v>4</v>
+      </c>
+      <c r="F26" t="n">
+        <v>5</v>
+      </c>
+      <c r="G26" t="n">
+        <v>4</v>
+      </c>
+      <c r="H26" t="n">
+        <v>3</v>
+      </c>
+      <c r="I26" t="n">
+        <v>3</v>
+      </c>
+      <c r="J26" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L26" t="n">
         <v>6</v>
       </c>
-      <c r="D26" t="n">
-        <v>6</v>
-      </c>
-      <c r="F26" t="n">
-        <v>8</v>
-      </c>
-      <c r="G26" t="n">
-        <v>6</v>
-      </c>
-      <c r="J26" t="n">
-        <v>7</v>
-      </c>
-      <c r="L26" t="n">
-        <v>7.5</v>
-      </c>
       <c r="M26" t="n">
-        <v>7</v>
+        <v>4.5</v>
+      </c>
+      <c r="N26" t="n">
+        <v>1</v>
       </c>
       <c r="O26" t="n">
         <v>1</v>
@@ -2279,6 +2285,12 @@
       <c r="P26" t="n">
         <v>1</v>
       </c>
+      <c r="Q26" t="n">
+        <v>1</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1</v>
+      </c>
       <c r="S26" t="n">
         <v>1</v>
       </c>
@@ -2288,11 +2300,8 @@
       <c r="V26" t="n">
         <v>1</v>
       </c>
-      <c r="Z26" t="n">
-        <v>1</v>
-      </c>
       <c r="AF26" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AG26" t="inlineStr">
         <is>
@@ -2301,14 +2310,14 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>tardio</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Agricultura y seguridad alimentaria</t>
+          <t>ADN y cromosomas</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2317,22 +2326,25 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D27" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F27" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G27" t="n">
         <v>6</v>
       </c>
-      <c r="K27" t="n">
-        <v>2</v>
+      <c r="J27" t="n">
+        <v>7</v>
+      </c>
+      <c r="L27" t="n">
+        <v>7.5</v>
       </c>
       <c r="M27" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="O27" t="n">
         <v>1</v>
@@ -2340,14 +2352,20 @@
       <c r="P27" t="n">
         <v>1</v>
       </c>
-      <c r="T27" t="n">
+      <c r="S27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="n">
         <v>1</v>
       </c>
       <c r="V27" t="n">
         <v>1</v>
       </c>
+      <c r="Z27" t="n">
+        <v>1</v>
+      </c>
       <c r="AF27" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AG27" t="inlineStr">
         <is>
@@ -2363,7 +2381,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Biodiversidad</t>
+          <t>Agricultura y seguridad alimentaria</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2372,40 +2390,22 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D28" t="n">
-        <v>2</v>
-      </c>
-      <c r="E28" t="n">
+        <v>4</v>
+      </c>
+      <c r="F28" t="n">
+        <v>5</v>
+      </c>
+      <c r="G28" t="n">
         <v>6</v>
       </c>
-      <c r="F28" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="G28" t="n">
-        <v>2</v>
-      </c>
-      <c r="H28" t="n">
-        <v>2</v>
-      </c>
-      <c r="I28" t="n">
-        <v>6</v>
-      </c>
-      <c r="J28" t="n">
-        <v>2.5</v>
-      </c>
       <c r="K28" t="n">
         <v>2</v>
       </c>
-      <c r="L28" t="n">
-        <v>3</v>
-      </c>
       <c r="M28" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N28" t="n">
-        <v>1</v>
+        <v>4.5</v>
       </c>
       <c r="O28" t="n">
         <v>1</v>
@@ -2413,26 +2413,14 @@
       <c r="P28" t="n">
         <v>1</v>
       </c>
-      <c r="Q28" t="n">
-        <v>1</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1</v>
-      </c>
-      <c r="S28" t="n">
-        <v>1</v>
-      </c>
       <c r="T28" t="n">
         <v>1</v>
       </c>
-      <c r="U28" t="n">
-        <v>1</v>
-      </c>
       <c r="V28" t="n">
         <v>1</v>
       </c>
       <c r="AF28" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AG28" t="inlineStr">
         <is>
@@ -2448,7 +2436,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Biomoléculas</t>
+          <t>Biodiversidad</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2457,28 +2445,40 @@
         </is>
       </c>
       <c r="C29" t="n">
+        <v>2</v>
+      </c>
+      <c r="D29" t="n">
+        <v>2</v>
+      </c>
+      <c r="E29" t="n">
         <v>6</v>
       </c>
-      <c r="D29" t="n">
+      <c r="F29" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G29" t="n">
+        <v>2</v>
+      </c>
+      <c r="H29" t="n">
+        <v>2</v>
+      </c>
+      <c r="I29" t="n">
         <v>6</v>
       </c>
-      <c r="F29" t="n">
-        <v>8</v>
-      </c>
-      <c r="G29" t="n">
-        <v>6</v>
-      </c>
-      <c r="H29" t="n">
-        <v>2</v>
-      </c>
       <c r="J29" t="n">
-        <v>7</v>
+        <v>2.5</v>
+      </c>
+      <c r="K29" t="n">
+        <v>2</v>
       </c>
       <c r="L29" t="n">
-        <v>7.5</v>
+        <v>3</v>
       </c>
       <c r="M29" t="n">
-        <v>7</v>
+        <v>2.5</v>
+      </c>
+      <c r="N29" t="n">
+        <v>1</v>
       </c>
       <c r="O29" t="n">
         <v>1</v>
@@ -2489,20 +2489,23 @@
       <c r="Q29" t="n">
         <v>1</v>
       </c>
+      <c r="R29" t="n">
+        <v>1</v>
+      </c>
       <c r="S29" t="n">
         <v>1</v>
       </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
       <c r="U29" t="n">
         <v>1</v>
       </c>
       <c r="V29" t="n">
         <v>1</v>
       </c>
-      <c r="Z29" t="n">
-        <v>1</v>
-      </c>
       <c r="AF29" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AG29" t="inlineStr">
         <is>
@@ -2518,7 +2521,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Biotecnología vegetal y agroindustria</t>
+          <t>Biomoléculas</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2536,7 +2539,16 @@
         <v>8</v>
       </c>
       <c r="G30" t="n">
-        <v>8.5</v>
+        <v>6</v>
+      </c>
+      <c r="H30" t="n">
+        <v>2</v>
+      </c>
+      <c r="J30" t="n">
+        <v>7</v>
+      </c>
+      <c r="L30" t="n">
+        <v>7.5</v>
       </c>
       <c r="M30" t="n">
         <v>7</v>
@@ -2547,7 +2559,19 @@
       <c r="P30" t="n">
         <v>1</v>
       </c>
+      <c r="Q30" t="n">
+        <v>1</v>
+      </c>
+      <c r="S30" t="n">
+        <v>1</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
+      </c>
       <c r="V30" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z30" t="n">
         <v>1</v>
       </c>
       <c r="AF30" t="n">
@@ -2555,19 +2579,19 @@
       </c>
       <c r="AG30" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Cadena alimentaria</t>
+          <t>Biotecnología vegetal y agroindustria</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2576,83 +2600,47 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D31" t="n">
-        <v>4</v>
-      </c>
-      <c r="E31" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F31" t="n">
-        <v>2.5</v>
+        <v>8</v>
       </c>
       <c r="G31" t="n">
-        <v>2</v>
-      </c>
-      <c r="H31" t="n">
-        <v>3</v>
-      </c>
-      <c r="I31" t="n">
-        <v>5</v>
-      </c>
-      <c r="J31" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K31" t="n">
-        <v>2</v>
-      </c>
-      <c r="L31" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="M31" t="n">
+        <v>7</v>
+      </c>
+      <c r="O31" t="n">
+        <v>1</v>
+      </c>
+      <c r="P31" t="n">
+        <v>1</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF31" t="n">
         <v>6</v>
       </c>
-      <c r="M31" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="N31" t="n">
-        <v>1</v>
-      </c>
-      <c r="O31" t="n">
-        <v>1</v>
-      </c>
-      <c r="P31" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>1</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1</v>
-      </c>
-      <c r="S31" t="n">
-        <v>1</v>
-      </c>
-      <c r="T31" t="n">
-        <v>1</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1</v>
-      </c>
-      <c r="V31" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>4</v>
-      </c>
       <c r="AG31" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Cambio climático y seres vivos</t>
+          <t>Cadena alimentaria</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2661,19 +2649,31 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D32" t="n">
-        <v>7</v>
+        <v>4</v>
+      </c>
+      <c r="E32" t="n">
+        <v>3</v>
       </c>
       <c r="F32" t="n">
-        <v>8</v>
+        <v>2.5</v>
+      </c>
+      <c r="G32" t="n">
+        <v>2</v>
       </c>
       <c r="H32" t="n">
-        <v>7</v>
+        <v>3</v>
+      </c>
+      <c r="I32" t="n">
+        <v>5</v>
+      </c>
+      <c r="J32" t="n">
+        <v>2.5</v>
       </c>
       <c r="K32" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L32" t="n">
         <v>6</v>
@@ -2681,12 +2681,24 @@
       <c r="M32" t="n">
         <v>4.5</v>
       </c>
+      <c r="N32" t="n">
+        <v>1</v>
+      </c>
       <c r="O32" t="n">
         <v>1</v>
       </c>
+      <c r="P32" t="n">
+        <v>1</v>
+      </c>
       <c r="Q32" t="n">
         <v>1</v>
       </c>
+      <c r="R32" t="n">
+        <v>1</v>
+      </c>
+      <c r="S32" t="n">
+        <v>1</v>
+      </c>
       <c r="T32" t="n">
         <v>1</v>
       </c>
@@ -2697,7 +2709,7 @@
         <v>1</v>
       </c>
       <c r="AF32" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="AG32" t="inlineStr">
         <is>
@@ -2706,14 +2718,14 @@
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Célula animal y célula vegetal</t>
+          <t>Cambio climático y seres vivos</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2722,56 +2734,32 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D33" t="n">
-        <v>6</v>
-      </c>
-      <c r="E33" t="n">
         <v>7</v>
       </c>
       <c r="F33" t="n">
         <v>8</v>
       </c>
-      <c r="G33" t="n">
+      <c r="H33" t="n">
+        <v>7</v>
+      </c>
+      <c r="K33" t="n">
+        <v>5</v>
+      </c>
+      <c r="L33" t="n">
         <v>6</v>
       </c>
-      <c r="H33" t="n">
-        <v>5</v>
-      </c>
-      <c r="I33" t="n">
-        <v>7</v>
-      </c>
-      <c r="J33" t="n">
+      <c r="M33" t="n">
         <v>4.5</v>
       </c>
-      <c r="K33" t="n">
-        <v>7</v>
-      </c>
-      <c r="L33" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="M33" t="n">
-        <v>7</v>
-      </c>
-      <c r="N33" t="n">
-        <v>1</v>
-      </c>
       <c r="O33" t="n">
         <v>1</v>
       </c>
-      <c r="P33" t="n">
-        <v>1</v>
-      </c>
       <c r="Q33" t="n">
         <v>1</v>
       </c>
-      <c r="R33" t="n">
-        <v>1</v>
-      </c>
-      <c r="S33" t="n">
-        <v>1</v>
-      </c>
       <c r="T33" t="n">
         <v>1</v>
       </c>
@@ -2782,7 +2770,7 @@
         <v>1</v>
       </c>
       <c r="AF33" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AG33" t="inlineStr">
         <is>
@@ -2791,14 +2779,14 @@
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>tardio</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Ciclo de vida de las plantas</t>
+          <t>Célula animal y célula vegetal</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2807,37 +2795,37 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D34" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E34" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F34" t="n">
         <v>8</v>
       </c>
       <c r="G34" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H34" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I34" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J34" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="K34" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="L34" t="n">
-        <v>3</v>
+        <v>7.5</v>
       </c>
       <c r="M34" t="n">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="N34" t="n">
         <v>1</v>
@@ -2867,7 +2855,7 @@
         <v>1</v>
       </c>
       <c r="AF34" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AG34" t="inlineStr">
         <is>
@@ -2883,7 +2871,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Ciclo de vida de los animales</t>
+          <t>Ciclo de vida de las plantas</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2892,10 +2880,10 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E35" t="n">
         <v>2</v>
@@ -2915,6 +2903,9 @@
       <c r="J35" t="n">
         <v>2.5</v>
       </c>
+      <c r="K35" t="n">
+        <v>2</v>
+      </c>
       <c r="L35" t="n">
         <v>3</v>
       </c>
@@ -2939,6 +2930,9 @@
       <c r="S35" t="n">
         <v>1</v>
       </c>
+      <c r="T35" t="n">
+        <v>1</v>
+      </c>
       <c r="U35" t="n">
         <v>1</v>
       </c>
@@ -2946,7 +2940,7 @@
         <v>1</v>
       </c>
       <c r="AF35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AG35" t="inlineStr">
         <is>
@@ -2962,7 +2956,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Papel de los seres vivos en el ciclo del agua</t>
+          <t>Ciclo de vida de los animales</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2976,26 +2970,35 @@
       <c r="D36" t="n">
         <v>3</v>
       </c>
+      <c r="E36" t="n">
+        <v>2</v>
+      </c>
+      <c r="F36" t="n">
+        <v>8</v>
+      </c>
       <c r="G36" t="n">
-        <v>8.5</v>
+        <v>2</v>
       </c>
       <c r="H36" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I36" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J36" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K36" t="n">
-        <v>8</v>
+        <v>2.5</v>
       </c>
       <c r="L36" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M36" t="n">
-        <v>7</v>
+        <v>2.5</v>
+      </c>
+      <c r="N36" t="n">
+        <v>1</v>
+      </c>
+      <c r="O36" t="n">
+        <v>1</v>
       </c>
       <c r="P36" t="n">
         <v>1</v>
@@ -3009,9 +3012,6 @@
       <c r="S36" t="n">
         <v>1</v>
       </c>
-      <c r="T36" t="n">
-        <v>1</v>
-      </c>
       <c r="U36" t="n">
         <v>1</v>
       </c>
@@ -3019,11 +3019,11 @@
         <v>1</v>
       </c>
       <c r="AF36" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AG36" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH36" t="inlineStr">
@@ -3035,7 +3035,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Ciclos del carbono y del oxígeno</t>
+          <t>Papel de los seres vivos en el ciclo del agua</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3049,35 +3049,26 @@
       <c r="D37" t="n">
         <v>3</v>
       </c>
-      <c r="E37" t="n">
-        <v>8</v>
-      </c>
-      <c r="F37" t="n">
-        <v>5</v>
-      </c>
       <c r="G37" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="H37" t="n">
+        <v>7</v>
+      </c>
+      <c r="I37" t="n">
         <v>5</v>
       </c>
       <c r="J37" t="n">
         <v>4.5</v>
       </c>
       <c r="K37" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L37" t="n">
-        <v>7.5</v>
+        <v>5</v>
       </c>
       <c r="M37" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N37" t="n">
-        <v>1</v>
-      </c>
-      <c r="O37" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="P37" t="n">
         <v>1</v>
@@ -3085,6 +3076,9 @@
       <c r="Q37" t="n">
         <v>1</v>
       </c>
+      <c r="R37" t="n">
+        <v>1</v>
+      </c>
       <c r="S37" t="n">
         <v>1</v>
       </c>
@@ -3098,7 +3092,7 @@
         <v>1</v>
       </c>
       <c r="AF37" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG37" t="inlineStr">
         <is>
@@ -3114,7 +3108,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Circulación e intercambio capilar</t>
+          <t>Ciclos del carbono y del oxígeno</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3123,23 +3117,38 @@
         </is>
       </c>
       <c r="C38" t="n">
+        <v>3</v>
+      </c>
+      <c r="D38" t="n">
+        <v>3</v>
+      </c>
+      <c r="E38" t="n">
         <v>8</v>
       </c>
-      <c r="D38" t="n">
-        <v>8</v>
-      </c>
       <c r="F38" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G38" t="n">
+        <v>6</v>
+      </c>
+      <c r="H38" t="n">
+        <v>5</v>
+      </c>
+      <c r="J38" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K38" t="n">
         <v>4</v>
-      </c>
-      <c r="H38" t="n">
-        <v>7</v>
       </c>
       <c r="L38" t="n">
         <v>7.5</v>
       </c>
+      <c r="M38" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N38" t="n">
+        <v>1</v>
+      </c>
       <c r="O38" t="n">
         <v>1</v>
       </c>
@@ -3149,27 +3158,36 @@
       <c r="Q38" t="n">
         <v>1</v>
       </c>
+      <c r="S38" t="n">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1</v>
+      </c>
       <c r="U38" t="n">
         <v>1</v>
       </c>
+      <c r="V38" t="n">
+        <v>1</v>
+      </c>
       <c r="AF38" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="AG38" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Clasificación de seres vivos por sus rasgos</t>
+          <t>Circulación e intercambio capilar</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3178,40 +3196,22 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D39" t="n">
-        <v>2</v>
-      </c>
-      <c r="E39" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F39" t="n">
-        <v>2.5</v>
+        <v>8</v>
       </c>
       <c r="G39" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H39" t="n">
-        <v>2</v>
-      </c>
-      <c r="I39" t="n">
-        <v>2</v>
-      </c>
-      <c r="J39" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K39" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L39" t="n">
-        <v>3</v>
-      </c>
-      <c r="M39" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N39" t="n">
-        <v>1</v>
+        <v>7.5</v>
       </c>
       <c r="O39" t="n">
         <v>1</v>
@@ -3222,23 +3222,11 @@
       <c r="Q39" t="n">
         <v>1</v>
       </c>
-      <c r="R39" t="n">
-        <v>1</v>
-      </c>
-      <c r="S39" t="n">
-        <v>1</v>
-      </c>
-      <c r="T39" t="n">
-        <v>1</v>
-      </c>
       <c r="U39" t="n">
         <v>1</v>
       </c>
-      <c r="V39" t="n">
-        <v>1</v>
-      </c>
       <c r="AF39" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="AG39" t="inlineStr">
         <is>
@@ -3247,14 +3235,14 @@
       </c>
       <c r="AH39" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>posterior</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Clasificación jerárquica y nomenclatura</t>
+          <t>Clasificación de seres vivos por sus rasgos</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3263,28 +3251,40 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D40" t="n">
-        <v>7</v>
+        <v>2</v>
+      </c>
+      <c r="E40" t="n">
+        <v>2</v>
       </c>
       <c r="F40" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="G40" t="n">
-        <v>8.5</v>
+        <v>2</v>
       </c>
       <c r="H40" t="n">
-        <v>7</v>
+        <v>2</v>
+      </c>
+      <c r="I40" t="n">
+        <v>2</v>
       </c>
       <c r="J40" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="K40" t="n">
-        <v>5</v>
+        <v>3</v>
+      </c>
+      <c r="L40" t="n">
+        <v>3</v>
       </c>
       <c r="M40" t="n">
-        <v>7</v>
+        <v>2.5</v>
+      </c>
+      <c r="N40" t="n">
+        <v>1</v>
       </c>
       <c r="O40" t="n">
         <v>1</v>
@@ -3295,21 +3295,27 @@
       <c r="Q40" t="n">
         <v>1</v>
       </c>
+      <c r="R40" t="n">
+        <v>1</v>
+      </c>
       <c r="S40" t="n">
         <v>1</v>
       </c>
       <c r="T40" t="n">
         <v>1</v>
       </c>
+      <c r="U40" t="n">
+        <v>1</v>
+      </c>
       <c r="V40" t="n">
         <v>1</v>
       </c>
       <c r="AF40" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AG40" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH40" t="inlineStr">
@@ -3321,7 +3327,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Competencia por recursos</t>
+          <t>Clasificación jerárquica y nomenclatura</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3330,28 +3336,28 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D41" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F41" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G41" t="n">
-        <v>2</v>
+        <v>8.5</v>
       </c>
       <c r="H41" t="n">
-        <v>3</v>
-      </c>
-      <c r="I41" t="n">
+        <v>7</v>
+      </c>
+      <c r="J41" t="n">
+        <v>7</v>
+      </c>
+      <c r="K41" t="n">
         <v>5</v>
       </c>
-      <c r="K41" t="n">
-        <v>3</v>
-      </c>
       <c r="M41" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="O41" t="n">
         <v>1</v>
@@ -3362,7 +3368,7 @@
       <c r="Q41" t="n">
         <v>1</v>
       </c>
-      <c r="R41" t="n">
+      <c r="S41" t="n">
         <v>1</v>
       </c>
       <c r="T41" t="n">
@@ -3372,11 +3378,11 @@
         <v>1</v>
       </c>
       <c r="AF41" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AG41" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH41" t="inlineStr">
@@ -3388,7 +3394,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Concepto de especie</t>
+          <t>Competencia por recursos</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3397,22 +3403,25 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D42" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F42" t="n">
-        <v>2.5</v>
+        <v>8</v>
       </c>
       <c r="G42" t="n">
-        <v>6</v>
-      </c>
-      <c r="J42" t="n">
-        <v>7</v>
-      </c>
-      <c r="L42" t="n">
-        <v>6</v>
+        <v>2</v>
+      </c>
+      <c r="H42" t="n">
+        <v>3</v>
+      </c>
+      <c r="I42" t="n">
+        <v>5</v>
+      </c>
+      <c r="K42" t="n">
+        <v>3</v>
       </c>
       <c r="M42" t="n">
         <v>4.5</v>
@@ -3423,17 +3432,20 @@
       <c r="P42" t="n">
         <v>1</v>
       </c>
-      <c r="S42" t="n">
-        <v>1</v>
-      </c>
-      <c r="U42" t="n">
+      <c r="Q42" t="n">
+        <v>1</v>
+      </c>
+      <c r="R42" t="n">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
         <v>1</v>
       </c>
       <c r="V42" t="n">
         <v>1</v>
       </c>
       <c r="AF42" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AG42" t="inlineStr">
         <is>
@@ -3449,7 +3461,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Contagio y prevención de enfermedades</t>
+          <t>Concepto de especie</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3458,22 +3470,25 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D43" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F43" t="n">
-        <v>8</v>
+        <v>2.5</v>
       </c>
       <c r="G43" t="n">
-        <v>2</v>
-      </c>
-      <c r="H43" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J43" t="n">
-        <v>2.5</v>
+        <v>7</v>
+      </c>
+      <c r="L43" t="n">
+        <v>6</v>
+      </c>
+      <c r="M43" t="n">
+        <v>4.5</v>
       </c>
       <c r="O43" t="n">
         <v>1</v>
@@ -3481,17 +3496,17 @@
       <c r="P43" t="n">
         <v>1</v>
       </c>
-      <c r="Q43" t="n">
-        <v>1</v>
-      </c>
       <c r="S43" t="n">
         <v>1</v>
       </c>
-      <c r="Z43" t="n">
+      <c r="U43" t="n">
+        <v>1</v>
+      </c>
+      <c r="V43" t="n">
         <v>1</v>
       </c>
       <c r="AF43" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AG43" t="inlineStr">
         <is>
@@ -3507,7 +3522,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Contaminación y sus efectos en los seres vivos</t>
+          <t>Contagio y prevención de enfermedades</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3522,41 +3537,29 @@
         <v>2</v>
       </c>
       <c r="F44" t="n">
-        <v>5</v>
+        <v>8</v>
+      </c>
+      <c r="G44" t="n">
+        <v>2</v>
       </c>
       <c r="H44" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J44" t="n">
         <v>2.5</v>
       </c>
-      <c r="K44" t="n">
-        <v>4</v>
-      </c>
-      <c r="L44" t="n">
-        <v>6</v>
-      </c>
-      <c r="M44" t="n">
-        <v>2.5</v>
-      </c>
       <c r="O44" t="n">
         <v>1</v>
       </c>
+      <c r="P44" t="n">
+        <v>1</v>
+      </c>
       <c r="Q44" t="n">
         <v>1</v>
       </c>
       <c r="S44" t="n">
         <v>1</v>
       </c>
-      <c r="T44" t="n">
-        <v>1</v>
-      </c>
-      <c r="U44" t="n">
-        <v>1</v>
-      </c>
-      <c r="V44" t="n">
-        <v>1</v>
-      </c>
       <c r="Z44" t="n">
         <v>1</v>
       </c>
@@ -3565,7 +3568,7 @@
       </c>
       <c r="AG44" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH44" t="inlineStr">
@@ -3577,7 +3580,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Crecimiento poblacional</t>
+          <t>Contaminación y sus efectos en los seres vivos</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3586,22 +3589,28 @@
         </is>
       </c>
       <c r="C45" t="n">
+        <v>2</v>
+      </c>
+      <c r="D45" t="n">
+        <v>2</v>
+      </c>
+      <c r="F45" t="n">
+        <v>5</v>
+      </c>
+      <c r="H45" t="n">
+        <v>2</v>
+      </c>
+      <c r="J45" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K45" t="n">
+        <v>4</v>
+      </c>
+      <c r="L45" t="n">
         <v>6</v>
       </c>
-      <c r="D45" t="n">
-        <v>6</v>
-      </c>
-      <c r="F45" t="n">
-        <v>8</v>
-      </c>
-      <c r="H45" t="n">
-        <v>7</v>
-      </c>
-      <c r="L45" t="n">
-        <v>7.5</v>
-      </c>
       <c r="M45" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="O45" t="n">
         <v>1</v>
@@ -3609,18 +3618,27 @@
       <c r="Q45" t="n">
         <v>1</v>
       </c>
+      <c r="S45" t="n">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1</v>
+      </c>
       <c r="U45" t="n">
         <v>1</v>
       </c>
       <c r="V45" t="n">
         <v>1</v>
       </c>
+      <c r="Z45" t="n">
+        <v>1</v>
+      </c>
       <c r="AF45" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AG45" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH45" t="inlineStr">
@@ -3632,7 +3650,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Depredación</t>
+          <t>Crecimiento poblacional</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3641,49 +3659,37 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D46" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F46" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="G46" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H46" t="n">
-        <v>3</v>
-      </c>
-      <c r="I46" t="n">
-        <v>5</v>
-      </c>
-      <c r="K46" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L46" t="n">
-        <v>6</v>
+        <v>7.5</v>
+      </c>
+      <c r="M46" t="n">
+        <v>7</v>
       </c>
       <c r="O46" t="n">
         <v>1</v>
       </c>
-      <c r="P46" t="n">
-        <v>1</v>
-      </c>
       <c r="Q46" t="n">
         <v>1</v>
       </c>
-      <c r="R46" t="n">
-        <v>1</v>
-      </c>
-      <c r="T46" t="n">
-        <v>1</v>
-      </c>
       <c r="U46" t="n">
         <v>1</v>
       </c>
+      <c r="V46" t="n">
+        <v>1</v>
+      </c>
       <c r="AF46" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AG46" t="inlineStr">
         <is>
@@ -3699,7 +3705,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Diferenciación y especialización celular</t>
+          <t>Depredación</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3708,27 +3714,30 @@
         </is>
       </c>
       <c r="C47" t="n">
+        <v>4</v>
+      </c>
+      <c r="D47" t="n">
+        <v>4</v>
+      </c>
+      <c r="F47" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G47" t="n">
+        <v>2</v>
+      </c>
+      <c r="H47" t="n">
+        <v>3</v>
+      </c>
+      <c r="I47" t="n">
+        <v>5</v>
+      </c>
+      <c r="K47" t="n">
+        <v>5</v>
+      </c>
+      <c r="L47" t="n">
         <v>6</v>
       </c>
-      <c r="D47" t="n">
-        <v>6</v>
-      </c>
-      <c r="E47" t="n">
-        <v>7</v>
-      </c>
-      <c r="G47" t="n">
-        <v>6</v>
-      </c>
-      <c r="H47" t="n">
-        <v>7</v>
-      </c>
-      <c r="K47" t="n">
-        <v>7</v>
-      </c>
-      <c r="L47" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="N47" t="n">
+      <c r="O47" t="n">
         <v>1</v>
       </c>
       <c r="P47" t="n">
@@ -3737,21 +3746,21 @@
       <c r="Q47" t="n">
         <v>1</v>
       </c>
+      <c r="R47" t="n">
+        <v>1</v>
+      </c>
       <c r="T47" t="n">
         <v>1</v>
       </c>
       <c r="U47" t="n">
         <v>1</v>
       </c>
-      <c r="Z47" t="n">
-        <v>1</v>
-      </c>
       <c r="AF47" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AG47" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH47" t="inlineStr">
@@ -3763,7 +3772,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Difusión y ósmosis</t>
+          <t>Diferenciación y especialización celular</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3777,16 +3786,28 @@
       <c r="D48" t="n">
         <v>6</v>
       </c>
+      <c r="E48" t="n">
+        <v>7</v>
+      </c>
       <c r="G48" t="n">
         <v>6</v>
       </c>
+      <c r="H48" t="n">
+        <v>7</v>
+      </c>
       <c r="K48" t="n">
         <v>7</v>
       </c>
       <c r="L48" t="n">
         <v>7.5</v>
       </c>
+      <c r="N48" t="n">
+        <v>1</v>
+      </c>
       <c r="P48" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q48" t="n">
         <v>1</v>
       </c>
       <c r="T48" t="n">
@@ -3803,7 +3824,7 @@
       </c>
       <c r="AG48" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH48" t="inlineStr">
@@ -3815,7 +3836,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Digestión química y absorción de nutrientes</t>
+          <t>Difusión y ósmosis</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3824,52 +3845,34 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D49" t="n">
-        <v>8</v>
-      </c>
-      <c r="F49" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G49" t="n">
-        <v>4</v>
-      </c>
-      <c r="I49" t="n">
-        <v>5</v>
-      </c>
-      <c r="J49" t="n">
+        <v>6</v>
+      </c>
+      <c r="K49" t="n">
         <v>7</v>
       </c>
       <c r="L49" t="n">
         <v>7.5</v>
       </c>
-      <c r="M49" t="n">
-        <v>7</v>
-      </c>
-      <c r="O49" t="n">
-        <v>1</v>
-      </c>
       <c r="P49" t="n">
         <v>1</v>
       </c>
-      <c r="R49" t="n">
-        <v>1</v>
-      </c>
-      <c r="S49" t="n">
+      <c r="T49" t="n">
         <v>1</v>
       </c>
       <c r="U49" t="n">
         <v>1</v>
       </c>
-      <c r="V49" t="n">
-        <v>1</v>
-      </c>
       <c r="Z49" t="n">
         <v>1</v>
       </c>
       <c r="AF49" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AG49" t="inlineStr">
         <is>
@@ -3885,7 +3888,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Diversidad genética de poblaciones</t>
+          <t>Digestión química y absorción de nutrientes</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3894,35 +3897,56 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D50" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="F50" t="n">
+        <v>8</v>
       </c>
       <c r="G50" t="n">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="I50" t="n">
+        <v>5</v>
       </c>
       <c r="J50" t="n">
         <v>7</v>
       </c>
-      <c r="K50" t="n">
-        <v>5</v>
+      <c r="L50" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="M50" t="n">
+        <v>7</v>
+      </c>
+      <c r="O50" t="n">
+        <v>1</v>
       </c>
       <c r="P50" t="n">
         <v>1</v>
       </c>
+      <c r="R50" t="n">
+        <v>1</v>
+      </c>
       <c r="S50" t="n">
         <v>1</v>
       </c>
-      <c r="T50" t="n">
+      <c r="U50" t="n">
+        <v>1</v>
+      </c>
+      <c r="V50" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z50" t="n">
         <v>1</v>
       </c>
       <c r="AF50" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG50" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH50" t="inlineStr">
@@ -3934,7 +3958,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Enzimas</t>
+          <t>Diversidad genética de poblaciones</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3943,10 +3967,10 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D51" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G51" t="n">
         <v>6</v>
@@ -3954,11 +3978,8 @@
       <c r="J51" t="n">
         <v>7</v>
       </c>
-      <c r="L51" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="M51" t="n">
-        <v>7</v>
+      <c r="K51" t="n">
+        <v>5</v>
       </c>
       <c r="P51" t="n">
         <v>1</v>
@@ -3966,21 +3987,15 @@
       <c r="S51" t="n">
         <v>1</v>
       </c>
-      <c r="U51" t="n">
-        <v>1</v>
-      </c>
-      <c r="V51" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z51" t="n">
+      <c r="T51" t="n">
         <v>1</v>
       </c>
       <c r="AF51" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG51" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH51" t="inlineStr">
@@ -3992,7 +4007,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Propagación de enfermedades y control de brotes</t>
+          <t>Enzimas</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4001,43 +4016,49 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>11</v>
+        <v>6</v>
+      </c>
+      <c r="D52" t="n">
+        <v>6</v>
       </c>
       <c r="G52" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="H52" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J52" t="n">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="L52" t="n">
         <v>7.5</v>
       </c>
+      <c r="M52" t="n">
+        <v>7</v>
+      </c>
       <c r="P52" t="n">
         <v>1</v>
       </c>
-      <c r="Q52" t="n">
-        <v>1</v>
-      </c>
       <c r="S52" t="n">
         <v>1</v>
       </c>
       <c r="U52" t="n">
         <v>1</v>
       </c>
+      <c r="V52" t="n">
+        <v>1</v>
+      </c>
       <c r="Z52" t="n">
         <v>1</v>
       </c>
+      <c r="AF52" t="n">
+        <v>6</v>
+      </c>
       <c r="AG52" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
-          <t>no_aplica</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
@@ -5626,7 +5647,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Mitosis y ciclo celular</t>
+          <t>Necesidades de los seres vivos</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -5635,31 +5656,43 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D75" t="n">
-        <v>6</v>
+        <v>2</v>
+      </c>
+      <c r="E75" t="n">
+        <v>2</v>
+      </c>
+      <c r="F75" t="n">
+        <v>2.5</v>
       </c>
       <c r="G75" t="n">
-        <v>8.5</v>
+        <v>2</v>
       </c>
       <c r="H75" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I75" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J75" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="K75" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="L75" t="n">
-        <v>7.5</v>
+        <v>3</v>
       </c>
       <c r="M75" t="n">
-        <v>7</v>
+        <v>2.5</v>
+      </c>
+      <c r="N75" t="n">
+        <v>1</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
       </c>
       <c r="P75" t="n">
         <v>1</v>
@@ -5683,11 +5716,11 @@
         <v>1</v>
       </c>
       <c r="AF75" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AG75" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH75" t="inlineStr">
@@ -5699,7 +5732,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Necesidades de los seres vivos</t>
+          <t>Niveles de organización de los seres vivos</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5708,71 +5741,74 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D76" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E76" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F76" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="G76" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H76" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I76" t="n">
+        <v>5</v>
+      </c>
+      <c r="J76" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K76" t="n">
+        <v>7</v>
+      </c>
+      <c r="L76" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="M76" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="N76" t="n">
+        <v>1</v>
+      </c>
+      <c r="O76" t="n">
+        <v>1</v>
+      </c>
+      <c r="P76" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>1</v>
+      </c>
+      <c r="R76" t="n">
+        <v>1</v>
+      </c>
+      <c r="S76" t="n">
+        <v>1</v>
+      </c>
+      <c r="T76" t="n">
+        <v>1</v>
+      </c>
+      <c r="U76" t="n">
+        <v>1</v>
+      </c>
+      <c r="V76" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z76" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF76" t="n">
         <v>4</v>
       </c>
-      <c r="J76" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K76" t="n">
-        <v>2</v>
-      </c>
-      <c r="L76" t="n">
-        <v>3</v>
-      </c>
-      <c r="M76" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N76" t="n">
-        <v>1</v>
-      </c>
-      <c r="O76" t="n">
-        <v>1</v>
-      </c>
-      <c r="P76" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q76" t="n">
-        <v>1</v>
-      </c>
-      <c r="R76" t="n">
-        <v>1</v>
-      </c>
-      <c r="S76" t="n">
-        <v>1</v>
-      </c>
-      <c r="T76" t="n">
-        <v>1</v>
-      </c>
-      <c r="U76" t="n">
-        <v>1</v>
-      </c>
-      <c r="V76" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF76" t="n">
-        <v>2</v>
-      </c>
       <c r="AG76" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH76" t="inlineStr">
@@ -5784,7 +5820,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Niveles de organización de los seres vivos</t>
+          <t>Nutrición autótrofa y heterótrofa</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5793,40 +5829,34 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D77" t="n">
-        <v>4</v>
-      </c>
-      <c r="E77" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F77" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="G77" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H77" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I77" t="n">
         <v>5</v>
       </c>
       <c r="J77" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="K77" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="L77" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="M77" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="N77" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O77" t="n">
         <v>1</v>
@@ -5852,11 +5882,8 @@
       <c r="V77" t="n">
         <v>1</v>
       </c>
-      <c r="Z77" t="n">
-        <v>1</v>
-      </c>
       <c r="AF77" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AG77" t="inlineStr">
         <is>
@@ -5872,7 +5899,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Nutrición autótrofa y heterótrofa</t>
+          <t>Órganos de los sentidos</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5881,35 +5908,29 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D78" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F78" t="n">
+        <v>8</v>
+      </c>
+      <c r="G78" t="n">
+        <v>2</v>
+      </c>
+      <c r="H78" t="n">
+        <v>2</v>
+      </c>
+      <c r="I78" t="n">
+        <v>7</v>
+      </c>
+      <c r="J78" t="n">
+        <v>7</v>
+      </c>
+      <c r="M78" t="n">
         <v>2.5</v>
       </c>
-      <c r="G78" t="n">
-        <v>2</v>
-      </c>
-      <c r="H78" t="n">
-        <v>2</v>
-      </c>
-      <c r="I78" t="n">
-        <v>5</v>
-      </c>
-      <c r="J78" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K78" t="n">
-        <v>2</v>
-      </c>
-      <c r="L78" t="n">
-        <v>5</v>
-      </c>
-      <c r="M78" t="n">
-        <v>7</v>
-      </c>
       <c r="O78" t="n">
         <v>1</v>
       </c>
@@ -5925,21 +5946,15 @@
       <c r="S78" t="n">
         <v>1</v>
       </c>
-      <c r="T78" t="n">
-        <v>1</v>
-      </c>
-      <c r="U78" t="n">
-        <v>1</v>
-      </c>
       <c r="V78" t="n">
         <v>1</v>
       </c>
       <c r="AF78" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG78" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH78" t="inlineStr">
@@ -5951,7 +5966,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Órganos de los sentidos</t>
+          <t>Partes de la planta y sus funciones</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5960,29 +5975,41 @@
         </is>
       </c>
       <c r="C79" t="n">
+        <v>2</v>
+      </c>
+      <c r="D79" t="n">
+        <v>2</v>
+      </c>
+      <c r="E79" t="n">
+        <v>2</v>
+      </c>
+      <c r="F79" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G79" t="n">
+        <v>2</v>
+      </c>
+      <c r="H79" t="n">
+        <v>2</v>
+      </c>
+      <c r="I79" t="n">
+        <v>2</v>
+      </c>
+      <c r="J79" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K79" t="n">
+        <v>2</v>
+      </c>
+      <c r="L79" t="n">
         <v>4</v>
-      </c>
-      <c r="D79" t="n">
-        <v>4</v>
-      </c>
-      <c r="F79" t="n">
-        <v>8</v>
-      </c>
-      <c r="G79" t="n">
-        <v>2</v>
-      </c>
-      <c r="H79" t="n">
-        <v>2</v>
-      </c>
-      <c r="I79" t="n">
-        <v>7</v>
-      </c>
-      <c r="J79" t="n">
-        <v>7</v>
       </c>
       <c r="M79" t="n">
         <v>2.5</v>
       </c>
+      <c r="N79" t="n">
+        <v>1</v>
+      </c>
       <c r="O79" t="n">
         <v>1</v>
       </c>
@@ -5998,11 +6025,17 @@
       <c r="S79" t="n">
         <v>1</v>
       </c>
+      <c r="T79" t="n">
+        <v>1</v>
+      </c>
+      <c r="U79" t="n">
+        <v>1</v>
+      </c>
       <c r="V79" t="n">
         <v>1</v>
       </c>
       <c r="AF79" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AG79" t="inlineStr">
         <is>
@@ -6018,7 +6051,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Partes de la planta y sus funciones</t>
+          <t>Productores, consumidores y descomponedores</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6027,13 +6060,13 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D80" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E80" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F80" t="n">
         <v>2.5</v>
@@ -6042,10 +6075,10 @@
         <v>2</v>
       </c>
       <c r="H80" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I80" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J80" t="n">
         <v>2.5</v>
@@ -6054,10 +6087,10 @@
         <v>2</v>
       </c>
       <c r="L80" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M80" t="n">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="N80" t="n">
         <v>1</v>
@@ -6087,7 +6120,7 @@
         <v>1</v>
       </c>
       <c r="AF80" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG80" t="inlineStr">
         <is>
@@ -6103,7 +6136,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Productores, consumidores y descomponedores</t>
+          <t>Reproducción sexual de las plantas con flor</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6112,67 +6145,61 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D81" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E81" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F81" t="n">
-        <v>2.5</v>
+        <v>8</v>
       </c>
       <c r="G81" t="n">
         <v>2</v>
       </c>
       <c r="H81" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I81" t="n">
-        <v>8</v>
-      </c>
-      <c r="J81" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="K81" t="n">
         <v>2</v>
       </c>
       <c r="L81" t="n">
+        <v>5</v>
+      </c>
+      <c r="M81" t="n">
+        <v>7</v>
+      </c>
+      <c r="N81" t="n">
+        <v>1</v>
+      </c>
+      <c r="O81" t="n">
+        <v>1</v>
+      </c>
+      <c r="P81" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>1</v>
+      </c>
+      <c r="R81" t="n">
+        <v>1</v>
+      </c>
+      <c r="T81" t="n">
+        <v>1</v>
+      </c>
+      <c r="U81" t="n">
+        <v>1</v>
+      </c>
+      <c r="V81" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF81" t="n">
         <v>6</v>
-      </c>
-      <c r="M81" t="n">
-        <v>7</v>
-      </c>
-      <c r="N81" t="n">
-        <v>1</v>
-      </c>
-      <c r="O81" t="n">
-        <v>1</v>
-      </c>
-      <c r="P81" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q81" t="n">
-        <v>1</v>
-      </c>
-      <c r="R81" t="n">
-        <v>1</v>
-      </c>
-      <c r="S81" t="n">
-        <v>1</v>
-      </c>
-      <c r="T81" t="n">
-        <v>1</v>
-      </c>
-      <c r="U81" t="n">
-        <v>1</v>
-      </c>
-      <c r="V81" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF81" t="n">
-        <v>3</v>
       </c>
       <c r="AG81" t="inlineStr">
         <is>
@@ -6188,7 +6215,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Reproducción sexual de las plantas con flor</t>
+          <t>Reproducción humana y pubertad</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6197,10 +6224,10 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D82" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E82" t="n">
         <v>8</v>
@@ -6209,17 +6236,14 @@
         <v>8</v>
       </c>
       <c r="G82" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H82" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I82" t="n">
         <v>4</v>
       </c>
-      <c r="K82" t="n">
-        <v>2</v>
-      </c>
       <c r="L82" t="n">
         <v>5</v>
       </c>
@@ -6241,21 +6265,21 @@
       <c r="R82" t="n">
         <v>1</v>
       </c>
-      <c r="T82" t="n">
-        <v>1</v>
-      </c>
       <c r="U82" t="n">
         <v>1</v>
       </c>
       <c r="V82" t="n">
         <v>1</v>
       </c>
+      <c r="Z82" t="n">
+        <v>1</v>
+      </c>
       <c r="AF82" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AG82" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH82" t="inlineStr">
@@ -6267,7 +6291,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Reproducción humana y pubertad</t>
+          <t>Reproducción sexual y asexual</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6276,10 +6300,10 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D83" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E83" t="n">
         <v>8</v>
@@ -6291,7 +6315,7 @@
         <v>3</v>
       </c>
       <c r="H83" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I83" t="n">
         <v>4</v>
@@ -6300,7 +6324,7 @@
         <v>5</v>
       </c>
       <c r="M83" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="N83" t="n">
         <v>1</v>
@@ -6327,11 +6351,11 @@
         <v>1</v>
       </c>
       <c r="AF83" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AG83" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH83" t="inlineStr">
@@ -6343,7 +6367,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Reproducción sexual y asexual</t>
+          <t>Requerimientos de materia y energía de la célula</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6357,32 +6381,23 @@
       <c r="D84" t="n">
         <v>6</v>
       </c>
-      <c r="E84" t="n">
-        <v>8</v>
-      </c>
-      <c r="F84" t="n">
-        <v>8</v>
-      </c>
       <c r="G84" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H84" t="n">
-        <v>3</v>
-      </c>
-      <c r="I84" t="n">
-        <v>4</v>
+        <v>7</v>
+      </c>
+      <c r="J84" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K84" t="n">
+        <v>7</v>
       </c>
       <c r="L84" t="n">
         <v>5</v>
       </c>
       <c r="M84" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N84" t="n">
-        <v>1</v>
-      </c>
-      <c r="O84" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="P84" t="n">
         <v>1</v>
@@ -6390,7 +6405,10 @@
       <c r="Q84" t="n">
         <v>1</v>
       </c>
-      <c r="R84" t="n">
+      <c r="S84" t="n">
+        <v>1</v>
+      </c>
+      <c r="T84" t="n">
         <v>1</v>
       </c>
       <c r="U84" t="n">
@@ -6407,7 +6425,7 @@
       </c>
       <c r="AG84" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH84" t="inlineStr">
@@ -6419,7 +6437,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Requerimientos de materia y energía de la célula</t>
+          <t>Antibióticos y resistencia bacteriana</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6428,28 +6446,19 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D85" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G85" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="H85" t="n">
-        <v>7</v>
-      </c>
-      <c r="J85" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K85" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L85" t="n">
-        <v>5</v>
-      </c>
-      <c r="M85" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="P85" t="n">
         <v>1</v>
@@ -6457,27 +6466,18 @@
       <c r="Q85" t="n">
         <v>1</v>
       </c>
-      <c r="S85" t="n">
-        <v>1</v>
-      </c>
-      <c r="T85" t="n">
-        <v>1</v>
-      </c>
       <c r="U85" t="n">
         <v>1</v>
       </c>
-      <c r="V85" t="n">
-        <v>1</v>
-      </c>
       <c r="Z85" t="n">
         <v>1</v>
       </c>
       <c r="AF85" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG85" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH85" t="inlineStr">
@@ -6489,7 +6489,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Antibióticos y resistencia bacteriana</t>
+          <t>Respiración celular</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6498,19 +6498,43 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D86" t="n">
-        <v>7</v>
+        <v>6</v>
+      </c>
+      <c r="E86" t="n">
+        <v>8</v>
+      </c>
+      <c r="F86" t="n">
+        <v>5</v>
       </c>
       <c r="G86" t="n">
-        <v>8.5</v>
+        <v>6</v>
       </c>
       <c r="H86" t="n">
-        <v>4</v>
+        <v>7</v>
+      </c>
+      <c r="I86" t="n">
+        <v>7</v>
+      </c>
+      <c r="J86" t="n">
+        <v>7</v>
+      </c>
+      <c r="K86" t="n">
+        <v>7</v>
       </c>
       <c r="L86" t="n">
-        <v>7.5</v>
+        <v>6</v>
+      </c>
+      <c r="M86" t="n">
+        <v>7</v>
+      </c>
+      <c r="N86" t="n">
+        <v>1</v>
+      </c>
+      <c r="O86" t="n">
+        <v>1</v>
       </c>
       <c r="P86" t="n">
         <v>1</v>
@@ -6518,14 +6542,23 @@
       <c r="Q86" t="n">
         <v>1</v>
       </c>
+      <c r="R86" t="n">
+        <v>1</v>
+      </c>
+      <c r="S86" t="n">
+        <v>1</v>
+      </c>
+      <c r="T86" t="n">
+        <v>1</v>
+      </c>
       <c r="U86" t="n">
         <v>1</v>
       </c>
-      <c r="Z86" t="n">
+      <c r="V86" t="n">
         <v>1</v>
       </c>
       <c r="AF86" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AG86" t="inlineStr">
         <is>
@@ -6541,7 +6574,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Respiración celular</t>
+          <t>Respuesta de los seres vivos a estímulos</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -6550,37 +6583,37 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D87" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E87" t="n">
         <v>8</v>
       </c>
       <c r="F87" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G87" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="H87" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I87" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J87" t="n">
         <v>7</v>
       </c>
       <c r="K87" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="L87" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M87" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="N87" t="n">
         <v>1</v>
@@ -6610,11 +6643,11 @@
         <v>1</v>
       </c>
       <c r="AF87" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AG87" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH87" t="inlineStr">
@@ -6626,7 +6659,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Respuesta de los seres vivos a estímulos</t>
+          <t>Modelo estímulo-respuesta y retroalimentación negativa</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -6635,10 +6668,7 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>2</v>
-      </c>
-      <c r="D88" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E88" t="n">
         <v>8</v>
@@ -6650,22 +6680,16 @@
         <v>8.5</v>
       </c>
       <c r="H88" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I88" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J88" t="n">
         <v>7</v>
       </c>
-      <c r="K88" t="n">
-        <v>2</v>
-      </c>
-      <c r="L88" t="n">
-        <v>3</v>
-      </c>
       <c r="M88" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="N88" t="n">
         <v>1</v>
@@ -6685,21 +6709,15 @@
       <c r="S88" t="n">
         <v>1</v>
       </c>
-      <c r="T88" t="n">
-        <v>1</v>
-      </c>
-      <c r="U88" t="n">
-        <v>1</v>
-      </c>
       <c r="V88" t="n">
         <v>1</v>
       </c>
       <c r="AF88" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="AG88" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH88" t="inlineStr">
@@ -6711,7 +6729,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Modelo estímulo-respuesta y retroalimentación negativa</t>
+          <t>Selección natural</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -6720,31 +6738,22 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>9</v>
-      </c>
-      <c r="E89" t="n">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="D89" t="n">
+        <v>7</v>
       </c>
       <c r="F89" t="n">
         <v>8</v>
       </c>
       <c r="G89" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="H89" t="n">
-        <v>7</v>
-      </c>
-      <c r="I89" t="n">
-        <v>7</v>
-      </c>
-      <c r="J89" t="n">
-        <v>7</v>
-      </c>
-      <c r="M89" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="N89" t="n">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="K89" t="n">
+        <v>5</v>
+      </c>
+      <c r="L89" t="n">
+        <v>6</v>
       </c>
       <c r="O89" t="n">
         <v>1</v>
@@ -6752,20 +6761,17 @@
       <c r="P89" t="n">
         <v>1</v>
       </c>
-      <c r="Q89" t="n">
-        <v>1</v>
-      </c>
-      <c r="R89" t="n">
-        <v>1</v>
-      </c>
-      <c r="S89" t="n">
-        <v>1</v>
-      </c>
-      <c r="V89" t="n">
+      <c r="T89" t="n">
+        <v>1</v>
+      </c>
+      <c r="U89" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z89" t="n">
         <v>1</v>
       </c>
       <c r="AF89" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AG89" t="inlineStr">
         <is>
@@ -6781,7 +6787,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Selección natural</t>
+          <t>Seres vivos y no vivos</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -6790,22 +6796,31 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D90" t="n">
-        <v>7</v>
+        <v>2</v>
+      </c>
+      <c r="E90" t="n">
+        <v>2</v>
       </c>
       <c r="F90" t="n">
-        <v>8</v>
+        <v>2.5</v>
       </c>
       <c r="G90" t="n">
-        <v>4</v>
-      </c>
-      <c r="K90" t="n">
-        <v>5</v>
+        <v>2</v>
+      </c>
+      <c r="H90" t="n">
+        <v>2</v>
       </c>
       <c r="L90" t="n">
-        <v>6</v>
+        <v>3</v>
+      </c>
+      <c r="M90" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N90" t="n">
+        <v>1</v>
       </c>
       <c r="O90" t="n">
         <v>1</v>
@@ -6813,17 +6828,17 @@
       <c r="P90" t="n">
         <v>1</v>
       </c>
-      <c r="T90" t="n">
+      <c r="Q90" t="n">
         <v>1</v>
       </c>
       <c r="U90" t="n">
         <v>1</v>
       </c>
-      <c r="Z90" t="n">
+      <c r="V90" t="n">
         <v>1</v>
       </c>
       <c r="AF90" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AG90" t="inlineStr">
         <is>
@@ -6839,7 +6854,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Seres vivos y no vivos</t>
+          <t>Sistema circulatorio</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -6848,31 +6863,34 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D91" t="n">
-        <v>2</v>
-      </c>
-      <c r="E91" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F91" t="n">
-        <v>2.5</v>
+        <v>8</v>
       </c>
       <c r="G91" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H91" t="n">
         <v>2</v>
       </c>
+      <c r="I91" t="n">
+        <v>5</v>
+      </c>
+      <c r="J91" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K91" t="n">
+        <v>4</v>
+      </c>
       <c r="L91" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M91" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N91" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O91" t="n">
         <v>1</v>
@@ -6883,14 +6901,26 @@
       <c r="Q91" t="n">
         <v>1</v>
       </c>
+      <c r="R91" t="n">
+        <v>1</v>
+      </c>
+      <c r="S91" t="n">
+        <v>1</v>
+      </c>
+      <c r="T91" t="n">
+        <v>1</v>
+      </c>
       <c r="U91" t="n">
         <v>1</v>
       </c>
       <c r="V91" t="n">
         <v>1</v>
       </c>
+      <c r="Z91" t="n">
+        <v>1</v>
+      </c>
       <c r="AF91" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AG91" t="inlineStr">
         <is>
@@ -6906,7 +6936,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Sistema circulatorio</t>
+          <t>Sistema digestivo</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6924,10 +6954,10 @@
         <v>8</v>
       </c>
       <c r="G92" t="n">
+        <v>2</v>
+      </c>
+      <c r="H92" t="n">
         <v>4</v>
-      </c>
-      <c r="H92" t="n">
-        <v>2</v>
       </c>
       <c r="I92" t="n">
         <v>5</v>
@@ -6988,7 +7018,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Sistema digestivo</t>
+          <t>Sistema endocrino y hormonas</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6997,53 +7027,38 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>4</v>
-      </c>
-      <c r="D93" t="n">
-        <v>4</v>
+        <v>9</v>
+      </c>
+      <c r="E93" t="n">
+        <v>8</v>
       </c>
       <c r="F93" t="n">
         <v>8</v>
       </c>
       <c r="G93" t="n">
-        <v>2</v>
-      </c>
-      <c r="H93" t="n">
-        <v>4</v>
-      </c>
-      <c r="I93" t="n">
-        <v>5</v>
+        <v>8.5</v>
       </c>
       <c r="J93" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K93" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L93" t="n">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="M93" t="n">
         <v>7</v>
       </c>
+      <c r="N93" t="n">
+        <v>1</v>
+      </c>
       <c r="O93" t="n">
         <v>1</v>
       </c>
       <c r="P93" t="n">
         <v>1</v>
       </c>
-      <c r="Q93" t="n">
-        <v>1</v>
-      </c>
-      <c r="R93" t="n">
-        <v>1</v>
-      </c>
       <c r="S93" t="n">
         <v>1</v>
       </c>
-      <c r="T93" t="n">
-        <v>1</v>
-      </c>
       <c r="U93" t="n">
         <v>1</v>
       </c>
@@ -7054,7 +7069,7 @@
         <v>1</v>
       </c>
       <c r="AF93" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AG93" t="inlineStr">
         <is>
@@ -7070,7 +7085,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Sistema endocrino y hormonas</t>
+          <t>Sistema locomotor</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7079,28 +7094,28 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>9</v>
-      </c>
-      <c r="E94" t="n">
-        <v>8</v>
+        <v>4</v>
+      </c>
+      <c r="D94" t="n">
+        <v>4</v>
       </c>
       <c r="F94" t="n">
         <v>8</v>
       </c>
       <c r="G94" t="n">
-        <v>8.5</v>
+        <v>2</v>
+      </c>
+      <c r="H94" t="n">
+        <v>2</v>
+      </c>
+      <c r="I94" t="n">
+        <v>3</v>
       </c>
       <c r="J94" t="n">
-        <v>7</v>
-      </c>
-      <c r="L94" t="n">
-        <v>7.5</v>
+        <v>4.5</v>
       </c>
       <c r="M94" t="n">
-        <v>7</v>
-      </c>
-      <c r="N94" t="n">
-        <v>1</v>
+        <v>4.5</v>
       </c>
       <c r="O94" t="n">
         <v>1</v>
@@ -7108,20 +7123,20 @@
       <c r="P94" t="n">
         <v>1</v>
       </c>
+      <c r="Q94" t="n">
+        <v>1</v>
+      </c>
+      <c r="R94" t="n">
+        <v>1</v>
+      </c>
       <c r="S94" t="n">
         <v>1</v>
       </c>
-      <c r="U94" t="n">
-        <v>1</v>
-      </c>
       <c r="V94" t="n">
         <v>1</v>
       </c>
-      <c r="Z94" t="n">
-        <v>1</v>
-      </c>
       <c r="AF94" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="AG94" t="inlineStr">
         <is>
@@ -7137,7 +7152,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Sistema locomotor</t>
+          <t>Sistema respiratorio</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7146,28 +7161,34 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D95" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F95" t="n">
         <v>8</v>
       </c>
       <c r="G95" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H95" t="n">
         <v>2</v>
       </c>
       <c r="I95" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J95" t="n">
         <v>4.5</v>
       </c>
+      <c r="K95" t="n">
+        <v>4</v>
+      </c>
+      <c r="L95" t="n">
+        <v>4</v>
+      </c>
       <c r="M95" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="O95" t="n">
         <v>1</v>
@@ -7184,7 +7205,16 @@
       <c r="S95" t="n">
         <v>1</v>
       </c>
+      <c r="T95" t="n">
+        <v>1</v>
+      </c>
+      <c r="U95" t="n">
+        <v>1</v>
+      </c>
       <c r="V95" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z95" t="n">
         <v>1</v>
       </c>
       <c r="AF95" t="n">
@@ -7192,7 +7222,7 @@
       </c>
       <c r="AG95" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH95" t="inlineStr">
@@ -7204,7 +7234,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Sistema respiratorio</t>
+          <t>Tejidos animales</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7213,34 +7243,25 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D96" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="E96" t="n">
+        <v>7</v>
       </c>
       <c r="F96" t="n">
         <v>8</v>
       </c>
       <c r="G96" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="H96" t="n">
-        <v>2</v>
-      </c>
-      <c r="I96" t="n">
-        <v>5</v>
-      </c>
-      <c r="J96" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K96" t="n">
-        <v>4</v>
-      </c>
-      <c r="L96" t="n">
-        <v>4</v>
-      </c>
-      <c r="M96" t="n">
-        <v>7</v>
+        <v>7</v>
+      </c>
+      <c r="N96" t="n">
+        <v>1</v>
       </c>
       <c r="O96" t="n">
         <v>1</v>
@@ -7249,21 +7270,6 @@
         <v>1</v>
       </c>
       <c r="Q96" t="n">
-        <v>1</v>
-      </c>
-      <c r="R96" t="n">
-        <v>1</v>
-      </c>
-      <c r="S96" t="n">
-        <v>1</v>
-      </c>
-      <c r="T96" t="n">
-        <v>1</v>
-      </c>
-      <c r="U96" t="n">
-        <v>1</v>
-      </c>
-      <c r="V96" t="n">
         <v>1</v>
       </c>
       <c r="Z96" t="n">
@@ -7274,19 +7280,19 @@
       </c>
       <c r="AG96" t="inlineStr">
         <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+      <c r="AH96" t="inlineStr">
+        <is>
           <t>adelantado</t>
-        </is>
-      </c>
-      <c r="AH96" t="inlineStr">
-        <is>
-          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Tejidos animales</t>
+          <t>Tejidos vegetales</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7295,10 +7301,10 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D97" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E97" t="n">
         <v>7</v>
@@ -7312,6 +7318,15 @@
       <c r="H97" t="n">
         <v>7</v>
       </c>
+      <c r="J97" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L97" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="M97" t="n">
+        <v>7</v>
+      </c>
       <c r="N97" t="n">
         <v>1</v>
       </c>
@@ -7324,27 +7339,33 @@
       <c r="Q97" t="n">
         <v>1</v>
       </c>
-      <c r="Z97" t="n">
+      <c r="S97" t="n">
+        <v>1</v>
+      </c>
+      <c r="U97" t="n">
+        <v>1</v>
+      </c>
+      <c r="V97" t="n">
         <v>1</v>
       </c>
       <c r="AF97" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AG97" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Tejidos vegetales</t>
+          <t>Transporte en plantas: xilema y floema</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -7353,42 +7374,36 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D98" t="n">
-        <v>8</v>
-      </c>
-      <c r="E98" t="n">
-        <v>7</v>
-      </c>
-      <c r="F98" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G98" t="n">
-        <v>8.5</v>
+        <v>2</v>
       </c>
       <c r="H98" t="n">
         <v>7</v>
+      </c>
+      <c r="I98" t="n">
+        <v>5</v>
       </c>
       <c r="J98" t="n">
         <v>4.5</v>
       </c>
       <c r="L98" t="n">
-        <v>7.5</v>
+        <v>5</v>
       </c>
       <c r="M98" t="n">
         <v>7</v>
       </c>
-      <c r="N98" t="n">
-        <v>1</v>
-      </c>
-      <c r="O98" t="n">
-        <v>1</v>
-      </c>
       <c r="P98" t="n">
         <v>1</v>
       </c>
       <c r="Q98" t="n">
+        <v>1</v>
+      </c>
+      <c r="R98" t="n">
         <v>1</v>
       </c>
       <c r="S98" t="n">
@@ -7417,7 +7432,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Transporte en plantas: xilema y floema</t>
+          <t>Variación genética en la descendencia</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -7431,23 +7446,29 @@
       <c r="D99" t="n">
         <v>6</v>
       </c>
+      <c r="F99" t="n">
+        <v>8</v>
+      </c>
       <c r="G99" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H99" t="n">
         <v>7</v>
       </c>
       <c r="I99" t="n">
+        <v>8</v>
+      </c>
+      <c r="K99" t="n">
         <v>5</v>
       </c>
-      <c r="J99" t="n">
+      <c r="L99" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="M99" t="n">
         <v>4.5</v>
       </c>
-      <c r="L99" t="n">
-        <v>5</v>
-      </c>
-      <c r="M99" t="n">
-        <v>7</v>
+      <c r="O99" t="n">
+        <v>1</v>
       </c>
       <c r="P99" t="n">
         <v>1</v>
@@ -7458,7 +7479,7 @@
       <c r="R99" t="n">
         <v>1</v>
       </c>
-      <c r="S99" t="n">
+      <c r="T99" t="n">
         <v>1</v>
       </c>
       <c r="U99" t="n">
@@ -7468,7 +7489,7 @@
         <v>1</v>
       </c>
       <c r="AF99" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AG99" t="inlineStr">
         <is>
@@ -7484,80 +7505,41 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Variación genética en la descendencia</t>
+          <t>Especies clave</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>incierto</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D100" t="n">
-        <v>6</v>
-      </c>
-      <c r="F100" t="n">
-        <v>8</v>
-      </c>
-      <c r="G100" t="n">
-        <v>4</v>
-      </c>
-      <c r="H100" t="n">
-        <v>7</v>
-      </c>
-      <c r="I100" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K100" t="n">
-        <v>5</v>
-      </c>
-      <c r="L100" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="M100" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O100" t="n">
-        <v>1</v>
-      </c>
-      <c r="P100" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q100" t="n">
-        <v>1</v>
-      </c>
-      <c r="R100" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T100" t="n">
         <v>1</v>
       </c>
-      <c r="U100" t="n">
-        <v>1</v>
-      </c>
-      <c r="V100" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF100" t="n">
-        <v>7</v>
-      </c>
       <c r="AG100" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH100" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>no_aplica</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Especies clave</t>
+          <t>Niveles de organización ecológica</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -7566,32 +7548,71 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D101" t="n">
-        <v>7</v>
+        <v>4</v>
+      </c>
+      <c r="F101" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G101" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H101" t="n">
+        <v>3</v>
+      </c>
+      <c r="J101" t="n">
+        <v>2.5</v>
       </c>
       <c r="K101" t="n">
         <v>3</v>
       </c>
+      <c r="L101" t="n">
+        <v>6</v>
+      </c>
+      <c r="M101" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O101" t="n">
+        <v>1</v>
+      </c>
+      <c r="P101" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q101" t="n">
+        <v>1</v>
+      </c>
+      <c r="S101" t="n">
+        <v>1</v>
+      </c>
       <c r="T101" t="n">
         <v>1</v>
       </c>
+      <c r="U101" t="n">
+        <v>1</v>
+      </c>
+      <c r="V101" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF101" t="n">
+        <v>4</v>
+      </c>
       <c r="AG101" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
-          <t>no_aplica</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Niveles de organización ecológica</t>
+          <t>Plantas y animales útiles al ser humano</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -7600,10 +7621,10 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D102" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F102" t="n">
         <v>2.5</v>
@@ -7612,19 +7633,16 @@
         <v>8.5</v>
       </c>
       <c r="H102" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J102" t="n">
         <v>2.5</v>
       </c>
       <c r="K102" t="n">
-        <v>3</v>
-      </c>
-      <c r="L102" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M102" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="O102" t="n">
         <v>1</v>
@@ -7641,14 +7659,11 @@
       <c r="T102" t="n">
         <v>1</v>
       </c>
-      <c r="U102" t="n">
-        <v>1</v>
-      </c>
       <c r="V102" t="n">
         <v>1</v>
       </c>
       <c r="AF102" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AG102" t="inlineStr">
         <is>
@@ -7664,74 +7679,53 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Plantas y animales útiles al ser humano</t>
+          <t>Adaptaciones fisiológicas</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>2</v>
-      </c>
-      <c r="D103" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F103" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="G103" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="H103" t="n">
-        <v>2</v>
-      </c>
-      <c r="J103" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="K103" t="n">
-        <v>2</v>
-      </c>
-      <c r="M103" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="O103" t="n">
         <v>1</v>
       </c>
-      <c r="P103" t="n">
-        <v>1</v>
-      </c>
       <c r="Q103" t="n">
         <v>1</v>
       </c>
-      <c r="S103" t="n">
-        <v>1</v>
-      </c>
       <c r="T103" t="n">
         <v>1</v>
       </c>
-      <c r="V103" t="n">
-        <v>1</v>
-      </c>
       <c r="AF103" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="AG103" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>posterior</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Adaptaciones fisiológicas</t>
+          <t>Capacidad de carga</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -7740,28 +7734,16 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>10</v>
-      </c>
-      <c r="F104" t="n">
-        <v>8</v>
-      </c>
-      <c r="H104" t="n">
+        <v>11</v>
+      </c>
+      <c r="K104" t="n">
         <v>3</v>
       </c>
-      <c r="K104" t="n">
-        <v>5</v>
-      </c>
-      <c r="O104" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q104" t="n">
-        <v>1</v>
-      </c>
       <c r="T104" t="n">
         <v>1</v>
       </c>
       <c r="AF104" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG104" t="inlineStr">
         <is>
@@ -7777,7 +7759,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Capacidad de carga</t>
+          <t>Ciclo del nitrógeno</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -7786,16 +7768,28 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>11</v>
+        <v>9</v>
+      </c>
+      <c r="F105" t="n">
+        <v>8</v>
+      </c>
+      <c r="G105" t="n">
+        <v>8.5</v>
       </c>
       <c r="K105" t="n">
-        <v>3</v>
+        <v>6</v>
+      </c>
+      <c r="O105" t="n">
+        <v>1</v>
+      </c>
+      <c r="P105" t="n">
+        <v>1</v>
       </c>
       <c r="T105" t="n">
         <v>1</v>
       </c>
       <c r="AF105" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AG105" t="inlineStr">
         <is>
@@ -7811,7 +7805,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Ciclo del nitrógeno</t>
+          <t>Ciclos del fósforo y del azufre</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -7820,32 +7814,17 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>9</v>
-      </c>
-      <c r="F106" t="n">
         <v>8</v>
       </c>
-      <c r="G106" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="K106" t="n">
-        <v>6</v>
-      </c>
-      <c r="O106" t="n">
-        <v>1</v>
-      </c>
-      <c r="P106" t="n">
-        <v>1</v>
-      </c>
-      <c r="T106" t="n">
-        <v>1</v>
+      <c r="D106" t="n">
+        <v>8</v>
       </c>
       <c r="AF106" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG106" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH106" t="inlineStr">
@@ -7857,7 +7836,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Ciclos del fósforo y del azufre</t>
+          <t>Propagación de enfermedades y control de brotes</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -7866,22 +7845,43 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>8</v>
-      </c>
-      <c r="D107" t="n">
-        <v>8</v>
-      </c>
-      <c r="AF107" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="G107" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H107" t="n">
+        <v>3</v>
+      </c>
+      <c r="J107" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L107" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="P107" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q107" t="n">
+        <v>1</v>
+      </c>
+      <c r="S107" t="n">
+        <v>1</v>
+      </c>
+      <c r="U107" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z107" t="n">
+        <v>1</v>
       </c>
       <c r="AG107" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>no_aplica</t>
         </is>
       </c>
     </row>

--- a/internacional/2_8/Contraste_biologia.xlsx
+++ b/internacional/2_8/Contraste_biologia.xlsx
@@ -3117,10 +3117,10 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D38" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E38" t="n">
         <v>8</v>
@@ -3171,16 +3171,16 @@
         <v>1</v>
       </c>
       <c r="AF38" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AG38" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>tardio</t>
         </is>
       </c>
     </row>
@@ -7845,7 +7845,7 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G107" t="n">
         <v>8.5</v>
@@ -7874,6 +7874,9 @@
       <c r="Z107" t="n">
         <v>1</v>
       </c>
+      <c r="AF107" t="n">
+        <v>9</v>
+      </c>
       <c r="AG107" t="inlineStr">
         <is>
           <t>posterior</t>
@@ -7881,7 +7884,7 @@
       </c>
       <c r="AH107" t="inlineStr">
         <is>
-          <t>no_aplica</t>
+          <t>posterior</t>
         </is>
       </c>
     </row>

--- a/internacional/2_8/Contraste_biologia.xlsx
+++ b/internacional/2_8/Contraste_biologia.xlsx
@@ -5820,7 +5820,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Nutrición autótrofa y heterótrofa</t>
+          <t>Niveles de organización ecológica</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5829,34 +5829,31 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D77" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F77" t="n">
         <v>2.5</v>
       </c>
       <c r="G77" t="n">
-        <v>2</v>
+        <v>8.5</v>
       </c>
       <c r="H77" t="n">
-        <v>2</v>
-      </c>
-      <c r="I77" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J77" t="n">
         <v>2.5</v>
       </c>
       <c r="K77" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L77" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M77" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="O77" t="n">
         <v>1</v>
@@ -5867,9 +5864,6 @@
       <c r="Q77" t="n">
         <v>1</v>
       </c>
-      <c r="R77" t="n">
-        <v>1</v>
-      </c>
       <c r="S77" t="n">
         <v>1</v>
       </c>
@@ -5883,7 +5877,7 @@
         <v>1</v>
       </c>
       <c r="AF77" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG77" t="inlineStr">
         <is>
@@ -5899,7 +5893,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Órganos de los sentidos</t>
+          <t>Nutrición autótrofa y heterótrofa</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5908,13 +5902,13 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D78" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F78" t="n">
-        <v>8</v>
+        <v>2.5</v>
       </c>
       <c r="G78" t="n">
         <v>2</v>
@@ -5923,13 +5917,19 @@
         <v>2</v>
       </c>
       <c r="I78" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J78" t="n">
-        <v>7</v>
+        <v>2.5</v>
+      </c>
+      <c r="K78" t="n">
+        <v>2</v>
+      </c>
+      <c r="L78" t="n">
+        <v>5</v>
       </c>
       <c r="M78" t="n">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="O78" t="n">
         <v>1</v>
@@ -5946,15 +5946,21 @@
       <c r="S78" t="n">
         <v>1</v>
       </c>
+      <c r="T78" t="n">
+        <v>1</v>
+      </c>
+      <c r="U78" t="n">
+        <v>1</v>
+      </c>
       <c r="V78" t="n">
         <v>1</v>
       </c>
       <c r="AF78" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AG78" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH78" t="inlineStr">
@@ -5966,7 +5972,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Partes de la planta y sus funciones</t>
+          <t>Órganos de los sentidos</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5975,16 +5981,13 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D79" t="n">
-        <v>2</v>
-      </c>
-      <c r="E79" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F79" t="n">
-        <v>2.5</v>
+        <v>8</v>
       </c>
       <c r="G79" t="n">
         <v>2</v>
@@ -5993,23 +5996,14 @@
         <v>2</v>
       </c>
       <c r="I79" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J79" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K79" t="n">
-        <v>2</v>
-      </c>
-      <c r="L79" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M79" t="n">
         <v>2.5</v>
       </c>
-      <c r="N79" t="n">
-        <v>1</v>
-      </c>
       <c r="O79" t="n">
         <v>1</v>
       </c>
@@ -6025,17 +6019,11 @@
       <c r="S79" t="n">
         <v>1</v>
       </c>
-      <c r="T79" t="n">
-        <v>1</v>
-      </c>
-      <c r="U79" t="n">
-        <v>1</v>
-      </c>
       <c r="V79" t="n">
         <v>1</v>
       </c>
       <c r="AF79" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AG79" t="inlineStr">
         <is>
@@ -6051,7 +6039,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Productores, consumidores y descomponedores</t>
+          <t>Partes de la planta y sus funciones</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6060,13 +6048,13 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D80" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E80" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F80" t="n">
         <v>2.5</v>
@@ -6075,10 +6063,10 @@
         <v>2</v>
       </c>
       <c r="H80" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I80" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J80" t="n">
         <v>2.5</v>
@@ -6087,10 +6075,10 @@
         <v>2</v>
       </c>
       <c r="L80" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M80" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="N80" t="n">
         <v>1</v>
@@ -6120,7 +6108,7 @@
         <v>1</v>
       </c>
       <c r="AF80" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AG80" t="inlineStr">
         <is>
@@ -6136,7 +6124,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Reproducción sexual de las plantas con flor</t>
+          <t>Plantas y animales útiles al ser humano</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6145,37 +6133,28 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D81" t="n">
-        <v>6</v>
-      </c>
-      <c r="E81" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F81" t="n">
-        <v>8</v>
+        <v>2.5</v>
       </c>
       <c r="G81" t="n">
-        <v>2</v>
+        <v>8.5</v>
       </c>
       <c r="H81" t="n">
         <v>2</v>
       </c>
-      <c r="I81" t="n">
-        <v>4</v>
+      <c r="J81" t="n">
+        <v>2.5</v>
       </c>
       <c r="K81" t="n">
         <v>2</v>
       </c>
-      <c r="L81" t="n">
-        <v>5</v>
-      </c>
       <c r="M81" t="n">
-        <v>7</v>
-      </c>
-      <c r="N81" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="O81" t="n">
         <v>1</v>
@@ -6186,24 +6165,21 @@
       <c r="Q81" t="n">
         <v>1</v>
       </c>
-      <c r="R81" t="n">
+      <c r="S81" t="n">
         <v>1</v>
       </c>
       <c r="T81" t="n">
         <v>1</v>
       </c>
-      <c r="U81" t="n">
-        <v>1</v>
-      </c>
       <c r="V81" t="n">
         <v>1</v>
       </c>
       <c r="AF81" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AG81" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH81" t="inlineStr">
@@ -6215,7 +6191,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Reproducción humana y pubertad</t>
+          <t>Productores, consumidores y descomponedores</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6224,62 +6200,71 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D82" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E82" t="n">
+        <v>3</v>
+      </c>
+      <c r="F82" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G82" t="n">
+        <v>2</v>
+      </c>
+      <c r="H82" t="n">
+        <v>3</v>
+      </c>
+      <c r="I82" t="n">
         <v>8</v>
       </c>
-      <c r="F82" t="n">
-        <v>8</v>
-      </c>
-      <c r="G82" t="n">
+      <c r="J82" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K82" t="n">
+        <v>2</v>
+      </c>
+      <c r="L82" t="n">
+        <v>6</v>
+      </c>
+      <c r="M82" t="n">
+        <v>7</v>
+      </c>
+      <c r="N82" t="n">
+        <v>1</v>
+      </c>
+      <c r="O82" t="n">
+        <v>1</v>
+      </c>
+      <c r="P82" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>1</v>
+      </c>
+      <c r="R82" t="n">
+        <v>1</v>
+      </c>
+      <c r="S82" t="n">
+        <v>1</v>
+      </c>
+      <c r="T82" t="n">
+        <v>1</v>
+      </c>
+      <c r="U82" t="n">
+        <v>1</v>
+      </c>
+      <c r="V82" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF82" t="n">
         <v>3</v>
       </c>
-      <c r="H82" t="n">
-        <v>4</v>
-      </c>
-      <c r="I82" t="n">
-        <v>4</v>
-      </c>
-      <c r="L82" t="n">
-        <v>5</v>
-      </c>
-      <c r="M82" t="n">
-        <v>7</v>
-      </c>
-      <c r="N82" t="n">
-        <v>1</v>
-      </c>
-      <c r="O82" t="n">
-        <v>1</v>
-      </c>
-      <c r="P82" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q82" t="n">
-        <v>1</v>
-      </c>
-      <c r="R82" t="n">
-        <v>1</v>
-      </c>
-      <c r="U82" t="n">
-        <v>1</v>
-      </c>
-      <c r="V82" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z82" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF82" t="n">
-        <v>4</v>
-      </c>
       <c r="AG82" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH82" t="inlineStr">
@@ -6291,7 +6276,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Reproducción sexual y asexual</t>
+          <t>Reproducción sexual de las plantas con flor</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6312,19 +6297,22 @@
         <v>8</v>
       </c>
       <c r="G83" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H83" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I83" t="n">
         <v>4</v>
       </c>
+      <c r="K83" t="n">
+        <v>2</v>
+      </c>
       <c r="L83" t="n">
         <v>5</v>
       </c>
       <c r="M83" t="n">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="N83" t="n">
         <v>1</v>
@@ -6341,13 +6329,13 @@
       <c r="R83" t="n">
         <v>1</v>
       </c>
+      <c r="T83" t="n">
+        <v>1</v>
+      </c>
       <c r="U83" t="n">
         <v>1</v>
       </c>
       <c r="V83" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z83" t="n">
         <v>1</v>
       </c>
       <c r="AF83" t="n">
@@ -6367,7 +6355,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Requerimientos de materia y energía de la célula</t>
+          <t>Reproducción humana y pubertad</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6376,22 +6364,25 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D84" t="n">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="E84" t="n">
+        <v>8</v>
+      </c>
+      <c r="F84" t="n">
+        <v>8</v>
       </c>
       <c r="G84" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H84" t="n">
-        <v>7</v>
-      </c>
-      <c r="J84" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K84" t="n">
-        <v>7</v>
+        <v>4</v>
+      </c>
+      <c r="I84" t="n">
+        <v>4</v>
       </c>
       <c r="L84" t="n">
         <v>5</v>
@@ -6399,16 +6390,19 @@
       <c r="M84" t="n">
         <v>7</v>
       </c>
+      <c r="N84" t="n">
+        <v>1</v>
+      </c>
+      <c r="O84" t="n">
+        <v>1</v>
+      </c>
       <c r="P84" t="n">
         <v>1</v>
       </c>
       <c r="Q84" t="n">
         <v>1</v>
       </c>
-      <c r="S84" t="n">
-        <v>1</v>
-      </c>
-      <c r="T84" t="n">
+      <c r="R84" t="n">
         <v>1</v>
       </c>
       <c r="U84" t="n">
@@ -6421,11 +6415,11 @@
         <v>1</v>
       </c>
       <c r="AF84" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AG84" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH84" t="inlineStr">
@@ -6437,7 +6431,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Antibióticos y resistencia bacteriana</t>
+          <t>Reproducción sexual y asexual</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6446,19 +6440,37 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D85" t="n">
-        <v>7</v>
+        <v>6</v>
+      </c>
+      <c r="E85" t="n">
+        <v>8</v>
+      </c>
+      <c r="F85" t="n">
+        <v>8</v>
       </c>
       <c r="G85" t="n">
-        <v>8.5</v>
+        <v>3</v>
       </c>
       <c r="H85" t="n">
+        <v>3</v>
+      </c>
+      <c r="I85" t="n">
         <v>4</v>
       </c>
       <c r="L85" t="n">
-        <v>7.5</v>
+        <v>5</v>
+      </c>
+      <c r="M85" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N85" t="n">
+        <v>1</v>
+      </c>
+      <c r="O85" t="n">
+        <v>1</v>
       </c>
       <c r="P85" t="n">
         <v>1</v>
@@ -6466,14 +6478,20 @@
       <c r="Q85" t="n">
         <v>1</v>
       </c>
+      <c r="R85" t="n">
+        <v>1</v>
+      </c>
       <c r="U85" t="n">
         <v>1</v>
       </c>
+      <c r="V85" t="n">
+        <v>1</v>
+      </c>
       <c r="Z85" t="n">
         <v>1</v>
       </c>
       <c r="AF85" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AG85" t="inlineStr">
         <is>
@@ -6489,7 +6507,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Respiración celular</t>
+          <t>Requerimientos de materia y energía de la célula</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6503,48 +6521,30 @@
       <c r="D86" t="n">
         <v>6</v>
       </c>
-      <c r="E86" t="n">
-        <v>8</v>
-      </c>
-      <c r="F86" t="n">
-        <v>5</v>
-      </c>
       <c r="G86" t="n">
         <v>6</v>
       </c>
       <c r="H86" t="n">
         <v>7</v>
       </c>
-      <c r="I86" t="n">
-        <v>7</v>
-      </c>
       <c r="J86" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="K86" t="n">
         <v>7</v>
       </c>
       <c r="L86" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M86" t="n">
         <v>7</v>
       </c>
-      <c r="N86" t="n">
-        <v>1</v>
-      </c>
-      <c r="O86" t="n">
-        <v>1</v>
-      </c>
       <c r="P86" t="n">
         <v>1</v>
       </c>
       <c r="Q86" t="n">
         <v>1</v>
       </c>
-      <c r="R86" t="n">
-        <v>1</v>
-      </c>
       <c r="S86" t="n">
         <v>1</v>
       </c>
@@ -6555,6 +6555,9 @@
         <v>1</v>
       </c>
       <c r="V86" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z86" t="n">
         <v>1</v>
       </c>
       <c r="AF86" t="n">
@@ -6562,7 +6565,7 @@
       </c>
       <c r="AG86" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH86" t="inlineStr">
@@ -6574,7 +6577,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Respuesta de los seres vivos a estímulos</t>
+          <t>Antibióticos y resistencia bacteriana</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -6583,43 +6586,19 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D87" t="n">
-        <v>2</v>
-      </c>
-      <c r="E87" t="n">
-        <v>8</v>
-      </c>
-      <c r="F87" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G87" t="n">
         <v>8.5</v>
       </c>
       <c r="H87" t="n">
-        <v>2</v>
-      </c>
-      <c r="I87" t="n">
-        <v>3</v>
-      </c>
-      <c r="J87" t="n">
-        <v>7</v>
-      </c>
-      <c r="K87" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L87" t="n">
-        <v>3</v>
-      </c>
-      <c r="M87" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N87" t="n">
-        <v>1</v>
-      </c>
-      <c r="O87" t="n">
-        <v>1</v>
+        <v>7.5</v>
       </c>
       <c r="P87" t="n">
         <v>1</v>
@@ -6627,27 +6606,18 @@
       <c r="Q87" t="n">
         <v>1</v>
       </c>
-      <c r="R87" t="n">
-        <v>1</v>
-      </c>
-      <c r="S87" t="n">
-        <v>1</v>
-      </c>
-      <c r="T87" t="n">
-        <v>1</v>
-      </c>
       <c r="U87" t="n">
         <v>1</v>
       </c>
-      <c r="V87" t="n">
+      <c r="Z87" t="n">
         <v>1</v>
       </c>
       <c r="AF87" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AG87" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH87" t="inlineStr">
@@ -6659,7 +6629,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Modelo estímulo-respuesta y retroalimentación negativa</t>
+          <t>Respiración celular</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -6668,16 +6638,19 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>9</v>
+        <v>6</v>
+      </c>
+      <c r="D88" t="n">
+        <v>6</v>
       </c>
       <c r="E88" t="n">
         <v>8</v>
       </c>
       <c r="F88" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G88" t="n">
-        <v>8.5</v>
+        <v>6</v>
       </c>
       <c r="H88" t="n">
         <v>7</v>
@@ -6688,8 +6661,14 @@
       <c r="J88" t="n">
         <v>7</v>
       </c>
+      <c r="K88" t="n">
+        <v>7</v>
+      </c>
+      <c r="L88" t="n">
+        <v>6</v>
+      </c>
       <c r="M88" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="N88" t="n">
         <v>1</v>
@@ -6709,11 +6688,17 @@
       <c r="S88" t="n">
         <v>1</v>
       </c>
+      <c r="T88" t="n">
+        <v>1</v>
+      </c>
+      <c r="U88" t="n">
+        <v>1</v>
+      </c>
       <c r="V88" t="n">
         <v>1</v>
       </c>
       <c r="AF88" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AG88" t="inlineStr">
         <is>
@@ -6729,7 +6714,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Selección natural</t>
+          <t>Respuesta de los seres vivos a estímulos</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -6738,22 +6723,40 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D89" t="n">
-        <v>7</v>
+        <v>2</v>
+      </c>
+      <c r="E89" t="n">
+        <v>8</v>
       </c>
       <c r="F89" t="n">
         <v>8</v>
       </c>
       <c r="G89" t="n">
-        <v>4</v>
+        <v>8.5</v>
+      </c>
+      <c r="H89" t="n">
+        <v>2</v>
+      </c>
+      <c r="I89" t="n">
+        <v>3</v>
+      </c>
+      <c r="J89" t="n">
+        <v>7</v>
       </c>
       <c r="K89" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L89" t="n">
-        <v>6</v>
+        <v>3</v>
+      </c>
+      <c r="M89" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N89" t="n">
+        <v>1</v>
       </c>
       <c r="O89" t="n">
         <v>1</v>
@@ -6761,21 +6764,30 @@
       <c r="P89" t="n">
         <v>1</v>
       </c>
+      <c r="Q89" t="n">
+        <v>1</v>
+      </c>
+      <c r="R89" t="n">
+        <v>1</v>
+      </c>
+      <c r="S89" t="n">
+        <v>1</v>
+      </c>
       <c r="T89" t="n">
         <v>1</v>
       </c>
       <c r="U89" t="n">
         <v>1</v>
       </c>
-      <c r="Z89" t="n">
+      <c r="V89" t="n">
         <v>1</v>
       </c>
       <c r="AF89" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AG89" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH89" t="inlineStr">
@@ -6787,7 +6799,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Seres vivos y no vivos</t>
+          <t>Modelo estímulo-respuesta y retroalimentación negativa</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -6796,28 +6808,28 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>2</v>
-      </c>
-      <c r="D90" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E90" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F90" t="n">
-        <v>2.5</v>
+        <v>8</v>
       </c>
       <c r="G90" t="n">
-        <v>2</v>
+        <v>8.5</v>
       </c>
       <c r="H90" t="n">
-        <v>2</v>
-      </c>
-      <c r="L90" t="n">
-        <v>3</v>
+        <v>7</v>
+      </c>
+      <c r="I90" t="n">
+        <v>7</v>
+      </c>
+      <c r="J90" t="n">
+        <v>7</v>
       </c>
       <c r="M90" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="N90" t="n">
         <v>1</v>
@@ -6831,14 +6843,17 @@
       <c r="Q90" t="n">
         <v>1</v>
       </c>
-      <c r="U90" t="n">
+      <c r="R90" t="n">
+        <v>1</v>
+      </c>
+      <c r="S90" t="n">
         <v>1</v>
       </c>
       <c r="V90" t="n">
         <v>1</v>
       </c>
       <c r="AF90" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="AG90" t="inlineStr">
         <is>
@@ -6854,7 +6869,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Sistema circulatorio</t>
+          <t>Selección natural</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -6863,10 +6878,10 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D91" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F91" t="n">
         <v>8</v>
@@ -6874,23 +6889,11 @@
       <c r="G91" t="n">
         <v>4</v>
       </c>
-      <c r="H91" t="n">
-        <v>2</v>
-      </c>
-      <c r="I91" t="n">
+      <c r="K91" t="n">
         <v>5</v>
       </c>
-      <c r="J91" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K91" t="n">
-        <v>4</v>
-      </c>
       <c r="L91" t="n">
-        <v>4</v>
-      </c>
-      <c r="M91" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O91" t="n">
         <v>1</v>
@@ -6898,29 +6901,17 @@
       <c r="P91" t="n">
         <v>1</v>
       </c>
-      <c r="Q91" t="n">
-        <v>1</v>
-      </c>
-      <c r="R91" t="n">
-        <v>1</v>
-      </c>
-      <c r="S91" t="n">
-        <v>1</v>
-      </c>
       <c r="T91" t="n">
         <v>1</v>
       </c>
       <c r="U91" t="n">
         <v>1</v>
       </c>
-      <c r="V91" t="n">
-        <v>1</v>
-      </c>
       <c r="Z91" t="n">
         <v>1</v>
       </c>
       <c r="AF91" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AG91" t="inlineStr">
         <is>
@@ -6936,7 +6927,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Sistema digestivo</t>
+          <t>Seres vivos y no vivos</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6945,34 +6936,31 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D92" t="n">
-        <v>4</v>
+        <v>2</v>
+      </c>
+      <c r="E92" t="n">
+        <v>2</v>
       </c>
       <c r="F92" t="n">
-        <v>8</v>
+        <v>2.5</v>
       </c>
       <c r="G92" t="n">
         <v>2</v>
       </c>
       <c r="H92" t="n">
-        <v>4</v>
-      </c>
-      <c r="I92" t="n">
-        <v>5</v>
-      </c>
-      <c r="J92" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K92" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L92" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M92" t="n">
-        <v>7</v>
+        <v>2.5</v>
+      </c>
+      <c r="N92" t="n">
+        <v>1</v>
       </c>
       <c r="O92" t="n">
         <v>1</v>
@@ -6983,26 +6971,14 @@
       <c r="Q92" t="n">
         <v>1</v>
       </c>
-      <c r="R92" t="n">
-        <v>1</v>
-      </c>
-      <c r="S92" t="n">
-        <v>1</v>
-      </c>
-      <c r="T92" t="n">
-        <v>1</v>
-      </c>
       <c r="U92" t="n">
         <v>1</v>
       </c>
       <c r="V92" t="n">
         <v>1</v>
       </c>
-      <c r="Z92" t="n">
-        <v>1</v>
-      </c>
       <c r="AF92" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AG92" t="inlineStr">
         <is>
@@ -7018,7 +6994,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Sistema endocrino y hormonas</t>
+          <t>Sistema circulatorio</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7027,38 +7003,53 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>9</v>
-      </c>
-      <c r="E93" t="n">
-        <v>8</v>
+        <v>4</v>
+      </c>
+      <c r="D93" t="n">
+        <v>4</v>
       </c>
       <c r="F93" t="n">
         <v>8</v>
       </c>
       <c r="G93" t="n">
-        <v>8.5</v>
+        <v>4</v>
+      </c>
+      <c r="H93" t="n">
+        <v>2</v>
+      </c>
+      <c r="I93" t="n">
+        <v>5</v>
       </c>
       <c r="J93" t="n">
-        <v>7</v>
+        <v>4.5</v>
+      </c>
+      <c r="K93" t="n">
+        <v>4</v>
       </c>
       <c r="L93" t="n">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="M93" t="n">
         <v>7</v>
       </c>
-      <c r="N93" t="n">
-        <v>1</v>
-      </c>
       <c r="O93" t="n">
         <v>1</v>
       </c>
       <c r="P93" t="n">
         <v>1</v>
       </c>
+      <c r="Q93" t="n">
+        <v>1</v>
+      </c>
+      <c r="R93" t="n">
+        <v>1</v>
+      </c>
       <c r="S93" t="n">
         <v>1</v>
       </c>
+      <c r="T93" t="n">
+        <v>1</v>
+      </c>
       <c r="U93" t="n">
         <v>1</v>
       </c>
@@ -7069,7 +7060,7 @@
         <v>1</v>
       </c>
       <c r="AF93" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="AG93" t="inlineStr">
         <is>
@@ -7085,7 +7076,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Sistema locomotor</t>
+          <t>Sistema digestivo</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7106,16 +7097,22 @@
         <v>2</v>
       </c>
       <c r="H94" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I94" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J94" t="n">
         <v>4.5</v>
       </c>
+      <c r="K94" t="n">
+        <v>4</v>
+      </c>
+      <c r="L94" t="n">
+        <v>4</v>
+      </c>
       <c r="M94" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="O94" t="n">
         <v>1</v>
@@ -7132,7 +7129,16 @@
       <c r="S94" t="n">
         <v>1</v>
       </c>
+      <c r="T94" t="n">
+        <v>1</v>
+      </c>
+      <c r="U94" t="n">
+        <v>1</v>
+      </c>
       <c r="V94" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z94" t="n">
         <v>1</v>
       </c>
       <c r="AF94" t="n">
@@ -7152,7 +7158,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Sistema respiratorio</t>
+          <t>Sistema endocrino y hormonas</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7161,53 +7167,38 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>3</v>
-      </c>
-      <c r="D95" t="n">
-        <v>3</v>
+        <v>9</v>
+      </c>
+      <c r="E95" t="n">
+        <v>8</v>
       </c>
       <c r="F95" t="n">
         <v>8</v>
       </c>
       <c r="G95" t="n">
-        <v>6</v>
-      </c>
-      <c r="H95" t="n">
-        <v>2</v>
-      </c>
-      <c r="I95" t="n">
-        <v>5</v>
+        <v>8.5</v>
       </c>
       <c r="J95" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K95" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L95" t="n">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="M95" t="n">
         <v>7</v>
       </c>
+      <c r="N95" t="n">
+        <v>1</v>
+      </c>
       <c r="O95" t="n">
         <v>1</v>
       </c>
       <c r="P95" t="n">
         <v>1</v>
       </c>
-      <c r="Q95" t="n">
-        <v>1</v>
-      </c>
-      <c r="R95" t="n">
-        <v>1</v>
-      </c>
       <c r="S95" t="n">
         <v>1</v>
       </c>
-      <c r="T95" t="n">
-        <v>1</v>
-      </c>
       <c r="U95" t="n">
         <v>1</v>
       </c>
@@ -7218,11 +7209,11 @@
         <v>1</v>
       </c>
       <c r="AF95" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AG95" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH95" t="inlineStr">
@@ -7234,7 +7225,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Tejidos animales</t>
+          <t>Sistema locomotor</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7248,20 +7239,23 @@
       <c r="D96" t="n">
         <v>4</v>
       </c>
-      <c r="E96" t="n">
-        <v>7</v>
-      </c>
       <c r="F96" t="n">
         <v>8</v>
       </c>
       <c r="G96" t="n">
-        <v>8.5</v>
+        <v>2</v>
       </c>
       <c r="H96" t="n">
-        <v>7</v>
-      </c>
-      <c r="N96" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="I96" t="n">
+        <v>3</v>
+      </c>
+      <c r="J96" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="M96" t="n">
+        <v>4.5</v>
       </c>
       <c r="O96" t="n">
         <v>1</v>
@@ -7272,7 +7266,13 @@
       <c r="Q96" t="n">
         <v>1</v>
       </c>
-      <c r="Z96" t="n">
+      <c r="R96" t="n">
+        <v>1</v>
+      </c>
+      <c r="S96" t="n">
+        <v>1</v>
+      </c>
+      <c r="V96" t="n">
         <v>1</v>
       </c>
       <c r="AF96" t="n">
@@ -7280,19 +7280,19 @@
       </c>
       <c r="AG96" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Tejidos vegetales</t>
+          <t>Sistema respiratorio</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7301,35 +7301,35 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D97" t="n">
-        <v>8</v>
-      </c>
-      <c r="E97" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F97" t="n">
         <v>8</v>
       </c>
       <c r="G97" t="n">
-        <v>8.5</v>
+        <v>6</v>
       </c>
       <c r="H97" t="n">
-        <v>7</v>
+        <v>2</v>
+      </c>
+      <c r="I97" t="n">
+        <v>5</v>
       </c>
       <c r="J97" t="n">
         <v>4.5</v>
       </c>
+      <c r="K97" t="n">
+        <v>4</v>
+      </c>
       <c r="L97" t="n">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="M97" t="n">
         <v>7</v>
       </c>
-      <c r="N97" t="n">
-        <v>1</v>
-      </c>
       <c r="O97" t="n">
         <v>1</v>
       </c>
@@ -7339,21 +7339,30 @@
       <c r="Q97" t="n">
         <v>1</v>
       </c>
+      <c r="R97" t="n">
+        <v>1</v>
+      </c>
       <c r="S97" t="n">
         <v>1</v>
       </c>
+      <c r="T97" t="n">
+        <v>1</v>
+      </c>
       <c r="U97" t="n">
         <v>1</v>
       </c>
       <c r="V97" t="n">
         <v>1</v>
       </c>
+      <c r="Z97" t="n">
+        <v>1</v>
+      </c>
       <c r="AF97" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AG97" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH97" t="inlineStr">
@@ -7365,7 +7374,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Transporte en plantas: xilema y floema</t>
+          <t>Tejidos animales</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -7374,28 +7383,28 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D98" t="n">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="E98" t="n">
+        <v>7</v>
+      </c>
+      <c r="F98" t="n">
+        <v>8</v>
       </c>
       <c r="G98" t="n">
-        <v>2</v>
+        <v>8.5</v>
       </c>
       <c r="H98" t="n">
         <v>7</v>
       </c>
-      <c r="I98" t="n">
-        <v>5</v>
-      </c>
-      <c r="J98" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L98" t="n">
-        <v>5</v>
-      </c>
-      <c r="M98" t="n">
-        <v>7</v>
+      <c r="N98" t="n">
+        <v>1</v>
+      </c>
+      <c r="O98" t="n">
+        <v>1</v>
       </c>
       <c r="P98" t="n">
         <v>1</v>
@@ -7403,36 +7412,27 @@
       <c r="Q98" t="n">
         <v>1</v>
       </c>
-      <c r="R98" t="n">
-        <v>1</v>
-      </c>
-      <c r="S98" t="n">
-        <v>1</v>
-      </c>
-      <c r="U98" t="n">
-        <v>1</v>
-      </c>
-      <c r="V98" t="n">
+      <c r="Z98" t="n">
         <v>1</v>
       </c>
       <c r="AF98" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AG98" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Variación genética en la descendencia</t>
+          <t>Tejidos vegetales</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -7441,31 +7441,34 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D99" t="n">
-        <v>6</v>
+        <v>8</v>
+      </c>
+      <c r="E99" t="n">
+        <v>7</v>
       </c>
       <c r="F99" t="n">
         <v>8</v>
       </c>
       <c r="G99" t="n">
-        <v>4</v>
+        <v>8.5</v>
       </c>
       <c r="H99" t="n">
         <v>7</v>
       </c>
-      <c r="I99" t="n">
-        <v>8</v>
-      </c>
-      <c r="K99" t="n">
-        <v>5</v>
+      <c r="J99" t="n">
+        <v>4.5</v>
       </c>
       <c r="L99" t="n">
         <v>7.5</v>
       </c>
       <c r="M99" t="n">
-        <v>4.5</v>
+        <v>7</v>
+      </c>
+      <c r="N99" t="n">
+        <v>1</v>
       </c>
       <c r="O99" t="n">
         <v>1</v>
@@ -7476,10 +7479,7 @@
       <c r="Q99" t="n">
         <v>1</v>
       </c>
-      <c r="R99" t="n">
-        <v>1</v>
-      </c>
-      <c r="T99" t="n">
+      <c r="S99" t="n">
         <v>1</v>
       </c>
       <c r="U99" t="n">
@@ -7489,7 +7489,7 @@
         <v>1</v>
       </c>
       <c r="AF99" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG99" t="inlineStr">
         <is>
@@ -7505,71 +7505,104 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Especies clave</t>
+          <t>Transporte en plantas: xilema y floema</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D100" t="n">
-        <v>7</v>
-      </c>
-      <c r="K100" t="n">
-        <v>3</v>
-      </c>
-      <c r="T100" t="n">
-        <v>1</v>
+        <v>6</v>
+      </c>
+      <c r="G100" t="n">
+        <v>2</v>
+      </c>
+      <c r="H100" t="n">
+        <v>7</v>
+      </c>
+      <c r="I100" t="n">
+        <v>5</v>
+      </c>
+      <c r="J100" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L100" t="n">
+        <v>5</v>
+      </c>
+      <c r="M100" t="n">
+        <v>7</v>
+      </c>
+      <c r="P100" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q100" t="n">
+        <v>1</v>
+      </c>
+      <c r="R100" t="n">
+        <v>1</v>
+      </c>
+      <c r="S100" t="n">
+        <v>1</v>
+      </c>
+      <c r="U100" t="n">
+        <v>1</v>
+      </c>
+      <c r="V100" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF100" t="n">
+        <v>8</v>
       </c>
       <c r="AG100" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH100" t="inlineStr">
         <is>
-          <t>no_aplica</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Niveles de organización ecológica</t>
+          <t>Variación genética en la descendencia</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C101" t="n">
+        <v>6</v>
+      </c>
+      <c r="D101" t="n">
+        <v>6</v>
+      </c>
+      <c r="F101" t="n">
+        <v>8</v>
+      </c>
+      <c r="G101" t="n">
         <v>4</v>
       </c>
-      <c r="D101" t="n">
-        <v>4</v>
-      </c>
-      <c r="F101" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="G101" t="n">
-        <v>8.5</v>
-      </c>
       <c r="H101" t="n">
-        <v>3</v>
-      </c>
-      <c r="J101" t="n">
-        <v>2.5</v>
+        <v>7</v>
+      </c>
+      <c r="I101" t="n">
+        <v>8</v>
       </c>
       <c r="K101" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L101" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="M101" t="n">
         <v>4.5</v>
@@ -7583,7 +7616,7 @@
       <c r="Q101" t="n">
         <v>1</v>
       </c>
-      <c r="S101" t="n">
+      <c r="R101" t="n">
         <v>1</v>
       </c>
       <c r="T101" t="n">
@@ -7596,11 +7629,11 @@
         <v>1</v>
       </c>
       <c r="AF101" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AG101" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH101" t="inlineStr">
@@ -7612,67 +7645,34 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Plantas y animales útiles al ser humano</t>
+          <t>Especies clave</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>no_aplica</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D102" t="n">
-        <v>2</v>
-      </c>
-      <c r="F102" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="G102" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="H102" t="n">
-        <v>2</v>
-      </c>
-      <c r="J102" t="n">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="K102" t="n">
-        <v>2</v>
-      </c>
-      <c r="M102" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O102" t="n">
-        <v>1</v>
-      </c>
-      <c r="P102" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q102" t="n">
-        <v>1</v>
-      </c>
-      <c r="S102" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T102" t="n">
         <v>1</v>
       </c>
-      <c r="V102" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF102" t="n">
-        <v>2</v>
-      </c>
       <c r="AG102" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>no_aplica</t>
         </is>
       </c>
     </row>

--- a/internacional/2_8/Contraste_biologia.xlsx
+++ b/internacional/2_8/Contraste_biologia.xlsx
@@ -922,7 +922,7 @@
         <v>2</v>
       </c>
       <c r="K6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L6" t="n">
         <v>6</v>
@@ -1848,7 +1848,7 @@
         <v>7</v>
       </c>
       <c r="K20" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L20" t="n">
         <v>7.5</v>
@@ -2270,6 +2270,9 @@
       <c r="J26" t="n">
         <v>2.5</v>
       </c>
+      <c r="K26" t="n">
+        <v>2</v>
+      </c>
       <c r="L26" t="n">
         <v>6</v>
       </c>
@@ -2294,6 +2297,9 @@
       <c r="S26" t="n">
         <v>1</v>
       </c>
+      <c r="T26" t="n">
+        <v>1</v>
+      </c>
       <c r="U26" t="n">
         <v>1</v>
       </c>
@@ -2988,6 +2994,9 @@
       <c r="J36" t="n">
         <v>2.5</v>
       </c>
+      <c r="K36" t="n">
+        <v>2</v>
+      </c>
       <c r="L36" t="n">
         <v>3</v>
       </c>
@@ -3012,6 +3021,9 @@
       <c r="S36" t="n">
         <v>1</v>
       </c>
+      <c r="T36" t="n">
+        <v>1</v>
+      </c>
       <c r="U36" t="n">
         <v>1</v>
       </c>
@@ -3062,7 +3074,7 @@
         <v>4.5</v>
       </c>
       <c r="K37" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="L37" t="n">
         <v>5</v>
@@ -3138,7 +3150,7 @@
         <v>4.5</v>
       </c>
       <c r="K38" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L38" t="n">
         <v>7.5</v>
@@ -3275,7 +3287,7 @@
         <v>2.5</v>
       </c>
       <c r="K40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L40" t="n">
         <v>3</v>
@@ -4186,7 +4198,7 @@
         <v>2.5</v>
       </c>
       <c r="K54" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L54" t="n">
         <v>4</v>
@@ -4977,7 +4989,7 @@
         <v>4</v>
       </c>
       <c r="K65" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M65" t="n">
         <v>2.5</v>
@@ -5005,7 +5017,7 @@
       </c>
       <c r="AG65" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH65" t="inlineStr">
@@ -5533,6 +5545,9 @@
       <c r="I73" t="n">
         <v>2</v>
       </c>
+      <c r="K73" t="n">
+        <v>2</v>
+      </c>
       <c r="O73" t="n">
         <v>1</v>
       </c>
@@ -5543,6 +5558,9 @@
         <v>1</v>
       </c>
       <c r="R73" t="n">
+        <v>1</v>
+      </c>
+      <c r="T73" t="n">
         <v>1</v>
       </c>
       <c r="AF73" t="n">
@@ -6001,6 +6019,9 @@
       <c r="J79" t="n">
         <v>7</v>
       </c>
+      <c r="K79" t="n">
+        <v>2</v>
+      </c>
       <c r="M79" t="n">
         <v>2.5</v>
       </c>
@@ -6019,6 +6040,9 @@
       <c r="S79" t="n">
         <v>1</v>
       </c>
+      <c r="T79" t="n">
+        <v>1</v>
+      </c>
       <c r="V79" t="n">
         <v>1</v>
       </c>
@@ -6890,7 +6914,7 @@
         <v>4</v>
       </c>
       <c r="K91" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L91" t="n">
         <v>6</v>
@@ -6953,6 +6977,9 @@
       <c r="H92" t="n">
         <v>2</v>
       </c>
+      <c r="K92" t="n">
+        <v>2</v>
+      </c>
       <c r="L92" t="n">
         <v>3</v>
       </c>
@@ -6971,6 +6998,9 @@
       <c r="Q92" t="n">
         <v>1</v>
       </c>
+      <c r="T92" t="n">
+        <v>1</v>
+      </c>
       <c r="U92" t="n">
         <v>1</v>
       </c>
@@ -7254,6 +7284,9 @@
       <c r="J96" t="n">
         <v>4.5</v>
       </c>
+      <c r="K96" t="n">
+        <v>2</v>
+      </c>
       <c r="M96" t="n">
         <v>4.5</v>
       </c>
@@ -7272,6 +7305,9 @@
       <c r="S96" t="n">
         <v>1</v>
       </c>
+      <c r="T96" t="n">
+        <v>1</v>
+      </c>
       <c r="V96" t="n">
         <v>1</v>
       </c>
@@ -7697,7 +7733,7 @@
         <v>3</v>
       </c>
       <c r="K103" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O103" t="n">
         <v>1</v>

--- a/internacional/2_8/Contraste_biologia.xlsx
+++ b/internacional/2_8/Contraste_biologia.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH152"/>
+  <dimension ref="A1:AH151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -7841,7 +7841,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Ciclos del fósforo y del azufre</t>
+          <t>Propagación de enfermedades y control de brotes</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -7850,17 +7850,41 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>8</v>
-      </c>
-      <c r="D106" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="G106" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H106" t="n">
+        <v>3</v>
+      </c>
+      <c r="J106" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L106" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="P106" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q106" t="n">
+        <v>1</v>
+      </c>
+      <c r="S106" t="n">
+        <v>1</v>
+      </c>
+      <c r="U106" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z106" t="n">
+        <v>1</v>
       </c>
       <c r="AF106" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG106" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH106" t="inlineStr">
@@ -7872,7 +7896,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Propagación de enfermedades y control de brotes</t>
+          <t>Especiación y macroevolución</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -7881,37 +7905,22 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="F107" t="n">
+        <v>8</v>
       </c>
       <c r="G107" t="n">
         <v>8.5</v>
       </c>
-      <c r="H107" t="n">
-        <v>3</v>
-      </c>
-      <c r="J107" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="L107" t="n">
-        <v>7.5</v>
+      <c r="O107" t="n">
+        <v>1</v>
       </c>
       <c r="P107" t="n">
         <v>1</v>
       </c>
-      <c r="Q107" t="n">
-        <v>1</v>
-      </c>
-      <c r="S107" t="n">
-        <v>1</v>
-      </c>
-      <c r="U107" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z107" t="n">
-        <v>1</v>
-      </c>
       <c r="AF107" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG107" t="inlineStr">
         <is>
@@ -7927,7 +7936,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Especiación y macroevolución</t>
+          <t>Eutrofización</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -7936,26 +7945,17 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>10</v>
-      </c>
-      <c r="F108" t="n">
-        <v>8</v>
-      </c>
-      <c r="G108" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="O108" t="n">
-        <v>1</v>
-      </c>
-      <c r="P108" t="n">
-        <v>1</v>
+        <v>7</v>
+      </c>
+      <c r="D108" t="n">
+        <v>7</v>
       </c>
       <c r="AF108" t="n">
         <v>10</v>
       </c>
       <c r="AG108" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH108" t="inlineStr">
@@ -7967,7 +7967,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Eutrofización</t>
+          <t>Evidencias de la evolución</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7976,17 +7976,38 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>7</v>
-      </c>
-      <c r="D109" t="n">
-        <v>7</v>
+        <v>9</v>
+      </c>
+      <c r="F109" t="n">
+        <v>8</v>
+      </c>
+      <c r="G109" t="n">
+        <v>4</v>
+      </c>
+      <c r="I109" t="n">
+        <v>8</v>
+      </c>
+      <c r="M109" t="n">
+        <v>7</v>
+      </c>
+      <c r="O109" t="n">
+        <v>1</v>
+      </c>
+      <c r="P109" t="n">
+        <v>1</v>
+      </c>
+      <c r="R109" t="n">
+        <v>1</v>
+      </c>
+      <c r="V109" t="n">
+        <v>1</v>
       </c>
       <c r="AF109" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG109" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH109" t="inlineStr">
@@ -7998,7 +8019,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Evidencias de la evolución</t>
+          <t>Fases de la fotosíntesis y ciclo de Calvin</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8007,38 +8028,23 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>9</v>
+        <v>6</v>
+      </c>
+      <c r="D110" t="n">
+        <v>6</v>
       </c>
       <c r="F110" t="n">
         <v>8</v>
       </c>
-      <c r="G110" t="n">
-        <v>4</v>
-      </c>
-      <c r="I110" t="n">
-        <v>8</v>
-      </c>
-      <c r="M110" t="n">
-        <v>7</v>
-      </c>
       <c r="O110" t="n">
         <v>1</v>
       </c>
-      <c r="P110" t="n">
-        <v>1</v>
-      </c>
-      <c r="R110" t="n">
-        <v>1</v>
-      </c>
-      <c r="V110" t="n">
-        <v>1</v>
-      </c>
       <c r="AF110" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG110" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH110" t="inlineStr">
@@ -8050,7 +8056,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Fases de la fotosíntesis y ciclo de Calvin</t>
+          <t>Secuenciación del ADN y perfiles genéticos</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -8059,15 +8065,18 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>6</v>
-      </c>
-      <c r="D111" t="n">
-        <v>6</v>
-      </c>
-      <c r="F111" t="n">
-        <v>8</v>
-      </c>
-      <c r="O111" t="n">
+        <v>9</v>
+      </c>
+      <c r="G111" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H111" t="n">
+        <v>7</v>
+      </c>
+      <c r="P111" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q111" t="n">
         <v>1</v>
       </c>
       <c r="AF111" t="n">
@@ -8075,7 +8084,7 @@
       </c>
       <c r="AG111" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH111" t="inlineStr">
@@ -8087,7 +8096,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Secuenciación del ADN y perfiles genéticos</t>
+          <t>Impulso nervioso y sinapsis</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -8096,18 +8105,18 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>9</v>
-      </c>
-      <c r="G112" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="H112" t="n">
-        <v>7</v>
-      </c>
-      <c r="P112" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q112" t="n">
+        <v>10</v>
+      </c>
+      <c r="F112" t="n">
+        <v>8</v>
+      </c>
+      <c r="J112" t="n">
+        <v>7</v>
+      </c>
+      <c r="O112" t="n">
+        <v>1</v>
+      </c>
+      <c r="S112" t="n">
         <v>1</v>
       </c>
       <c r="AF112" t="n">
@@ -8127,7 +8136,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Impulso nervioso y sinapsis</t>
+          <t>Ingeniería genética y ADN recombinante</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -8136,22 +8145,37 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F113" t="n">
         <v>8</v>
       </c>
-      <c r="J113" t="n">
+      <c r="G113" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H113" t="n">
+        <v>7</v>
+      </c>
+      <c r="M113" t="n">
         <v>7</v>
       </c>
       <c r="O113" t="n">
         <v>1</v>
       </c>
-      <c r="S113" t="n">
+      <c r="P113" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q113" t="n">
+        <v>1</v>
+      </c>
+      <c r="V113" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z113" t="n">
         <v>1</v>
       </c>
       <c r="AF113" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG113" t="inlineStr">
         <is>
@@ -8167,7 +8191,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Ingeniería genética y ADN recombinante</t>
+          <t>Inmunidad adaptativa</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -8178,27 +8202,15 @@
       <c r="C114" t="n">
         <v>9</v>
       </c>
-      <c r="F114" t="n">
-        <v>8</v>
-      </c>
       <c r="G114" t="n">
         <v>8.5</v>
       </c>
-      <c r="H114" t="n">
-        <v>7</v>
-      </c>
       <c r="M114" t="n">
         <v>7</v>
       </c>
-      <c r="O114" t="n">
-        <v>1</v>
-      </c>
       <c r="P114" t="n">
         <v>1</v>
       </c>
-      <c r="Q114" t="n">
-        <v>1</v>
-      </c>
       <c r="V114" t="n">
         <v>1</v>
       </c>
@@ -8206,7 +8218,7 @@
         <v>1</v>
       </c>
       <c r="AF114" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG114" t="inlineStr">
         <is>
@@ -8222,7 +8234,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Inmunidad adaptativa</t>
+          <t>Inmunidad innata</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -8245,9 +8257,6 @@
       <c r="V115" t="n">
         <v>1</v>
       </c>
-      <c r="Z115" t="n">
-        <v>1</v>
-      </c>
       <c r="AF115" t="n">
         <v>10</v>
       </c>
@@ -8265,7 +8274,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Inmunidad innata</t>
+          <t>Nutrición mineral de las plantas</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -8274,22 +8283,28 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>9</v>
+        <v>11</v>
+      </c>
+      <c r="F116" t="n">
+        <v>5</v>
       </c>
       <c r="G116" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="M116" t="n">
-        <v>7</v>
+        <v>2</v>
+      </c>
+      <c r="I116" t="n">
+        <v>4</v>
+      </c>
+      <c r="O116" t="n">
+        <v>1</v>
       </c>
       <c r="P116" t="n">
         <v>1</v>
       </c>
-      <c r="V116" t="n">
+      <c r="R116" t="n">
         <v>1</v>
       </c>
       <c r="AF116" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG116" t="inlineStr">
         <is>
@@ -8305,7 +8320,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Nutrición mineral de las plantas</t>
+          <t>Presión y flujo de fluidos en los seres vivos</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -8316,22 +8331,16 @@
       <c r="C117" t="n">
         <v>11</v>
       </c>
-      <c r="F117" t="n">
-        <v>5</v>
-      </c>
-      <c r="G117" t="n">
-        <v>2</v>
-      </c>
-      <c r="I117" t="n">
-        <v>4</v>
-      </c>
-      <c r="O117" t="n">
-        <v>1</v>
-      </c>
-      <c r="P117" t="n">
-        <v>1</v>
-      </c>
-      <c r="R117" t="n">
+      <c r="H117" t="n">
+        <v>7</v>
+      </c>
+      <c r="M117" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>1</v>
+      </c>
+      <c r="V117" t="n">
         <v>1</v>
       </c>
       <c r="AF117" t="n">
@@ -8351,7 +8360,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Presión y flujo de fluidos en los seres vivos</t>
+          <t>Proteínas: estructura y función</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -8360,26 +8369,23 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>11</v>
-      </c>
-      <c r="H118" t="n">
-        <v>7</v>
-      </c>
-      <c r="M118" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q118" t="n">
-        <v>1</v>
-      </c>
-      <c r="V118" t="n">
+        <v>6</v>
+      </c>
+      <c r="D118" t="n">
+        <v>6</v>
+      </c>
+      <c r="G118" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="P118" t="n">
         <v>1</v>
       </c>
       <c r="AF118" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AG118" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH118" t="inlineStr">
@@ -8391,7 +8397,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Proteínas: estructura y función</t>
+          <t>Regulación de la expresión génica</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -8400,14 +8406,17 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>6</v>
-      </c>
-      <c r="D119" t="n">
-        <v>6</v>
+        <v>9</v>
+      </c>
+      <c r="F119" t="n">
+        <v>8</v>
       </c>
       <c r="G119" t="n">
         <v>8.5</v>
       </c>
+      <c r="O119" t="n">
+        <v>1</v>
+      </c>
       <c r="P119" t="n">
         <v>1</v>
       </c>
@@ -8416,7 +8425,7 @@
       </c>
       <c r="AG119" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH119" t="inlineStr">
@@ -8428,7 +8437,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Regulación de la expresión génica</t>
+          <t>Relación superficie-volumen</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -8437,7 +8446,7 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F120" t="n">
         <v>8</v>
@@ -8445,14 +8454,32 @@
       <c r="G120" t="n">
         <v>8.5</v>
       </c>
+      <c r="J120" t="n">
+        <v>7</v>
+      </c>
+      <c r="K120" t="n">
+        <v>7</v>
+      </c>
+      <c r="L120" t="n">
+        <v>7.5</v>
+      </c>
       <c r="O120" t="n">
         <v>1</v>
       </c>
       <c r="P120" t="n">
         <v>1</v>
       </c>
+      <c r="S120" t="n">
+        <v>1</v>
+      </c>
+      <c r="T120" t="n">
+        <v>1</v>
+      </c>
+      <c r="U120" t="n">
+        <v>1</v>
+      </c>
       <c r="AF120" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG120" t="inlineStr">
         <is>
@@ -8461,14 +8488,14 @@
       </c>
       <c r="AH120" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>tardio</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Relación superficie-volumen</t>
+          <t>Relaciones intraespecíficas</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -8477,56 +8504,35 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>10</v>
-      </c>
-      <c r="F121" t="n">
-        <v>8</v>
-      </c>
-      <c r="G121" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="J121" t="n">
-        <v>7</v>
-      </c>
-      <c r="K121" t="n">
-        <v>7</v>
-      </c>
-      <c r="L121" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="O121" t="n">
-        <v>1</v>
-      </c>
-      <c r="P121" t="n">
-        <v>1</v>
-      </c>
-      <c r="S121" t="n">
-        <v>1</v>
-      </c>
-      <c r="T121" t="n">
-        <v>1</v>
-      </c>
-      <c r="U121" t="n">
+        <v>7</v>
+      </c>
+      <c r="D121" t="n">
+        <v>7</v>
+      </c>
+      <c r="M121" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="V121" t="n">
         <v>1</v>
       </c>
       <c r="AF121" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG121" t="inlineStr">
         <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+      <c r="AH121" t="inlineStr">
+        <is>
           <t>posterior</t>
-        </is>
-      </c>
-      <c r="AH121" t="inlineStr">
-        <is>
-          <t>tardio</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Relaciones intraespecíficas</t>
+          <t>Sistema inmunitario</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -8535,23 +8541,35 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>7</v>
-      </c>
-      <c r="D122" t="n">
-        <v>7</v>
+        <v>9</v>
+      </c>
+      <c r="F122" t="n">
+        <v>8</v>
+      </c>
+      <c r="G122" t="n">
+        <v>8.5</v>
       </c>
       <c r="M122" t="n">
-        <v>4.5</v>
+        <v>7</v>
+      </c>
+      <c r="O122" t="n">
+        <v>1</v>
+      </c>
+      <c r="P122" t="n">
+        <v>1</v>
       </c>
       <c r="V122" t="n">
         <v>1</v>
       </c>
+      <c r="Z122" t="n">
+        <v>1</v>
+      </c>
       <c r="AF122" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AG122" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH122" t="inlineStr">
@@ -8563,7 +8581,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Sistema inmunitario</t>
+          <t>Termorregulación</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -8572,31 +8590,16 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F123" t="n">
         <v>8</v>
       </c>
-      <c r="G123" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="M123" t="n">
-        <v>7</v>
-      </c>
       <c r="O123" t="n">
         <v>1</v>
       </c>
-      <c r="P123" t="n">
-        <v>1</v>
-      </c>
-      <c r="V123" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z123" t="n">
-        <v>1</v>
-      </c>
       <c r="AF123" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG123" t="inlineStr">
         <is>
@@ -8612,7 +8615,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Termorregulación</t>
+          <t>Virus</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -8621,20 +8624,41 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>10</v>
+        <v>3</v>
+      </c>
+      <c r="D124" t="n">
+        <v>3</v>
       </c>
       <c r="F124" t="n">
         <v>8</v>
       </c>
+      <c r="G124" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H124" t="n">
+        <v>4</v>
+      </c>
+      <c r="L124" t="n">
+        <v>7.5</v>
+      </c>
       <c r="O124" t="n">
         <v>1</v>
       </c>
+      <c r="P124" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>1</v>
+      </c>
+      <c r="U124" t="n">
+        <v>1</v>
+      </c>
       <c r="AF124" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG124" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH124" t="inlineStr">
@@ -8646,59 +8670,44 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Virus</t>
+          <t>Acervo génico y frecuencias alélicas</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>9</v>
-      </c>
-      <c r="F125" t="n">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="D125" t="n">
+        <v>7</v>
       </c>
       <c r="G125" t="n">
         <v>8.5</v>
       </c>
-      <c r="H125" t="n">
-        <v>4</v>
-      </c>
-      <c r="L125" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="O125" t="n">
-        <v>1</v>
-      </c>
       <c r="P125" t="n">
         <v>1</v>
       </c>
-      <c r="Q125" t="n">
-        <v>1</v>
-      </c>
-      <c r="U125" t="n">
-        <v>1</v>
-      </c>
       <c r="AF125" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AG125" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH125" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Acervo génico y frecuencias alélicas</t>
+          <t>ATP y energía en los sistemas vivos</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -8707,19 +8716,31 @@
         </is>
       </c>
       <c r="C126" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D126" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G126" t="n">
-        <v>8.5</v>
+        <v>6</v>
+      </c>
+      <c r="H126" t="n">
+        <v>7</v>
+      </c>
+      <c r="J126" t="n">
+        <v>7</v>
       </c>
       <c r="P126" t="n">
         <v>1</v>
       </c>
+      <c r="Q126" t="n">
+        <v>1</v>
+      </c>
+      <c r="S126" t="n">
+        <v>1</v>
+      </c>
       <c r="AF126" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AG126" t="inlineStr">
         <is>
@@ -8728,14 +8749,14 @@
       </c>
       <c r="AH126" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>ATP y energía en los sistemas vivos</t>
+          <t>Atributos de las poblaciones</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -8744,31 +8765,37 @@
         </is>
       </c>
       <c r="C127" t="n">
+        <v>7</v>
+      </c>
+      <c r="D127" t="n">
+        <v>7</v>
+      </c>
+      <c r="F127" t="n">
+        <v>8</v>
+      </c>
+      <c r="G127" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="L127" t="n">
         <v>6</v>
       </c>
-      <c r="D127" t="n">
-        <v>6</v>
-      </c>
-      <c r="G127" t="n">
-        <v>6</v>
-      </c>
-      <c r="H127" t="n">
-        <v>7</v>
-      </c>
-      <c r="J127" t="n">
-        <v>7</v>
+      <c r="M127" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O127" t="n">
+        <v>1</v>
       </c>
       <c r="P127" t="n">
         <v>1</v>
       </c>
-      <c r="Q127" t="n">
-        <v>1</v>
-      </c>
-      <c r="S127" t="n">
+      <c r="U127" t="n">
+        <v>1</v>
+      </c>
+      <c r="V127" t="n">
         <v>1</v>
       </c>
       <c r="AF127" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG127" t="inlineStr">
         <is>
@@ -8784,7 +8811,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Atributos de las poblaciones</t>
+          <t>Biomas y clasificación de ambientes</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -8793,37 +8820,25 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D128" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F128" t="n">
         <v>8</v>
       </c>
-      <c r="G128" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="L128" t="n">
-        <v>6</v>
-      </c>
-      <c r="M128" t="n">
-        <v>4.5</v>
+      <c r="H128" t="n">
+        <v>3</v>
       </c>
       <c r="O128" t="n">
         <v>1</v>
       </c>
-      <c r="P128" t="n">
-        <v>1</v>
-      </c>
-      <c r="U128" t="n">
-        <v>1</v>
-      </c>
-      <c r="V128" t="n">
+      <c r="Q128" t="n">
         <v>1</v>
       </c>
       <c r="AF128" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AG128" t="inlineStr">
         <is>
@@ -8832,14 +8847,14 @@
       </c>
       <c r="AH128" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>sin_referente</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Biomas y clasificación de ambientes</t>
+          <t>Célula procariota y eucariota</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -8848,25 +8863,25 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D129" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F129" t="n">
         <v>8</v>
       </c>
-      <c r="H129" t="n">
-        <v>3</v>
+      <c r="G129" t="n">
+        <v>8.5</v>
       </c>
       <c r="O129" t="n">
         <v>1</v>
       </c>
-      <c r="Q129" t="n">
+      <c r="P129" t="n">
         <v>1</v>
       </c>
       <c r="AF129" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AG129" t="inlineStr">
         <is>
@@ -8882,7 +8897,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Célula procariota y eucariota</t>
+          <t>Conservación e inocuidad de los alimentos</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -8891,25 +8906,25 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D130" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F130" t="n">
         <v>8</v>
       </c>
-      <c r="G130" t="n">
-        <v>8.5</v>
+      <c r="H130" t="n">
+        <v>2</v>
       </c>
       <c r="O130" t="n">
         <v>1</v>
       </c>
-      <c r="P130" t="n">
+      <c r="Q130" t="n">
         <v>1</v>
       </c>
       <c r="AF130" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AG130" t="inlineStr">
         <is>
@@ -8925,7 +8940,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Conservación e inocuidad de los alimentos</t>
+          <t>Ecosistemas acuáticos y marinos</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -8934,25 +8949,25 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D131" t="n">
-        <v>2</v>
-      </c>
-      <c r="F131" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H131" t="n">
-        <v>2</v>
-      </c>
-      <c r="O131" t="n">
-        <v>1</v>
+        <v>7</v>
+      </c>
+      <c r="J131" t="n">
+        <v>2.5</v>
       </c>
       <c r="Q131" t="n">
         <v>1</v>
       </c>
+      <c r="S131" t="n">
+        <v>1</v>
+      </c>
       <c r="AF131" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AG131" t="inlineStr">
         <is>
@@ -8968,7 +8983,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Ecosistemas acuáticos y marinos</t>
+          <t>Ecosistemas naturales, rurales y urbanos</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -8977,25 +8992,25 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D132" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H132" t="n">
         <v>7</v>
       </c>
-      <c r="J132" t="n">
+      <c r="M132" t="n">
         <v>2.5</v>
       </c>
       <c r="Q132" t="n">
         <v>1</v>
       </c>
-      <c r="S132" t="n">
+      <c r="V132" t="n">
         <v>1</v>
       </c>
       <c r="AF132" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AG132" t="inlineStr">
         <is>
@@ -9011,7 +9026,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Ecosistemas naturales, rurales y urbanos</t>
+          <t>Estrategias reproductivas y supervivencia de la descendencia</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -9020,25 +9035,43 @@
         </is>
       </c>
       <c r="C133" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D133" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="E133" t="n">
+        <v>8</v>
+      </c>
+      <c r="F133" t="n">
+        <v>8</v>
       </c>
       <c r="H133" t="n">
-        <v>7</v>
+        <v>3</v>
+      </c>
+      <c r="L133" t="n">
+        <v>6</v>
       </c>
       <c r="M133" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
+      </c>
+      <c r="N133" t="n">
+        <v>1</v>
+      </c>
+      <c r="O133" t="n">
+        <v>1</v>
       </c>
       <c r="Q133" t="n">
         <v>1</v>
       </c>
+      <c r="U133" t="n">
+        <v>1</v>
+      </c>
       <c r="V133" t="n">
         <v>1</v>
       </c>
       <c r="AF133" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG133" t="inlineStr">
         <is>
@@ -9047,14 +9080,14 @@
       </c>
       <c r="AH133" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>adelantado</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Estrategias reproductivas y supervivencia de la descendencia</t>
+          <t>Estructura del ADN</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -9063,43 +9096,22 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D134" t="n">
-        <v>3</v>
-      </c>
-      <c r="E134" t="n">
-        <v>8</v>
-      </c>
-      <c r="F134" t="n">
-        <v>8</v>
-      </c>
-      <c r="H134" t="n">
-        <v>3</v>
-      </c>
-      <c r="L134" t="n">
         <v>6</v>
       </c>
-      <c r="M134" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="N134" t="n">
-        <v>1</v>
-      </c>
-      <c r="O134" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q134" t="n">
-        <v>1</v>
-      </c>
-      <c r="U134" t="n">
-        <v>1</v>
-      </c>
-      <c r="V134" t="n">
+      <c r="G134" t="n">
+        <v>6</v>
+      </c>
+      <c r="P134" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z134" t="n">
         <v>1</v>
       </c>
       <c r="AF134" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AG134" t="inlineStr">
         <is>
@@ -9108,14 +9120,14 @@
       </c>
       <c r="AH134" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>sin_referente</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Estructura del ADN</t>
+          <t>Fermentación y respiración anaerobia</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -9124,22 +9136,25 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D135" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G135" t="n">
         <v>6</v>
       </c>
+      <c r="M135" t="n">
+        <v>7</v>
+      </c>
       <c r="P135" t="n">
         <v>1</v>
       </c>
-      <c r="Z135" t="n">
+      <c r="V135" t="n">
         <v>1</v>
       </c>
       <c r="AF135" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AG135" t="inlineStr">
         <is>
@@ -9155,7 +9170,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Fermentación y respiración anaerobia</t>
+          <t>Filogenia y parentesco evolutivo</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -9164,25 +9179,25 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D136" t="n">
-        <v>3</v>
+        <v>7</v>
+      </c>
+      <c r="F136" t="n">
+        <v>8</v>
       </c>
       <c r="G136" t="n">
-        <v>6</v>
-      </c>
-      <c r="M136" t="n">
-        <v>7</v>
+        <v>8.5</v>
+      </c>
+      <c r="O136" t="n">
+        <v>1</v>
       </c>
       <c r="P136" t="n">
         <v>1</v>
       </c>
-      <c r="V136" t="n">
-        <v>1</v>
-      </c>
       <c r="AF136" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AG136" t="inlineStr">
         <is>
@@ -9198,7 +9213,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Filogenia y parentesco evolutivo</t>
+          <t>Mecanismos de microevolución</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -9215,13 +9230,10 @@
       <c r="F137" t="n">
         <v>8</v>
       </c>
-      <c r="G137" t="n">
-        <v>8.5</v>
-      </c>
       <c r="O137" t="n">
         <v>1</v>
       </c>
-      <c r="P137" t="n">
+      <c r="Z137" t="n">
         <v>1</v>
       </c>
       <c r="AF137" t="n">
@@ -9241,7 +9253,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Mecanismos de microevolución</t>
+          <t>Medidas de biodiversidad</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -9255,13 +9267,10 @@
       <c r="D138" t="n">
         <v>7</v>
       </c>
-      <c r="F138" t="n">
-        <v>8</v>
-      </c>
-      <c r="O138" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z138" t="n">
+      <c r="H138" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q138" t="n">
         <v>1</v>
       </c>
       <c r="AF138" t="n">
@@ -9281,7 +9290,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Medidas de biodiversidad</t>
+          <t>Membrana celular</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -9290,19 +9299,28 @@
         </is>
       </c>
       <c r="C139" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D139" t="n">
-        <v>7</v>
-      </c>
-      <c r="H139" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q139" t="n">
+        <v>6</v>
+      </c>
+      <c r="G139" t="n">
+        <v>6</v>
+      </c>
+      <c r="K139" t="n">
+        <v>7</v>
+      </c>
+      <c r="P139" t="n">
+        <v>1</v>
+      </c>
+      <c r="T139" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z139" t="n">
         <v>1</v>
       </c>
       <c r="AF139" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AG139" t="inlineStr">
         <is>
@@ -9318,7 +9336,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Membrana celular</t>
+          <t>Modelos ecológicos basados en muestreo</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -9327,28 +9345,19 @@
         </is>
       </c>
       <c r="C140" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D140" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G140" t="n">
-        <v>6</v>
-      </c>
-      <c r="K140" t="n">
-        <v>7</v>
+        <v>8.5</v>
       </c>
       <c r="P140" t="n">
         <v>1</v>
       </c>
-      <c r="T140" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z140" t="n">
-        <v>1</v>
-      </c>
       <c r="AF140" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG140" t="inlineStr">
         <is>
@@ -9364,7 +9373,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Modelos ecológicos basados en muestreo</t>
+          <t>Mutaciones</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -9381,7 +9390,16 @@
       <c r="G141" t="n">
         <v>8.5</v>
       </c>
+      <c r="M141" t="n">
+        <v>7</v>
+      </c>
       <c r="P141" t="n">
+        <v>1</v>
+      </c>
+      <c r="V141" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z141" t="n">
         <v>1</v>
       </c>
       <c r="AF141" t="n">
@@ -9401,7 +9419,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Mutaciones</t>
+          <t>Nicho ecológico y exclusión competitiva</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -9410,28 +9428,19 @@
         </is>
       </c>
       <c r="C142" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D142" t="n">
-        <v>7</v>
-      </c>
-      <c r="G142" t="n">
-        <v>8.5</v>
+        <v>4</v>
       </c>
       <c r="M142" t="n">
         <v>7</v>
       </c>
-      <c r="P142" t="n">
-        <v>1</v>
-      </c>
       <c r="V142" t="n">
         <v>1</v>
       </c>
-      <c r="Z142" t="n">
-        <v>1</v>
-      </c>
       <c r="AF142" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AG142" t="inlineStr">
         <is>
@@ -9447,7 +9456,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Nicho ecológico y exclusión competitiva</t>
+          <t>Organelos de la célula eucariota</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -9456,19 +9465,37 @@
         </is>
       </c>
       <c r="C143" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D143" t="n">
-        <v>4</v>
-      </c>
-      <c r="M143" t="n">
-        <v>7</v>
-      </c>
-      <c r="V143" t="n">
+        <v>6</v>
+      </c>
+      <c r="E143" t="n">
+        <v>7</v>
+      </c>
+      <c r="G143" t="n">
+        <v>6</v>
+      </c>
+      <c r="K143" t="n">
+        <v>7</v>
+      </c>
+      <c r="L143" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="N143" t="n">
+        <v>1</v>
+      </c>
+      <c r="P143" t="n">
+        <v>1</v>
+      </c>
+      <c r="T143" t="n">
+        <v>1</v>
+      </c>
+      <c r="U143" t="n">
         <v>1</v>
       </c>
       <c r="AF143" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AG143" t="inlineStr">
         <is>
@@ -9477,14 +9504,14 @@
       </c>
       <c r="AH143" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Organelos de la célula eucariota</t>
+          <t>Osmorregulación y equilibrio hídrico</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -9493,37 +9520,13 @@
         </is>
       </c>
       <c r="C144" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D144" t="n">
-        <v>6</v>
-      </c>
-      <c r="E144" t="n">
-        <v>7</v>
-      </c>
-      <c r="G144" t="n">
-        <v>6</v>
-      </c>
-      <c r="K144" t="n">
-        <v>7</v>
-      </c>
-      <c r="L144" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="N144" t="n">
-        <v>1</v>
-      </c>
-      <c r="P144" t="n">
-        <v>1</v>
-      </c>
-      <c r="T144" t="n">
-        <v>1</v>
-      </c>
-      <c r="U144" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AF144" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AG144" t="inlineStr">
         <is>
@@ -9532,14 +9535,14 @@
       </c>
       <c r="AH144" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>sin_referente</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Osmorregulación y equilibrio hídrico</t>
+          <t>PCR y electroforesis en gel</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -9553,8 +9556,14 @@
       <c r="D145" t="n">
         <v>7</v>
       </c>
+      <c r="H145" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q145" t="n">
+        <v>1</v>
+      </c>
       <c r="AF145" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AG145" t="inlineStr">
         <is>
@@ -9570,7 +9579,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>PCR y electroforesis en gel</t>
+          <t>Replicación del ADN</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -9583,12 +9592,6 @@
       </c>
       <c r="D146" t="n">
         <v>7</v>
-      </c>
-      <c r="H146" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q146" t="n">
-        <v>1</v>
       </c>
       <c r="AF146" t="n">
         <v>7</v>
@@ -9607,7 +9610,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Replicación del ADN</t>
+          <t>Selección artificial</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -9620,6 +9623,18 @@
       </c>
       <c r="D147" t="n">
         <v>7</v>
+      </c>
+      <c r="G147" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="M147" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="P147" t="n">
+        <v>1</v>
+      </c>
+      <c r="V147" t="n">
+        <v>1</v>
       </c>
       <c r="AF147" t="n">
         <v>7</v>
@@ -9638,7 +9653,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Selección artificial</t>
+          <t>Síntesis de proteínas</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -9652,16 +9667,7 @@
       <c r="D148" t="n">
         <v>7</v>
       </c>
-      <c r="G148" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="M148" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="P148" t="n">
-        <v>1</v>
-      </c>
-      <c r="V148" t="n">
+      <c r="Z148" t="n">
         <v>1</v>
       </c>
       <c r="AF148" t="n">
@@ -9681,7 +9687,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Síntesis de proteínas</t>
+          <t>Sucesión ecológica</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -9695,7 +9701,16 @@
       <c r="D149" t="n">
         <v>7</v>
       </c>
-      <c r="Z149" t="n">
+      <c r="K149" t="n">
+        <v>5</v>
+      </c>
+      <c r="M149" t="n">
+        <v>7</v>
+      </c>
+      <c r="T149" t="n">
+        <v>1</v>
+      </c>
+      <c r="V149" t="n">
         <v>1</v>
       </c>
       <c r="AF149" t="n">
@@ -9715,7 +9730,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Sucesión ecológica</t>
+          <t>Transporte activo y endocitosis</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -9724,25 +9739,19 @@
         </is>
       </c>
       <c r="C150" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D150" t="n">
-        <v>7</v>
-      </c>
-      <c r="K150" t="n">
-        <v>5</v>
-      </c>
-      <c r="M150" t="n">
-        <v>7</v>
-      </c>
-      <c r="T150" t="n">
-        <v>1</v>
-      </c>
-      <c r="V150" t="n">
+        <v>6</v>
+      </c>
+      <c r="G150" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="P150" t="n">
         <v>1</v>
       </c>
       <c r="AF150" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AG150" t="inlineStr">
         <is>
@@ -9758,7 +9767,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Transporte activo y endocitosis</t>
+          <t>Tropismos y hormonas vegetales</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -9767,19 +9776,19 @@
         </is>
       </c>
       <c r="C151" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D151" t="n">
-        <v>6</v>
-      </c>
-      <c r="G151" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="P151" t="n">
+        <v>3</v>
+      </c>
+      <c r="K151" t="n">
+        <v>2</v>
+      </c>
+      <c r="T151" t="n">
         <v>1</v>
       </c>
       <c r="AF151" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AG151" t="inlineStr">
         <is>
@@ -9787,43 +9796,6 @@
         </is>
       </c>
       <c r="AH151" t="inlineStr">
-        <is>
-          <t>sin_referente</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>Tropismos y hormonas vegetales</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>sin_referente</t>
-        </is>
-      </c>
-      <c r="C152" t="n">
-        <v>3</v>
-      </c>
-      <c r="D152" t="n">
-        <v>3</v>
-      </c>
-      <c r="K152" t="n">
-        <v>2</v>
-      </c>
-      <c r="T152" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF152" t="n">
-        <v>3</v>
-      </c>
-      <c r="AG152" t="inlineStr">
-        <is>
-          <t>sin_referente</t>
-        </is>
-      </c>
-      <c r="AH152" t="inlineStr">
         <is>
           <t>sin_referente</t>
         </is>
@@ -9840,7 +9812,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J152"/>
+  <dimension ref="A1:J151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -16195,48 +16167,6 @@
       </c>
       <c r="J151">
         <f>Datos!B151</f>
-        <v/>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152">
-        <f>Datos!A152</f>
-        <v/>
-      </c>
-      <c r="B152">
-        <f>IF(Datos!C152="","",Datos!C152)</f>
-        <v/>
-      </c>
-      <c r="C152">
-        <f>COUNT(Datos!E152:M152)</f>
-        <v/>
-      </c>
-      <c r="D152">
-        <f>IF(C152=0,"",MEDIAN(Datos!E152:M152))</f>
-        <v/>
-      </c>
-      <c r="E152">
-        <f>COUNT(Datos!W152:AE152)</f>
-        <v/>
-      </c>
-      <c r="F152">
-        <f>IF(OR(B152="",D152=""),"",B152-D152)</f>
-        <v/>
-      </c>
-      <c r="G152">
-        <f>IF(Datos!D152="","",Datos!D152)</f>
-        <v/>
-      </c>
-      <c r="H152">
-        <f>COUNT(Datos!N152:V152)</f>
-        <v/>
-      </c>
-      <c r="I152">
-        <f>IF(B152="",IF(C152&gt;=5,"falta en SV",""),IF(G152="",IF(B152&gt;8,IF(C152&gt;=5,"SV tarde","despues del tramo"),IF(H152&gt;=5,"no retomado en 2-8","previo")),IF(B152&lt;2,"retomado",IF(AND(C152&lt;=1,E152&gt;=3),"solo especializacion",IF(F152="","coherente",IF(F152&lt;=-1.5,"SV adelantado",IF(F152&gt;=2,"SV tarde","coherente")))))))</f>
-        <v/>
-      </c>
-      <c r="J152">
-        <f>Datos!B152</f>
         <v/>
       </c>
     </row>
@@ -16276,7 +16206,7 @@
         </is>
       </c>
       <c r="B2">
-        <f>COUNTIF(Datos!B2:B152,A2)</f>
+        <f>COUNTIF(Datos!B2:B151,A2)</f>
         <v/>
       </c>
     </row>
@@ -16287,7 +16217,7 @@
         </is>
       </c>
       <c r="B3">
-        <f>COUNTIF(Datos!B2:B152,A3)</f>
+        <f>COUNTIF(Datos!B2:B151,A3)</f>
         <v/>
       </c>
     </row>
@@ -16298,7 +16228,7 @@
         </is>
       </c>
       <c r="B4">
-        <f>COUNTIF(Datos!B2:B152,A4)</f>
+        <f>COUNTIF(Datos!B2:B151,A4)</f>
         <v/>
       </c>
     </row>
@@ -16309,7 +16239,7 @@
         </is>
       </c>
       <c r="B5">
-        <f>COUNTIF(Datos!B2:B152,A5)</f>
+        <f>COUNTIF(Datos!B2:B151,A5)</f>
         <v/>
       </c>
     </row>
@@ -16320,7 +16250,7 @@
         </is>
       </c>
       <c r="B6">
-        <f>COUNTIF(Datos!B2:B152,A6)</f>
+        <f>COUNTIF(Datos!B2:B151,A6)</f>
         <v/>
       </c>
     </row>
@@ -16331,7 +16261,7 @@
         </is>
       </c>
       <c r="B7">
-        <f>COUNTIF(Datos!B2:B152,A7)</f>
+        <f>COUNTIF(Datos!B2:B151,A7)</f>
         <v/>
       </c>
     </row>
@@ -16342,7 +16272,7 @@
         </is>
       </c>
       <c r="B8">
-        <f>COUNTIF(Datos!B2:B152,A8)</f>
+        <f>COUNTIF(Datos!B2:B151,A8)</f>
         <v/>
       </c>
     </row>

--- a/internacional/2_8/Contraste_biologia.xlsx
+++ b/internacional/2_8/Contraste_biologia.xlsx
@@ -685,7 +685,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Amenazas a la biodiversidad</t>
+          <t>Agricultura y seguridad alimentaria</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -703,22 +703,10 @@
         <v>5</v>
       </c>
       <c r="G3" t="n">
-        <v>2</v>
-      </c>
-      <c r="H3" t="n">
-        <v>2</v>
-      </c>
-      <c r="I3" t="n">
-        <v>8</v>
-      </c>
-      <c r="J3" t="n">
-        <v>2.5</v>
+        <v>6</v>
       </c>
       <c r="K3" t="n">
         <v>2</v>
-      </c>
-      <c r="L3" t="n">
-        <v>6</v>
       </c>
       <c r="M3" t="n">
         <v>4.5</v>
@@ -729,19 +717,7 @@
       <c r="P3" t="n">
         <v>1</v>
       </c>
-      <c r="Q3" t="n">
-        <v>1</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1</v>
-      </c>
-      <c r="S3" t="n">
-        <v>1</v>
-      </c>
       <c r="T3" t="n">
-        <v>1</v>
-      </c>
-      <c r="U3" t="n">
         <v>1</v>
       </c>
       <c r="V3" t="n">
@@ -764,7 +740,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Biotecnología microbiana</t>
+          <t>Amenazas a la biodiversidad</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -773,37 +749,61 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F4" t="n">
+        <v>5</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I4" t="n">
         <v>8</v>
-      </c>
-      <c r="H4" t="n">
-        <v>7</v>
       </c>
       <c r="J4" t="n">
         <v>2.5</v>
       </c>
+      <c r="K4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L4" t="n">
+        <v>6</v>
+      </c>
       <c r="M4" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
       </c>
+      <c r="P4" t="n">
+        <v>1</v>
+      </c>
       <c r="Q4" t="n">
         <v>1</v>
       </c>
+      <c r="R4" t="n">
+        <v>1</v>
+      </c>
       <c r="S4" t="n">
         <v>1</v>
       </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
+      </c>
       <c r="V4" t="n">
         <v>1</v>
       </c>
       <c r="AF4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Conservación de la biodiversidad</t>
+          <t>Biotecnología microbiana</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -828,61 +828,37 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F5" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="G5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
-      </c>
-      <c r="I5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J5" t="n">
         <v>2.5</v>
       </c>
-      <c r="K5" t="n">
-        <v>2</v>
-      </c>
-      <c r="L5" t="n">
-        <v>4.5</v>
-      </c>
       <c r="M5" t="n">
         <v>7</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
       </c>
-      <c r="P5" t="n">
-        <v>1</v>
-      </c>
       <c r="Q5" t="n">
         <v>1</v>
       </c>
-      <c r="R5" t="n">
-        <v>1</v>
-      </c>
       <c r="S5" t="n">
         <v>1</v>
       </c>
-      <c r="T5" t="n">
-        <v>1</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1</v>
-      </c>
       <c r="V5" t="n">
         <v>1</v>
       </c>
       <c r="AF5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
@@ -898,7 +874,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Energía de los alimentos y balance energético</t>
+          <t>Conservación de la biodiversidad</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -907,25 +883,34 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G6" t="n">
+        <v>6</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I6" t="n">
         <v>8</v>
       </c>
-      <c r="G6" t="n">
-        <v>2</v>
-      </c>
-      <c r="H6" t="n">
-        <v>2</v>
+      <c r="J6" t="n">
+        <v>2.5</v>
       </c>
       <c r="K6" t="n">
         <v>2</v>
       </c>
       <c r="L6" t="n">
-        <v>6</v>
+        <v>4.5</v>
+      </c>
+      <c r="M6" t="n">
+        <v>7</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -936,17 +921,23 @@
       <c r="Q6" t="n">
         <v>1</v>
       </c>
+      <c r="R6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1</v>
+      </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="n">
         <v>1</v>
       </c>
-      <c r="Z6" t="n">
+      <c r="V6" t="n">
         <v>1</v>
       </c>
       <c r="AF6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
@@ -955,14 +946,14 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Enfermedades infecciosas y no infecciosas</t>
+          <t>Energía de los alimentos y balance energético</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -971,53 +962,47 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F7" t="n">
         <v>8</v>
       </c>
       <c r="G7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K7" t="n">
+        <v>2</v>
+      </c>
+      <c r="L7" t="n">
         <v>6</v>
       </c>
-      <c r="H7" t="n">
-        <v>3</v>
-      </c>
-      <c r="J7" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K7" t="n">
+      <c r="O7" t="n">
+        <v>1</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF7" t="n">
         <v>4</v>
       </c>
-      <c r="L7" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1</v>
-      </c>
-      <c r="P7" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1</v>
-      </c>
-      <c r="S7" t="n">
-        <v>1</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>3</v>
-      </c>
       <c r="AG7" t="inlineStr">
         <is>
           <t>adelantado</t>
@@ -1025,14 +1010,14 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Fósiles y registro fósil</t>
+          <t>Enfermedades infecciosas y no infecciosas</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1050,22 +1035,19 @@
         <v>8</v>
       </c>
       <c r="G8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H8" t="n">
+        <v>3</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K8" t="n">
         <v>4</v>
       </c>
-      <c r="I8" t="n">
-        <v>5</v>
-      </c>
-      <c r="J8" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K8" t="n">
-        <v>3</v>
-      </c>
-      <c r="M8" t="n">
-        <v>4.5</v>
+      <c r="L8" t="n">
+        <v>7.5</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1076,16 +1058,16 @@
       <c r="Q8" t="n">
         <v>1</v>
       </c>
-      <c r="R8" t="n">
-        <v>1</v>
-      </c>
       <c r="S8" t="n">
         <v>1</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
       </c>
-      <c r="V8" t="n">
+      <c r="U8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z8" t="n">
         <v>1</v>
       </c>
       <c r="AF8" t="n">
@@ -1105,7 +1087,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Grupos de plantas</t>
+          <t>Fósiles y registro fósil</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1126,13 +1108,19 @@
         <v>2</v>
       </c>
       <c r="H9" t="n">
-        <v>2</v>
+        <v>4</v>
+      </c>
+      <c r="I9" t="n">
+        <v>5</v>
       </c>
       <c r="J9" t="n">
         <v>4.5</v>
       </c>
-      <c r="L9" t="n">
-        <v>5</v>
+      <c r="K9" t="n">
+        <v>3</v>
+      </c>
+      <c r="M9" t="n">
+        <v>4.5</v>
       </c>
       <c r="O9" t="n">
         <v>1</v>
@@ -1143,10 +1131,16 @@
       <c r="Q9" t="n">
         <v>1</v>
       </c>
+      <c r="R9" t="n">
+        <v>1</v>
+      </c>
       <c r="S9" t="n">
         <v>1</v>
       </c>
-      <c r="U9" t="n">
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="V9" t="n">
         <v>1</v>
       </c>
       <c r="AF9" t="n">
@@ -1166,7 +1160,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Herencia de rasgos</t>
+          <t>Grupos de plantas</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1187,20 +1181,14 @@
         <v>2</v>
       </c>
       <c r="H10" t="n">
-        <v>3</v>
-      </c>
-      <c r="I10" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J10" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="L10" t="n">
         <v>5</v>
       </c>
-      <c r="M10" t="n">
-        <v>4.5</v>
-      </c>
       <c r="O10" t="n">
         <v>1</v>
       </c>
@@ -1210,16 +1198,10 @@
       <c r="Q10" t="n">
         <v>1</v>
       </c>
-      <c r="R10" t="n">
-        <v>1</v>
-      </c>
       <c r="S10" t="n">
         <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>1</v>
-      </c>
-      <c r="V10" t="n">
         <v>1</v>
       </c>
       <c r="AF10" t="n">
@@ -1623,10 +1605,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D17" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F17" t="n">
         <v>8</v>
@@ -1875,7 +1857,7 @@
         <v>1</v>
       </c>
       <c r="AF20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
@@ -2221,9 +2203,6 @@
       <c r="U25" t="n">
         <v>1</v>
       </c>
-      <c r="AF25" t="n">
-        <v>9</v>
-      </c>
       <c r="AG25" t="inlineStr">
         <is>
           <t>adelantado</t>
@@ -2231,7 +2210,7 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>faltante</t>
         </is>
       </c>
     </row>
@@ -2306,9 +2285,6 @@
       <c r="V26" t="n">
         <v>1</v>
       </c>
-      <c r="AF26" t="n">
-        <v>10</v>
-      </c>
       <c r="AG26" t="inlineStr">
         <is>
           <t>alineado</t>
@@ -2316,7 +2292,7 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>faltante</t>
         </is>
       </c>
     </row>
@@ -2387,7 +2363,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Agricultura y seguridad alimentaria</t>
+          <t>Biodiversidad</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2396,22 +2372,40 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D28" t="n">
-        <v>4</v>
+        <v>2</v>
+      </c>
+      <c r="E28" t="n">
+        <v>6</v>
       </c>
       <c r="F28" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="G28" t="n">
+        <v>2</v>
+      </c>
+      <c r="H28" t="n">
+        <v>2</v>
+      </c>
+      <c r="I28" t="n">
         <v>6</v>
       </c>
+      <c r="J28" t="n">
+        <v>2.5</v>
+      </c>
       <c r="K28" t="n">
         <v>2</v>
       </c>
+      <c r="L28" t="n">
+        <v>3</v>
+      </c>
       <c r="M28" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
+      </c>
+      <c r="N28" t="n">
+        <v>1</v>
       </c>
       <c r="O28" t="n">
         <v>1</v>
@@ -2419,14 +2413,26 @@
       <c r="P28" t="n">
         <v>1</v>
       </c>
+      <c r="Q28" t="n">
+        <v>1</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1</v>
+      </c>
+      <c r="S28" t="n">
+        <v>1</v>
+      </c>
       <c r="T28" t="n">
         <v>1</v>
       </c>
+      <c r="U28" t="n">
+        <v>1</v>
+      </c>
       <c r="V28" t="n">
         <v>1</v>
       </c>
       <c r="AF28" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AG28" t="inlineStr">
         <is>
@@ -2442,7 +2448,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Biodiversidad</t>
+          <t>Biomoléculas</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2451,67 +2457,52 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D29" t="n">
-        <v>2</v>
-      </c>
-      <c r="E29" t="n">
         <v>6</v>
       </c>
       <c r="F29" t="n">
-        <v>2.5</v>
+        <v>8</v>
       </c>
       <c r="G29" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H29" t="n">
         <v>2</v>
       </c>
-      <c r="I29" t="n">
+      <c r="J29" t="n">
+        <v>7</v>
+      </c>
+      <c r="L29" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="M29" t="n">
+        <v>7</v>
+      </c>
+      <c r="O29" t="n">
+        <v>1</v>
+      </c>
+      <c r="P29" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>1</v>
+      </c>
+      <c r="S29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF29" t="n">
         <v>6</v>
-      </c>
-      <c r="J29" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K29" t="n">
-        <v>2</v>
-      </c>
-      <c r="L29" t="n">
-        <v>3</v>
-      </c>
-      <c r="M29" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N29" t="n">
-        <v>1</v>
-      </c>
-      <c r="O29" t="n">
-        <v>1</v>
-      </c>
-      <c r="P29" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>1</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1</v>
-      </c>
-      <c r="S29" t="n">
-        <v>1</v>
-      </c>
-      <c r="T29" t="n">
-        <v>1</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>2</v>
       </c>
       <c r="AG29" t="inlineStr">
         <is>
@@ -2527,7 +2518,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Biomoléculas</t>
+          <t>Biotecnología vegetal y agroindustria</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2545,16 +2536,7 @@
         <v>8</v>
       </c>
       <c r="G30" t="n">
-        <v>6</v>
-      </c>
-      <c r="H30" t="n">
-        <v>2</v>
-      </c>
-      <c r="J30" t="n">
-        <v>7</v>
-      </c>
-      <c r="L30" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="M30" t="n">
         <v>7</v>
@@ -2565,19 +2547,7 @@
       <c r="P30" t="n">
         <v>1</v>
       </c>
-      <c r="Q30" t="n">
-        <v>1</v>
-      </c>
-      <c r="S30" t="n">
-        <v>1</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1</v>
-      </c>
       <c r="V30" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z30" t="n">
         <v>1</v>
       </c>
       <c r="AF30" t="n">
@@ -2585,19 +2555,19 @@
       </c>
       <c r="AG30" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Biotecnología vegetal y agroindustria</t>
+          <t>Cadena alimentaria</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2606,19 +2576,40 @@
         </is>
       </c>
       <c r="C31" t="n">
+        <v>4</v>
+      </c>
+      <c r="D31" t="n">
+        <v>4</v>
+      </c>
+      <c r="E31" t="n">
+        <v>3</v>
+      </c>
+      <c r="F31" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G31" t="n">
+        <v>2</v>
+      </c>
+      <c r="H31" t="n">
+        <v>3</v>
+      </c>
+      <c r="I31" t="n">
+        <v>5</v>
+      </c>
+      <c r="J31" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K31" t="n">
+        <v>2</v>
+      </c>
+      <c r="L31" t="n">
         <v>6</v>
       </c>
-      <c r="D31" t="n">
-        <v>6</v>
-      </c>
-      <c r="F31" t="n">
-        <v>8</v>
-      </c>
-      <c r="G31" t="n">
-        <v>8.5</v>
-      </c>
       <c r="M31" t="n">
-        <v>7</v>
+        <v>4.5</v>
+      </c>
+      <c r="N31" t="n">
+        <v>1</v>
       </c>
       <c r="O31" t="n">
         <v>1</v>
@@ -2626,27 +2617,42 @@
       <c r="P31" t="n">
         <v>1</v>
       </c>
+      <c r="Q31" t="n">
+        <v>1</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1</v>
+      </c>
+      <c r="S31" t="n">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
+      </c>
       <c r="V31" t="n">
         <v>1</v>
       </c>
       <c r="AF31" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AG31" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Cadena alimentaria</t>
+          <t>Cambio climático y seres vivos</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2655,31 +2661,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D32" t="n">
-        <v>4</v>
-      </c>
-      <c r="E32" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F32" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="G32" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H32" t="n">
-        <v>3</v>
-      </c>
-      <c r="I32" t="n">
+        <v>7</v>
+      </c>
+      <c r="K32" t="n">
         <v>5</v>
-      </c>
-      <c r="J32" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K32" t="n">
-        <v>2</v>
       </c>
       <c r="L32" t="n">
         <v>6</v>
@@ -2687,24 +2681,12 @@
       <c r="M32" t="n">
         <v>4.5</v>
       </c>
-      <c r="N32" t="n">
-        <v>1</v>
-      </c>
       <c r="O32" t="n">
         <v>1</v>
       </c>
-      <c r="P32" t="n">
-        <v>1</v>
-      </c>
       <c r="Q32" t="n">
         <v>1</v>
       </c>
-      <c r="R32" t="n">
-        <v>1</v>
-      </c>
-      <c r="S32" t="n">
-        <v>1</v>
-      </c>
       <c r="T32" t="n">
         <v>1</v>
       </c>
@@ -2715,7 +2697,7 @@
         <v>1</v>
       </c>
       <c r="AF32" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="AG32" t="inlineStr">
         <is>
@@ -2724,14 +2706,14 @@
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>tardio</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Cambio climático y seres vivos</t>
+          <t>Ciclo de vida de las plantas</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2740,32 +2722,56 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D33" t="n">
-        <v>7</v>
+        <v>2</v>
+      </c>
+      <c r="E33" t="n">
+        <v>2</v>
       </c>
       <c r="F33" t="n">
         <v>8</v>
       </c>
+      <c r="G33" t="n">
+        <v>2</v>
+      </c>
       <c r="H33" t="n">
-        <v>7</v>
+        <v>2</v>
+      </c>
+      <c r="I33" t="n">
+        <v>2</v>
+      </c>
+      <c r="J33" t="n">
+        <v>2.5</v>
       </c>
       <c r="K33" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L33" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M33" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
+      </c>
+      <c r="N33" t="n">
+        <v>1</v>
       </c>
       <c r="O33" t="n">
         <v>1</v>
       </c>
+      <c r="P33" t="n">
+        <v>1</v>
+      </c>
       <c r="Q33" t="n">
         <v>1</v>
       </c>
+      <c r="R33" t="n">
+        <v>1</v>
+      </c>
+      <c r="S33" t="n">
+        <v>1</v>
+      </c>
       <c r="T33" t="n">
         <v>1</v>
       </c>
@@ -2776,7 +2782,7 @@
         <v>1</v>
       </c>
       <c r="AF33" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="AG33" t="inlineStr">
         <is>
@@ -2785,14 +2791,14 @@
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Célula animal y célula vegetal</t>
+          <t>Ciclo de vida de los animales</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2801,37 +2807,37 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D34" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F34" t="n">
         <v>8</v>
       </c>
       <c r="G34" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H34" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I34" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="J34" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="K34" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="L34" t="n">
-        <v>7.5</v>
+        <v>3</v>
       </c>
       <c r="M34" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="N34" t="n">
         <v>1</v>
@@ -2861,7 +2867,7 @@
         <v>1</v>
       </c>
       <c r="AF34" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AG34" t="inlineStr">
         <is>
@@ -2877,7 +2883,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Ciclo de vida de las plantas</t>
+          <t>Papel de los seres vivos en el ciclo del agua</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2886,43 +2892,31 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D35" t="n">
-        <v>2</v>
-      </c>
-      <c r="E35" t="n">
-        <v>2</v>
-      </c>
-      <c r="F35" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G35" t="n">
-        <v>2</v>
+        <v>8.5</v>
       </c>
       <c r="H35" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I35" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J35" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="K35" t="n">
         <v>2</v>
       </c>
       <c r="L35" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M35" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N35" t="n">
-        <v>1</v>
-      </c>
-      <c r="O35" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="P35" t="n">
         <v>1</v>
@@ -2946,23 +2940,23 @@
         <v>1</v>
       </c>
       <c r="AF35" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="AG35" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>tardio</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Ciclo de vida de los animales</t>
+          <t>Ciclos del carbono y del oxígeno</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2971,34 +2965,31 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D36" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E36" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F36" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G36" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H36" t="n">
-        <v>2</v>
-      </c>
-      <c r="I36" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J36" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="K36" t="n">
         <v>2</v>
       </c>
       <c r="L36" t="n">
-        <v>3</v>
+        <v>7.5</v>
       </c>
       <c r="M36" t="n">
         <v>2.5</v>
@@ -3015,9 +3006,6 @@
       <c r="Q36" t="n">
         <v>1</v>
       </c>
-      <c r="R36" t="n">
-        <v>1</v>
-      </c>
       <c r="S36" t="n">
         <v>1</v>
       </c>
@@ -3031,7 +3019,7 @@
         <v>1</v>
       </c>
       <c r="AF36" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AG36" t="inlineStr">
         <is>
@@ -3040,14 +3028,14 @@
       </c>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>tardio</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Papel de los seres vivos en el ciclo del agua</t>
+          <t>Circulación e intercambio capilar</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3056,31 +3044,25 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D37" t="n">
-        <v>3</v>
+        <v>8</v>
+      </c>
+      <c r="F37" t="n">
+        <v>8</v>
       </c>
       <c r="G37" t="n">
-        <v>8.5</v>
+        <v>4</v>
       </c>
       <c r="H37" t="n">
         <v>7</v>
       </c>
-      <c r="I37" t="n">
-        <v>5</v>
-      </c>
-      <c r="J37" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K37" t="n">
-        <v>2</v>
-      </c>
       <c r="L37" t="n">
-        <v>5</v>
-      </c>
-      <c r="M37" t="n">
-        <v>7</v>
+        <v>7.5</v>
+      </c>
+      <c r="O37" t="n">
+        <v>1</v>
       </c>
       <c r="P37" t="n">
         <v>1</v>
@@ -3088,39 +3070,27 @@
       <c r="Q37" t="n">
         <v>1</v>
       </c>
-      <c r="R37" t="n">
-        <v>1</v>
-      </c>
-      <c r="S37" t="n">
-        <v>1</v>
-      </c>
-      <c r="T37" t="n">
-        <v>1</v>
-      </c>
       <c r="U37" t="n">
         <v>1</v>
       </c>
-      <c r="V37" t="n">
-        <v>1</v>
-      </c>
       <c r="AF37" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AG37" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>posterior</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Ciclos del carbono y del oxígeno</t>
+          <t>Clasificación de seres vivos por sus rasgos</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3129,31 +3099,34 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D38" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E38" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F38" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="G38" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H38" t="n">
-        <v>5</v>
+        <v>2</v>
+      </c>
+      <c r="I38" t="n">
+        <v>2</v>
       </c>
       <c r="J38" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="K38" t="n">
         <v>2</v>
       </c>
       <c r="L38" t="n">
-        <v>7.5</v>
+        <v>3</v>
       </c>
       <c r="M38" t="n">
         <v>2.5</v>
@@ -3170,6 +3143,9 @@
       <c r="Q38" t="n">
         <v>1</v>
       </c>
+      <c r="R38" t="n">
+        <v>1</v>
+      </c>
       <c r="S38" t="n">
         <v>1</v>
       </c>
@@ -3183,7 +3159,7 @@
         <v>1</v>
       </c>
       <c r="AF38" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AG38" t="inlineStr">
         <is>
@@ -3192,14 +3168,14 @@
       </c>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Circulación e intercambio capilar</t>
+          <t>Clasificación jerárquica y nomenclatura</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3208,22 +3184,28 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D39" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F39" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G39" t="n">
-        <v>4</v>
+        <v>8.5</v>
       </c>
       <c r="H39" t="n">
         <v>7</v>
       </c>
-      <c r="L39" t="n">
-        <v>7.5</v>
+      <c r="J39" t="n">
+        <v>7</v>
+      </c>
+      <c r="K39" t="n">
+        <v>5</v>
+      </c>
+      <c r="M39" t="n">
+        <v>7</v>
       </c>
       <c r="O39" t="n">
         <v>1</v>
@@ -3234,27 +3216,33 @@
       <c r="Q39" t="n">
         <v>1</v>
       </c>
-      <c r="U39" t="n">
+      <c r="S39" t="n">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
+      <c r="V39" t="n">
         <v>1</v>
       </c>
       <c r="AF39" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="AG39" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Clasificación de seres vivos por sus rasgos</t>
+          <t>Competencia por recursos</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3263,40 +3251,28 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D40" t="n">
-        <v>2</v>
-      </c>
-      <c r="E40" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F40" t="n">
-        <v>2.5</v>
+        <v>8</v>
       </c>
       <c r="G40" t="n">
         <v>2</v>
       </c>
       <c r="H40" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I40" t="n">
-        <v>2</v>
-      </c>
-      <c r="J40" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="K40" t="n">
-        <v>2</v>
-      </c>
-      <c r="L40" t="n">
         <v>3</v>
       </c>
       <c r="M40" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N40" t="n">
-        <v>1</v>
+        <v>4.5</v>
       </c>
       <c r="O40" t="n">
         <v>1</v>
@@ -3310,20 +3286,14 @@
       <c r="R40" t="n">
         <v>1</v>
       </c>
-      <c r="S40" t="n">
-        <v>1</v>
-      </c>
       <c r="T40" t="n">
         <v>1</v>
       </c>
-      <c r="U40" t="n">
-        <v>1</v>
-      </c>
       <c r="V40" t="n">
         <v>1</v>
       </c>
       <c r="AF40" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AG40" t="inlineStr">
         <is>
@@ -3339,7 +3309,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Clasificación jerárquica y nomenclatura</t>
+          <t>Concepto de especie</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3354,22 +3324,19 @@
         <v>7</v>
       </c>
       <c r="F41" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="G41" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="H41" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J41" t="n">
         <v>7</v>
       </c>
-      <c r="K41" t="n">
-        <v>5</v>
+      <c r="L41" t="n">
+        <v>6</v>
       </c>
       <c r="M41" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="O41" t="n">
         <v>1</v>
@@ -3377,13 +3344,10 @@
       <c r="P41" t="n">
         <v>1</v>
       </c>
-      <c r="Q41" t="n">
-        <v>1</v>
-      </c>
       <c r="S41" t="n">
         <v>1</v>
       </c>
-      <c r="T41" t="n">
+      <c r="U41" t="n">
         <v>1</v>
       </c>
       <c r="V41" t="n">
@@ -3394,7 +3358,7 @@
       </c>
       <c r="AG41" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH41" t="inlineStr">
@@ -3406,7 +3370,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Competencia por recursos</t>
+          <t>Contagio y prevención de enfermedades</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3415,10 +3379,10 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D42" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F42" t="n">
         <v>8</v>
@@ -3429,14 +3393,8 @@
       <c r="H42" t="n">
         <v>3</v>
       </c>
-      <c r="I42" t="n">
-        <v>5</v>
-      </c>
-      <c r="K42" t="n">
-        <v>3</v>
-      </c>
-      <c r="M42" t="n">
-        <v>4.5</v>
+      <c r="J42" t="n">
+        <v>2.5</v>
       </c>
       <c r="O42" t="n">
         <v>1</v>
@@ -3447,17 +3405,14 @@
       <c r="Q42" t="n">
         <v>1</v>
       </c>
-      <c r="R42" t="n">
-        <v>1</v>
-      </c>
-      <c r="T42" t="n">
-        <v>1</v>
-      </c>
-      <c r="V42" t="n">
+      <c r="S42" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z42" t="n">
         <v>1</v>
       </c>
       <c r="AF42" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AG42" t="inlineStr">
         <is>
@@ -3473,7 +3428,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Concepto de especie</t>
+          <t>Contaminación y sus efectos en los seres vivos</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3482,47 +3437,56 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D43" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F43" t="n">
+        <v>5</v>
+      </c>
+      <c r="H43" t="n">
+        <v>2</v>
+      </c>
+      <c r="J43" t="n">
         <v>2.5</v>
       </c>
-      <c r="G43" t="n">
-        <v>6</v>
-      </c>
-      <c r="J43" t="n">
-        <v>7</v>
+      <c r="K43" t="n">
+        <v>4</v>
       </c>
       <c r="L43" t="n">
         <v>6</v>
       </c>
       <c r="M43" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="O43" t="n">
         <v>1</v>
       </c>
-      <c r="P43" t="n">
+      <c r="Q43" t="n">
         <v>1</v>
       </c>
       <c r="S43" t="n">
         <v>1</v>
       </c>
+      <c r="T43" t="n">
+        <v>1</v>
+      </c>
       <c r="U43" t="n">
         <v>1</v>
       </c>
       <c r="V43" t="n">
         <v>1</v>
       </c>
+      <c r="Z43" t="n">
+        <v>1</v>
+      </c>
       <c r="AF43" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AG43" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH43" t="inlineStr">
@@ -3534,7 +3498,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Contagio y prevención de enfermedades</t>
+          <t>Crecimiento poblacional</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3543,40 +3507,37 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D44" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F44" t="n">
         <v>8</v>
       </c>
-      <c r="G44" t="n">
-        <v>2</v>
-      </c>
       <c r="H44" t="n">
-        <v>3</v>
-      </c>
-      <c r="J44" t="n">
-        <v>2.5</v>
+        <v>7</v>
+      </c>
+      <c r="L44" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="M44" t="n">
+        <v>7</v>
       </c>
       <c r="O44" t="n">
         <v>1</v>
       </c>
-      <c r="P44" t="n">
-        <v>1</v>
-      </c>
       <c r="Q44" t="n">
         <v>1</v>
       </c>
-      <c r="S44" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z44" t="n">
+      <c r="U44" t="n">
+        <v>1</v>
+      </c>
+      <c r="V44" t="n">
         <v>1</v>
       </c>
       <c r="AF44" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AG44" t="inlineStr">
         <is>
@@ -3592,7 +3553,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Contaminación y sus efectos en los seres vivos</t>
+          <t>Depredación</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3601,36 +3562,39 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D45" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F45" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G45" t="n">
+        <v>2</v>
+      </c>
+      <c r="H45" t="n">
+        <v>3</v>
+      </c>
+      <c r="I45" t="n">
         <v>5</v>
       </c>
-      <c r="H45" t="n">
-        <v>2</v>
-      </c>
-      <c r="J45" t="n">
-        <v>2.5</v>
-      </c>
       <c r="K45" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L45" t="n">
         <v>6</v>
       </c>
-      <c r="M45" t="n">
-        <v>2.5</v>
-      </c>
       <c r="O45" t="n">
         <v>1</v>
       </c>
+      <c r="P45" t="n">
+        <v>1</v>
+      </c>
       <c r="Q45" t="n">
         <v>1</v>
       </c>
-      <c r="S45" t="n">
+      <c r="R45" t="n">
         <v>1</v>
       </c>
       <c r="T45" t="n">
@@ -3639,18 +3603,12 @@
       <c r="U45" t="n">
         <v>1</v>
       </c>
-      <c r="V45" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>1</v>
-      </c>
       <c r="AF45" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AG45" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH45" t="inlineStr">
@@ -3662,7 +3620,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Crecimiento poblacional</t>
+          <t>Diferenciación y especialización celular</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3676,36 +3634,45 @@
       <c r="D46" t="n">
         <v>6</v>
       </c>
-      <c r="F46" t="n">
-        <v>8</v>
+      <c r="E46" t="n">
+        <v>7</v>
+      </c>
+      <c r="G46" t="n">
+        <v>6</v>
       </c>
       <c r="H46" t="n">
+        <v>7</v>
+      </c>
+      <c r="K46" t="n">
         <v>7</v>
       </c>
       <c r="L46" t="n">
         <v>7.5</v>
       </c>
-      <c r="M46" t="n">
-        <v>7</v>
-      </c>
-      <c r="O46" t="n">
+      <c r="N46" t="n">
+        <v>1</v>
+      </c>
+      <c r="P46" t="n">
         <v>1</v>
       </c>
       <c r="Q46" t="n">
         <v>1</v>
       </c>
+      <c r="T46" t="n">
+        <v>1</v>
+      </c>
       <c r="U46" t="n">
         <v>1</v>
       </c>
-      <c r="V46" t="n">
+      <c r="Z46" t="n">
         <v>1</v>
       </c>
       <c r="AF46" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AG46" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH46" t="inlineStr">
@@ -3717,7 +3684,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Depredación</t>
+          <t>Difusión y ósmosis</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3726,49 +3693,34 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D47" t="n">
-        <v>4</v>
-      </c>
-      <c r="F47" t="n">
-        <v>2.5</v>
+        <v>6</v>
       </c>
       <c r="G47" t="n">
-        <v>2</v>
-      </c>
-      <c r="H47" t="n">
-        <v>3</v>
-      </c>
-      <c r="I47" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K47" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L47" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="P47" t="n">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>1</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF47" t="n">
         <v>6</v>
-      </c>
-      <c r="O47" t="n">
-        <v>1</v>
-      </c>
-      <c r="P47" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>1</v>
-      </c>
-      <c r="R47" t="n">
-        <v>1</v>
-      </c>
-      <c r="T47" t="n">
-        <v>1</v>
-      </c>
-      <c r="U47" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF47" t="n">
-        <v>4</v>
       </c>
       <c r="AG47" t="inlineStr">
         <is>
@@ -3784,7 +3736,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Diferenciación y especialización celular</t>
+          <t>Digestión química y absorción de nutrientes</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3793,50 +3745,56 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D48" t="n">
-        <v>6</v>
-      </c>
-      <c r="E48" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="F48" t="n">
+        <v>8</v>
       </c>
       <c r="G48" t="n">
-        <v>6</v>
-      </c>
-      <c r="H48" t="n">
-        <v>7</v>
-      </c>
-      <c r="K48" t="n">
+        <v>4</v>
+      </c>
+      <c r="I48" t="n">
+        <v>5</v>
+      </c>
+      <c r="J48" t="n">
         <v>7</v>
       </c>
       <c r="L48" t="n">
         <v>7.5</v>
       </c>
-      <c r="N48" t="n">
+      <c r="M48" t="n">
+        <v>7</v>
+      </c>
+      <c r="O48" t="n">
         <v>1</v>
       </c>
       <c r="P48" t="n">
         <v>1</v>
       </c>
-      <c r="Q48" t="n">
-        <v>1</v>
-      </c>
-      <c r="T48" t="n">
+      <c r="R48" t="n">
+        <v>1</v>
+      </c>
+      <c r="S48" t="n">
         <v>1</v>
       </c>
       <c r="U48" t="n">
         <v>1</v>
       </c>
+      <c r="V48" t="n">
+        <v>1</v>
+      </c>
       <c r="Z48" t="n">
         <v>1</v>
       </c>
       <c r="AF48" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AG48" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH48" t="inlineStr">
@@ -3848,7 +3806,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Difusión y ósmosis</t>
+          <t>Diversidad genética de poblaciones</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3857,38 +3815,35 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D49" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G49" t="n">
         <v>6</v>
       </c>
+      <c r="J49" t="n">
+        <v>7</v>
+      </c>
       <c r="K49" t="n">
-        <v>7</v>
-      </c>
-      <c r="L49" t="n">
-        <v>7.5</v>
+        <v>5</v>
       </c>
       <c r="P49" t="n">
         <v>1</v>
       </c>
+      <c r="S49" t="n">
+        <v>1</v>
+      </c>
       <c r="T49" t="n">
         <v>1</v>
       </c>
-      <c r="U49" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z49" t="n">
-        <v>1</v>
-      </c>
       <c r="AF49" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG49" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH49" t="inlineStr">
@@ -3900,7 +3855,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Digestión química y absorción de nutrientes</t>
+          <t>Enzimas</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3909,19 +3864,13 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D50" t="n">
-        <v>8</v>
-      </c>
-      <c r="F50" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G50" t="n">
-        <v>4</v>
-      </c>
-      <c r="I50" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J50" t="n">
         <v>7</v>
@@ -3932,15 +3881,9 @@
       <c r="M50" t="n">
         <v>7</v>
       </c>
-      <c r="O50" t="n">
-        <v>1</v>
-      </c>
       <c r="P50" t="n">
         <v>1</v>
       </c>
-      <c r="R50" t="n">
-        <v>1</v>
-      </c>
       <c r="S50" t="n">
         <v>1</v>
       </c>
@@ -3954,11 +3897,11 @@
         <v>1</v>
       </c>
       <c r="AF50" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AG50" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH50" t="inlineStr">
@@ -3970,7 +3913,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Diversidad genética de poblaciones</t>
+          <t>Estructuras del cuerpo animal y su función</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3979,35 +3922,74 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D51" t="n">
-        <v>7</v>
+        <v>2</v>
+      </c>
+      <c r="E51" t="n">
+        <v>2</v>
+      </c>
+      <c r="F51" t="n">
+        <v>2.5</v>
       </c>
       <c r="G51" t="n">
-        <v>6</v>
+        <v>2</v>
+      </c>
+      <c r="H51" t="n">
+        <v>2</v>
+      </c>
+      <c r="I51" t="n">
+        <v>3</v>
       </c>
       <c r="J51" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="K51" t="n">
-        <v>5</v>
+        <v>2</v>
+      </c>
+      <c r="L51" t="n">
+        <v>4</v>
+      </c>
+      <c r="M51" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N51" t="n">
+        <v>1</v>
+      </c>
+      <c r="O51" t="n">
+        <v>1</v>
       </c>
       <c r="P51" t="n">
         <v>1</v>
       </c>
+      <c r="Q51" t="n">
+        <v>1</v>
+      </c>
+      <c r="R51" t="n">
+        <v>1</v>
+      </c>
       <c r="S51" t="n">
         <v>1</v>
       </c>
       <c r="T51" t="n">
         <v>1</v>
       </c>
+      <c r="U51" t="n">
+        <v>1</v>
+      </c>
+      <c r="V51" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>1</v>
+      </c>
       <c r="AF51" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AG51" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH51" t="inlineStr">
@@ -4019,7 +4001,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Enzimas</t>
+          <t>Extinción de especies</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4028,27 +4010,39 @@
         </is>
       </c>
       <c r="C52" t="n">
+        <v>5</v>
+      </c>
+      <c r="D52" t="n">
+        <v>5</v>
+      </c>
+      <c r="F52" t="n">
+        <v>8</v>
+      </c>
+      <c r="G52" t="n">
+        <v>2</v>
+      </c>
+      <c r="H52" t="n">
+        <v>5</v>
+      </c>
+      <c r="K52" t="n">
+        <v>3</v>
+      </c>
+      <c r="L52" t="n">
         <v>6</v>
       </c>
-      <c r="D52" t="n">
-        <v>6</v>
-      </c>
-      <c r="G52" t="n">
-        <v>6</v>
-      </c>
-      <c r="J52" t="n">
-        <v>7</v>
-      </c>
-      <c r="L52" t="n">
-        <v>7.5</v>
-      </c>
       <c r="M52" t="n">
-        <v>7</v>
+        <v>4.5</v>
+      </c>
+      <c r="O52" t="n">
+        <v>1</v>
       </c>
       <c r="P52" t="n">
         <v>1</v>
       </c>
-      <c r="S52" t="n">
+      <c r="Q52" t="n">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
         <v>1</v>
       </c>
       <c r="U52" t="n">
@@ -4057,15 +4051,12 @@
       <c r="V52" t="n">
         <v>1</v>
       </c>
-      <c r="Z52" t="n">
-        <v>1</v>
-      </c>
       <c r="AF52" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AG52" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH52" t="inlineStr">
@@ -4077,7 +4068,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Estructuras celulares básicas</t>
+          <t>Factores bióticos y abióticos</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4086,37 +4077,37 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D53" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E53" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F53" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G53" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H53" t="n">
+        <v>2</v>
+      </c>
+      <c r="I53" t="n">
         <v>5</v>
       </c>
-      <c r="I53" t="n">
-        <v>7</v>
-      </c>
       <c r="J53" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K53" t="n">
+        <v>2</v>
+      </c>
+      <c r="L53" t="n">
         <v>4.5</v>
       </c>
-      <c r="K53" t="n">
-        <v>7</v>
-      </c>
-      <c r="L53" t="n">
-        <v>7.5</v>
-      </c>
       <c r="M53" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="N53" t="n">
         <v>1</v>
@@ -4145,11 +4136,8 @@
       <c r="V53" t="n">
         <v>1</v>
       </c>
-      <c r="Z53" t="n">
-        <v>1</v>
-      </c>
       <c r="AF53" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AG53" t="inlineStr">
         <is>
@@ -4158,14 +4146,14 @@
       </c>
       <c r="AH53" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>tardio</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Estructuras del cuerpo animal y su función</t>
+          <t>Factores limitantes de las poblaciones</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4174,37 +4162,28 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D54" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E54" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F54" t="n">
-        <v>2.5</v>
+        <v>8</v>
       </c>
       <c r="G54" t="n">
-        <v>2</v>
-      </c>
-      <c r="H54" t="n">
-        <v>2</v>
-      </c>
-      <c r="I54" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="K54" t="n">
         <v>3</v>
       </c>
-      <c r="J54" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K54" t="n">
-        <v>2</v>
-      </c>
       <c r="L54" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M54" t="n">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="N54" t="n">
         <v>1</v>
@@ -4215,15 +4194,6 @@
       <c r="P54" t="n">
         <v>1</v>
       </c>
-      <c r="Q54" t="n">
-        <v>1</v>
-      </c>
-      <c r="R54" t="n">
-        <v>1</v>
-      </c>
-      <c r="S54" t="n">
-        <v>1</v>
-      </c>
       <c r="T54" t="n">
         <v>1</v>
       </c>
@@ -4233,27 +4203,24 @@
       <c r="V54" t="n">
         <v>1</v>
       </c>
-      <c r="Z54" t="n">
-        <v>1</v>
-      </c>
       <c r="AF54" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="AG54" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>tardio</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Extinción de especies</t>
+          <t>Fecundación y desarrollo embrionario</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4262,49 +4229,52 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D55" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F55" t="n">
         <v>8</v>
       </c>
       <c r="G55" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H55" t="n">
+        <v>7</v>
+      </c>
+      <c r="I55" t="n">
+        <v>4</v>
+      </c>
+      <c r="J55" t="n">
+        <v>7</v>
+      </c>
+      <c r="L55" t="n">
         <v>5</v>
       </c>
-      <c r="K55" t="n">
-        <v>3</v>
-      </c>
-      <c r="L55" t="n">
+      <c r="O55" t="n">
+        <v>1</v>
+      </c>
+      <c r="P55" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>1</v>
+      </c>
+      <c r="R55" t="n">
+        <v>1</v>
+      </c>
+      <c r="S55" t="n">
+        <v>1</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF55" t="n">
         <v>6</v>
-      </c>
-      <c r="M55" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O55" t="n">
-        <v>1</v>
-      </c>
-      <c r="P55" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q55" t="n">
-        <v>1</v>
-      </c>
-      <c r="T55" t="n">
-        <v>1</v>
-      </c>
-      <c r="U55" t="n">
-        <v>1</v>
-      </c>
-      <c r="V55" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF55" t="n">
-        <v>5</v>
       </c>
       <c r="AG55" t="inlineStr">
         <is>
@@ -4320,7 +4290,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Factores bióticos y abióticos</t>
+          <t>Flujo de energía y pirámides ecológicas</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4329,68 +4299,50 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D56" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E56" t="n">
+        <v>6</v>
+      </c>
+      <c r="G56" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H56" t="n">
         <v>5</v>
       </c>
-      <c r="F56" t="n">
+      <c r="K56" t="n">
+        <v>6</v>
+      </c>
+      <c r="L56" t="n">
+        <v>6</v>
+      </c>
+      <c r="M56" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="N56" t="n">
+        <v>1</v>
+      </c>
+      <c r="P56" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>1</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
+      </c>
+      <c r="V56" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF56" t="n">
         <v>5</v>
       </c>
-      <c r="G56" t="n">
-        <v>2</v>
-      </c>
-      <c r="H56" t="n">
-        <v>2</v>
-      </c>
-      <c r="I56" t="n">
-        <v>5</v>
-      </c>
-      <c r="J56" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K56" t="n">
-        <v>2</v>
-      </c>
-      <c r="L56" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="M56" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N56" t="n">
-        <v>1</v>
-      </c>
-      <c r="O56" t="n">
-        <v>1</v>
-      </c>
-      <c r="P56" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q56" t="n">
-        <v>1</v>
-      </c>
-      <c r="R56" t="n">
-        <v>1</v>
-      </c>
-      <c r="S56" t="n">
-        <v>1</v>
-      </c>
-      <c r="T56" t="n">
-        <v>1</v>
-      </c>
-      <c r="U56" t="n">
-        <v>1</v>
-      </c>
-      <c r="V56" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF56" t="n">
-        <v>4</v>
-      </c>
       <c r="AG56" t="inlineStr">
         <is>
           <t>alineado</t>
@@ -4398,14 +4350,14 @@
       </c>
       <c r="AH56" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Factores limitantes de las poblaciones</t>
+          <t>Fotosíntesis</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4414,28 +4366,37 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D57" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E57" t="n">
+        <v>8</v>
+      </c>
+      <c r="F57" t="n">
+        <v>5</v>
+      </c>
+      <c r="G57" t="n">
         <v>6</v>
       </c>
-      <c r="F57" t="n">
-        <v>8</v>
-      </c>
-      <c r="G57" t="n">
-        <v>8.5</v>
+      <c r="H57" t="n">
+        <v>2</v>
+      </c>
+      <c r="I57" t="n">
+        <v>4</v>
+      </c>
+      <c r="J57" t="n">
+        <v>4.5</v>
       </c>
       <c r="K57" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L57" t="n">
         <v>6</v>
       </c>
       <c r="M57" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="N57" t="n">
         <v>1</v>
@@ -4446,6 +4407,15 @@
       <c r="P57" t="n">
         <v>1</v>
       </c>
+      <c r="Q57" t="n">
+        <v>1</v>
+      </c>
+      <c r="R57" t="n">
+        <v>1</v>
+      </c>
+      <c r="S57" t="n">
+        <v>1</v>
+      </c>
       <c r="T57" t="n">
         <v>1</v>
       </c>
@@ -4456,23 +4426,23 @@
         <v>1</v>
       </c>
       <c r="AF57" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AG57" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>tardio</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Fecundación y desarrollo embrionario</t>
+          <t>Genes y alelos</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4496,14 +4466,11 @@
         <v>7</v>
       </c>
       <c r="I58" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J58" t="n">
         <v>7</v>
       </c>
-      <c r="L58" t="n">
-        <v>5</v>
-      </c>
       <c r="O58" t="n">
         <v>1</v>
       </c>
@@ -4519,18 +4486,15 @@
       <c r="S58" t="n">
         <v>1</v>
       </c>
-      <c r="U58" t="n">
-        <v>1</v>
-      </c>
       <c r="Z58" t="n">
         <v>1</v>
       </c>
       <c r="AF58" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG58" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH58" t="inlineStr">
@@ -4542,7 +4506,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Flujo de energía y pirámides ecológicas</t>
+          <t>Genética humana y enfermedades hereditarias</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4551,30 +4515,24 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>7</v>
-      </c>
-      <c r="D59" t="n">
-        <v>7</v>
-      </c>
-      <c r="E59" t="n">
-        <v>6</v>
+        <v>9</v>
+      </c>
+      <c r="F59" t="n">
+        <v>8</v>
       </c>
       <c r="G59" t="n">
         <v>8.5</v>
       </c>
       <c r="H59" t="n">
-        <v>5</v>
-      </c>
-      <c r="K59" t="n">
-        <v>6</v>
-      </c>
-      <c r="L59" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="J59" t="n">
+        <v>7</v>
       </c>
       <c r="M59" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="N59" t="n">
+        <v>7</v>
+      </c>
+      <c r="O59" t="n">
         <v>1</v>
       </c>
       <c r="P59" t="n">
@@ -4583,17 +4541,17 @@
       <c r="Q59" t="n">
         <v>1</v>
       </c>
-      <c r="T59" t="n">
-        <v>1</v>
-      </c>
-      <c r="U59" t="n">
+      <c r="S59" t="n">
         <v>1</v>
       </c>
       <c r="V59" t="n">
         <v>1</v>
       </c>
+      <c r="Z59" t="n">
+        <v>1</v>
+      </c>
       <c r="AF59" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AG59" t="inlineStr">
         <is>
@@ -4609,7 +4567,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Fotosíntesis</t>
+          <t>Genotipo y fenotipo</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4618,40 +4576,28 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D60" t="n">
-        <v>6</v>
-      </c>
-      <c r="E60" t="n">
+        <v>7</v>
+      </c>
+      <c r="F60" t="n">
         <v>8</v>
-      </c>
-      <c r="F60" t="n">
-        <v>5</v>
       </c>
       <c r="G60" t="n">
         <v>6</v>
       </c>
       <c r="H60" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I60" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J60" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K60" t="n">
-        <v>2</v>
-      </c>
-      <c r="L60" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M60" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="N60" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O60" t="n">
         <v>1</v>
@@ -4668,17 +4614,14 @@
       <c r="S60" t="n">
         <v>1</v>
       </c>
-      <c r="T60" t="n">
-        <v>1</v>
-      </c>
-      <c r="U60" t="n">
-        <v>1</v>
-      </c>
       <c r="V60" t="n">
         <v>1</v>
       </c>
+      <c r="Z60" t="n">
+        <v>1</v>
+      </c>
       <c r="AF60" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG60" t="inlineStr">
         <is>
@@ -4687,14 +4630,14 @@
       </c>
       <c r="AH60" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Genes y alelos</t>
+          <t>Grupos de alimentos y dieta balanceada</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4703,25 +4646,28 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D61" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F61" t="n">
         <v>8</v>
       </c>
       <c r="G61" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H61" t="n">
-        <v>7</v>
-      </c>
-      <c r="I61" t="n">
-        <v>8</v>
-      </c>
-      <c r="J61" t="n">
-        <v>7</v>
+        <v>2</v>
+      </c>
+      <c r="K61" t="n">
+        <v>4</v>
+      </c>
+      <c r="L61" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="M61" t="n">
+        <v>2.5</v>
       </c>
       <c r="O61" t="n">
         <v>1</v>
@@ -4732,21 +4678,24 @@
       <c r="Q61" t="n">
         <v>1</v>
       </c>
-      <c r="R61" t="n">
-        <v>1</v>
-      </c>
-      <c r="S61" t="n">
+      <c r="T61" t="n">
+        <v>1</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
+      </c>
+      <c r="V61" t="n">
         <v>1</v>
       </c>
       <c r="Z61" t="n">
         <v>1</v>
       </c>
       <c r="AF61" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AG61" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH61" t="inlineStr">
@@ -4758,7 +4707,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Genética humana y enfermedades hereditarias</t>
+          <t>Grupos de vertebrados</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4767,25 +4716,28 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D62" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F62" t="n">
-        <v>8</v>
+        <v>2.5</v>
       </c>
       <c r="G62" t="n">
-        <v>8.5</v>
+        <v>2</v>
       </c>
       <c r="H62" t="n">
-        <v>7</v>
-      </c>
-      <c r="J62" t="n">
-        <v>7</v>
+        <v>2</v>
+      </c>
+      <c r="I62" t="n">
+        <v>4</v>
+      </c>
+      <c r="K62" t="n">
+        <v>2</v>
       </c>
       <c r="M62" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="O62" t="n">
         <v>1</v>
@@ -4796,21 +4748,21 @@
       <c r="Q62" t="n">
         <v>1</v>
       </c>
-      <c r="S62" t="n">
+      <c r="R62" t="n">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
         <v>1</v>
       </c>
       <c r="V62" t="n">
         <v>1</v>
       </c>
-      <c r="Z62" t="n">
-        <v>1</v>
-      </c>
       <c r="AF62" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AG62" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH62" t="inlineStr">
@@ -4822,7 +4774,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Genotipo y fenotipo</t>
+          <t>Hábitat y ecosistemas comunes</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4831,28 +4783,40 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D63" t="n">
-        <v>7</v>
+        <v>2</v>
+      </c>
+      <c r="E63" t="n">
+        <v>2</v>
       </c>
       <c r="F63" t="n">
-        <v>8</v>
+        <v>2.5</v>
       </c>
       <c r="G63" t="n">
+        <v>2</v>
+      </c>
+      <c r="H63" t="n">
+        <v>2</v>
+      </c>
+      <c r="I63" t="n">
+        <v>2</v>
+      </c>
+      <c r="J63" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K63" t="n">
+        <v>2</v>
+      </c>
+      <c r="L63" t="n">
         <v>6</v>
       </c>
-      <c r="H63" t="n">
-        <v>3</v>
-      </c>
-      <c r="I63" t="n">
-        <v>8</v>
-      </c>
-      <c r="J63" t="n">
-        <v>7</v>
-      </c>
       <c r="M63" t="n">
-        <v>7</v>
+        <v>2.5</v>
+      </c>
+      <c r="N63" t="n">
+        <v>1</v>
       </c>
       <c r="O63" t="n">
         <v>1</v>
@@ -4869,14 +4833,17 @@
       <c r="S63" t="n">
         <v>1</v>
       </c>
+      <c r="T63" t="n">
+        <v>1</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
+      </c>
       <c r="V63" t="n">
         <v>1</v>
       </c>
-      <c r="Z63" t="n">
-        <v>1</v>
-      </c>
       <c r="AF63" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AG63" t="inlineStr">
         <is>
@@ -4892,7 +4859,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Grupos de alimentos y dieta balanceada</t>
+          <t>Hábitos de vida saludable</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4907,13 +4874,16 @@
         <v>2</v>
       </c>
       <c r="F64" t="n">
-        <v>8</v>
+        <v>2.5</v>
       </c>
       <c r="G64" t="n">
         <v>2</v>
       </c>
       <c r="H64" t="n">
         <v>2</v>
+      </c>
+      <c r="J64" t="n">
+        <v>2.5</v>
       </c>
       <c r="K64" t="n">
         <v>4</v>
@@ -4921,9 +4891,6 @@
       <c r="L64" t="n">
         <v>7.5</v>
       </c>
-      <c r="M64" t="n">
-        <v>2.5</v>
-      </c>
       <c r="O64" t="n">
         <v>1</v>
       </c>
@@ -4933,15 +4900,15 @@
       <c r="Q64" t="n">
         <v>1</v>
       </c>
+      <c r="S64" t="n">
+        <v>1</v>
+      </c>
       <c r="T64" t="n">
         <v>1</v>
       </c>
       <c r="U64" t="n">
         <v>1</v>
       </c>
-      <c r="V64" t="n">
-        <v>1</v>
-      </c>
       <c r="Z64" t="n">
         <v>1</v>
       </c>
@@ -4950,7 +4917,7 @@
       </c>
       <c r="AG64" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH64" t="inlineStr">
@@ -4962,7 +4929,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Grupos de vertebrados</t>
+          <t>Herencia mendeliana</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4971,28 +4938,28 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D65" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F65" t="n">
-        <v>2.5</v>
+        <v>8</v>
       </c>
       <c r="G65" t="n">
-        <v>2</v>
+        <v>8.5</v>
       </c>
       <c r="H65" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I65" t="n">
-        <v>4</v>
-      </c>
-      <c r="K65" t="n">
-        <v>2</v>
+        <v>8</v>
+      </c>
+      <c r="J65" t="n">
+        <v>7</v>
       </c>
       <c r="M65" t="n">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="O65" t="n">
         <v>1</v>
@@ -5006,18 +4973,18 @@
       <c r="R65" t="n">
         <v>1</v>
       </c>
-      <c r="T65" t="n">
+      <c r="S65" t="n">
         <v>1</v>
       </c>
       <c r="V65" t="n">
         <v>1</v>
       </c>
       <c r="AF65" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AG65" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH65" t="inlineStr">
@@ -5029,7 +4996,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Hábitat y ecosistemas comunes</t>
+          <t>Herencia ligada al sexo, alelos múltiples y poligénica</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5038,43 +5005,22 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D66" t="n">
-        <v>2</v>
-      </c>
-      <c r="E66" t="n">
-        <v>2</v>
-      </c>
-      <c r="F66" t="n">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="G66" t="n">
-        <v>2</v>
+        <v>8.5</v>
       </c>
       <c r="H66" t="n">
-        <v>2</v>
-      </c>
-      <c r="I66" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J66" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K66" t="n">
-        <v>2</v>
-      </c>
-      <c r="L66" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M66" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N66" t="n">
-        <v>1</v>
-      </c>
-      <c r="O66" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="P66" t="n">
         <v>1</v>
@@ -5082,23 +5028,17 @@
       <c r="Q66" t="n">
         <v>1</v>
       </c>
-      <c r="R66" t="n">
-        <v>1</v>
-      </c>
       <c r="S66" t="n">
         <v>1</v>
       </c>
-      <c r="T66" t="n">
-        <v>1</v>
-      </c>
-      <c r="U66" t="n">
-        <v>1</v>
-      </c>
       <c r="V66" t="n">
         <v>1</v>
       </c>
+      <c r="Z66" t="n">
+        <v>1</v>
+      </c>
       <c r="AF66" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="AG66" t="inlineStr">
         <is>
@@ -5107,14 +5047,14 @@
       </c>
       <c r="AH66" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>posterior</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Hábitos de vida saludable</t>
+          <t>Homeostasis</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5123,28 +5063,31 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>2</v>
-      </c>
-      <c r="D67" t="n">
-        <v>2</v>
+        <v>9</v>
+      </c>
+      <c r="E67" t="n">
+        <v>8</v>
       </c>
       <c r="F67" t="n">
-        <v>2.5</v>
+        <v>8</v>
       </c>
       <c r="G67" t="n">
-        <v>2</v>
+        <v>8.5</v>
       </c>
       <c r="H67" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J67" t="n">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="K67" t="n">
         <v>4</v>
       </c>
-      <c r="L67" t="n">
-        <v>7.5</v>
+      <c r="M67" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="N67" t="n">
+        <v>1</v>
       </c>
       <c r="O67" t="n">
         <v>1</v>
@@ -5161,14 +5104,14 @@
       <c r="T67" t="n">
         <v>1</v>
       </c>
-      <c r="U67" t="n">
+      <c r="V67" t="n">
         <v>1</v>
       </c>
       <c r="Z67" t="n">
         <v>1</v>
       </c>
       <c r="AF67" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="AG67" t="inlineStr">
         <is>
@@ -5184,7 +5127,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Herencia mendeliana</t>
+          <t>Impacto humano en los ecosistemas</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5193,28 +5136,34 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D68" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F68" t="n">
-        <v>8</v>
+        <v>2.5</v>
       </c>
       <c r="G68" t="n">
-        <v>8.5</v>
+        <v>6</v>
       </c>
       <c r="H68" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I68" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J68" t="n">
-        <v>7</v>
+        <v>2.5</v>
+      </c>
+      <c r="K68" t="n">
+        <v>2</v>
+      </c>
+      <c r="L68" t="n">
+        <v>4.5</v>
       </c>
       <c r="M68" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="O68" t="n">
         <v>1</v>
@@ -5231,15 +5180,21 @@
       <c r="S68" t="n">
         <v>1</v>
       </c>
+      <c r="T68" t="n">
+        <v>1</v>
+      </c>
+      <c r="U68" t="n">
+        <v>1</v>
+      </c>
       <c r="V68" t="n">
         <v>1</v>
       </c>
       <c r="AF68" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AG68" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH68" t="inlineStr">
@@ -5251,7 +5206,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Herencia ligada al sexo, alelos múltiples y poligénica</t>
+          <t>Intercambio de gases en plantas</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5260,56 +5215,53 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D69" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G69" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="H69" t="n">
+        <v>6</v>
+      </c>
+      <c r="I69" t="n">
         <v>7</v>
       </c>
       <c r="J69" t="n">
-        <v>7</v>
-      </c>
-      <c r="M69" t="n">
-        <v>7</v>
+        <v>4.5</v>
+      </c>
+      <c r="L69" t="n">
+        <v>5</v>
       </c>
       <c r="P69" t="n">
         <v>1</v>
       </c>
-      <c r="Q69" t="n">
+      <c r="R69" t="n">
         <v>1</v>
       </c>
       <c r="S69" t="n">
         <v>1</v>
       </c>
-      <c r="V69" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z69" t="n">
+      <c r="U69" t="n">
         <v>1</v>
       </c>
       <c r="AF69" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AG69" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Homeostasis</t>
+          <t>Invertebrados e insectos</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5318,34 +5270,25 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D70" t="n">
-        <v>8</v>
-      </c>
-      <c r="E70" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F70" t="n">
-        <v>8</v>
+        <v>2.5</v>
       </c>
       <c r="G70" t="n">
-        <v>8.5</v>
+        <v>3</v>
       </c>
       <c r="H70" t="n">
-        <v>7</v>
-      </c>
-      <c r="J70" t="n">
-        <v>7</v>
+        <v>2</v>
+      </c>
+      <c r="I70" t="n">
+        <v>2</v>
       </c>
       <c r="K70" t="n">
-        <v>4</v>
-      </c>
-      <c r="M70" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="N70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O70" t="n">
         <v>1</v>
@@ -5356,20 +5299,14 @@
       <c r="Q70" t="n">
         <v>1</v>
       </c>
-      <c r="S70" t="n">
+      <c r="R70" t="n">
         <v>1</v>
       </c>
       <c r="T70" t="n">
         <v>1</v>
       </c>
-      <c r="V70" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z70" t="n">
-        <v>1</v>
-      </c>
       <c r="AF70" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AG70" t="inlineStr">
         <is>
@@ -5385,7 +5322,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Impacto humano en los ecosistemas</t>
+          <t>La célula como unidad de la vida</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5394,34 +5331,40 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D71" t="n">
-        <v>2</v>
+        <v>6</v>
+      </c>
+      <c r="E71" t="n">
+        <v>7</v>
       </c>
       <c r="F71" t="n">
-        <v>2.5</v>
+        <v>8</v>
       </c>
       <c r="G71" t="n">
         <v>6</v>
       </c>
       <c r="H71" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I71" t="n">
+        <v>7</v>
+      </c>
+      <c r="J71" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K71" t="n">
+        <v>7</v>
+      </c>
+      <c r="L71" t="n">
         <v>5</v>
       </c>
-      <c r="J71" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K71" t="n">
-        <v>2</v>
-      </c>
-      <c r="L71" t="n">
+      <c r="M71" t="n">
         <v>4.5</v>
       </c>
-      <c r="M71" t="n">
-        <v>2.5</v>
+      <c r="N71" t="n">
+        <v>1</v>
       </c>
       <c r="O71" t="n">
         <v>1</v>
@@ -5448,11 +5391,11 @@
         <v>1</v>
       </c>
       <c r="AF71" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AG71" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH71" t="inlineStr">
@@ -5464,7 +5407,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Intercambio de gases en plantas</t>
+          <t>Necesidades de los seres vivos</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5473,41 +5416,71 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D72" t="n">
-        <v>8</v>
+        <v>2</v>
+      </c>
+      <c r="E72" t="n">
+        <v>2</v>
+      </c>
+      <c r="F72" t="n">
+        <v>2.5</v>
       </c>
       <c r="G72" t="n">
-        <v>6</v>
+        <v>2</v>
+      </c>
+      <c r="H72" t="n">
+        <v>2</v>
       </c>
       <c r="I72" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J72" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
+      </c>
+      <c r="K72" t="n">
+        <v>2</v>
       </c>
       <c r="L72" t="n">
-        <v>5</v>
+        <v>3</v>
+      </c>
+      <c r="M72" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N72" t="n">
+        <v>1</v>
+      </c>
+      <c r="O72" t="n">
+        <v>1</v>
       </c>
       <c r="P72" t="n">
         <v>1</v>
       </c>
+      <c r="Q72" t="n">
+        <v>1</v>
+      </c>
       <c r="R72" t="n">
         <v>1</v>
       </c>
       <c r="S72" t="n">
         <v>1</v>
       </c>
+      <c r="T72" t="n">
+        <v>1</v>
+      </c>
       <c r="U72" t="n">
         <v>1</v>
       </c>
+      <c r="V72" t="n">
+        <v>1</v>
+      </c>
       <c r="AF72" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AG72" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH72" t="inlineStr">
@@ -5519,7 +5492,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Invertebrados e insectos</t>
+          <t>Niveles de organización de los seres vivos</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5528,25 +5501,40 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D73" t="n">
-        <v>2</v>
+        <v>4</v>
+      </c>
+      <c r="E73" t="n">
+        <v>7</v>
       </c>
       <c r="F73" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="G73" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H73" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I73" t="n">
-        <v>2</v>
+        <v>5</v>
+      </c>
+      <c r="J73" t="n">
+        <v>4.5</v>
       </c>
       <c r="K73" t="n">
-        <v>2</v>
+        <v>7</v>
+      </c>
+      <c r="L73" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="M73" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="N73" t="n">
+        <v>1</v>
       </c>
       <c r="O73" t="n">
         <v>1</v>
@@ -5560,15 +5548,27 @@
       <c r="R73" t="n">
         <v>1</v>
       </c>
+      <c r="S73" t="n">
+        <v>1</v>
+      </c>
       <c r="T73" t="n">
         <v>1</v>
       </c>
+      <c r="U73" t="n">
+        <v>1</v>
+      </c>
+      <c r="V73" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z73" t="n">
+        <v>1</v>
+      </c>
       <c r="AF73" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AG73" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH73" t="inlineStr">
@@ -5580,7 +5580,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>La célula como unidad de la vida</t>
+          <t>Niveles de organización ecológica</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5589,41 +5589,32 @@
         </is>
       </c>
       <c r="C74" t="n">
+        <v>4</v>
+      </c>
+      <c r="D74" t="n">
+        <v>4</v>
+      </c>
+      <c r="F74" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G74" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H74" t="n">
         <v>3</v>
       </c>
-      <c r="D74" t="n">
+      <c r="J74" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K74" t="n">
         <v>3</v>
       </c>
-      <c r="E74" t="n">
-        <v>7</v>
-      </c>
-      <c r="F74" t="n">
-        <v>8</v>
-      </c>
-      <c r="G74" t="n">
+      <c r="L74" t="n">
         <v>6</v>
-      </c>
-      <c r="H74" t="n">
-        <v>5</v>
-      </c>
-      <c r="I74" t="n">
-        <v>7</v>
-      </c>
-      <c r="J74" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K74" t="n">
-        <v>7</v>
-      </c>
-      <c r="L74" t="n">
-        <v>5</v>
       </c>
       <c r="M74" t="n">
         <v>4.5</v>
       </c>
-      <c r="N74" t="n">
-        <v>1</v>
-      </c>
       <c r="O74" t="n">
         <v>1</v>
       </c>
@@ -5633,9 +5624,6 @@
       <c r="Q74" t="n">
         <v>1</v>
       </c>
-      <c r="R74" t="n">
-        <v>1</v>
-      </c>
       <c r="S74" t="n">
         <v>1</v>
       </c>
@@ -5649,7 +5637,7 @@
         <v>1</v>
       </c>
       <c r="AF74" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AG74" t="inlineStr">
         <is>
@@ -5665,7 +5653,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Necesidades de los seres vivos</t>
+          <t>Nutrición autótrofa y heterótrofa</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -5677,9 +5665,6 @@
         <v>2</v>
       </c>
       <c r="D75" t="n">
-        <v>2</v>
-      </c>
-      <c r="E75" t="n">
         <v>2</v>
       </c>
       <c r="F75" t="n">
@@ -5692,7 +5677,7 @@
         <v>2</v>
       </c>
       <c r="I75" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J75" t="n">
         <v>2.5</v>
@@ -5701,44 +5686,41 @@
         <v>2</v>
       </c>
       <c r="L75" t="n">
+        <v>5</v>
+      </c>
+      <c r="M75" t="n">
+        <v>7</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
         <v>3</v>
       </c>
-      <c r="M75" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N75" t="n">
-        <v>1</v>
-      </c>
-      <c r="O75" t="n">
-        <v>1</v>
-      </c>
-      <c r="P75" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q75" t="n">
-        <v>1</v>
-      </c>
-      <c r="R75" t="n">
-        <v>1</v>
-      </c>
-      <c r="S75" t="n">
-        <v>1</v>
-      </c>
-      <c r="T75" t="n">
-        <v>1</v>
-      </c>
-      <c r="U75" t="n">
-        <v>1</v>
-      </c>
-      <c r="V75" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF75" t="n">
-        <v>2</v>
-      </c>
       <c r="AG75" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH75" t="inlineStr">
@@ -5750,7 +5732,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Niveles de organización de los seres vivos</t>
+          <t>Órganos de los sentidos</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5764,35 +5746,26 @@
       <c r="D76" t="n">
         <v>4</v>
       </c>
-      <c r="E76" t="n">
-        <v>7</v>
-      </c>
       <c r="F76" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G76" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H76" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I76" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J76" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="K76" t="n">
-        <v>7</v>
-      </c>
-      <c r="L76" t="n">
-        <v>4.5</v>
+        <v>2</v>
       </c>
       <c r="M76" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="N76" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="O76" t="n">
         <v>1</v>
@@ -5812,13 +5785,7 @@
       <c r="T76" t="n">
         <v>1</v>
       </c>
-      <c r="U76" t="n">
-        <v>1</v>
-      </c>
       <c r="V76" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z76" t="n">
         <v>1</v>
       </c>
       <c r="AF76" t="n">
@@ -5826,7 +5793,7 @@
       </c>
       <c r="AG76" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH76" t="inlineStr">
@@ -5838,7 +5805,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Niveles de organización ecológica</t>
+          <t>Partes de la planta y sus funciones</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5847,31 +5814,40 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D77" t="n">
-        <v>4</v>
+        <v>2</v>
+      </c>
+      <c r="E77" t="n">
+        <v>2</v>
       </c>
       <c r="F77" t="n">
         <v>2.5</v>
       </c>
       <c r="G77" t="n">
-        <v>8.5</v>
+        <v>2</v>
       </c>
       <c r="H77" t="n">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="I77" t="n">
+        <v>2</v>
       </c>
       <c r="J77" t="n">
         <v>2.5</v>
       </c>
       <c r="K77" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L77" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M77" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
+      </c>
+      <c r="N77" t="n">
+        <v>1</v>
       </c>
       <c r="O77" t="n">
         <v>1</v>
@@ -5882,6 +5858,9 @@
       <c r="Q77" t="n">
         <v>1</v>
       </c>
+      <c r="R77" t="n">
+        <v>1</v>
+      </c>
       <c r="S77" t="n">
         <v>1</v>
       </c>
@@ -5895,11 +5874,11 @@
         <v>1</v>
       </c>
       <c r="AF77" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AG77" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH77" t="inlineStr">
@@ -5911,7 +5890,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Nutrición autótrofa y heterótrofa</t>
+          <t>Plantas y animales útiles al ser humano</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5929,13 +5908,10 @@
         <v>2.5</v>
       </c>
       <c r="G78" t="n">
-        <v>2</v>
+        <v>8.5</v>
       </c>
       <c r="H78" t="n">
         <v>2</v>
-      </c>
-      <c r="I78" t="n">
-        <v>5</v>
       </c>
       <c r="J78" t="n">
         <v>2.5</v>
@@ -5943,11 +5919,8 @@
       <c r="K78" t="n">
         <v>2</v>
       </c>
-      <c r="L78" t="n">
-        <v>5</v>
-      </c>
       <c r="M78" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="O78" t="n">
         <v>1</v>
@@ -5958,23 +5931,17 @@
       <c r="Q78" t="n">
         <v>1</v>
       </c>
-      <c r="R78" t="n">
-        <v>1</v>
-      </c>
       <c r="S78" t="n">
         <v>1</v>
       </c>
       <c r="T78" t="n">
         <v>1</v>
       </c>
-      <c r="U78" t="n">
-        <v>1</v>
-      </c>
       <c r="V78" t="n">
         <v>1</v>
       </c>
       <c r="AF78" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AG78" t="inlineStr">
         <is>
@@ -5990,7 +5957,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Órganos de los sentidos</t>
+          <t>Productores, consumidores y descomponedores</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5999,31 +5966,40 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D79" t="n">
-        <v>4</v>
+        <v>3</v>
+      </c>
+      <c r="E79" t="n">
+        <v>3</v>
       </c>
       <c r="F79" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G79" t="n">
+        <v>2</v>
+      </c>
+      <c r="H79" t="n">
+        <v>3</v>
+      </c>
+      <c r="I79" t="n">
         <v>8</v>
       </c>
-      <c r="G79" t="n">
-        <v>2</v>
-      </c>
-      <c r="H79" t="n">
-        <v>2</v>
-      </c>
-      <c r="I79" t="n">
-        <v>7</v>
-      </c>
       <c r="J79" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="K79" t="n">
         <v>2</v>
       </c>
+      <c r="L79" t="n">
+        <v>6</v>
+      </c>
       <c r="M79" t="n">
-        <v>2.5</v>
+        <v>7</v>
+      </c>
+      <c r="N79" t="n">
+        <v>1</v>
       </c>
       <c r="O79" t="n">
         <v>1</v>
@@ -6043,11 +6019,14 @@
       <c r="T79" t="n">
         <v>1</v>
       </c>
+      <c r="U79" t="n">
+        <v>1</v>
+      </c>
       <c r="V79" t="n">
         <v>1</v>
       </c>
       <c r="AF79" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AG79" t="inlineStr">
         <is>
@@ -6063,7 +6042,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Partes de la planta y sus funciones</t>
+          <t>Reproducción humana y pubertad</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6072,71 +6051,62 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D80" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E80" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F80" t="n">
-        <v>2.5</v>
+        <v>8</v>
       </c>
       <c r="G80" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H80" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I80" t="n">
-        <v>2</v>
-      </c>
-      <c r="J80" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K80" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L80" t="n">
+        <v>5</v>
+      </c>
+      <c r="M80" t="n">
+        <v>7</v>
+      </c>
+      <c r="N80" t="n">
+        <v>1</v>
+      </c>
+      <c r="O80" t="n">
+        <v>1</v>
+      </c>
+      <c r="P80" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>1</v>
+      </c>
+      <c r="R80" t="n">
+        <v>1</v>
+      </c>
+      <c r="U80" t="n">
+        <v>1</v>
+      </c>
+      <c r="V80" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z80" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF80" t="n">
         <v>4</v>
       </c>
-      <c r="M80" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N80" t="n">
-        <v>1</v>
-      </c>
-      <c r="O80" t="n">
-        <v>1</v>
-      </c>
-      <c r="P80" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q80" t="n">
-        <v>1</v>
-      </c>
-      <c r="R80" t="n">
-        <v>1</v>
-      </c>
-      <c r="S80" t="n">
-        <v>1</v>
-      </c>
-      <c r="T80" t="n">
-        <v>1</v>
-      </c>
-      <c r="U80" t="n">
-        <v>1</v>
-      </c>
-      <c r="V80" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF80" t="n">
-        <v>2</v>
-      </c>
       <c r="AG80" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH80" t="inlineStr">
@@ -6148,7 +6118,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Plantas y animales útiles al ser humano</t>
+          <t>Reproducción sexual y asexual</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6157,29 +6127,35 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D81" t="n">
-        <v>2</v>
+        <v>6</v>
+      </c>
+      <c r="E81" t="n">
+        <v>8</v>
       </c>
       <c r="F81" t="n">
-        <v>2.5</v>
+        <v>8</v>
       </c>
       <c r="G81" t="n">
-        <v>8.5</v>
+        <v>3</v>
       </c>
       <c r="H81" t="n">
-        <v>2</v>
-      </c>
-      <c r="J81" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K81" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="I81" t="n">
+        <v>4</v>
+      </c>
+      <c r="L81" t="n">
+        <v>5</v>
       </c>
       <c r="M81" t="n">
         <v>2.5</v>
       </c>
+      <c r="N81" t="n">
+        <v>1</v>
+      </c>
       <c r="O81" t="n">
         <v>1</v>
       </c>
@@ -6189,21 +6165,24 @@
       <c r="Q81" t="n">
         <v>1</v>
       </c>
-      <c r="S81" t="n">
-        <v>1</v>
-      </c>
-      <c r="T81" t="n">
+      <c r="R81" t="n">
+        <v>1</v>
+      </c>
+      <c r="U81" t="n">
         <v>1</v>
       </c>
       <c r="V81" t="n">
         <v>1</v>
       </c>
+      <c r="Z81" t="n">
+        <v>1</v>
+      </c>
       <c r="AF81" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AG81" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH81" t="inlineStr">
@@ -6215,7 +6194,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Productores, consumidores y descomponedores</t>
+          <t>Requerimientos de materia y energía de la célula</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6224,53 +6203,32 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>3</v>
-      </c>
-      <c r="D82" t="n">
-        <v>3</v>
-      </c>
-      <c r="E82" t="n">
-        <v>3</v>
-      </c>
-      <c r="F82" t="n">
-        <v>2.5</v>
+        <v>9</v>
       </c>
       <c r="G82" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H82" t="n">
-        <v>3</v>
-      </c>
-      <c r="I82" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J82" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="K82" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="L82" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M82" t="n">
         <v>7</v>
       </c>
-      <c r="N82" t="n">
-        <v>1</v>
-      </c>
-      <c r="O82" t="n">
-        <v>1</v>
-      </c>
       <c r="P82" t="n">
         <v>1</v>
       </c>
       <c r="Q82" t="n">
         <v>1</v>
       </c>
-      <c r="R82" t="n">
-        <v>1</v>
-      </c>
       <c r="S82" t="n">
         <v>1</v>
       </c>
@@ -6283,24 +6241,27 @@
       <c r="V82" t="n">
         <v>1</v>
       </c>
+      <c r="Z82" t="n">
+        <v>1</v>
+      </c>
       <c r="AF82" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="AG82" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>tardio</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Reproducción sexual de las plantas con flor</t>
+          <t>Respiración celular</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6318,22 +6279,25 @@
         <v>8</v>
       </c>
       <c r="F83" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G83" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H83" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I83" t="n">
-        <v>4</v>
+        <v>7</v>
+      </c>
+      <c r="J83" t="n">
+        <v>7</v>
       </c>
       <c r="K83" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="L83" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M83" t="n">
         <v>7</v>
@@ -6351,6 +6315,9 @@
         <v>1</v>
       </c>
       <c r="R83" t="n">
+        <v>1</v>
+      </c>
+      <c r="S83" t="n">
         <v>1</v>
       </c>
       <c r="T83" t="n">
@@ -6379,7 +6346,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Reproducción humana y pubertad</t>
+          <t>Respuesta de los seres vivos a estímulos</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6388,10 +6355,10 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D84" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E84" t="n">
         <v>8</v>
@@ -6400,19 +6367,25 @@
         <v>8</v>
       </c>
       <c r="G84" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H84" t="n">
+        <v>2</v>
+      </c>
+      <c r="I84" t="n">
         <v>3</v>
       </c>
-      <c r="H84" t="n">
-        <v>4</v>
-      </c>
-      <c r="I84" t="n">
-        <v>4</v>
+      <c r="J84" t="n">
+        <v>7</v>
+      </c>
+      <c r="K84" t="n">
+        <v>2</v>
       </c>
       <c r="L84" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M84" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="N84" t="n">
         <v>1</v>
@@ -6429,17 +6402,20 @@
       <c r="R84" t="n">
         <v>1</v>
       </c>
+      <c r="S84" t="n">
+        <v>1</v>
+      </c>
+      <c r="T84" t="n">
+        <v>1</v>
+      </c>
       <c r="U84" t="n">
         <v>1</v>
       </c>
       <c r="V84" t="n">
         <v>1</v>
       </c>
-      <c r="Z84" t="n">
-        <v>1</v>
-      </c>
       <c r="AF84" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AG84" t="inlineStr">
         <is>
@@ -6455,7 +6431,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Reproducción sexual y asexual</t>
+          <t>Modelo estímulo-respuesta y retroalimentación negativa</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6464,10 +6440,7 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>6</v>
-      </c>
-      <c r="D85" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E85" t="n">
         <v>8</v>
@@ -6476,19 +6449,19 @@
         <v>8</v>
       </c>
       <c r="G85" t="n">
-        <v>3</v>
+        <v>8.5</v>
       </c>
       <c r="H85" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I85" t="n">
-        <v>4</v>
-      </c>
-      <c r="L85" t="n">
-        <v>5</v>
+        <v>7</v>
+      </c>
+      <c r="J85" t="n">
+        <v>7</v>
       </c>
       <c r="M85" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="N85" t="n">
         <v>1</v>
@@ -6505,17 +6478,14 @@
       <c r="R85" t="n">
         <v>1</v>
       </c>
-      <c r="U85" t="n">
+      <c r="S85" t="n">
         <v>1</v>
       </c>
       <c r="V85" t="n">
         <v>1</v>
       </c>
-      <c r="Z85" t="n">
-        <v>1</v>
-      </c>
       <c r="AF85" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AG85" t="inlineStr">
         <is>
@@ -6531,7 +6501,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Requerimientos de materia y energía de la célula</t>
+          <t>Seres vivos y no vivos</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6540,28 +6510,37 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D86" t="n">
-        <v>6</v>
+        <v>2</v>
+      </c>
+      <c r="E86" t="n">
+        <v>2</v>
+      </c>
+      <c r="F86" t="n">
+        <v>2.5</v>
       </c>
       <c r="G86" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H86" t="n">
-        <v>7</v>
-      </c>
-      <c r="J86" t="n">
-        <v>4.5</v>
+        <v>2</v>
       </c>
       <c r="K86" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="L86" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M86" t="n">
-        <v>7</v>
+        <v>2.5</v>
+      </c>
+      <c r="N86" t="n">
+        <v>1</v>
+      </c>
+      <c r="O86" t="n">
+        <v>1</v>
       </c>
       <c r="P86" t="n">
         <v>1</v>
@@ -6569,9 +6548,6 @@
       <c r="Q86" t="n">
         <v>1</v>
       </c>
-      <c r="S86" t="n">
-        <v>1</v>
-      </c>
       <c r="T86" t="n">
         <v>1</v>
       </c>
@@ -6581,15 +6557,12 @@
       <c r="V86" t="n">
         <v>1</v>
       </c>
-      <c r="Z86" t="n">
-        <v>1</v>
-      </c>
       <c r="AF86" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AG86" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH86" t="inlineStr">
@@ -6601,7 +6574,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Antibióticos y resistencia bacteriana</t>
+          <t>Sistema circulatorio</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -6610,19 +6583,37 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D87" t="n">
-        <v>7</v>
+        <v>4</v>
+      </c>
+      <c r="F87" t="n">
+        <v>8</v>
       </c>
       <c r="G87" t="n">
-        <v>8.5</v>
+        <v>4</v>
       </c>
       <c r="H87" t="n">
+        <v>2</v>
+      </c>
+      <c r="I87" t="n">
+        <v>5</v>
+      </c>
+      <c r="J87" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K87" t="n">
         <v>4</v>
       </c>
       <c r="L87" t="n">
-        <v>7.5</v>
+        <v>4</v>
+      </c>
+      <c r="M87" t="n">
+        <v>7</v>
+      </c>
+      <c r="O87" t="n">
+        <v>1</v>
       </c>
       <c r="P87" t="n">
         <v>1</v>
@@ -6630,14 +6621,26 @@
       <c r="Q87" t="n">
         <v>1</v>
       </c>
+      <c r="R87" t="n">
+        <v>1</v>
+      </c>
+      <c r="S87" t="n">
+        <v>1</v>
+      </c>
+      <c r="T87" t="n">
+        <v>1</v>
+      </c>
       <c r="U87" t="n">
         <v>1</v>
       </c>
+      <c r="V87" t="n">
+        <v>1</v>
+      </c>
       <c r="Z87" t="n">
         <v>1</v>
       </c>
       <c r="AF87" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AG87" t="inlineStr">
         <is>
@@ -6653,7 +6656,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Respiración celular</t>
+          <t>Sistema digestivo</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -6662,41 +6665,35 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D88" t="n">
-        <v>6</v>
-      </c>
-      <c r="E88" t="n">
+        <v>4</v>
+      </c>
+      <c r="F88" t="n">
         <v>8</v>
       </c>
-      <c r="F88" t="n">
+      <c r="G88" t="n">
+        <v>2</v>
+      </c>
+      <c r="H88" t="n">
+        <v>4</v>
+      </c>
+      <c r="I88" t="n">
         <v>5</v>
       </c>
-      <c r="G88" t="n">
-        <v>6</v>
-      </c>
-      <c r="H88" t="n">
-        <v>7</v>
-      </c>
-      <c r="I88" t="n">
-        <v>7</v>
-      </c>
       <c r="J88" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="K88" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L88" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M88" t="n">
         <v>7</v>
       </c>
-      <c r="N88" t="n">
-        <v>1</v>
-      </c>
       <c r="O88" t="n">
         <v>1</v>
       </c>
@@ -6721,8 +6718,11 @@
       <c r="V88" t="n">
         <v>1</v>
       </c>
+      <c r="Z88" t="n">
+        <v>1</v>
+      </c>
       <c r="AF88" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AG88" t="inlineStr">
         <is>
@@ -6738,7 +6738,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Respuesta de los seres vivos a estímulos</t>
+          <t>Sistema endocrino y hormonas</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -6747,10 +6747,7 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>2</v>
-      </c>
-      <c r="D89" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E89" t="n">
         <v>8</v>
@@ -6761,23 +6758,14 @@
       <c r="G89" t="n">
         <v>8.5</v>
       </c>
-      <c r="H89" t="n">
-        <v>2</v>
-      </c>
-      <c r="I89" t="n">
-        <v>3</v>
-      </c>
       <c r="J89" t="n">
         <v>7</v>
       </c>
-      <c r="K89" t="n">
-        <v>2</v>
-      </c>
       <c r="L89" t="n">
-        <v>3</v>
+        <v>7.5</v>
       </c>
       <c r="M89" t="n">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="N89" t="n">
         <v>1</v>
@@ -6788,30 +6776,24 @@
       <c r="P89" t="n">
         <v>1</v>
       </c>
-      <c r="Q89" t="n">
-        <v>1</v>
-      </c>
-      <c r="R89" t="n">
-        <v>1</v>
-      </c>
       <c r="S89" t="n">
         <v>1</v>
       </c>
-      <c r="T89" t="n">
-        <v>1</v>
-      </c>
       <c r="U89" t="n">
         <v>1</v>
       </c>
       <c r="V89" t="n">
         <v>1</v>
       </c>
+      <c r="Z89" t="n">
+        <v>1</v>
+      </c>
       <c r="AF89" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="AG89" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH89" t="inlineStr">
@@ -6823,7 +6805,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Modelo estímulo-respuesta y retroalimentación negativa</t>
+          <t>Sistema locomotor</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -6832,32 +6814,32 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>9</v>
-      </c>
-      <c r="E90" t="n">
-        <v>8</v>
+        <v>4</v>
+      </c>
+      <c r="D90" t="n">
+        <v>4</v>
       </c>
       <c r="F90" t="n">
         <v>8</v>
       </c>
       <c r="G90" t="n">
-        <v>8.5</v>
+        <v>2</v>
       </c>
       <c r="H90" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I90" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J90" t="n">
-        <v>7</v>
+        <v>4.5</v>
+      </c>
+      <c r="K90" t="n">
+        <v>2</v>
       </c>
       <c r="M90" t="n">
         <v>4.5</v>
       </c>
-      <c r="N90" t="n">
-        <v>1</v>
-      </c>
       <c r="O90" t="n">
         <v>1</v>
       </c>
@@ -6873,11 +6855,14 @@
       <c r="S90" t="n">
         <v>1</v>
       </c>
+      <c r="T90" t="n">
+        <v>1</v>
+      </c>
       <c r="V90" t="n">
         <v>1</v>
       </c>
       <c r="AF90" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="AG90" t="inlineStr">
         <is>
@@ -6893,7 +6878,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Selección natural</t>
+          <t>Sistema respiratorio</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -6902,22 +6887,34 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D91" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F91" t="n">
         <v>8</v>
       </c>
       <c r="G91" t="n">
+        <v>6</v>
+      </c>
+      <c r="H91" t="n">
+        <v>2</v>
+      </c>
+      <c r="I91" t="n">
+        <v>5</v>
+      </c>
+      <c r="J91" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K91" t="n">
         <v>4</v>
       </c>
-      <c r="K91" t="n">
-        <v>2</v>
-      </c>
       <c r="L91" t="n">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="M91" t="n">
+        <v>7</v>
       </c>
       <c r="O91" t="n">
         <v>1</v>
@@ -6925,21 +6922,33 @@
       <c r="P91" t="n">
         <v>1</v>
       </c>
+      <c r="Q91" t="n">
+        <v>1</v>
+      </c>
+      <c r="R91" t="n">
+        <v>1</v>
+      </c>
+      <c r="S91" t="n">
+        <v>1</v>
+      </c>
       <c r="T91" t="n">
         <v>1</v>
       </c>
       <c r="U91" t="n">
         <v>1</v>
       </c>
+      <c r="V91" t="n">
+        <v>1</v>
+      </c>
       <c r="Z91" t="n">
         <v>1</v>
       </c>
       <c r="AF91" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AG91" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH91" t="inlineStr">
@@ -6951,7 +6960,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Seres vivos y no vivos</t>
+          <t>Tejidos animales</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6960,31 +6969,22 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D92" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E92" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F92" t="n">
-        <v>2.5</v>
+        <v>8</v>
       </c>
       <c r="G92" t="n">
-        <v>2</v>
+        <v>8.5</v>
       </c>
       <c r="H92" t="n">
-        <v>2</v>
-      </c>
-      <c r="K92" t="n">
-        <v>2</v>
-      </c>
-      <c r="L92" t="n">
-        <v>3</v>
-      </c>
-      <c r="M92" t="n">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="N92" t="n">
         <v>1</v>
@@ -6998,33 +6998,27 @@
       <c r="Q92" t="n">
         <v>1</v>
       </c>
-      <c r="T92" t="n">
-        <v>1</v>
-      </c>
-      <c r="U92" t="n">
-        <v>1</v>
-      </c>
-      <c r="V92" t="n">
+      <c r="Z92" t="n">
         <v>1</v>
       </c>
       <c r="AF92" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AG92" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Sistema circulatorio</t>
+          <t>Tejidos vegetales</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7033,35 +7027,35 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D93" t="n">
-        <v>4</v>
+        <v>8</v>
+      </c>
+      <c r="E93" t="n">
+        <v>7</v>
       </c>
       <c r="F93" t="n">
         <v>8</v>
       </c>
       <c r="G93" t="n">
-        <v>4</v>
+        <v>8.5</v>
       </c>
       <c r="H93" t="n">
-        <v>2</v>
-      </c>
-      <c r="I93" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J93" t="n">
         <v>4.5</v>
       </c>
-      <c r="K93" t="n">
-        <v>4</v>
-      </c>
       <c r="L93" t="n">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="M93" t="n">
         <v>7</v>
       </c>
+      <c r="N93" t="n">
+        <v>1</v>
+      </c>
       <c r="O93" t="n">
         <v>1</v>
       </c>
@@ -7071,26 +7065,17 @@
       <c r="Q93" t="n">
         <v>1</v>
       </c>
-      <c r="R93" t="n">
-        <v>1</v>
-      </c>
       <c r="S93" t="n">
         <v>1</v>
       </c>
-      <c r="T93" t="n">
-        <v>1</v>
-      </c>
       <c r="U93" t="n">
         <v>1</v>
       </c>
       <c r="V93" t="n">
         <v>1</v>
       </c>
-      <c r="Z93" t="n">
-        <v>1</v>
-      </c>
       <c r="AF93" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AG93" t="inlineStr">
         <is>
@@ -7106,7 +7091,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Sistema digestivo</t>
+          <t>Transporte en plantas: xilema y floema</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7115,19 +7100,16 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D94" t="n">
-        <v>4</v>
-      </c>
-      <c r="F94" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G94" t="n">
         <v>2</v>
       </c>
       <c r="H94" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I94" t="n">
         <v>5</v>
@@ -7135,18 +7117,12 @@
       <c r="J94" t="n">
         <v>4.5</v>
       </c>
-      <c r="K94" t="n">
-        <v>4</v>
-      </c>
       <c r="L94" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M94" t="n">
         <v>7</v>
       </c>
-      <c r="O94" t="n">
-        <v>1</v>
-      </c>
       <c r="P94" t="n">
         <v>1</v>
       </c>
@@ -7159,20 +7135,14 @@
       <c r="S94" t="n">
         <v>1</v>
       </c>
-      <c r="T94" t="n">
-        <v>1</v>
-      </c>
       <c r="U94" t="n">
         <v>1</v>
       </c>
       <c r="V94" t="n">
         <v>1</v>
       </c>
-      <c r="Z94" t="n">
-        <v>1</v>
-      </c>
       <c r="AF94" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AG94" t="inlineStr">
         <is>
@@ -7188,7 +7158,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Sistema endocrino y hormonas</t>
+          <t>Variación genética en la descendencia</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7197,28 +7167,31 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>9</v>
-      </c>
-      <c r="E95" t="n">
-        <v>8</v>
+        <v>6</v>
+      </c>
+      <c r="D95" t="n">
+        <v>6</v>
       </c>
       <c r="F95" t="n">
         <v>8</v>
       </c>
       <c r="G95" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="J95" t="n">
-        <v>7</v>
+        <v>4</v>
+      </c>
+      <c r="H95" t="n">
+        <v>7</v>
+      </c>
+      <c r="I95" t="n">
+        <v>8</v>
+      </c>
+      <c r="K95" t="n">
+        <v>5</v>
       </c>
       <c r="L95" t="n">
         <v>7.5</v>
       </c>
       <c r="M95" t="n">
-        <v>7</v>
-      </c>
-      <c r="N95" t="n">
-        <v>1</v>
+        <v>4.5</v>
       </c>
       <c r="O95" t="n">
         <v>1</v>
@@ -7226,7 +7199,13 @@
       <c r="P95" t="n">
         <v>1</v>
       </c>
-      <c r="S95" t="n">
+      <c r="Q95" t="n">
+        <v>1</v>
+      </c>
+      <c r="R95" t="n">
+        <v>1</v>
+      </c>
+      <c r="T95" t="n">
         <v>1</v>
       </c>
       <c r="U95" t="n">
@@ -7235,11 +7214,8 @@
       <c r="V95" t="n">
         <v>1</v>
       </c>
-      <c r="Z95" t="n">
-        <v>1</v>
-      </c>
       <c r="AF95" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AG95" t="inlineStr">
         <is>
@@ -7255,40 +7231,49 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Sistema locomotor</t>
+          <t>Célula animal y célula vegetal</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>incierto</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D96" t="n">
-        <v>4</v>
+        <v>6</v>
+      </c>
+      <c r="E96" t="n">
+        <v>7</v>
       </c>
       <c r="F96" t="n">
         <v>8</v>
       </c>
       <c r="G96" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H96" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I96" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J96" t="n">
         <v>4.5</v>
       </c>
       <c r="K96" t="n">
-        <v>2</v>
+        <v>7</v>
+      </c>
+      <c r="L96" t="n">
+        <v>7.5</v>
       </c>
       <c r="M96" t="n">
-        <v>4.5</v>
+        <v>7</v>
+      </c>
+      <c r="N96" t="n">
+        <v>1</v>
       </c>
       <c r="O96" t="n">
         <v>1</v>
@@ -7308,11 +7293,14 @@
       <c r="T96" t="n">
         <v>1</v>
       </c>
+      <c r="U96" t="n">
+        <v>1</v>
+      </c>
       <c r="V96" t="n">
         <v>1</v>
       </c>
       <c r="AF96" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AG96" t="inlineStr">
         <is>
@@ -7321,50 +7309,32 @@
       </c>
       <c r="AH96" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>tardio</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Sistema respiratorio</t>
+          <t>Especiación y macroevolución</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>incierto</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D97" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F97" t="n">
         <v>8</v>
       </c>
       <c r="G97" t="n">
-        <v>6</v>
-      </c>
-      <c r="H97" t="n">
-        <v>2</v>
-      </c>
-      <c r="I97" t="n">
-        <v>5</v>
-      </c>
-      <c r="J97" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K97" t="n">
-        <v>4</v>
-      </c>
-      <c r="L97" t="n">
-        <v>4</v>
-      </c>
-      <c r="M97" t="n">
-        <v>7</v>
+        <v>8.5</v>
       </c>
       <c r="O97" t="n">
         <v>1</v>
@@ -7372,57 +7342,36 @@
       <c r="P97" t="n">
         <v>1</v>
       </c>
-      <c r="Q97" t="n">
-        <v>1</v>
-      </c>
-      <c r="R97" t="n">
-        <v>1</v>
-      </c>
-      <c r="S97" t="n">
-        <v>1</v>
-      </c>
-      <c r="T97" t="n">
-        <v>1</v>
-      </c>
-      <c r="U97" t="n">
-        <v>1</v>
-      </c>
-      <c r="V97" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z97" t="n">
-        <v>1</v>
-      </c>
       <c r="AF97" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="AG97" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>posterior</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Tejidos animales</t>
+          <t>Estructuras celulares básicas</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>incierto</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D98" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E98" t="n">
         <v>7</v>
@@ -7431,9 +7380,24 @@
         <v>8</v>
       </c>
       <c r="G98" t="n">
-        <v>8.5</v>
+        <v>6</v>
       </c>
       <c r="H98" t="n">
+        <v>5</v>
+      </c>
+      <c r="I98" t="n">
+        <v>7</v>
+      </c>
+      <c r="J98" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K98" t="n">
+        <v>7</v>
+      </c>
+      <c r="L98" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="M98" t="n">
         <v>7</v>
       </c>
       <c r="N98" t="n">
@@ -7448,64 +7412,76 @@
       <c r="Q98" t="n">
         <v>1</v>
       </c>
+      <c r="R98" t="n">
+        <v>1</v>
+      </c>
+      <c r="S98" t="n">
+        <v>1</v>
+      </c>
+      <c r="T98" t="n">
+        <v>1</v>
+      </c>
+      <c r="U98" t="n">
+        <v>1</v>
+      </c>
+      <c r="V98" t="n">
+        <v>1</v>
+      </c>
       <c r="Z98" t="n">
         <v>1</v>
       </c>
       <c r="AF98" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AG98" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>tardio</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Tejidos vegetales</t>
+          <t>Herencia de rasgos</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>incierto</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D99" t="n">
-        <v>8</v>
-      </c>
-      <c r="E99" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F99" t="n">
         <v>8</v>
       </c>
       <c r="G99" t="n">
-        <v>8.5</v>
+        <v>2</v>
       </c>
       <c r="H99" t="n">
-        <v>7</v>
+        <v>3</v>
+      </c>
+      <c r="I99" t="n">
+        <v>8</v>
       </c>
       <c r="J99" t="n">
+        <v>7</v>
+      </c>
+      <c r="L99" t="n">
+        <v>5</v>
+      </c>
+      <c r="M99" t="n">
         <v>4.5</v>
       </c>
-      <c r="L99" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="M99" t="n">
-        <v>7</v>
-      </c>
-      <c r="N99" t="n">
-        <v>1</v>
-      </c>
       <c r="O99" t="n">
         <v>1</v>
       </c>
@@ -7515,6 +7491,9 @@
       <c r="Q99" t="n">
         <v>1</v>
       </c>
+      <c r="R99" t="n">
+        <v>1</v>
+      </c>
       <c r="S99" t="n">
         <v>1</v>
       </c>
@@ -7525,7 +7504,7 @@
         <v>1</v>
       </c>
       <c r="AF99" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AG99" t="inlineStr">
         <is>
@@ -7534,41 +7513,29 @@
       </c>
       <c r="AH99" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>tardio</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Transporte en plantas: xilema y floema</t>
+          <t>Mutaciones</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>incierto</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D100" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G100" t="n">
-        <v>2</v>
-      </c>
-      <c r="H100" t="n">
-        <v>7</v>
-      </c>
-      <c r="I100" t="n">
-        <v>5</v>
-      </c>
-      <c r="J100" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L100" t="n">
-        <v>5</v>
+        <v>8.5</v>
       </c>
       <c r="M100" t="n">
         <v>7</v>
@@ -7576,44 +7543,35 @@
       <c r="P100" t="n">
         <v>1</v>
       </c>
-      <c r="Q100" t="n">
-        <v>1</v>
-      </c>
-      <c r="R100" t="n">
-        <v>1</v>
-      </c>
-      <c r="S100" t="n">
-        <v>1</v>
-      </c>
-      <c r="U100" t="n">
-        <v>1</v>
-      </c>
       <c r="V100" t="n">
         <v>1</v>
       </c>
+      <c r="Z100" t="n">
+        <v>1</v>
+      </c>
       <c r="AF100" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG100" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH100" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>posterior</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Variación genética en la descendencia</t>
+          <t>Reproducción sexual de las plantas con flor</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>incierto</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -7622,26 +7580,32 @@
       <c r="D101" t="n">
         <v>6</v>
       </c>
+      <c r="E101" t="n">
+        <v>8</v>
+      </c>
       <c r="F101" t="n">
         <v>8</v>
       </c>
       <c r="G101" t="n">
+        <v>2</v>
+      </c>
+      <c r="H101" t="n">
+        <v>2</v>
+      </c>
+      <c r="I101" t="n">
         <v>4</v>
       </c>
-      <c r="H101" t="n">
-        <v>7</v>
-      </c>
-      <c r="I101" t="n">
-        <v>8</v>
-      </c>
       <c r="K101" t="n">
+        <v>2</v>
+      </c>
+      <c r="L101" t="n">
         <v>5</v>
       </c>
-      <c r="L101" t="n">
-        <v>7.5</v>
-      </c>
       <c r="M101" t="n">
-        <v>4.5</v>
+        <v>7</v>
+      </c>
+      <c r="N101" t="n">
+        <v>1</v>
       </c>
       <c r="O101" t="n">
         <v>1</v>
@@ -7665,7 +7629,7 @@
         <v>1</v>
       </c>
       <c r="AF101" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AG101" t="inlineStr">
         <is>
@@ -7674,7 +7638,7 @@
       </c>
       <c r="AH101" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>tardio</t>
         </is>
       </c>
     </row>
@@ -7724,7 +7688,10 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>10</v>
+        <v>8</v>
+      </c>
+      <c r="D103" t="n">
+        <v>8</v>
       </c>
       <c r="F103" t="n">
         <v>8</v>
@@ -7745,11 +7712,11 @@
         <v>1</v>
       </c>
       <c r="AF103" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG103" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH103" t="inlineStr">
@@ -7896,7 +7863,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Especiación y macroevolución</t>
+          <t>Eutrofización</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -7905,26 +7872,17 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>10</v>
-      </c>
-      <c r="F107" t="n">
-        <v>8</v>
-      </c>
-      <c r="G107" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="O107" t="n">
-        <v>1</v>
-      </c>
-      <c r="P107" t="n">
-        <v>1</v>
+        <v>7</v>
+      </c>
+      <c r="D107" t="n">
+        <v>7</v>
       </c>
       <c r="AF107" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG107" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH107" t="inlineStr">
@@ -7936,7 +7894,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Eutrofización</t>
+          <t>Evidencias de la evolución</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -7945,17 +7903,38 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>7</v>
-      </c>
-      <c r="D108" t="n">
-        <v>7</v>
+        <v>9</v>
+      </c>
+      <c r="F108" t="n">
+        <v>8</v>
+      </c>
+      <c r="G108" t="n">
+        <v>4</v>
+      </c>
+      <c r="I108" t="n">
+        <v>8</v>
+      </c>
+      <c r="M108" t="n">
+        <v>7</v>
+      </c>
+      <c r="O108" t="n">
+        <v>1</v>
+      </c>
+      <c r="P108" t="n">
+        <v>1</v>
+      </c>
+      <c r="R108" t="n">
+        <v>1</v>
+      </c>
+      <c r="V108" t="n">
+        <v>1</v>
       </c>
       <c r="AF108" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG108" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH108" t="inlineStr">
@@ -7967,7 +7946,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Evidencias de la evolución</t>
+          <t>Fases de la fotosíntesis y ciclo de Calvin</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7976,38 +7955,23 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>9</v>
+        <v>6</v>
+      </c>
+      <c r="D109" t="n">
+        <v>6</v>
       </c>
       <c r="F109" t="n">
         <v>8</v>
       </c>
-      <c r="G109" t="n">
-        <v>4</v>
-      </c>
-      <c r="I109" t="n">
-        <v>8</v>
-      </c>
-      <c r="M109" t="n">
-        <v>7</v>
-      </c>
       <c r="O109" t="n">
         <v>1</v>
       </c>
-      <c r="P109" t="n">
-        <v>1</v>
-      </c>
-      <c r="R109" t="n">
-        <v>1</v>
-      </c>
-      <c r="V109" t="n">
-        <v>1</v>
-      </c>
       <c r="AF109" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG109" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH109" t="inlineStr">
@@ -8019,7 +7983,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Fases de la fotosíntesis y ciclo de Calvin</t>
+          <t>Secuenciación del ADN y perfiles genéticos</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8028,15 +7992,18 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>6</v>
-      </c>
-      <c r="D110" t="n">
-        <v>6</v>
-      </c>
-      <c r="F110" t="n">
-        <v>8</v>
-      </c>
-      <c r="O110" t="n">
+        <v>9</v>
+      </c>
+      <c r="G110" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H110" t="n">
+        <v>7</v>
+      </c>
+      <c r="P110" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q110" t="n">
         <v>1</v>
       </c>
       <c r="AF110" t="n">
@@ -8044,7 +8011,7 @@
       </c>
       <c r="AG110" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH110" t="inlineStr">
@@ -8056,7 +8023,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Secuenciación del ADN y perfiles genéticos</t>
+          <t>Impulso nervioso y sinapsis</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -8065,18 +8032,18 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>9</v>
-      </c>
-      <c r="G111" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="H111" t="n">
-        <v>7</v>
-      </c>
-      <c r="P111" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q111" t="n">
+        <v>10</v>
+      </c>
+      <c r="F111" t="n">
+        <v>8</v>
+      </c>
+      <c r="J111" t="n">
+        <v>7</v>
+      </c>
+      <c r="O111" t="n">
+        <v>1</v>
+      </c>
+      <c r="S111" t="n">
         <v>1</v>
       </c>
       <c r="AF111" t="n">
@@ -8096,7 +8063,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Impulso nervioso y sinapsis</t>
+          <t>Ingeniería genética y ADN recombinante</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -8105,22 +8072,37 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F112" t="n">
         <v>8</v>
       </c>
-      <c r="J112" t="n">
+      <c r="G112" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H112" t="n">
+        <v>7</v>
+      </c>
+      <c r="M112" t="n">
         <v>7</v>
       </c>
       <c r="O112" t="n">
         <v>1</v>
       </c>
-      <c r="S112" t="n">
+      <c r="P112" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q112" t="n">
+        <v>1</v>
+      </c>
+      <c r="V112" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z112" t="n">
         <v>1</v>
       </c>
       <c r="AF112" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG112" t="inlineStr">
         <is>
@@ -8136,7 +8118,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Ingeniería genética y ADN recombinante</t>
+          <t>Inmunidad adaptativa</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -8147,27 +8129,15 @@
       <c r="C113" t="n">
         <v>9</v>
       </c>
-      <c r="F113" t="n">
-        <v>8</v>
-      </c>
       <c r="G113" t="n">
         <v>8.5</v>
       </c>
-      <c r="H113" t="n">
-        <v>7</v>
-      </c>
       <c r="M113" t="n">
         <v>7</v>
       </c>
-      <c r="O113" t="n">
-        <v>1</v>
-      </c>
       <c r="P113" t="n">
         <v>1</v>
       </c>
-      <c r="Q113" t="n">
-        <v>1</v>
-      </c>
       <c r="V113" t="n">
         <v>1</v>
       </c>
@@ -8175,7 +8145,7 @@
         <v>1</v>
       </c>
       <c r="AF113" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG113" t="inlineStr">
         <is>
@@ -8191,7 +8161,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Inmunidad adaptativa</t>
+          <t>Inmunidad innata</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -8214,9 +8184,6 @@
       <c r="V114" t="n">
         <v>1</v>
       </c>
-      <c r="Z114" t="n">
-        <v>1</v>
-      </c>
       <c r="AF114" t="n">
         <v>10</v>
       </c>
@@ -8234,7 +8201,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Inmunidad innata</t>
+          <t>Nutrición mineral de las plantas</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -8243,22 +8210,28 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>9</v>
+        <v>11</v>
+      </c>
+      <c r="F115" t="n">
+        <v>5</v>
       </c>
       <c r="G115" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="M115" t="n">
-        <v>7</v>
+        <v>2</v>
+      </c>
+      <c r="I115" t="n">
+        <v>4</v>
+      </c>
+      <c r="O115" t="n">
+        <v>1</v>
       </c>
       <c r="P115" t="n">
         <v>1</v>
       </c>
-      <c r="V115" t="n">
+      <c r="R115" t="n">
         <v>1</v>
       </c>
       <c r="AF115" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG115" t="inlineStr">
         <is>
@@ -8274,7 +8247,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Nutrición mineral de las plantas</t>
+          <t>Presión y flujo de fluidos en los seres vivos</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -8285,22 +8258,16 @@
       <c r="C116" t="n">
         <v>11</v>
       </c>
-      <c r="F116" t="n">
-        <v>5</v>
-      </c>
-      <c r="G116" t="n">
-        <v>2</v>
-      </c>
-      <c r="I116" t="n">
-        <v>4</v>
-      </c>
-      <c r="O116" t="n">
-        <v>1</v>
-      </c>
-      <c r="P116" t="n">
-        <v>1</v>
-      </c>
-      <c r="R116" t="n">
+      <c r="H116" t="n">
+        <v>7</v>
+      </c>
+      <c r="M116" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q116" t="n">
+        <v>1</v>
+      </c>
+      <c r="V116" t="n">
         <v>1</v>
       </c>
       <c r="AF116" t="n">
@@ -8320,7 +8287,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Presión y flujo de fluidos en los seres vivos</t>
+          <t>Proteínas: estructura y función</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -8329,38 +8296,35 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>11</v>
-      </c>
-      <c r="H117" t="n">
-        <v>7</v>
-      </c>
-      <c r="M117" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q117" t="n">
-        <v>1</v>
-      </c>
-      <c r="V117" t="n">
+        <v>6</v>
+      </c>
+      <c r="D117" t="n">
+        <v>6</v>
+      </c>
+      <c r="G117" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="P117" t="n">
         <v>1</v>
       </c>
       <c r="AF117" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="AG117" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH117" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Proteínas: estructura y función</t>
+          <t>Regulación de la expresión génica</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -8369,14 +8333,17 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>6</v>
-      </c>
-      <c r="D118" t="n">
-        <v>6</v>
+        <v>9</v>
+      </c>
+      <c r="F118" t="n">
+        <v>8</v>
       </c>
       <c r="G118" t="n">
         <v>8.5</v>
       </c>
+      <c r="O118" t="n">
+        <v>1</v>
+      </c>
       <c r="P118" t="n">
         <v>1</v>
       </c>
@@ -8385,7 +8352,7 @@
       </c>
       <c r="AG118" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH118" t="inlineStr">
@@ -8397,7 +8364,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Regulación de la expresión génica</t>
+          <t>Relación superficie-volumen</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -8406,7 +8373,7 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F119" t="n">
         <v>8</v>
@@ -8414,14 +8381,29 @@
       <c r="G119" t="n">
         <v>8.5</v>
       </c>
+      <c r="J119" t="n">
+        <v>7</v>
+      </c>
+      <c r="K119" t="n">
+        <v>7</v>
+      </c>
+      <c r="L119" t="n">
+        <v>7.5</v>
+      </c>
       <c r="O119" t="n">
         <v>1</v>
       </c>
       <c r="P119" t="n">
         <v>1</v>
       </c>
-      <c r="AF119" t="n">
-        <v>9</v>
+      <c r="S119" t="n">
+        <v>1</v>
+      </c>
+      <c r="T119" t="n">
+        <v>1</v>
+      </c>
+      <c r="U119" t="n">
+        <v>1</v>
       </c>
       <c r="AG119" t="inlineStr">
         <is>
@@ -8430,14 +8412,14 @@
       </c>
       <c r="AH119" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>faltante</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Relación superficie-volumen</t>
+          <t>Relaciones intraespecíficas</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -8446,56 +8428,35 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>10</v>
-      </c>
-      <c r="F120" t="n">
-        <v>8</v>
-      </c>
-      <c r="G120" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="J120" t="n">
-        <v>7</v>
-      </c>
-      <c r="K120" t="n">
-        <v>7</v>
-      </c>
-      <c r="L120" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="O120" t="n">
-        <v>1</v>
-      </c>
-      <c r="P120" t="n">
-        <v>1</v>
-      </c>
-      <c r="S120" t="n">
-        <v>1</v>
-      </c>
-      <c r="T120" t="n">
-        <v>1</v>
-      </c>
-      <c r="U120" t="n">
+        <v>7</v>
+      </c>
+      <c r="D120" t="n">
+        <v>7</v>
+      </c>
+      <c r="M120" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="V120" t="n">
         <v>1</v>
       </c>
       <c r="AF120" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG120" t="inlineStr">
         <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+      <c r="AH120" t="inlineStr">
+        <is>
           <t>posterior</t>
-        </is>
-      </c>
-      <c r="AH120" t="inlineStr">
-        <is>
-          <t>tardio</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Relaciones intraespecíficas</t>
+          <t>Antibióticos y resistencia bacteriana</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -8504,23 +8465,35 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>7</v>
-      </c>
-      <c r="D121" t="n">
-        <v>7</v>
-      </c>
-      <c r="M121" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="V121" t="n">
+        <v>9</v>
+      </c>
+      <c r="G121" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H121" t="n">
+        <v>4</v>
+      </c>
+      <c r="L121" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="P121" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>1</v>
+      </c>
+      <c r="U121" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z121" t="n">
         <v>1</v>
       </c>
       <c r="AF121" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AG121" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH121" t="inlineStr">
@@ -8532,7 +8505,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Sistema inmunitario</t>
+          <t>Selección natural</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -8541,16 +8514,22 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>9</v>
+        <v>7</v>
+      </c>
+      <c r="D122" t="n">
+        <v>7</v>
       </c>
       <c r="F122" t="n">
         <v>8</v>
       </c>
       <c r="G122" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="M122" t="n">
-        <v>7</v>
+        <v>4</v>
+      </c>
+      <c r="K122" t="n">
+        <v>2</v>
+      </c>
+      <c r="L122" t="n">
+        <v>6</v>
       </c>
       <c r="O122" t="n">
         <v>1</v>
@@ -8558,7 +8537,10 @@
       <c r="P122" t="n">
         <v>1</v>
       </c>
-      <c r="V122" t="n">
+      <c r="T122" t="n">
+        <v>1</v>
+      </c>
+      <c r="U122" t="n">
         <v>1</v>
       </c>
       <c r="Z122" t="n">
@@ -8569,7 +8551,7 @@
       </c>
       <c r="AG122" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH122" t="inlineStr">
@@ -8581,7 +8563,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Termorregulación</t>
+          <t>Sistema inmunitario</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -8590,16 +8572,31 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F123" t="n">
         <v>8</v>
       </c>
+      <c r="G123" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="M123" t="n">
+        <v>7</v>
+      </c>
       <c r="O123" t="n">
         <v>1</v>
       </c>
+      <c r="P123" t="n">
+        <v>1</v>
+      </c>
+      <c r="V123" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>1</v>
+      </c>
       <c r="AF123" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG123" t="inlineStr">
         <is>
@@ -8615,7 +8612,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Virus</t>
+          <t>Termorregulación</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -8624,41 +8621,20 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>3</v>
-      </c>
-      <c r="D124" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F124" t="n">
         <v>8</v>
       </c>
-      <c r="G124" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="H124" t="n">
-        <v>4</v>
-      </c>
-      <c r="L124" t="n">
-        <v>7.5</v>
-      </c>
       <c r="O124" t="n">
         <v>1</v>
       </c>
-      <c r="P124" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q124" t="n">
-        <v>1</v>
-      </c>
-      <c r="U124" t="n">
-        <v>1</v>
-      </c>
       <c r="AF124" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG124" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH124" t="inlineStr">
@@ -8670,28 +8646,46 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Acervo génico y frecuencias alélicas</t>
+          <t>Virus</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D125" t="n">
-        <v>7</v>
+        <v>3</v>
+      </c>
+      <c r="F125" t="n">
+        <v>8</v>
       </c>
       <c r="G125" t="n">
         <v>8.5</v>
       </c>
+      <c r="H125" t="n">
+        <v>4</v>
+      </c>
+      <c r="L125" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="O125" t="n">
+        <v>1</v>
+      </c>
       <c r="P125" t="n">
         <v>1</v>
       </c>
+      <c r="Q125" t="n">
+        <v>1</v>
+      </c>
+      <c r="U125" t="n">
+        <v>1</v>
+      </c>
       <c r="AF125" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AG125" t="inlineStr">
         <is>
@@ -8700,14 +8694,14 @@
       </c>
       <c r="AH125" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>posterior</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>ATP y energía en los sistemas vivos</t>
+          <t>Acervo génico y frecuencias alélicas</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -8716,31 +8710,19 @@
         </is>
       </c>
       <c r="C126" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D126" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G126" t="n">
-        <v>6</v>
-      </c>
-      <c r="H126" t="n">
-        <v>7</v>
-      </c>
-      <c r="J126" t="n">
-        <v>7</v>
+        <v>8.5</v>
       </c>
       <c r="P126" t="n">
         <v>1</v>
       </c>
-      <c r="Q126" t="n">
-        <v>1</v>
-      </c>
-      <c r="S126" t="n">
-        <v>1</v>
-      </c>
       <c r="AF126" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG126" t="inlineStr">
         <is>
@@ -8749,14 +8731,14 @@
       </c>
       <c r="AH126" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>sin_referente</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Atributos de las poblaciones</t>
+          <t>ATP y energía en los sistemas vivos</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -8765,37 +8747,31 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D127" t="n">
-        <v>7</v>
-      </c>
-      <c r="F127" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G127" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="L127" t="n">
         <v>6</v>
       </c>
-      <c r="M127" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O127" t="n">
-        <v>1</v>
+      <c r="H127" t="n">
+        <v>7</v>
+      </c>
+      <c r="J127" t="n">
+        <v>7</v>
       </c>
       <c r="P127" t="n">
         <v>1</v>
       </c>
-      <c r="U127" t="n">
-        <v>1</v>
-      </c>
-      <c r="V127" t="n">
+      <c r="Q127" t="n">
+        <v>1</v>
+      </c>
+      <c r="S127" t="n">
         <v>1</v>
       </c>
       <c r="AF127" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AG127" t="inlineStr">
         <is>
@@ -8811,7 +8787,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Biomas y clasificación de ambientes</t>
+          <t>Atributos de las poblaciones</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -8820,25 +8796,37 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D128" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F128" t="n">
         <v>8</v>
       </c>
-      <c r="H128" t="n">
-        <v>3</v>
+      <c r="G128" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="L128" t="n">
+        <v>6</v>
+      </c>
+      <c r="M128" t="n">
+        <v>4.5</v>
       </c>
       <c r="O128" t="n">
         <v>1</v>
       </c>
-      <c r="Q128" t="n">
+      <c r="P128" t="n">
+        <v>1</v>
+      </c>
+      <c r="U128" t="n">
+        <v>1</v>
+      </c>
+      <c r="V128" t="n">
         <v>1</v>
       </c>
       <c r="AF128" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AG128" t="inlineStr">
         <is>
@@ -8847,14 +8835,14 @@
       </c>
       <c r="AH128" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Célula procariota y eucariota</t>
+          <t>Biomas y clasificación de ambientes</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -8863,25 +8851,25 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D129" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F129" t="n">
         <v>8</v>
       </c>
-      <c r="G129" t="n">
-        <v>8.5</v>
+      <c r="H129" t="n">
+        <v>3</v>
       </c>
       <c r="O129" t="n">
         <v>1</v>
       </c>
-      <c r="P129" t="n">
+      <c r="Q129" t="n">
         <v>1</v>
       </c>
       <c r="AF129" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG129" t="inlineStr">
         <is>
@@ -8897,7 +8885,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Conservación e inocuidad de los alimentos</t>
+          <t>Célula procariota y eucariota</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -8906,25 +8894,25 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D130" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F130" t="n">
         <v>8</v>
       </c>
-      <c r="H130" t="n">
-        <v>2</v>
+      <c r="G130" t="n">
+        <v>8.5</v>
       </c>
       <c r="O130" t="n">
         <v>1</v>
       </c>
-      <c r="Q130" t="n">
+      <c r="P130" t="n">
         <v>1</v>
       </c>
       <c r="AF130" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AG130" t="inlineStr">
         <is>
@@ -8940,7 +8928,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Ecosistemas acuáticos y marinos</t>
+          <t>Conservación e inocuidad de los alimentos</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -8949,25 +8937,25 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D131" t="n">
-        <v>4</v>
+        <v>2</v>
+      </c>
+      <c r="F131" t="n">
+        <v>8</v>
       </c>
       <c r="H131" t="n">
-        <v>7</v>
-      </c>
-      <c r="J131" t="n">
-        <v>2.5</v>
+        <v>2</v>
+      </c>
+      <c r="O131" t="n">
+        <v>1</v>
       </c>
       <c r="Q131" t="n">
         <v>1</v>
       </c>
-      <c r="S131" t="n">
-        <v>1</v>
-      </c>
       <c r="AF131" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AG131" t="inlineStr">
         <is>
@@ -8983,7 +8971,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Ecosistemas naturales, rurales y urbanos</t>
+          <t>Ecosistemas acuáticos y marinos</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -8992,25 +8980,25 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D132" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H132" t="n">
         <v>7</v>
       </c>
-      <c r="M132" t="n">
+      <c r="J132" t="n">
         <v>2.5</v>
       </c>
       <c r="Q132" t="n">
         <v>1</v>
       </c>
-      <c r="V132" t="n">
+      <c r="S132" t="n">
         <v>1</v>
       </c>
       <c r="AF132" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AG132" t="inlineStr">
         <is>
@@ -9026,7 +9014,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Estrategias reproductivas y supervivencia de la descendencia</t>
+          <t>Ecosistemas naturales, rurales y urbanos</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -9035,43 +9023,25 @@
         </is>
       </c>
       <c r="C133" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D133" t="n">
-        <v>3</v>
-      </c>
-      <c r="E133" t="n">
-        <v>8</v>
-      </c>
-      <c r="F133" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H133" t="n">
-        <v>3</v>
-      </c>
-      <c r="L133" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M133" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="N133" t="n">
-        <v>1</v>
-      </c>
-      <c r="O133" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="Q133" t="n">
         <v>1</v>
       </c>
-      <c r="U133" t="n">
-        <v>1</v>
-      </c>
       <c r="V133" t="n">
         <v>1</v>
       </c>
       <c r="AF133" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AG133" t="inlineStr">
         <is>
@@ -9080,14 +9050,14 @@
       </c>
       <c r="AH133" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>sin_referente</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Estructura del ADN</t>
+          <t>Estrategias reproductivas y supervivencia de la descendencia</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -9096,22 +9066,43 @@
         </is>
       </c>
       <c r="C134" t="n">
+        <v>3</v>
+      </c>
+      <c r="D134" t="n">
+        <v>3</v>
+      </c>
+      <c r="E134" t="n">
+        <v>8</v>
+      </c>
+      <c r="F134" t="n">
+        <v>8</v>
+      </c>
+      <c r="H134" t="n">
+        <v>3</v>
+      </c>
+      <c r="L134" t="n">
         <v>6</v>
       </c>
-      <c r="D134" t="n">
-        <v>6</v>
-      </c>
-      <c r="G134" t="n">
-        <v>6</v>
-      </c>
-      <c r="P134" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z134" t="n">
+      <c r="M134" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="N134" t="n">
+        <v>1</v>
+      </c>
+      <c r="O134" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>1</v>
+      </c>
+      <c r="U134" t="n">
+        <v>1</v>
+      </c>
+      <c r="V134" t="n">
         <v>1</v>
       </c>
       <c r="AF134" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AG134" t="inlineStr">
         <is>
@@ -9120,14 +9111,14 @@
       </c>
       <c r="AH134" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>adelantado</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Fermentación y respiración anaerobia</t>
+          <t>Estructura del ADN</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -9136,25 +9127,22 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D135" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G135" t="n">
         <v>6</v>
       </c>
-      <c r="M135" t="n">
-        <v>7</v>
-      </c>
       <c r="P135" t="n">
         <v>1</v>
       </c>
-      <c r="V135" t="n">
+      <c r="Z135" t="n">
         <v>1</v>
       </c>
       <c r="AF135" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AG135" t="inlineStr">
         <is>
@@ -9170,7 +9158,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Filogenia y parentesco evolutivo</t>
+          <t>Fermentación y respiración anaerobia</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -9179,25 +9167,25 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D136" t="n">
-        <v>7</v>
-      </c>
-      <c r="F136" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G136" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="O136" t="n">
-        <v>1</v>
+        <v>6</v>
+      </c>
+      <c r="M136" t="n">
+        <v>7</v>
       </c>
       <c r="P136" t="n">
         <v>1</v>
       </c>
+      <c r="V136" t="n">
+        <v>1</v>
+      </c>
       <c r="AF136" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AG136" t="inlineStr">
         <is>
@@ -9213,7 +9201,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Mecanismos de microevolución</t>
+          <t>Filogenia y parentesco evolutivo</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -9230,10 +9218,13 @@
       <c r="F137" t="n">
         <v>8</v>
       </c>
+      <c r="G137" t="n">
+        <v>8.5</v>
+      </c>
       <c r="O137" t="n">
         <v>1</v>
       </c>
-      <c r="Z137" t="n">
+      <c r="P137" t="n">
         <v>1</v>
       </c>
       <c r="AF137" t="n">
@@ -9253,7 +9244,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Medidas de biodiversidad</t>
+          <t>Mecanismos de microevolución</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -9267,10 +9258,13 @@
       <c r="D138" t="n">
         <v>7</v>
       </c>
-      <c r="H138" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q138" t="n">
+      <c r="F138" t="n">
+        <v>8</v>
+      </c>
+      <c r="O138" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z138" t="n">
         <v>1</v>
       </c>
       <c r="AF138" t="n">
@@ -9290,7 +9284,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Membrana celular</t>
+          <t>Medidas de biodiversidad</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -9299,28 +9293,19 @@
         </is>
       </c>
       <c r="C139" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D139" t="n">
-        <v>6</v>
-      </c>
-      <c r="G139" t="n">
-        <v>6</v>
-      </c>
-      <c r="K139" t="n">
-        <v>7</v>
-      </c>
-      <c r="P139" t="n">
-        <v>1</v>
-      </c>
-      <c r="T139" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z139" t="n">
+        <v>7</v>
+      </c>
+      <c r="H139" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q139" t="n">
         <v>1</v>
       </c>
       <c r="AF139" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG139" t="inlineStr">
         <is>
@@ -9336,7 +9321,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Modelos ecológicos basados en muestreo</t>
+          <t>Membrana celular</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -9345,19 +9330,28 @@
         </is>
       </c>
       <c r="C140" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D140" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G140" t="n">
-        <v>8.5</v>
+        <v>6</v>
+      </c>
+      <c r="K140" t="n">
+        <v>7</v>
       </c>
       <c r="P140" t="n">
         <v>1</v>
       </c>
+      <c r="T140" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>1</v>
+      </c>
       <c r="AF140" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AG140" t="inlineStr">
         <is>
@@ -9373,7 +9367,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Mutaciones</t>
+          <t>Modelos ecológicos basados en muestreo</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -9390,16 +9384,7 @@
       <c r="G141" t="n">
         <v>8.5</v>
       </c>
-      <c r="M141" t="n">
-        <v>7</v>
-      </c>
       <c r="P141" t="n">
-        <v>1</v>
-      </c>
-      <c r="V141" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z141" t="n">
         <v>1</v>
       </c>
       <c r="AF141" t="n">
@@ -9619,10 +9604,10 @@
         </is>
       </c>
       <c r="C147" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D147" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G147" t="n">
         <v>8.5</v>
@@ -9637,7 +9622,7 @@
         <v>1</v>
       </c>
       <c r="AF147" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AG147" t="inlineStr">
         <is>
@@ -9662,10 +9647,10 @@
         </is>
       </c>
       <c r="C148" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D148" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z148" t="n">
         <v>1</v>

--- a/internacional/2_8/Contraste_biologia.xlsx
+++ b/internacional/2_8/Contraste_biologia.xlsx
@@ -2518,7 +2518,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Biotecnología vegetal y agroindustria</t>
+          <t>Cadena alimentaria</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2527,19 +2527,40 @@
         </is>
       </c>
       <c r="C30" t="n">
+        <v>4</v>
+      </c>
+      <c r="D30" t="n">
+        <v>4</v>
+      </c>
+      <c r="E30" t="n">
+        <v>3</v>
+      </c>
+      <c r="F30" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G30" t="n">
+        <v>2</v>
+      </c>
+      <c r="H30" t="n">
+        <v>3</v>
+      </c>
+      <c r="I30" t="n">
+        <v>5</v>
+      </c>
+      <c r="J30" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K30" t="n">
+        <v>2</v>
+      </c>
+      <c r="L30" t="n">
         <v>6</v>
       </c>
-      <c r="D30" t="n">
-        <v>6</v>
-      </c>
-      <c r="F30" t="n">
-        <v>8</v>
-      </c>
-      <c r="G30" t="n">
-        <v>8.5</v>
-      </c>
       <c r="M30" t="n">
-        <v>7</v>
+        <v>4.5</v>
+      </c>
+      <c r="N30" t="n">
+        <v>1</v>
       </c>
       <c r="O30" t="n">
         <v>1</v>
@@ -2547,27 +2568,42 @@
       <c r="P30" t="n">
         <v>1</v>
       </c>
+      <c r="Q30" t="n">
+        <v>1</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1</v>
+      </c>
+      <c r="S30" t="n">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
+      </c>
       <c r="V30" t="n">
         <v>1</v>
       </c>
       <c r="AF30" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AG30" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Cadena alimentaria</t>
+          <t>Cambio climático y seres vivos</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2576,31 +2612,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D31" t="n">
-        <v>4</v>
-      </c>
-      <c r="E31" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F31" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="G31" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H31" t="n">
-        <v>3</v>
-      </c>
-      <c r="I31" t="n">
+        <v>7</v>
+      </c>
+      <c r="K31" t="n">
         <v>5</v>
-      </c>
-      <c r="J31" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K31" t="n">
-        <v>2</v>
       </c>
       <c r="L31" t="n">
         <v>6</v>
@@ -2608,24 +2632,12 @@
       <c r="M31" t="n">
         <v>4.5</v>
       </c>
-      <c r="N31" t="n">
-        <v>1</v>
-      </c>
       <c r="O31" t="n">
         <v>1</v>
       </c>
-      <c r="P31" t="n">
-        <v>1</v>
-      </c>
       <c r="Q31" t="n">
         <v>1</v>
       </c>
-      <c r="R31" t="n">
-        <v>1</v>
-      </c>
-      <c r="S31" t="n">
-        <v>1</v>
-      </c>
       <c r="T31" t="n">
         <v>1</v>
       </c>
@@ -2636,7 +2648,7 @@
         <v>1</v>
       </c>
       <c r="AF31" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="AG31" t="inlineStr">
         <is>
@@ -2645,14 +2657,14 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>tardio</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Cambio climático y seres vivos</t>
+          <t>Célula animal y célula vegetal</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2661,32 +2673,56 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D32" t="n">
+        <v>6</v>
+      </c>
+      <c r="E32" t="n">
         <v>7</v>
       </c>
       <c r="F32" t="n">
         <v>8</v>
       </c>
+      <c r="G32" t="n">
+        <v>6</v>
+      </c>
       <c r="H32" t="n">
-        <v>7</v>
+        <v>5</v>
+      </c>
+      <c r="I32" t="n">
+        <v>7</v>
+      </c>
+      <c r="J32" t="n">
+        <v>4.5</v>
       </c>
       <c r="K32" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L32" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="M32" t="n">
-        <v>4.5</v>
+        <v>7</v>
+      </c>
+      <c r="N32" t="n">
+        <v>1</v>
       </c>
       <c r="O32" t="n">
         <v>1</v>
       </c>
+      <c r="P32" t="n">
+        <v>1</v>
+      </c>
       <c r="Q32" t="n">
         <v>1</v>
       </c>
+      <c r="R32" t="n">
+        <v>1</v>
+      </c>
+      <c r="S32" t="n">
+        <v>1</v>
+      </c>
       <c r="T32" t="n">
         <v>1</v>
       </c>
@@ -2697,7 +2733,7 @@
         <v>1</v>
       </c>
       <c r="AF32" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG32" t="inlineStr">
         <is>
@@ -3913,7 +3949,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Estructuras del cuerpo animal y su función</t>
+          <t>Estructuras celulares básicas</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3922,37 +3958,37 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D51" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E51" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F51" t="n">
-        <v>2.5</v>
+        <v>8</v>
       </c>
       <c r="G51" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H51" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I51" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J51" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="K51" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="L51" t="n">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="M51" t="n">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="N51" t="n">
         <v>1</v>
@@ -3985,7 +4021,7 @@
         <v>1</v>
       </c>
       <c r="AF51" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="AG51" t="inlineStr">
         <is>
@@ -3994,14 +4030,14 @@
       </c>
       <c r="AH51" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>tardio</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Extinción de especies</t>
+          <t>Estructuras del cuerpo animal y su función</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4010,28 +4046,40 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D52" t="n">
-        <v>5</v>
+        <v>2</v>
+      </c>
+      <c r="E52" t="n">
+        <v>2</v>
       </c>
       <c r="F52" t="n">
-        <v>8</v>
+        <v>2.5</v>
       </c>
       <c r="G52" t="n">
         <v>2</v>
       </c>
       <c r="H52" t="n">
-        <v>5</v>
+        <v>2</v>
+      </c>
+      <c r="I52" t="n">
+        <v>3</v>
+      </c>
+      <c r="J52" t="n">
+        <v>2.5</v>
       </c>
       <c r="K52" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L52" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M52" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
+      </c>
+      <c r="N52" t="n">
+        <v>1</v>
       </c>
       <c r="O52" t="n">
         <v>1</v>
@@ -4042,6 +4090,12 @@
       <c r="Q52" t="n">
         <v>1</v>
       </c>
+      <c r="R52" t="n">
+        <v>1</v>
+      </c>
+      <c r="S52" t="n">
+        <v>1</v>
+      </c>
       <c r="T52" t="n">
         <v>1</v>
       </c>
@@ -4051,8 +4105,11 @@
       <c r="V52" t="n">
         <v>1</v>
       </c>
+      <c r="Z52" t="n">
+        <v>1</v>
+      </c>
       <c r="AF52" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AG52" t="inlineStr">
         <is>
@@ -4068,7 +4125,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Factores bióticos y abióticos</t>
+          <t>Extinción de especies</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4077,68 +4134,50 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D53" t="n">
-        <v>2</v>
-      </c>
-      <c r="E53" t="n">
         <v>5</v>
       </c>
       <c r="F53" t="n">
+        <v>8</v>
+      </c>
+      <c r="G53" t="n">
+        <v>2</v>
+      </c>
+      <c r="H53" t="n">
         <v>5</v>
       </c>
-      <c r="G53" t="n">
-        <v>2</v>
-      </c>
-      <c r="H53" t="n">
-        <v>2</v>
-      </c>
-      <c r="I53" t="n">
+      <c r="K53" t="n">
+        <v>3</v>
+      </c>
+      <c r="L53" t="n">
+        <v>6</v>
+      </c>
+      <c r="M53" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O53" t="n">
+        <v>1</v>
+      </c>
+      <c r="P53" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>1</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
+      </c>
+      <c r="V53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF53" t="n">
         <v>5</v>
       </c>
-      <c r="J53" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K53" t="n">
-        <v>2</v>
-      </c>
-      <c r="L53" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="M53" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N53" t="n">
-        <v>1</v>
-      </c>
-      <c r="O53" t="n">
-        <v>1</v>
-      </c>
-      <c r="P53" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q53" t="n">
-        <v>1</v>
-      </c>
-      <c r="R53" t="n">
-        <v>1</v>
-      </c>
-      <c r="S53" t="n">
-        <v>1</v>
-      </c>
-      <c r="T53" t="n">
-        <v>1</v>
-      </c>
-      <c r="U53" t="n">
-        <v>1</v>
-      </c>
-      <c r="V53" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF53" t="n">
-        <v>4</v>
-      </c>
       <c r="AG53" t="inlineStr">
         <is>
           <t>alineado</t>
@@ -4146,14 +4185,14 @@
       </c>
       <c r="AH53" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Factores limitantes de las poblaciones</t>
+          <t>Factores bióticos y abióticos</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4162,28 +4201,37 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D54" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F54" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G54" t="n">
-        <v>8.5</v>
+        <v>2</v>
+      </c>
+      <c r="H54" t="n">
+        <v>2</v>
+      </c>
+      <c r="I54" t="n">
+        <v>5</v>
+      </c>
+      <c r="J54" t="n">
+        <v>2.5</v>
       </c>
       <c r="K54" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L54" t="n">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="M54" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="N54" t="n">
         <v>1</v>
@@ -4194,6 +4242,15 @@
       <c r="P54" t="n">
         <v>1</v>
       </c>
+      <c r="Q54" t="n">
+        <v>1</v>
+      </c>
+      <c r="R54" t="n">
+        <v>1</v>
+      </c>
+      <c r="S54" t="n">
+        <v>1</v>
+      </c>
       <c r="T54" t="n">
         <v>1</v>
       </c>
@@ -4204,11 +4261,11 @@
         <v>1</v>
       </c>
       <c r="AF54" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="AG54" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH54" t="inlineStr">
@@ -4220,7 +4277,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Fecundación y desarrollo embrionario</t>
+          <t>Factores limitantes de las poblaciones</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4229,28 +4286,31 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D55" t="n">
+        <v>7</v>
+      </c>
+      <c r="E55" t="n">
         <v>6</v>
       </c>
       <c r="F55" t="n">
         <v>8</v>
       </c>
       <c r="G55" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="K55" t="n">
+        <v>3</v>
+      </c>
+      <c r="L55" t="n">
         <v>6</v>
       </c>
-      <c r="H55" t="n">
-        <v>7</v>
-      </c>
-      <c r="I55" t="n">
-        <v>4</v>
-      </c>
-      <c r="J55" t="n">
-        <v>7</v>
-      </c>
-      <c r="L55" t="n">
-        <v>5</v>
+      <c r="M55" t="n">
+        <v>7</v>
+      </c>
+      <c r="N55" t="n">
+        <v>1</v>
       </c>
       <c r="O55" t="n">
         <v>1</v>
@@ -4258,39 +4318,33 @@
       <c r="P55" t="n">
         <v>1</v>
       </c>
-      <c r="Q55" t="n">
-        <v>1</v>
-      </c>
-      <c r="R55" t="n">
-        <v>1</v>
-      </c>
-      <c r="S55" t="n">
+      <c r="T55" t="n">
         <v>1</v>
       </c>
       <c r="U55" t="n">
         <v>1</v>
       </c>
-      <c r="Z55" t="n">
+      <c r="V55" t="n">
         <v>1</v>
       </c>
       <c r="AF55" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AG55" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>tardio</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Flujo de energía y pirámides ecológicas</t>
+          <t>Fecundación y desarrollo embrionario</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4299,49 +4353,52 @@
         </is>
       </c>
       <c r="C56" t="n">
+        <v>6</v>
+      </c>
+      <c r="D56" t="n">
+        <v>6</v>
+      </c>
+      <c r="F56" t="n">
+        <v>8</v>
+      </c>
+      <c r="G56" t="n">
+        <v>6</v>
+      </c>
+      <c r="H56" t="n">
+        <v>7</v>
+      </c>
+      <c r="I56" t="n">
+        <v>4</v>
+      </c>
+      <c r="J56" t="n">
+        <v>7</v>
+      </c>
+      <c r="L56" t="n">
         <v>5</v>
       </c>
-      <c r="D56" t="n">
-        <v>5</v>
-      </c>
-      <c r="E56" t="n">
+      <c r="O56" t="n">
+        <v>1</v>
+      </c>
+      <c r="P56" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>1</v>
+      </c>
+      <c r="R56" t="n">
+        <v>1</v>
+      </c>
+      <c r="S56" t="n">
+        <v>1</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF56" t="n">
         <v>6</v>
-      </c>
-      <c r="G56" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="H56" t="n">
-        <v>5</v>
-      </c>
-      <c r="K56" t="n">
-        <v>6</v>
-      </c>
-      <c r="L56" t="n">
-        <v>6</v>
-      </c>
-      <c r="M56" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="N56" t="n">
-        <v>1</v>
-      </c>
-      <c r="P56" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q56" t="n">
-        <v>1</v>
-      </c>
-      <c r="T56" t="n">
-        <v>1</v>
-      </c>
-      <c r="U56" t="n">
-        <v>1</v>
-      </c>
-      <c r="V56" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF56" t="n">
-        <v>5</v>
       </c>
       <c r="AG56" t="inlineStr">
         <is>
@@ -4357,7 +4414,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Fotosíntesis</t>
+          <t>Flujo de energía y pirámides ecológicas</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4366,31 +4423,22 @@
         </is>
       </c>
       <c r="C57" t="n">
+        <v>5</v>
+      </c>
+      <c r="D57" t="n">
+        <v>5</v>
+      </c>
+      <c r="E57" t="n">
         <v>6</v>
       </c>
-      <c r="D57" t="n">
+      <c r="G57" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H57" t="n">
+        <v>5</v>
+      </c>
+      <c r="K57" t="n">
         <v>6</v>
-      </c>
-      <c r="E57" t="n">
-        <v>8</v>
-      </c>
-      <c r="F57" t="n">
-        <v>5</v>
-      </c>
-      <c r="G57" t="n">
-        <v>6</v>
-      </c>
-      <c r="H57" t="n">
-        <v>2</v>
-      </c>
-      <c r="I57" t="n">
-        <v>4</v>
-      </c>
-      <c r="J57" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K57" t="n">
-        <v>2</v>
       </c>
       <c r="L57" t="n">
         <v>6</v>
@@ -4401,21 +4449,12 @@
       <c r="N57" t="n">
         <v>1</v>
       </c>
-      <c r="O57" t="n">
-        <v>1</v>
-      </c>
       <c r="P57" t="n">
         <v>1</v>
       </c>
       <c r="Q57" t="n">
         <v>1</v>
       </c>
-      <c r="R57" t="n">
-        <v>1</v>
-      </c>
-      <c r="S57" t="n">
-        <v>1</v>
-      </c>
       <c r="T57" t="n">
         <v>1</v>
       </c>
@@ -4426,7 +4465,7 @@
         <v>1</v>
       </c>
       <c r="AF57" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AG57" t="inlineStr">
         <is>
@@ -4435,14 +4474,14 @@
       </c>
       <c r="AH57" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Genes y alelos</t>
+          <t>Fotosíntesis</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4456,20 +4495,35 @@
       <c r="D58" t="n">
         <v>6</v>
       </c>
+      <c r="E58" t="n">
+        <v>8</v>
+      </c>
       <c r="F58" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G58" t="n">
         <v>6</v>
       </c>
       <c r="H58" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I58" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J58" t="n">
-        <v>7</v>
+        <v>4.5</v>
+      </c>
+      <c r="K58" t="n">
+        <v>2</v>
+      </c>
+      <c r="L58" t="n">
+        <v>6</v>
+      </c>
+      <c r="M58" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="N58" t="n">
+        <v>1</v>
       </c>
       <c r="O58" t="n">
         <v>1</v>
@@ -4486,27 +4540,33 @@
       <c r="S58" t="n">
         <v>1</v>
       </c>
-      <c r="Z58" t="n">
+      <c r="T58" t="n">
+        <v>1</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
+      </c>
+      <c r="V58" t="n">
         <v>1</v>
       </c>
       <c r="AF58" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AG58" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>tardio</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Genética humana y enfermedades hereditarias</t>
+          <t>Genes y alelos</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4515,23 +4575,26 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>9</v>
+        <v>6</v>
+      </c>
+      <c r="D59" t="n">
+        <v>6</v>
       </c>
       <c r="F59" t="n">
         <v>8</v>
       </c>
       <c r="G59" t="n">
-        <v>8.5</v>
+        <v>6</v>
       </c>
       <c r="H59" t="n">
         <v>7</v>
       </c>
+      <c r="I59" t="n">
+        <v>8</v>
+      </c>
       <c r="J59" t="n">
         <v>7</v>
       </c>
-      <c r="M59" t="n">
-        <v>7</v>
-      </c>
       <c r="O59" t="n">
         <v>1</v>
       </c>
@@ -4541,21 +4604,21 @@
       <c r="Q59" t="n">
         <v>1</v>
       </c>
+      <c r="R59" t="n">
+        <v>1</v>
+      </c>
       <c r="S59" t="n">
         <v>1</v>
       </c>
-      <c r="V59" t="n">
-        <v>1</v>
-      </c>
       <c r="Z59" t="n">
         <v>1</v>
       </c>
       <c r="AF59" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AG59" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH59" t="inlineStr">
@@ -4567,7 +4630,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Genotipo y fenotipo</t>
+          <t>Genética humana y enfermedades hereditarias</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4576,22 +4639,16 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>7</v>
-      </c>
-      <c r="D60" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F60" t="n">
         <v>8</v>
       </c>
       <c r="G60" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="H60" t="n">
-        <v>3</v>
-      </c>
-      <c r="I60" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J60" t="n">
         <v>7</v>
@@ -4608,9 +4665,6 @@
       <c r="Q60" t="n">
         <v>1</v>
       </c>
-      <c r="R60" t="n">
-        <v>1</v>
-      </c>
       <c r="S60" t="n">
         <v>1</v>
       </c>
@@ -4621,7 +4675,7 @@
         <v>1</v>
       </c>
       <c r="AF60" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AG60" t="inlineStr">
         <is>
@@ -4637,7 +4691,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Grupos de alimentos y dieta balanceada</t>
+          <t>Genotipo y fenotipo</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4646,28 +4700,28 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D61" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F61" t="n">
         <v>8</v>
       </c>
       <c r="G61" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H61" t="n">
-        <v>2</v>
-      </c>
-      <c r="K61" t="n">
-        <v>4</v>
-      </c>
-      <c r="L61" t="n">
-        <v>7.5</v>
+        <v>3</v>
+      </c>
+      <c r="I61" t="n">
+        <v>8</v>
+      </c>
+      <c r="J61" t="n">
+        <v>7</v>
       </c>
       <c r="M61" t="n">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="O61" t="n">
         <v>1</v>
@@ -4678,10 +4732,10 @@
       <c r="Q61" t="n">
         <v>1</v>
       </c>
-      <c r="T61" t="n">
-        <v>1</v>
-      </c>
-      <c r="U61" t="n">
+      <c r="R61" t="n">
+        <v>1</v>
+      </c>
+      <c r="S61" t="n">
         <v>1</v>
       </c>
       <c r="V61" t="n">
@@ -4691,11 +4745,11 @@
         <v>1</v>
       </c>
       <c r="AF61" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AG61" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH61" t="inlineStr">
@@ -4707,7 +4761,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Grupos de vertebrados</t>
+          <t>Grupos de alimentos y dieta balanceada</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4722,7 +4776,7 @@
         <v>2</v>
       </c>
       <c r="F62" t="n">
-        <v>2.5</v>
+        <v>8</v>
       </c>
       <c r="G62" t="n">
         <v>2</v>
@@ -4730,11 +4784,11 @@
       <c r="H62" t="n">
         <v>2</v>
       </c>
-      <c r="I62" t="n">
+      <c r="K62" t="n">
         <v>4</v>
       </c>
-      <c r="K62" t="n">
-        <v>2</v>
+      <c r="L62" t="n">
+        <v>7.5</v>
       </c>
       <c r="M62" t="n">
         <v>2.5</v>
@@ -4748,13 +4802,16 @@
       <c r="Q62" t="n">
         <v>1</v>
       </c>
-      <c r="R62" t="n">
-        <v>1</v>
-      </c>
       <c r="T62" t="n">
         <v>1</v>
       </c>
+      <c r="U62" t="n">
+        <v>1</v>
+      </c>
       <c r="V62" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z62" t="n">
         <v>1</v>
       </c>
       <c r="AF62" t="n">
@@ -4774,7 +4831,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Hábitat y ecosistemas comunes</t>
+          <t>Grupos de vertebrados</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4786,9 +4843,6 @@
         <v>2</v>
       </c>
       <c r="D63" t="n">
-        <v>2</v>
-      </c>
-      <c r="E63" t="n">
         <v>2</v>
       </c>
       <c r="F63" t="n">
@@ -4801,23 +4855,14 @@
         <v>2</v>
       </c>
       <c r="I63" t="n">
-        <v>2</v>
-      </c>
-      <c r="J63" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="K63" t="n">
         <v>2</v>
-      </c>
-      <c r="L63" t="n">
-        <v>6</v>
       </c>
       <c r="M63" t="n">
         <v>2.5</v>
       </c>
-      <c r="N63" t="n">
-        <v>1</v>
-      </c>
       <c r="O63" t="n">
         <v>1</v>
       </c>
@@ -4830,15 +4875,9 @@
       <c r="R63" t="n">
         <v>1</v>
       </c>
-      <c r="S63" t="n">
-        <v>1</v>
-      </c>
       <c r="T63" t="n">
         <v>1</v>
       </c>
-      <c r="U63" t="n">
-        <v>1</v>
-      </c>
       <c r="V63" t="n">
         <v>1</v>
       </c>
@@ -4847,7 +4886,7 @@
       </c>
       <c r="AG63" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH63" t="inlineStr">
@@ -4859,7 +4898,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Hábitos de vida saludable</t>
+          <t>Hábitat y ecosistemas comunes</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4871,6 +4910,9 @@
         <v>2</v>
       </c>
       <c r="D64" t="n">
+        <v>2</v>
+      </c>
+      <c r="E64" t="n">
         <v>2</v>
       </c>
       <c r="F64" t="n">
@@ -4882,14 +4924,23 @@
       <c r="H64" t="n">
         <v>2</v>
       </c>
+      <c r="I64" t="n">
+        <v>2</v>
+      </c>
       <c r="J64" t="n">
         <v>2.5</v>
       </c>
       <c r="K64" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L64" t="n">
-        <v>7.5</v>
+        <v>6</v>
+      </c>
+      <c r="M64" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N64" t="n">
+        <v>1</v>
       </c>
       <c r="O64" t="n">
         <v>1</v>
@@ -4900,6 +4951,9 @@
       <c r="Q64" t="n">
         <v>1</v>
       </c>
+      <c r="R64" t="n">
+        <v>1</v>
+      </c>
       <c r="S64" t="n">
         <v>1</v>
       </c>
@@ -4909,7 +4963,7 @@
       <c r="U64" t="n">
         <v>1</v>
       </c>
-      <c r="Z64" t="n">
+      <c r="V64" t="n">
         <v>1</v>
       </c>
       <c r="AF64" t="n">
@@ -4929,7 +4983,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Herencia mendeliana</t>
+          <t>Hábitos de vida saludable</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4938,28 +4992,28 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D65" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F65" t="n">
-        <v>8</v>
+        <v>2.5</v>
       </c>
       <c r="G65" t="n">
-        <v>8.5</v>
+        <v>2</v>
       </c>
       <c r="H65" t="n">
-        <v>7</v>
-      </c>
-      <c r="I65" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J65" t="n">
-        <v>7</v>
-      </c>
-      <c r="M65" t="n">
-        <v>7</v>
+        <v>2.5</v>
+      </c>
+      <c r="K65" t="n">
+        <v>4</v>
+      </c>
+      <c r="L65" t="n">
+        <v>7.5</v>
       </c>
       <c r="O65" t="n">
         <v>1</v>
@@ -4970,17 +5024,20 @@
       <c r="Q65" t="n">
         <v>1</v>
       </c>
-      <c r="R65" t="n">
-        <v>1</v>
-      </c>
       <c r="S65" t="n">
         <v>1</v>
       </c>
-      <c r="V65" t="n">
+      <c r="T65" t="n">
+        <v>1</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z65" t="n">
         <v>1</v>
       </c>
       <c r="AF65" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AG65" t="inlineStr">
         <is>
@@ -4996,7 +5053,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Herencia ligada al sexo, alelos múltiples y poligénica</t>
+          <t>Herencia de rasgos</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5005,22 +5062,34 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D66" t="n">
-        <v>7</v>
+        <v>6</v>
+      </c>
+      <c r="F66" t="n">
+        <v>8</v>
       </c>
       <c r="G66" t="n">
-        <v>8.5</v>
+        <v>2</v>
       </c>
       <c r="H66" t="n">
-        <v>7</v>
+        <v>3</v>
+      </c>
+      <c r="I66" t="n">
+        <v>8</v>
       </c>
       <c r="J66" t="n">
         <v>7</v>
       </c>
+      <c r="L66" t="n">
+        <v>5</v>
+      </c>
       <c r="M66" t="n">
-        <v>7</v>
+        <v>4.5</v>
+      </c>
+      <c r="O66" t="n">
+        <v>1</v>
       </c>
       <c r="P66" t="n">
         <v>1</v>
@@ -5028,13 +5097,16 @@
       <c r="Q66" t="n">
         <v>1</v>
       </c>
+      <c r="R66" t="n">
+        <v>1</v>
+      </c>
       <c r="S66" t="n">
         <v>1</v>
       </c>
+      <c r="U66" t="n">
+        <v>1</v>
+      </c>
       <c r="V66" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z66" t="n">
         <v>1</v>
       </c>
       <c r="AF66" t="n">
@@ -5047,14 +5119,14 @@
       </c>
       <c r="AH66" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>tardio</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Homeostasis</t>
+          <t>Herencia mendeliana</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5063,10 +5135,10 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>9</v>
-      </c>
-      <c r="E67" t="n">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="D67" t="n">
+        <v>7</v>
       </c>
       <c r="F67" t="n">
         <v>8</v>
@@ -5077,17 +5149,14 @@
       <c r="H67" t="n">
         <v>7</v>
       </c>
+      <c r="I67" t="n">
+        <v>8</v>
+      </c>
       <c r="J67" t="n">
         <v>7</v>
       </c>
-      <c r="K67" t="n">
-        <v>4</v>
-      </c>
       <c r="M67" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="N67" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O67" t="n">
         <v>1</v>
@@ -5098,20 +5167,17 @@
       <c r="Q67" t="n">
         <v>1</v>
       </c>
+      <c r="R67" t="n">
+        <v>1</v>
+      </c>
       <c r="S67" t="n">
         <v>1</v>
       </c>
-      <c r="T67" t="n">
-        <v>1</v>
-      </c>
       <c r="V67" t="n">
         <v>1</v>
       </c>
-      <c r="Z67" t="n">
-        <v>1</v>
-      </c>
       <c r="AF67" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AG67" t="inlineStr">
         <is>
@@ -5127,7 +5193,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Impacto humano en los ecosistemas</t>
+          <t>Herencia ligada al sexo, alelos múltiples y poligénica</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5136,37 +5202,22 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D68" t="n">
-        <v>2</v>
-      </c>
-      <c r="F68" t="n">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="G68" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="H68" t="n">
-        <v>2</v>
-      </c>
-      <c r="I68" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J68" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K68" t="n">
-        <v>2</v>
-      </c>
-      <c r="L68" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="M68" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O68" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="P68" t="n">
         <v>1</v>
@@ -5174,39 +5225,33 @@
       <c r="Q68" t="n">
         <v>1</v>
       </c>
-      <c r="R68" t="n">
-        <v>1</v>
-      </c>
       <c r="S68" t="n">
         <v>1</v>
       </c>
-      <c r="T68" t="n">
-        <v>1</v>
-      </c>
-      <c r="U68" t="n">
-        <v>1</v>
-      </c>
       <c r="V68" t="n">
         <v>1</v>
       </c>
+      <c r="Z68" t="n">
+        <v>1</v>
+      </c>
       <c r="AF68" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="AG68" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>posterior</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Intercambio de gases en plantas</t>
+          <t>Homeostasis</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5215,41 +5260,59 @@
         </is>
       </c>
       <c r="C69" t="n">
+        <v>9</v>
+      </c>
+      <c r="E69" t="n">
         <v>8</v>
       </c>
-      <c r="D69" t="n">
+      <c r="F69" t="n">
         <v>8</v>
       </c>
       <c r="G69" t="n">
-        <v>6</v>
-      </c>
-      <c r="I69" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H69" t="n">
         <v>7</v>
       </c>
       <c r="J69" t="n">
+        <v>7</v>
+      </c>
+      <c r="K69" t="n">
+        <v>4</v>
+      </c>
+      <c r="M69" t="n">
         <v>4.5</v>
       </c>
-      <c r="L69" t="n">
-        <v>5</v>
+      <c r="N69" t="n">
+        <v>1</v>
+      </c>
+      <c r="O69" t="n">
+        <v>1</v>
       </c>
       <c r="P69" t="n">
         <v>1</v>
       </c>
-      <c r="R69" t="n">
+      <c r="Q69" t="n">
         <v>1</v>
       </c>
       <c r="S69" t="n">
         <v>1</v>
       </c>
-      <c r="U69" t="n">
+      <c r="T69" t="n">
+        <v>1</v>
+      </c>
+      <c r="V69" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z69" t="n">
         <v>1</v>
       </c>
       <c r="AF69" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG69" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH69" t="inlineStr">
@@ -5261,7 +5324,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Invertebrados e insectos</t>
+          <t>Impacto humano en los ecosistemas</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5279,17 +5342,26 @@
         <v>2.5</v>
       </c>
       <c r="G70" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H70" t="n">
         <v>2</v>
       </c>
       <c r="I70" t="n">
-        <v>2</v>
+        <v>5</v>
+      </c>
+      <c r="J70" t="n">
+        <v>2.5</v>
       </c>
       <c r="K70" t="n">
         <v>2</v>
       </c>
+      <c r="L70" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="M70" t="n">
+        <v>2.5</v>
+      </c>
       <c r="O70" t="n">
         <v>1</v>
       </c>
@@ -5302,15 +5374,24 @@
       <c r="R70" t="n">
         <v>1</v>
       </c>
+      <c r="S70" t="n">
+        <v>1</v>
+      </c>
       <c r="T70" t="n">
         <v>1</v>
       </c>
+      <c r="U70" t="n">
+        <v>1</v>
+      </c>
+      <c r="V70" t="n">
+        <v>1</v>
+      </c>
       <c r="AF70" t="n">
         <v>2</v>
       </c>
       <c r="AG70" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH70" t="inlineStr">
@@ -5322,7 +5403,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>La célula como unidad de la vida</t>
+          <t>Intercambio de gases en plantas</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5331,71 +5412,41 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D71" t="n">
-        <v>6</v>
-      </c>
-      <c r="E71" t="n">
-        <v>7</v>
-      </c>
-      <c r="F71" t="n">
         <v>8</v>
       </c>
       <c r="G71" t="n">
         <v>6</v>
       </c>
-      <c r="H71" t="n">
-        <v>5</v>
-      </c>
       <c r="I71" t="n">
         <v>7</v>
       </c>
       <c r="J71" t="n">
         <v>4.5</v>
       </c>
-      <c r="K71" t="n">
-        <v>7</v>
-      </c>
       <c r="L71" t="n">
         <v>5</v>
       </c>
-      <c r="M71" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="N71" t="n">
-        <v>1</v>
-      </c>
-      <c r="O71" t="n">
-        <v>1</v>
-      </c>
       <c r="P71" t="n">
         <v>1</v>
       </c>
-      <c r="Q71" t="n">
-        <v>1</v>
-      </c>
       <c r="R71" t="n">
         <v>1</v>
       </c>
       <c r="S71" t="n">
         <v>1</v>
       </c>
-      <c r="T71" t="n">
-        <v>1</v>
-      </c>
       <c r="U71" t="n">
         <v>1</v>
       </c>
-      <c r="V71" t="n">
-        <v>1</v>
-      </c>
       <c r="AF71" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AG71" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH71" t="inlineStr">
@@ -5407,7 +5458,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Necesidades de los seres vivos</t>
+          <t>Invertebrados e insectos</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5419,38 +5470,23 @@
         <v>2</v>
       </c>
       <c r="D72" t="n">
-        <v>2</v>
-      </c>
-      <c r="E72" t="n">
         <v>2</v>
       </c>
       <c r="F72" t="n">
         <v>2.5</v>
       </c>
       <c r="G72" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H72" t="n">
         <v>2</v>
       </c>
       <c r="I72" t="n">
-        <v>4</v>
-      </c>
-      <c r="J72" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="K72" t="n">
         <v>2</v>
       </c>
-      <c r="L72" t="n">
-        <v>3</v>
-      </c>
-      <c r="M72" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N72" t="n">
-        <v>1</v>
-      </c>
       <c r="O72" t="n">
         <v>1</v>
       </c>
@@ -5463,16 +5499,7 @@
       <c r="R72" t="n">
         <v>1</v>
       </c>
-      <c r="S72" t="n">
-        <v>1</v>
-      </c>
       <c r="T72" t="n">
-        <v>1</v>
-      </c>
-      <c r="U72" t="n">
-        <v>1</v>
-      </c>
-      <c r="V72" t="n">
         <v>1</v>
       </c>
       <c r="AF72" t="n">
@@ -5492,7 +5519,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Niveles de organización de los seres vivos</t>
+          <t>La célula como unidad de la vida</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5501,25 +5528,25 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D73" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E73" t="n">
         <v>7</v>
       </c>
       <c r="F73" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G73" t="n">
         <v>6</v>
       </c>
       <c r="H73" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I73" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J73" t="n">
         <v>4.5</v>
@@ -5528,7 +5555,7 @@
         <v>7</v>
       </c>
       <c r="L73" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="M73" t="n">
         <v>4.5</v>
@@ -5560,15 +5587,12 @@
       <c r="V73" t="n">
         <v>1</v>
       </c>
-      <c r="Z73" t="n">
-        <v>1</v>
-      </c>
       <c r="AF73" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AG73" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH73" t="inlineStr">
@@ -5580,7 +5604,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Niveles de organización ecológica</t>
+          <t>Necesidades de los seres vivos</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5589,31 +5613,40 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D74" t="n">
-        <v>4</v>
+        <v>2</v>
+      </c>
+      <c r="E74" t="n">
+        <v>2</v>
       </c>
       <c r="F74" t="n">
         <v>2.5</v>
       </c>
       <c r="G74" t="n">
-        <v>8.5</v>
+        <v>2</v>
       </c>
       <c r="H74" t="n">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="I74" t="n">
+        <v>4</v>
       </c>
       <c r="J74" t="n">
         <v>2.5</v>
       </c>
       <c r="K74" t="n">
+        <v>2</v>
+      </c>
+      <c r="L74" t="n">
         <v>3</v>
       </c>
-      <c r="L74" t="n">
-        <v>6</v>
-      </c>
       <c r="M74" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
+      </c>
+      <c r="N74" t="n">
+        <v>1</v>
       </c>
       <c r="O74" t="n">
         <v>1</v>
@@ -5624,6 +5657,9 @@
       <c r="Q74" t="n">
         <v>1</v>
       </c>
+      <c r="R74" t="n">
+        <v>1</v>
+      </c>
       <c r="S74" t="n">
         <v>1</v>
       </c>
@@ -5637,11 +5673,11 @@
         <v>1</v>
       </c>
       <c r="AF74" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AG74" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH74" t="inlineStr">
@@ -5653,7 +5689,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Nutrición autótrofa y heterótrofa</t>
+          <t>Niveles de organización de los seres vivos</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -5662,34 +5698,40 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D75" t="n">
-        <v>2</v>
+        <v>4</v>
+      </c>
+      <c r="E75" t="n">
+        <v>7</v>
       </c>
       <c r="F75" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="G75" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H75" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I75" t="n">
         <v>5</v>
       </c>
       <c r="J75" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="K75" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="L75" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="M75" t="n">
-        <v>7</v>
+        <v>4.5</v>
+      </c>
+      <c r="N75" t="n">
+        <v>1</v>
       </c>
       <c r="O75" t="n">
         <v>1</v>
@@ -5715,8 +5757,11 @@
       <c r="V75" t="n">
         <v>1</v>
       </c>
+      <c r="Z75" t="n">
+        <v>1</v>
+      </c>
       <c r="AF75" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG75" t="inlineStr">
         <is>
@@ -5732,7 +5777,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Órganos de los sentidos</t>
+          <t>Niveles de organización ecológica</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5747,25 +5792,25 @@
         <v>4</v>
       </c>
       <c r="F76" t="n">
-        <v>8</v>
+        <v>2.5</v>
       </c>
       <c r="G76" t="n">
-        <v>2</v>
+        <v>8.5</v>
       </c>
       <c r="H76" t="n">
-        <v>2</v>
-      </c>
-      <c r="I76" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J76" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="K76" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="L76" t="n">
+        <v>6</v>
       </c>
       <c r="M76" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="O76" t="n">
         <v>1</v>
@@ -5776,13 +5821,13 @@
       <c r="Q76" t="n">
         <v>1</v>
       </c>
-      <c r="R76" t="n">
-        <v>1</v>
-      </c>
       <c r="S76" t="n">
         <v>1</v>
       </c>
       <c r="T76" t="n">
+        <v>1</v>
+      </c>
+      <c r="U76" t="n">
         <v>1</v>
       </c>
       <c r="V76" t="n">
@@ -5793,7 +5838,7 @@
       </c>
       <c r="AG76" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH76" t="inlineStr">
@@ -5805,7 +5850,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Partes de la planta y sus funciones</t>
+          <t>Nutrición autótrofa y heterótrofa</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5817,9 +5862,6 @@
         <v>2</v>
       </c>
       <c r="D77" t="n">
-        <v>2</v>
-      </c>
-      <c r="E77" t="n">
         <v>2</v>
       </c>
       <c r="F77" t="n">
@@ -5832,7 +5874,7 @@
         <v>2</v>
       </c>
       <c r="I77" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J77" t="n">
         <v>2.5</v>
@@ -5841,13 +5883,10 @@
         <v>2</v>
       </c>
       <c r="L77" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M77" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N77" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O77" t="n">
         <v>1</v>
@@ -5874,11 +5913,11 @@
         <v>1</v>
       </c>
       <c r="AF77" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG77" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH77" t="inlineStr">
@@ -5890,7 +5929,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Plantas y animales útiles al ser humano</t>
+          <t>Órganos de los sentidos</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5899,22 +5938,25 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D78" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F78" t="n">
-        <v>2.5</v>
+        <v>8</v>
       </c>
       <c r="G78" t="n">
-        <v>8.5</v>
+        <v>2</v>
       </c>
       <c r="H78" t="n">
         <v>2</v>
       </c>
+      <c r="I78" t="n">
+        <v>7</v>
+      </c>
       <c r="J78" t="n">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="K78" t="n">
         <v>2</v>
@@ -5931,6 +5973,9 @@
       <c r="Q78" t="n">
         <v>1</v>
       </c>
+      <c r="R78" t="n">
+        <v>1</v>
+      </c>
       <c r="S78" t="n">
         <v>1</v>
       </c>
@@ -5941,11 +5986,11 @@
         <v>1</v>
       </c>
       <c r="AF78" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AG78" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH78" t="inlineStr">
@@ -5957,7 +6002,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Productores, consumidores y descomponedores</t>
+          <t>Partes de la planta y sus funciones</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5966,13 +6011,13 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D79" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E79" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F79" t="n">
         <v>2.5</v>
@@ -5981,10 +6026,10 @@
         <v>2</v>
       </c>
       <c r="H79" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I79" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J79" t="n">
         <v>2.5</v>
@@ -5993,10 +6038,10 @@
         <v>2</v>
       </c>
       <c r="L79" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M79" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="N79" t="n">
         <v>1</v>
@@ -6026,7 +6071,7 @@
         <v>1</v>
       </c>
       <c r="AF79" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AG79" t="inlineStr">
         <is>
@@ -6042,7 +6087,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Reproducción humana y pubertad</t>
+          <t>Plantas y animales útiles al ser humano</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6051,34 +6096,28 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D80" t="n">
-        <v>4</v>
-      </c>
-      <c r="E80" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F80" t="n">
-        <v>8</v>
+        <v>2.5</v>
       </c>
       <c r="G80" t="n">
-        <v>3</v>
+        <v>8.5</v>
       </c>
       <c r="H80" t="n">
-        <v>4</v>
-      </c>
-      <c r="I80" t="n">
-        <v>4</v>
-      </c>
-      <c r="L80" t="n">
-        <v>5</v>
+        <v>2</v>
+      </c>
+      <c r="J80" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K80" t="n">
+        <v>2</v>
       </c>
       <c r="M80" t="n">
-        <v>7</v>
-      </c>
-      <c r="N80" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="O80" t="n">
         <v>1</v>
@@ -6089,20 +6128,17 @@
       <c r="Q80" t="n">
         <v>1</v>
       </c>
-      <c r="R80" t="n">
-        <v>1</v>
-      </c>
-      <c r="U80" t="n">
+      <c r="S80" t="n">
+        <v>1</v>
+      </c>
+      <c r="T80" t="n">
         <v>1</v>
       </c>
       <c r="V80" t="n">
         <v>1</v>
       </c>
-      <c r="Z80" t="n">
-        <v>1</v>
-      </c>
       <c r="AF80" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AG80" t="inlineStr">
         <is>
@@ -6118,7 +6154,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Reproducción sexual y asexual</t>
+          <t>Productores, consumidores y descomponedores</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6127,31 +6163,37 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D81" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E81" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F81" t="n">
-        <v>8</v>
+        <v>2.5</v>
       </c>
       <c r="G81" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H81" t="n">
         <v>3</v>
       </c>
       <c r="I81" t="n">
-        <v>4</v>
+        <v>8</v>
+      </c>
+      <c r="J81" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K81" t="n">
+        <v>2</v>
       </c>
       <c r="L81" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M81" t="n">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="N81" t="n">
         <v>1</v>
@@ -6168,17 +6210,20 @@
       <c r="R81" t="n">
         <v>1</v>
       </c>
+      <c r="S81" t="n">
+        <v>1</v>
+      </c>
+      <c r="T81" t="n">
+        <v>1</v>
+      </c>
       <c r="U81" t="n">
         <v>1</v>
       </c>
       <c r="V81" t="n">
         <v>1</v>
       </c>
-      <c r="Z81" t="n">
-        <v>1</v>
-      </c>
       <c r="AF81" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AG81" t="inlineStr">
         <is>
@@ -6194,7 +6239,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Requerimientos de materia y energía de la célula</t>
+          <t>Reproducción sexual de las plantas con flor</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6203,19 +6248,28 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>9</v>
+        <v>6</v>
+      </c>
+      <c r="D82" t="n">
+        <v>6</v>
+      </c>
+      <c r="E82" t="n">
+        <v>8</v>
+      </c>
+      <c r="F82" t="n">
+        <v>8</v>
       </c>
       <c r="G82" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H82" t="n">
-        <v>7</v>
-      </c>
-      <c r="J82" t="n">
-        <v>4.5</v>
+        <v>2</v>
+      </c>
+      <c r="I82" t="n">
+        <v>4</v>
       </c>
       <c r="K82" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="L82" t="n">
         <v>5</v>
@@ -6223,13 +6277,19 @@
       <c r="M82" t="n">
         <v>7</v>
       </c>
+      <c r="N82" t="n">
+        <v>1</v>
+      </c>
+      <c r="O82" t="n">
+        <v>1</v>
+      </c>
       <c r="P82" t="n">
         <v>1</v>
       </c>
       <c r="Q82" t="n">
         <v>1</v>
       </c>
-      <c r="S82" t="n">
+      <c r="R82" t="n">
         <v>1</v>
       </c>
       <c r="T82" t="n">
@@ -6241,15 +6301,12 @@
       <c r="V82" t="n">
         <v>1</v>
       </c>
-      <c r="Z82" t="n">
-        <v>1</v>
-      </c>
       <c r="AF82" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG82" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH82" t="inlineStr">
@@ -6261,7 +6318,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Respiración celular</t>
+          <t>Reproducción humana y pubertad</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6270,35 +6327,29 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D83" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E83" t="n">
         <v>8</v>
       </c>
       <c r="F83" t="n">
+        <v>8</v>
+      </c>
+      <c r="G83" t="n">
+        <v>3</v>
+      </c>
+      <c r="H83" t="n">
+        <v>4</v>
+      </c>
+      <c r="I83" t="n">
+        <v>4</v>
+      </c>
+      <c r="L83" t="n">
         <v>5</v>
       </c>
-      <c r="G83" t="n">
-        <v>6</v>
-      </c>
-      <c r="H83" t="n">
-        <v>7</v>
-      </c>
-      <c r="I83" t="n">
-        <v>7</v>
-      </c>
-      <c r="J83" t="n">
-        <v>7</v>
-      </c>
-      <c r="K83" t="n">
-        <v>7</v>
-      </c>
-      <c r="L83" t="n">
-        <v>6</v>
-      </c>
       <c r="M83" t="n">
         <v>7</v>
       </c>
@@ -6317,24 +6368,21 @@
       <c r="R83" t="n">
         <v>1</v>
       </c>
-      <c r="S83" t="n">
-        <v>1</v>
-      </c>
-      <c r="T83" t="n">
-        <v>1</v>
-      </c>
       <c r="U83" t="n">
         <v>1</v>
       </c>
       <c r="V83" t="n">
         <v>1</v>
       </c>
+      <c r="Z83" t="n">
+        <v>1</v>
+      </c>
       <c r="AF83" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AG83" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH83" t="inlineStr">
@@ -6346,7 +6394,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Respuesta de los seres vivos a estímulos</t>
+          <t>Reproducción sexual y asexual</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6355,10 +6403,10 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D84" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E84" t="n">
         <v>8</v>
@@ -6367,22 +6415,16 @@
         <v>8</v>
       </c>
       <c r="G84" t="n">
-        <v>8.5</v>
+        <v>3</v>
       </c>
       <c r="H84" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I84" t="n">
-        <v>3</v>
-      </c>
-      <c r="J84" t="n">
-        <v>7</v>
-      </c>
-      <c r="K84" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L84" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M84" t="n">
         <v>2.5</v>
@@ -6402,24 +6444,21 @@
       <c r="R84" t="n">
         <v>1</v>
       </c>
-      <c r="S84" t="n">
-        <v>1</v>
-      </c>
-      <c r="T84" t="n">
-        <v>1</v>
-      </c>
       <c r="U84" t="n">
         <v>1</v>
       </c>
       <c r="V84" t="n">
         <v>1</v>
       </c>
+      <c r="Z84" t="n">
+        <v>1</v>
+      </c>
       <c r="AF84" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AG84" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH84" t="inlineStr">
@@ -6431,7 +6470,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Modelo estímulo-respuesta y retroalimentación negativa</t>
+          <t>Requerimientos de materia y energía de la célula</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6442,32 +6481,23 @@
       <c r="C85" t="n">
         <v>9</v>
       </c>
-      <c r="E85" t="n">
-        <v>8</v>
-      </c>
-      <c r="F85" t="n">
-        <v>8</v>
-      </c>
       <c r="G85" t="n">
-        <v>8.5</v>
+        <v>6</v>
       </c>
       <c r="H85" t="n">
         <v>7</v>
       </c>
-      <c r="I85" t="n">
-        <v>7</v>
-      </c>
       <c r="J85" t="n">
-        <v>7</v>
+        <v>4.5</v>
+      </c>
+      <c r="K85" t="n">
+        <v>7</v>
+      </c>
+      <c r="L85" t="n">
+        <v>5</v>
       </c>
       <c r="M85" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="N85" t="n">
-        <v>1</v>
-      </c>
-      <c r="O85" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="P85" t="n">
         <v>1</v>
@@ -6475,33 +6505,39 @@
       <c r="Q85" t="n">
         <v>1</v>
       </c>
-      <c r="R85" t="n">
-        <v>1</v>
-      </c>
       <c r="S85" t="n">
         <v>1</v>
       </c>
+      <c r="T85" t="n">
+        <v>1</v>
+      </c>
+      <c r="U85" t="n">
+        <v>1</v>
+      </c>
       <c r="V85" t="n">
         <v>1</v>
       </c>
+      <c r="Z85" t="n">
+        <v>1</v>
+      </c>
       <c r="AF85" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG85" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>tardio</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Seres vivos y no vivos</t>
+          <t>Respiración celular</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6510,31 +6546,37 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D86" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E86" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F86" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="G86" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H86" t="n">
-        <v>2</v>
+        <v>7</v>
+      </c>
+      <c r="I86" t="n">
+        <v>7</v>
+      </c>
+      <c r="J86" t="n">
+        <v>7</v>
       </c>
       <c r="K86" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="L86" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M86" t="n">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="N86" t="n">
         <v>1</v>
@@ -6548,6 +6590,12 @@
       <c r="Q86" t="n">
         <v>1</v>
       </c>
+      <c r="R86" t="n">
+        <v>1</v>
+      </c>
+      <c r="S86" t="n">
+        <v>1</v>
+      </c>
       <c r="T86" t="n">
         <v>1</v>
       </c>
@@ -6558,7 +6606,7 @@
         <v>1</v>
       </c>
       <c r="AF86" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AG86" t="inlineStr">
         <is>
@@ -6574,7 +6622,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Sistema circulatorio</t>
+          <t>Respuesta de los seres vivos a estímulos</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -6583,34 +6631,40 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D87" t="n">
-        <v>4</v>
+        <v>2</v>
+      </c>
+      <c r="E87" t="n">
+        <v>8</v>
       </c>
       <c r="F87" t="n">
         <v>8</v>
       </c>
       <c r="G87" t="n">
-        <v>4</v>
+        <v>8.5</v>
       </c>
       <c r="H87" t="n">
         <v>2</v>
       </c>
       <c r="I87" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J87" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="K87" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L87" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M87" t="n">
-        <v>7</v>
+        <v>2.5</v>
+      </c>
+      <c r="N87" t="n">
+        <v>1</v>
       </c>
       <c r="O87" t="n">
         <v>1</v>
@@ -6636,15 +6690,12 @@
       <c r="V87" t="n">
         <v>1</v>
       </c>
-      <c r="Z87" t="n">
-        <v>1</v>
-      </c>
       <c r="AF87" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AG87" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH87" t="inlineStr">
@@ -6656,7 +6707,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Sistema digestivo</t>
+          <t>Modelo estímulo-respuesta y retroalimentación negativa</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -6665,34 +6716,31 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>4</v>
-      </c>
-      <c r="D88" t="n">
-        <v>4</v>
+        <v>9</v>
+      </c>
+      <c r="E88" t="n">
+        <v>8</v>
       </c>
       <c r="F88" t="n">
         <v>8</v>
       </c>
       <c r="G88" t="n">
-        <v>2</v>
+        <v>8.5</v>
       </c>
       <c r="H88" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I88" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J88" t="n">
+        <v>7</v>
+      </c>
+      <c r="M88" t="n">
         <v>4.5</v>
       </c>
-      <c r="K88" t="n">
-        <v>4</v>
-      </c>
-      <c r="L88" t="n">
-        <v>4</v>
-      </c>
-      <c r="M88" t="n">
-        <v>7</v>
+      <c r="N88" t="n">
+        <v>1</v>
       </c>
       <c r="O88" t="n">
         <v>1</v>
@@ -6709,20 +6757,11 @@
       <c r="S88" t="n">
         <v>1</v>
       </c>
-      <c r="T88" t="n">
-        <v>1</v>
-      </c>
-      <c r="U88" t="n">
-        <v>1</v>
-      </c>
       <c r="V88" t="n">
         <v>1</v>
       </c>
-      <c r="Z88" t="n">
-        <v>1</v>
-      </c>
       <c r="AF88" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AG88" t="inlineStr">
         <is>
@@ -6738,7 +6777,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Sistema endocrino y hormonas</t>
+          <t>Seres vivos y no vivos</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -6747,25 +6786,31 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>9</v>
+        <v>2</v>
+      </c>
+      <c r="D89" t="n">
+        <v>2</v>
       </c>
       <c r="E89" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F89" t="n">
-        <v>8</v>
+        <v>2.5</v>
       </c>
       <c r="G89" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="J89" t="n">
-        <v>7</v>
+        <v>2</v>
+      </c>
+      <c r="H89" t="n">
+        <v>2</v>
+      </c>
+      <c r="K89" t="n">
+        <v>2</v>
       </c>
       <c r="L89" t="n">
-        <v>7.5</v>
+        <v>3</v>
       </c>
       <c r="M89" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="N89" t="n">
         <v>1</v>
@@ -6776,7 +6821,10 @@
       <c r="P89" t="n">
         <v>1</v>
       </c>
-      <c r="S89" t="n">
+      <c r="Q89" t="n">
+        <v>1</v>
+      </c>
+      <c r="T89" t="n">
         <v>1</v>
       </c>
       <c r="U89" t="n">
@@ -6785,11 +6833,8 @@
       <c r="V89" t="n">
         <v>1</v>
       </c>
-      <c r="Z89" t="n">
-        <v>1</v>
-      </c>
       <c r="AF89" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="AG89" t="inlineStr">
         <is>
@@ -6805,7 +6850,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Sistema locomotor</t>
+          <t>Sistema circulatorio</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -6823,22 +6868,25 @@
         <v>8</v>
       </c>
       <c r="G90" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H90" t="n">
         <v>2</v>
       </c>
       <c r="I90" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J90" t="n">
         <v>4.5</v>
       </c>
       <c r="K90" t="n">
-        <v>2</v>
+        <v>4</v>
+      </c>
+      <c r="L90" t="n">
+        <v>4</v>
       </c>
       <c r="M90" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="O90" t="n">
         <v>1</v>
@@ -6858,7 +6906,13 @@
       <c r="T90" t="n">
         <v>1</v>
       </c>
+      <c r="U90" t="n">
+        <v>1</v>
+      </c>
       <c r="V90" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z90" t="n">
         <v>1</v>
       </c>
       <c r="AF90" t="n">
@@ -6878,7 +6932,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Sistema respiratorio</t>
+          <t>Sistema digestivo</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -6887,19 +6941,19 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D91" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F91" t="n">
         <v>8</v>
       </c>
       <c r="G91" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H91" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I91" t="n">
         <v>5</v>
@@ -6948,7 +7002,7 @@
       </c>
       <c r="AG91" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH91" t="inlineStr">
@@ -6960,7 +7014,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Tejidos animales</t>
+          <t>Sistema endocrino y hormonas</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6969,13 +7023,10 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>6</v>
-      </c>
-      <c r="D92" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E92" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F92" t="n">
         <v>8</v>
@@ -6983,7 +7034,13 @@
       <c r="G92" t="n">
         <v>8.5</v>
       </c>
-      <c r="H92" t="n">
+      <c r="J92" t="n">
+        <v>7</v>
+      </c>
+      <c r="L92" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="M92" t="n">
         <v>7</v>
       </c>
       <c r="N92" t="n">
@@ -6995,30 +7052,36 @@
       <c r="P92" t="n">
         <v>1</v>
       </c>
-      <c r="Q92" t="n">
+      <c r="S92" t="n">
+        <v>1</v>
+      </c>
+      <c r="U92" t="n">
+        <v>1</v>
+      </c>
+      <c r="V92" t="n">
         <v>1</v>
       </c>
       <c r="Z92" t="n">
         <v>1</v>
       </c>
       <c r="AF92" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AG92" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Tejidos vegetales</t>
+          <t>Sistema locomotor</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7027,34 +7090,31 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D93" t="n">
-        <v>8</v>
-      </c>
-      <c r="E93" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F93" t="n">
         <v>8</v>
       </c>
       <c r="G93" t="n">
-        <v>8.5</v>
+        <v>2</v>
       </c>
       <c r="H93" t="n">
-        <v>7</v>
+        <v>2</v>
+      </c>
+      <c r="I93" t="n">
+        <v>3</v>
       </c>
       <c r="J93" t="n">
         <v>4.5</v>
       </c>
-      <c r="L93" t="n">
-        <v>7.5</v>
+      <c r="K93" t="n">
+        <v>2</v>
       </c>
       <c r="M93" t="n">
-        <v>7</v>
-      </c>
-      <c r="N93" t="n">
-        <v>1</v>
+        <v>4.5</v>
       </c>
       <c r="O93" t="n">
         <v>1</v>
@@ -7065,17 +7125,20 @@
       <c r="Q93" t="n">
         <v>1</v>
       </c>
+      <c r="R93" t="n">
+        <v>1</v>
+      </c>
       <c r="S93" t="n">
         <v>1</v>
       </c>
-      <c r="U93" t="n">
+      <c r="T93" t="n">
         <v>1</v>
       </c>
       <c r="V93" t="n">
         <v>1</v>
       </c>
       <c r="AF93" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AG93" t="inlineStr">
         <is>
@@ -7091,7 +7154,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Transporte en plantas: xilema y floema</t>
+          <t>Sistema respiratorio</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7100,16 +7163,19 @@
         </is>
       </c>
       <c r="C94" t="n">
+        <v>3</v>
+      </c>
+      <c r="D94" t="n">
+        <v>3</v>
+      </c>
+      <c r="F94" t="n">
+        <v>8</v>
+      </c>
+      <c r="G94" t="n">
         <v>6</v>
       </c>
-      <c r="D94" t="n">
-        <v>6</v>
-      </c>
-      <c r="G94" t="n">
-        <v>2</v>
-      </c>
       <c r="H94" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I94" t="n">
         <v>5</v>
@@ -7117,12 +7183,18 @@
       <c r="J94" t="n">
         <v>4.5</v>
       </c>
+      <c r="K94" t="n">
+        <v>4</v>
+      </c>
       <c r="L94" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M94" t="n">
         <v>7</v>
       </c>
+      <c r="O94" t="n">
+        <v>1</v>
+      </c>
       <c r="P94" t="n">
         <v>1</v>
       </c>
@@ -7135,18 +7207,24 @@
       <c r="S94" t="n">
         <v>1</v>
       </c>
+      <c r="T94" t="n">
+        <v>1</v>
+      </c>
       <c r="U94" t="n">
         <v>1</v>
       </c>
       <c r="V94" t="n">
         <v>1</v>
       </c>
+      <c r="Z94" t="n">
+        <v>1</v>
+      </c>
       <c r="AF94" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AG94" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH94" t="inlineStr">
@@ -7158,7 +7236,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Variación genética en la descendencia</t>
+          <t>Tejidos animales</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7172,26 +7250,20 @@
       <c r="D95" t="n">
         <v>6</v>
       </c>
+      <c r="E95" t="n">
+        <v>7</v>
+      </c>
       <c r="F95" t="n">
         <v>8</v>
       </c>
       <c r="G95" t="n">
-        <v>4</v>
+        <v>8.5</v>
       </c>
       <c r="H95" t="n">
         <v>7</v>
       </c>
-      <c r="I95" t="n">
-        <v>8</v>
-      </c>
-      <c r="K95" t="n">
-        <v>5</v>
-      </c>
-      <c r="L95" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="M95" t="n">
-        <v>4.5</v>
+      <c r="N95" t="n">
+        <v>1</v>
       </c>
       <c r="O95" t="n">
         <v>1</v>
@@ -7202,48 +7274,39 @@
       <c r="Q95" t="n">
         <v>1</v>
       </c>
-      <c r="R95" t="n">
-        <v>1</v>
-      </c>
-      <c r="T95" t="n">
-        <v>1</v>
-      </c>
-      <c r="U95" t="n">
-        <v>1</v>
-      </c>
-      <c r="V95" t="n">
+      <c r="Z95" t="n">
         <v>1</v>
       </c>
       <c r="AF95" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AG95" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Célula animal y célula vegetal</t>
+          <t>Tejidos vegetales</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D96" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E96" t="n">
         <v>7</v>
@@ -7252,20 +7315,14 @@
         <v>8</v>
       </c>
       <c r="G96" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="H96" t="n">
-        <v>5</v>
-      </c>
-      <c r="I96" t="n">
         <v>7</v>
       </c>
       <c r="J96" t="n">
         <v>4.5</v>
       </c>
-      <c r="K96" t="n">
-        <v>7</v>
-      </c>
       <c r="L96" t="n">
         <v>7.5</v>
       </c>
@@ -7284,15 +7341,9 @@
       <c r="Q96" t="n">
         <v>1</v>
       </c>
-      <c r="R96" t="n">
-        <v>1</v>
-      </c>
       <c r="S96" t="n">
         <v>1</v>
       </c>
-      <c r="T96" t="n">
-        <v>1</v>
-      </c>
       <c r="U96" t="n">
         <v>1</v>
       </c>
@@ -7300,7 +7351,7 @@
         <v>1</v>
       </c>
       <c r="AF96" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AG96" t="inlineStr">
         <is>
@@ -7309,62 +7360,86 @@
       </c>
       <c r="AH96" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Especiación y macroevolución</t>
+          <t>Transporte en plantas: xilema y floema</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C97" t="n">
+        <v>6</v>
+      </c>
+      <c r="D97" t="n">
+        <v>6</v>
+      </c>
+      <c r="G97" t="n">
+        <v>2</v>
+      </c>
+      <c r="H97" t="n">
+        <v>7</v>
+      </c>
+      <c r="I97" t="n">
         <v>5</v>
       </c>
-      <c r="D97" t="n">
+      <c r="J97" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L97" t="n">
         <v>5</v>
       </c>
-      <c r="F97" t="n">
+      <c r="M97" t="n">
+        <v>7</v>
+      </c>
+      <c r="P97" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q97" t="n">
+        <v>1</v>
+      </c>
+      <c r="R97" t="n">
+        <v>1</v>
+      </c>
+      <c r="S97" t="n">
+        <v>1</v>
+      </c>
+      <c r="U97" t="n">
+        <v>1</v>
+      </c>
+      <c r="V97" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF97" t="n">
         <v>8</v>
       </c>
-      <c r="G97" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="O97" t="n">
-        <v>1</v>
-      </c>
-      <c r="P97" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF97" t="n">
-        <v>11</v>
-      </c>
       <c r="AG97" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Estructuras celulares básicas</t>
+          <t>Variación genética en la descendencia</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C98" t="n">
@@ -7373,35 +7448,26 @@
       <c r="D98" t="n">
         <v>6</v>
       </c>
-      <c r="E98" t="n">
-        <v>7</v>
-      </c>
       <c r="F98" t="n">
         <v>8</v>
       </c>
       <c r="G98" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H98" t="n">
+        <v>7</v>
+      </c>
+      <c r="I98" t="n">
+        <v>8</v>
+      </c>
+      <c r="K98" t="n">
         <v>5</v>
-      </c>
-      <c r="I98" t="n">
-        <v>7</v>
-      </c>
-      <c r="J98" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K98" t="n">
-        <v>7</v>
       </c>
       <c r="L98" t="n">
         <v>7.5</v>
       </c>
       <c r="M98" t="n">
-        <v>7</v>
-      </c>
-      <c r="N98" t="n">
-        <v>1</v>
+        <v>4.5</v>
       </c>
       <c r="O98" t="n">
         <v>1</v>
@@ -7415,9 +7481,6 @@
       <c r="R98" t="n">
         <v>1</v>
       </c>
-      <c r="S98" t="n">
-        <v>1</v>
-      </c>
       <c r="T98" t="n">
         <v>1</v>
       </c>
@@ -7427,11 +7490,8 @@
       <c r="V98" t="n">
         <v>1</v>
       </c>
-      <c r="Z98" t="n">
-        <v>1</v>
-      </c>
       <c r="AF98" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AG98" t="inlineStr">
         <is>
@@ -7440,121 +7500,85 @@
       </c>
       <c r="AH98" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Herencia de rasgos</t>
+          <t>Especies clave</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>no_aplica</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D99" t="n">
-        <v>6</v>
-      </c>
-      <c r="F99" t="n">
-        <v>8</v>
-      </c>
-      <c r="G99" t="n">
-        <v>2</v>
-      </c>
-      <c r="H99" t="n">
+        <v>7</v>
+      </c>
+      <c r="K99" t="n">
         <v>3</v>
       </c>
-      <c r="I99" t="n">
-        <v>8</v>
-      </c>
-      <c r="J99" t="n">
-        <v>7</v>
-      </c>
-      <c r="L99" t="n">
-        <v>5</v>
-      </c>
-      <c r="M99" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O99" t="n">
-        <v>1</v>
-      </c>
-      <c r="P99" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q99" t="n">
-        <v>1</v>
-      </c>
-      <c r="R99" t="n">
-        <v>1</v>
-      </c>
-      <c r="S99" t="n">
-        <v>1</v>
-      </c>
-      <c r="U99" t="n">
-        <v>1</v>
-      </c>
-      <c r="V99" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF99" t="n">
-        <v>10</v>
+      <c r="T99" t="n">
+        <v>1</v>
       </c>
       <c r="AG99" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH99" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>no_aplica</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Mutaciones</t>
+          <t>Adaptaciones fisiológicas</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D100" t="n">
-        <v>7</v>
-      </c>
-      <c r="G100" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="M100" t="n">
-        <v>7</v>
-      </c>
-      <c r="P100" t="n">
-        <v>1</v>
-      </c>
-      <c r="V100" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z100" t="n">
+        <v>8</v>
+      </c>
+      <c r="F100" t="n">
+        <v>8</v>
+      </c>
+      <c r="H100" t="n">
+        <v>3</v>
+      </c>
+      <c r="K100" t="n">
+        <v>2</v>
+      </c>
+      <c r="O100" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q100" t="n">
+        <v>1</v>
+      </c>
+      <c r="T100" t="n">
         <v>1</v>
       </c>
       <c r="AF100" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AG100" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH100" t="inlineStr">
@@ -7566,12 +7590,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Reproducción sexual de las plantas con flor</t>
+          <t>Biotecnología vegetal y agroindustria</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -7580,84 +7604,51 @@
       <c r="D101" t="n">
         <v>6</v>
       </c>
-      <c r="E101" t="n">
-        <v>8</v>
-      </c>
       <c r="F101" t="n">
         <v>8</v>
       </c>
       <c r="G101" t="n">
-        <v>2</v>
-      </c>
-      <c r="H101" t="n">
-        <v>2</v>
-      </c>
-      <c r="I101" t="n">
-        <v>4</v>
-      </c>
-      <c r="K101" t="n">
-        <v>2</v>
-      </c>
-      <c r="L101" t="n">
-        <v>5</v>
+        <v>8.5</v>
       </c>
       <c r="M101" t="n">
         <v>7</v>
       </c>
-      <c r="N101" t="n">
-        <v>1</v>
-      </c>
       <c r="O101" t="n">
         <v>1</v>
       </c>
       <c r="P101" t="n">
         <v>1</v>
       </c>
-      <c r="Q101" t="n">
-        <v>1</v>
-      </c>
-      <c r="R101" t="n">
-        <v>1</v>
-      </c>
-      <c r="T101" t="n">
-        <v>1</v>
-      </c>
-      <c r="U101" t="n">
-        <v>1</v>
-      </c>
       <c r="V101" t="n">
         <v>1</v>
       </c>
       <c r="AF101" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="AG101" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>adelantado</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Especies clave</t>
+          <t>Capacidad de carga</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>no_aplica</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>7</v>
-      </c>
-      <c r="D102" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="K102" t="n">
         <v>3</v>
@@ -7665,21 +7656,24 @@
       <c r="T102" t="n">
         <v>1</v>
       </c>
+      <c r="AF102" t="n">
+        <v>11</v>
+      </c>
       <c r="AG102" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
-          <t>no_aplica</t>
+          <t>posterior</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Adaptaciones fisiológicas</t>
+          <t>Ciclo del nitrógeno</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -7688,35 +7682,32 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>8</v>
-      </c>
-      <c r="D103" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F103" t="n">
         <v>8</v>
       </c>
-      <c r="H103" t="n">
-        <v>3</v>
+      <c r="G103" t="n">
+        <v>8.5</v>
       </c>
       <c r="K103" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O103" t="n">
         <v>1</v>
       </c>
-      <c r="Q103" t="n">
+      <c r="P103" t="n">
         <v>1</v>
       </c>
       <c r="T103" t="n">
         <v>1</v>
       </c>
       <c r="AF103" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AG103" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH103" t="inlineStr">
@@ -7728,7 +7719,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Capacidad de carga</t>
+          <t>Propagación de enfermedades y control de brotes</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -7737,16 +7728,37 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>11</v>
-      </c>
-      <c r="K104" t="n">
+        <v>9</v>
+      </c>
+      <c r="G104" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H104" t="n">
         <v>3</v>
       </c>
-      <c r="T104" t="n">
+      <c r="J104" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L104" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="P104" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q104" t="n">
+        <v>1</v>
+      </c>
+      <c r="S104" t="n">
+        <v>1</v>
+      </c>
+      <c r="U104" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z104" t="n">
         <v>1</v>
       </c>
       <c r="AF104" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AG104" t="inlineStr">
         <is>
@@ -7762,7 +7774,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Ciclo del nitrógeno</t>
+          <t>Especiación y macroevolución</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -7771,7 +7783,10 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>9</v>
+        <v>5</v>
+      </c>
+      <c r="D105" t="n">
+        <v>5</v>
       </c>
       <c r="F105" t="n">
         <v>8</v>
@@ -7779,24 +7794,18 @@
       <c r="G105" t="n">
         <v>8.5</v>
       </c>
-      <c r="K105" t="n">
-        <v>6</v>
-      </c>
       <c r="O105" t="n">
         <v>1</v>
       </c>
       <c r="P105" t="n">
         <v>1</v>
       </c>
-      <c r="T105" t="n">
-        <v>1</v>
-      </c>
       <c r="AF105" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AG105" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH105" t="inlineStr">
@@ -7808,7 +7817,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Propagación de enfermedades y control de brotes</t>
+          <t>Eutrofización</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -7817,41 +7826,17 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>9</v>
-      </c>
-      <c r="G106" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="H106" t="n">
-        <v>3</v>
-      </c>
-      <c r="J106" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="L106" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="P106" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q106" t="n">
-        <v>1</v>
-      </c>
-      <c r="S106" t="n">
-        <v>1</v>
-      </c>
-      <c r="U106" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z106" t="n">
-        <v>1</v>
+        <v>7</v>
+      </c>
+      <c r="D106" t="n">
+        <v>7</v>
       </c>
       <c r="AF106" t="n">
         <v>9</v>
       </c>
       <c r="AG106" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH106" t="inlineStr">
@@ -7863,7 +7848,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Eutrofización</t>
+          <t>Evidencias de la evolución</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -7872,17 +7857,38 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>7</v>
-      </c>
-      <c r="D107" t="n">
-        <v>7</v>
+        <v>9</v>
+      </c>
+      <c r="F107" t="n">
+        <v>8</v>
+      </c>
+      <c r="G107" t="n">
+        <v>4</v>
+      </c>
+      <c r="I107" t="n">
+        <v>8</v>
+      </c>
+      <c r="M107" t="n">
+        <v>7</v>
+      </c>
+      <c r="O107" t="n">
+        <v>1</v>
+      </c>
+      <c r="P107" t="n">
+        <v>1</v>
+      </c>
+      <c r="R107" t="n">
+        <v>1</v>
+      </c>
+      <c r="V107" t="n">
+        <v>1</v>
       </c>
       <c r="AF107" t="n">
         <v>9</v>
       </c>
       <c r="AG107" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH107" t="inlineStr">
@@ -7894,7 +7900,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Evidencias de la evolución</t>
+          <t>Fases de la fotosíntesis y ciclo de Calvin</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -7903,38 +7909,23 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>9</v>
+        <v>6</v>
+      </c>
+      <c r="D108" t="n">
+        <v>6</v>
       </c>
       <c r="F108" t="n">
         <v>8</v>
       </c>
-      <c r="G108" t="n">
-        <v>4</v>
-      </c>
-      <c r="I108" t="n">
-        <v>8</v>
-      </c>
-      <c r="M108" t="n">
-        <v>7</v>
-      </c>
       <c r="O108" t="n">
         <v>1</v>
       </c>
-      <c r="P108" t="n">
-        <v>1</v>
-      </c>
-      <c r="R108" t="n">
-        <v>1</v>
-      </c>
-      <c r="V108" t="n">
-        <v>1</v>
-      </c>
       <c r="AF108" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG108" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH108" t="inlineStr">
@@ -7946,7 +7937,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Fases de la fotosíntesis y ciclo de Calvin</t>
+          <t>Secuenciación del ADN y perfiles genéticos</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7955,15 +7946,18 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>6</v>
-      </c>
-      <c r="D109" t="n">
-        <v>6</v>
-      </c>
-      <c r="F109" t="n">
-        <v>8</v>
-      </c>
-      <c r="O109" t="n">
+        <v>9</v>
+      </c>
+      <c r="G109" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H109" t="n">
+        <v>7</v>
+      </c>
+      <c r="P109" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q109" t="n">
         <v>1</v>
       </c>
       <c r="AF109" t="n">
@@ -7971,7 +7965,7 @@
       </c>
       <c r="AG109" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH109" t="inlineStr">
@@ -7983,7 +7977,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Secuenciación del ADN y perfiles genéticos</t>
+          <t>Impulso nervioso y sinapsis</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -7992,18 +7986,18 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>9</v>
-      </c>
-      <c r="G110" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="H110" t="n">
-        <v>7</v>
-      </c>
-      <c r="P110" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q110" t="n">
+        <v>10</v>
+      </c>
+      <c r="F110" t="n">
+        <v>8</v>
+      </c>
+      <c r="J110" t="n">
+        <v>7</v>
+      </c>
+      <c r="O110" t="n">
+        <v>1</v>
+      </c>
+      <c r="S110" t="n">
         <v>1</v>
       </c>
       <c r="AF110" t="n">
@@ -8023,7 +8017,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Impulso nervioso y sinapsis</t>
+          <t>Ingeniería genética y ADN recombinante</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -8032,22 +8026,37 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F111" t="n">
         <v>8</v>
       </c>
-      <c r="J111" t="n">
+      <c r="G111" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H111" t="n">
+        <v>7</v>
+      </c>
+      <c r="M111" t="n">
         <v>7</v>
       </c>
       <c r="O111" t="n">
         <v>1</v>
       </c>
-      <c r="S111" t="n">
+      <c r="P111" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q111" t="n">
+        <v>1</v>
+      </c>
+      <c r="V111" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z111" t="n">
         <v>1</v>
       </c>
       <c r="AF111" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG111" t="inlineStr">
         <is>
@@ -8063,7 +8072,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Ingeniería genética y ADN recombinante</t>
+          <t>Inmunidad adaptativa</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -8072,29 +8081,17 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>11</v>
-      </c>
-      <c r="F112" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G112" t="n">
         <v>8.5</v>
       </c>
-      <c r="H112" t="n">
-        <v>7</v>
-      </c>
       <c r="M112" t="n">
         <v>7</v>
       </c>
-      <c r="O112" t="n">
-        <v>1</v>
-      </c>
       <c r="P112" t="n">
         <v>1</v>
       </c>
-      <c r="Q112" t="n">
-        <v>1</v>
-      </c>
       <c r="V112" t="n">
         <v>1</v>
       </c>
@@ -8102,7 +8099,7 @@
         <v>1</v>
       </c>
       <c r="AF112" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AG112" t="inlineStr">
         <is>
@@ -8118,7 +8115,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Inmunidad adaptativa</t>
+          <t>Inmunidad innata</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -8141,9 +8138,6 @@
       <c r="V113" t="n">
         <v>1</v>
       </c>
-      <c r="Z113" t="n">
-        <v>1</v>
-      </c>
       <c r="AF113" t="n">
         <v>10</v>
       </c>
@@ -8161,7 +8155,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Inmunidad innata</t>
+          <t>Mutaciones</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -8170,7 +8164,10 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>9</v>
+        <v>7</v>
+      </c>
+      <c r="D114" t="n">
+        <v>7</v>
       </c>
       <c r="G114" t="n">
         <v>8.5</v>
@@ -8184,12 +8181,15 @@
       <c r="V114" t="n">
         <v>1</v>
       </c>
+      <c r="Z114" t="n">
+        <v>1</v>
+      </c>
       <c r="AF114" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG114" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH114" t="inlineStr">
